--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -96,17 +96,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FCE7F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDE9FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE7F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -141,12 +141,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAE8FF"/>
+        <fgColor rgb="00E0E7FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E7FF"/>
+        <fgColor rgb="00FAE8FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -690,34 +690,34 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.528226735470864</v>
+        <v>2.240075533726315</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.517400140934638</v>
+        <v>1.328310111130494</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.345989629006861</v>
+        <v>1.345644399605916</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.5280971659919029</v>
+        <v>0.4281111558598469</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.05137227304714986</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.07306533234775681</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.03249808512966412</v>
+        <v>-0.1020511521904278</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>-0.00738998992274098</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>-0.06051292920729112</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -746,25 +746,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.058469324134955</v>
+        <v>1.851639896671285</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.275186135944013</v>
+        <v>1.122198294465897</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>1.301965588096367</v>
+        <v>1.293293956872363</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.5986689019641724</v>
+        <v>0.4993447168279066</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.1117634680468831</v>
+        <v>-0.178100060546436</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.01163329820864067</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.0234375</v>
+        <v>-0.07460694774594434</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>-0.05369098895475288</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -802,25 +802,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.832960617611076</v>
+        <v>1.596346696792424</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.113295683876187</v>
+        <v>0.9517026292359907</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.283781312775862</v>
+        <v>1.260313464353132</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.5239635176873678</v>
+        <v>0.4218712336233688</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.1428678370053988</v>
+        <v>-0.2201932448630207</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.07465059283301323</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.02705484487575349</v>
+        <v>-0.1365345293846053</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>-0.06292054402290614</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -858,34 +858,34 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.167773351040283</v>
+        <v>1.895399305555555</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.220291653738753</v>
+        <v>1.016626360338573</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>1.206639776605647</v>
+        <v>1.17956469165659</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.6630257959563095</v>
+        <v>0.541002541002541</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.06138509968520456</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.00618672665916753</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.02727533735285692</v>
+        <v>-0.1316063525123665</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>-0.07475728155339811</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>-0.06777529346003364</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.765812546103699</v>
+        <v>1.568510688323379</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.089285760544724</v>
+        <v>0.9667350459873336</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.166741589487831</v>
+        <v>1.168227358529634</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.5980046662008047</v>
+        <v>0.5094324824203698</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1015619018953053</v>
+        <v>-0.1617656400756099</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.03574760798375431</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.01863053939663351</v>
+        <v>-0.09292951301884733</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>-0.05219420570322741</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -966,25 +966,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.722368790881767</v>
+        <v>1.518463104640253</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.991868904136326</v>
+        <v>0.876909905464766</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.087290336063802</v>
+        <v>1.086400699445819</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.548874642180736</v>
+        <v>0.4679430069726984</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1016045602615546</v>
+        <v>-0.1612660453952527</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.04571545715457159</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.01770878880629634</v>
+        <v>-0.100407747196738</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>-0.05209452201933396</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1022,25 +1022,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.662211993200729</v>
+        <v>1.468522396073779</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8957519272585719</v>
+        <v>0.7910656403878054</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.9501039516272329</v>
+        <v>0.944372436407511</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4647927240872902</v>
+        <v>0.4010533653473782</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.06714250553778012</v>
+        <v>-0.1246693335053876</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.02787134722910944</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.0147247804669095</v>
+        <v>-0.0788464149918523</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>-0.04548572634689463</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1078,34 +1078,34 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.321038088471083</v>
+        <v>1.210577917775439</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.8543076022480798</v>
+        <v>0.7853042063953255</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.7752265909900022</v>
+        <v>0.7921393424922727</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5898795871559632</v>
+        <v>0.5300757251035864</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.08257686676427523</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.04454699566773401</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.01827029012118975</v>
+        <v>0.04355876047554075</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>-0.003813953488372102</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>-0.03444234063655205</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1125,43 +1125,43 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Natural Resources</t>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Dry Bulk Freight Futures</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.324898435733868</v>
+        <v>1.145658263305322</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.7554299302715264</v>
+        <v>0.8866995073891628</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.750869341951607</v>
+        <v>0.7105911330049264</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.1140060936447862</v>
+        <v>0.4604385128693995</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.06819197465345761</v>
+        <v>0.2435064935064934</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.002604756511891404</v>
+        <v>0.1029517638588913</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-0.0009028326373998752</v>
+        <v>-0.04309806371018121</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1171,49 +1171,53 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>COPX</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Defensive Equity</t>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8212516809452368</v>
+        <v>1.209185013743035</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.6710854196913243</v>
+        <v>0.6407556313874108</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7052132205160062</v>
+        <v>0.6570314312263976</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.2751046106414823</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0.1778915877405218</v>
+        <v>0.1122890874663018</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>-0.01165794760284222</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.0200138026224983</v>
+        <v>-0.009822263797941821</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.003953577349827819</v>
+        <v>-0.04348808313566022</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1223,53 +1227,49 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BDRY</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Transportation &amp; Trade</t>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dry Bulk Freight Futures</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.396706586826348</v>
+        <v>0.8058442697184656</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.9476885644768858</v>
+        <v>0.6442729697987886</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6630170316301702</v>
+        <v>0.6465823419473826</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.539423076923077</v>
+        <v>0.2869881359430653</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.2787539936102239</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.1711777615215802</v>
+        <v>0.1719393867856704</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>-0.001402524544179662</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.005653266331658413</v>
+        <v>0.0028169014084507</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EPU</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1287,45 +1287,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Peru Equity</t>
+          <t>Oil Services</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.318701845884589</v>
+        <v>0.6790386905469414</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6403435453669533</v>
+        <v>0.6100494267389664</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.617380182242879</v>
+        <v>0.6054743117895212</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1252915727557184</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0.07554979531526951</v>
+        <v>0.1094225743001105</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>-0.03837260901043982</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.01419787590832855</v>
+        <v>0.002849696763036702</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.0006609385327165374</v>
+        <v>-0.02122804098224262</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>EPU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1343,45 +1343,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oil Services</t>
+          <t>Peru Equity</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7214575587812926</v>
+        <v>1.242686079498196</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6456014841145226</v>
+        <v>0.5719225991675372</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.6165363760084752</v>
+        <v>0.56216791757505</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1294063951459177</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>-0.01223349300272369</v>
+        <v>0.1251797246164066</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.0289302865907255</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.01797986642145011</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0.001070867640759587</v>
+        <v>0.00624432334241587</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>-0.02303791887125228</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1406,25 +1406,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.9399198931909212</v>
+        <v>0.8788881535407016</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.5535952953755681</v>
+        <v>0.5025138925641706</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5787222667735901</v>
+        <v>0.5390314898121196</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.2400627615062763</v>
+        <v>-0.2188746732700508</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.04439329168036832</v>
+        <v>-0.07358459781367266</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.01591601760921102</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>0.01078260869565217</v>
+        <v>-0.02372764786795045</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>-0.02305574673090149</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8088254147505738</v>
+        <v>0.7604938650807305</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.5573371200091206</v>
+        <v>0.4825291918781633</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5652037005679669</v>
+        <v>0.5045301958672228</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.1158431465352825</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.001599614129865978</v>
+        <v>0.1169612151304087</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>-0.04986209966941169</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.00502591487356685</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0.0014226999683844</v>
+        <v>-0.01462317210348696</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>-0.03204419889502763</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1507,36 +1507,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.8070962662070127</v>
+        <v>0.7143534943040648</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.4752514817327453</v>
+        <v>0.3937053353613504</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.5520165609332743</v>
+        <v>0.4982778952795142</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.009097866793941867</v>
+        <v>0.3869086041791963</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.1107590833994205</v>
+        <v>-0.04837343710121089</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.049461507778221</v>
+        <v>-0.06979516967288302</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.004456203871327169</v>
+        <v>-0.0138074093281042</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>QTEC</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1563,36 +1563,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Lithium &amp; Battery</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.7611751421976563</v>
+        <v>0.7542041075899208</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.4300507708106831</v>
+        <v>0.3934054805656257</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4829829971830228</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>0.4045978831274677</v>
+        <v>0.4923490629612628</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>-0.005544605100627709</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.01722438011617078</v>
+        <v>-0.1500587176030883</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.03569307704328806</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0.008300924866825543</v>
+        <v>-0.06630056255022776</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>-0.02489858721499516</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Transportation &amp; Trade</t>
         </is>
@@ -1630,25 +1630,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.155922266406988</v>
+        <v>1.142077413592747</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.7235468106878229</v>
+        <v>0.697023681202972</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.4699865587308643</v>
+        <v>0.4898937147062012</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3839106859838479</v>
+        <v>0.4039955477823676</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.2718734617459508</v>
+        <v>0.2515750071788669</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.1724915445321307</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>0.01900842641583389</v>
+        <v>0.1390233172019357</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>-0.00423076923076926</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1667,49 +1667,53 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SIL</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>DXJ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Japan Hedged Equity</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.631810942117126</v>
+        <v>0.6630991703688478</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.5296691867679775</v>
+        <v>0.3889272890244726</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.449502837731258</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>-0.03294354045862891</v>
+        <v>0.4265756386651089</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.1501619868067132</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.2200391023081127</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0.05530610009856529</v>
+        <v>0.04580952792948989</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>-0.02639071397284276</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.001663201663201663</v>
+        <v>0.00338562239024931</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1719,53 +1723,49 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DXJ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XLK</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Japan Hedged Equity</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.6924699890413213</v>
+        <v>0.7501354768038586</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.3956764429488475</v>
+        <v>0.3620876944098592</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.4343446030598892</v>
+        <v>0.4149720619830586</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1380187266252049</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0.04994811364764096</v>
+        <v>0.3456693274152582</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>-0.005092142716405901</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.02695876571679567</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>0.02161757076151494</v>
+        <v>-0.0373748492949626</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>-0.02147386369691484</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>VDE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1785,34 +1785,34 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Defensive Equity</t>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.5197216604132471</v>
+        <v>0.5891877958846365</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.4464731559490118</v>
+        <v>0.5187455596562893</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.4307204053717324</v>
+        <v>0.4133397781732577</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.2218420227487286</v>
+        <v>0.1516509613081432</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.1904424702876826</v>
+        <v>0.1481680276558059</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.01101036269430056</v>
+        <v>0.07457922228670921</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.001431109356494487</v>
+        <v>0.008387342737323555</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1826,101 +1826,101 @@
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="A23" t="n">
+      <c r="A23" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>VDE</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr"/>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.570886584954402</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.5225623711919263</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0.4126676551432764</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>0.1562858408736478</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0.1517741828127546</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0.07779233540779562</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0.01028553883942274</v>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>XOP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>0.5839068190377157</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0.5058732909444468</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>0.4130325652024329</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>0.1465092973241364</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>0.1473819957349576</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>0.06570317487956356</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>0.003607543044547912</v>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>STEADY_POSITIVE</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr"/>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>Energy</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.5620114956230489</v>
+        <v>0.6546065515020687</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.5073996685386313</v>
+        <v>0.5495342215953742</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.4122904785218402</v>
+        <v>0.395546629552846</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.1482950850925691</v>
+        <v>0.1955359314723468</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.1486304762351014</v>
+        <v>0.2091149325734156</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.0673439292151401</v>
+        <v>0.1103421331696155</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.003234252271677063</v>
+        <v>0.01645207439198848</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>QCLN</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1947,45 +1947,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.7094036411929314</v>
+        <v>0.5169278624682669</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.3155133757020743</v>
+        <v>0.4149271274911202</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.4112064076787862</v>
+        <v>0.3869702032179523</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.05763173828759305</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>-0.1817129629629629</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>-0.06780938029760786</v>
+        <v>0.2272781071517227</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0.1893738863286207</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.02015683120538858</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.01999175597691671</v>
+        <v>9.855615236764592e-05</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1995,49 +1995,49 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>DBC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Broad Commodity Futures</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.8166923534565564</v>
+        <v>0.5808856733514705</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3966159884845188</v>
+        <v>0.5602531148817178</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.4054718153417503</v>
+        <v>0.3853410185204995</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.3648243756949896</v>
+        <v>0.168234064785789</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.02556508375167255</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>-0.006300963676797777</v>
+        <v>0.1747810858143608</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.1262592343854936</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.01322751322751325</v>
+        <v>0.01145958986730999</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DRIV</t>
+          <t>QCLN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2062,29 +2062,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Autonomous &amp; Electric Vehicles</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.5559284315770112</v>
+        <v>0.6493195437453771</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.3309442012511017</v>
+        <v>0.2521206094681121</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3974719587529836</v>
+        <v>0.3835111543716991</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.1272101908308223</v>
+        <v>0.03349730063685286</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>-0.1203884711633193</v>
+        <v>-0.2188973816880794</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>-0.04760579064587978</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>0.01033668044890734</v>
+        <v>-0.09496890898812882</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>-0.02950090927460092</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2103,49 +2103,53 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DBC</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+          <t>FTEC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Broad Commodity Futures</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.562974625173964</v>
+        <v>0.723392124056216</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.5308635432003916</v>
+        <v>0.3307078354230755</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.390057336723878</v>
+        <v>0.3778993868045706</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.1489951489951489</v>
+        <v>0.3331546362079096</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.1493934142114384</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>0.10129525074726</v>
+        <v>0.01707882858655241</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>-0.03424890948745918</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-0.01368233194527069</v>
+        <v>-0.01947962078748877</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2155,53 +2159,49 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>XOP</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>VGT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.6447433655482626</v>
+        <v>0.7194325805735347</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.5198263061792348</v>
+        <v>0.3280289745893044</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3867289074059257</v>
+        <v>0.3748677069422435</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.1845104957739603</v>
+        <v>0.3331660201418016</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.203593899735774</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>0.09597939298913638</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>0.001278968639689015</v>
+        <v>0.0188573859765131</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>-0.03406781039108864</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>-0.01874948376971997</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2211,53 +2211,49 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>XME</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
+          <t>SIL</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1.059802922193759</v>
+        <v>1.407555798725963</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3436071760934634</v>
+        <v>0.4241427388450694</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3809722968930354</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>0.008582601610808593</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>-0.03922487489642523</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>-0.02705711105402864</v>
+        <v>0.3724514027470198</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>-0.02283234545119628</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0.1281453377299329</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0.03766350924672968</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.009932909296854531</v>
+        <v>-0.04503943545039435</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2263,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FTEC</t>
+          <t>IYW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2286,25 +2282,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.7841368706037533</v>
+        <v>0.7315569901636605</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3643528217746541</v>
+        <v>0.3317249724468088</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.369923150228374</v>
+        <v>0.3672120620978938</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.3474940191559461</v>
+        <v>0.3356959984385284</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.04360808863488175</v>
+        <v>0.02113110238108473</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.004066161268091006</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>0.01240016813787292</v>
+        <v>-0.02595580498070837</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>-0.01310957551826253</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2313,7 +2309,7 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2323,10 +2319,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VGT</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>DRIV</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Autonomous &amp; Electric Vehicles</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.7781047964136221</v>
+        <v>0.5145644925141428</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.3606736503623302</v>
+        <v>0.2731522151902905</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3666301799294571</v>
+        <v>0.3622957275644758</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.3470263500878381</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0.04431908800245266</v>
+        <v>0.1110444707564924</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>-0.157774607974429</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.004358552631578916</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>0.01203711443617816</v>
+        <v>-0.06543624161073813</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>-0.02309266296404555</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IYW</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2383,45 +2383,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.7855374976543281</v>
+        <v>0.9928133460564925</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.3531597887009936</v>
+        <v>0.2876978795858327</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3522514484677097</v>
+        <v>0.3446230145833766</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.3405518235413874</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>0.0409882761141509</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>0.0006717243559348773</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>0.01174543565978192</v>
+        <v>0.01379411632433514</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>-0.08281696638329872</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>-0.04233538648390733</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>-0.02851359676141862</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2450,25 +2450,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.562616759507681</v>
+        <v>0.5323398749294579</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.129584958404253</v>
+        <v>0.1020977017856126</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3471802394629351</v>
+        <v>0.3275711934165428</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.08376094511511301</v>
+        <v>-0.08507270689784863</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.1349427065409418</v>
+        <v>-0.133682529342915</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.161519056385082</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>0.005313496280552554</v>
+        <v>-0.1698390961999315</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>-0.01410798503821764</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2487,40 +2487,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AIRR</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>ARKQ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>U.S. Industrial Renaissance</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5772802363930272</v>
+        <v>0.7782824200007499</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1695349526467302</v>
+        <v>0.2074357831072569</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.345690091380733</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>-0.01754040385317313</v>
+        <v>0.3175156871781777</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.01671356698217785</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1643430173689538</v>
+        <v>-0.07866470906421441</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.1309031996759822</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>0.02025484975275771</v>
+        <v>-0.08355111452728659</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>-0.01755108767303881</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2529,7 +2533,7 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2539,44 +2543,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ARKQ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>AIRR</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>U.S. Industrial Renaissance</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.8468671970988895</v>
+        <v>0.5368071802630852</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.2507361770547081</v>
+        <v>0.1243549959202865</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.3287525981185195</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>0.02146283982829722</v>
+        <v>0.3157482500866637</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>-0.03295910176436545</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.06818181818181823</v>
+        <v>-0.1894940131324835</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.05871403086946414</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>0.007220516225412865</v>
+        <v>-0.1454634305261443</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>-0.02208966352875386</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ROBO</t>
+          <t>CALF</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2603,45 +2603,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Small Cap Cash Flow</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.4665313583335677</v>
+        <v>0.5523915116936424</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2376071297541429</v>
+        <v>0.3003507488370594</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.3259964646436753</v>
+        <v>0.307935429216279</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.1151677473921624</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>-0.04027659832585229</v>
+        <v>0.286482345537405</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0.1245042012930848</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.06665880132137803</v>
+        <v>-0.005798971577491763</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.01657671549730155</v>
+        <v>0.01197711834107973</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CALF</t>
+          <t>ROBO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2659,45 +2659,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Small Cap Cash Flow</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.5128483400901598</v>
+        <v>0.4176786931152972</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.3041789113184341</v>
+        <v>0.1847246737783101</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.3061198273109094</v>
+        <v>0.3061009534158234</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.2689591442953836</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>0.1162782591203493</v>
+        <v>0.1037789865445176</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>-0.07096385542168671</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.001486016789494116</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>0.007202016564638036</v>
+        <v>-0.09293024350076473</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>-0.02528125395019598</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>SCHD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2718,38 +2718,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.4612922313542343</v>
+        <v>0.3254433995732973</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2345747044514754</v>
+        <v>0.2876767986120823</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2936346318131682</v>
+        <v>0.2876767986120823</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1725156932623859</v>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>-0.00286829271620026</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>-0.04565425654917243</v>
+        <v>0.1362909703441519</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>0.05741032644568711</v>
+      </c>
+      <c r="K39" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.004136253041362448</v>
+        <v>0.009085580304806662</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SCHA</t>
+          <t>SPMO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2770,29 +2770,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.4631178629848356</v>
+        <v>0.5685911471849954</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2451881088050085</v>
+        <v>0.208863038942213</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2934626403982186</v>
+        <v>0.2819773856485994</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1793998352084907</v>
+        <v>0.2449564600516696</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>-0.0160500165018973</v>
+        <v>-0.0540989747699786</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.03732193732193734</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>0.004160475482912318</v>
+        <v>-0.05703247773703513</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>-0.02899332479266414</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SCHD</t>
+          <t>SCHA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.2993042381735782</v>
+        <v>0.4447070470966654</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2862913961951783</v>
+        <v>0.211048733731108</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2915692624163777</v>
+        <v>0.2794757025428209</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1253293199473584</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>0.05723150131930654</v>
+        <v>0.1699724476358928</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>-0.03713377032069864</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.004086398131932345</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>0.003824654310091047</v>
+        <v>-0.0534804753820034</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>-0.01006214856466403</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2863,49 +2863,49 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HEFA</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Developed ex-US Currency-Hedged</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.3687990191726742</v>
+        <v>0.4561738178807442</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.242190807752497</v>
+        <v>0.2100300578895733</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2771482719448874</v>
+        <v>0.2734729265881319</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1112354638145077</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>0.02918174636163551</v>
+        <v>0.1743379616041814</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>-0.01325894442000697</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.02737150020894275</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>0.009104704097116834</v>
+        <v>-0.04981878088962111</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>-0.001765377825469816</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2915,40 +2915,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FNDX</t>
+          <t>HEFA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fundamental Large Cap</t>
+          <t>Developed ex-US Currency-Hedged</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4289271403776638</v>
+        <v>0.3521716305175431</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2765885791920064</v>
+        <v>0.2301881853174532</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2765885791920064</v>
+        <v>0.2707263701879186</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1713420394782803</v>
+        <v>0.1130828339141201</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.05042263646363399</v>
-      </c>
-      <c r="K43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>0.008387698042870539</v>
+        <v>0.02318560231030098</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>-0.03190158465387827</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>-0.002577873254564933</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SPMO</t>
+          <t>FNDX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -2978,38 +2978,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Fundamental Large Cap</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.6322879223962228</v>
+        <v>0.4332331500530524</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2515218599428812</v>
+        <v>0.2614608403647247</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2759936649043426</v>
+        <v>0.2688446222399339</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.2712966678261191</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>-0.01356366332923753</v>
+        <v>0.1742851675009072</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0.04102587495139032</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.01917862575226514</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>0.005287060258930332</v>
+        <v>-0.005819295558958548</v>
+      </c>
+      <c r="L44" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d flat.</t>
         </is>
       </c>
     </row>
@@ -3019,53 +3019,49 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IWO</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>EWJ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Russell 2000 Growth</t>
+          <t>Japan Equity</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.4321823459589804</v>
+        <v>0.4748477593057197</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.1928857541889115</v>
+        <v>0.2507144336800791</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2730647574966065</v>
+        <v>0.263027897492333</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1634606160109413</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>-0.02604490414987182</v>
+        <v>0.1761012269839763</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0.05748895904234774</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.06298108783198242</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>0.005360024065414137</v>
+        <v>-0.009749162181375004</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>-0.01065340909090906</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3075,40 +3071,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>QQQM</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4878864562360243</v>
+        <v>0.4925201116659261</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.1067068985409803</v>
+        <v>0.2151873519079543</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2714925793839618</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>-0.05263302996782693</v>
+        <v>0.2597840673404985</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>0.1923722963773591</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-0.07149747897044423</v>
+        <v>-0.01997756307574861</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.1296001907638503</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>0.003160498351044261</v>
+        <v>-0.03540028532563622</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>-0.0123985189714324</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3117,7 +3113,7 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3127,101 +3123,101 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>U.S. Infrastructure Development</t>
+          <t>Developed Markets</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.4453833985215745</v>
+        <v>0.4480732898169368</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.1754340598712509</v>
+        <v>0.2286352379341288</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2712858387919652</v>
+        <v>0.2596380231099376</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.07276900405884246</v>
-      </c>
-      <c r="J47" s="5" t="n">
-        <v>-0.05255625597256597</v>
+        <v>0.1317811087306213</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0.007792604258085367</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.07539750384681143</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>0.01349325337331342</v>
+        <v>-0.02461245580636395</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>-0.01320676846884017</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="21" customHeight="1">
+      <c r="A48" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.4914584847821535</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.2146460675070427</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.259409314694258</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>0.1920049227397247</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-0.02012097361776322</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>-0.03554304916196549</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>-0.01235172336615942</v>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N47" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>VEA</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Developed Markets</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>0.4783385435705116</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>0.2589105204745377</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>0.269475046784752</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>0.1336064941477157</v>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>0.02471759501569615</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>-0.008321964529331538</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>0.01070634037819795</v>
-      </c>
-      <c r="M48" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3231,10 +3227,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EWJ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>ARGT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>International</t>
@@ -3242,38 +3242,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Japan Equity</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.5182462495060387</v>
+        <v>0.1721139624853809</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2792844754755994</v>
+        <v>0.3172698808099992</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2692900655109463</v>
+        <v>0.255356955395607</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1770460173023944</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>0.07502180156475102</v>
+        <v>0.1212196012054356</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>-0.02077939000367623</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.007874015748031482</v>
+        <v>0.04931898066783824</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.02198257984238916</v>
+        <v>0.001362683438155043</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3283,53 +3283,49 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D50" s="13" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.1983932427264505</v>
+        <v>0.4559913206509885</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.2368138838034857</v>
+        <v>0.08390806540947748</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2604563967396789</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>0.128992621772217</v>
-      </c>
-      <c r="J50" s="3" t="n">
-        <v>0.08721587487050941</v>
+        <v>0.2543613498891937</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>-0.05794190077834704</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>-0.07647264706337131</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.01875710496400151</v>
+        <v>-0.1358885017421603</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>-0.001702701834420228</v>
+        <v>-0.01483950504543174</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3339,40 +3335,44 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>QQQM</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>MTUM</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.5287731803583604</v>
+        <v>0.5169097467126098</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.2376488043378708</v>
+        <v>0.1882548364972194</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2527415697428539</v>
+        <v>0.2532511546462963</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.2000269717336056</v>
+        <v>0.2333220955852053</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.0009807165515596239</v>
+        <v>-0.07530504815265393</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.01204778844217747</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>0.008875942426319394</v>
+        <v>-0.05186216498433693</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>-0.02410109431995844</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3381,50 +3381,54 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
-      <c r="A52" s="15" t="n">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr"/>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>Nasdaq-100</t>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>IWO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Russell 2000 Growth</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.5271462584416726</v>
+        <v>0.4213173949600446</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2369949355920995</v>
+        <v>0.1633282572897696</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2522566513093141</v>
+        <v>0.2499357209162836</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.1997588426263208</v>
+        <v>0.1613488214115184</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.002028063789779377</v>
+        <v>-0.03802726763131514</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.01218737045737195</v>
-      </c>
-      <c r="L52" s="3" t="n">
-        <v>0.008734425489282938</v>
+        <v>-0.06928953399541626</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>-0.005821070097652536</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3433,7 +3437,7 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3443,49 +3447,49 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="13" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>U.S. Infrastructure Development</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.1618883731594203</v>
+        <v>0.4134775592222828</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2251377447080336</v>
+        <v>0.134732567648965</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2479571947183186</v>
+        <v>0.2474784317422918</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1106290806725088</v>
-      </c>
-      <c r="J53" s="3" t="n">
-        <v>0.07787187561042241</v>
+        <v>0.05905945227660125</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>-0.08010712348235804</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>-0.01828544288767509</v>
+        <v>-0.09037900874635574</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.001810938065918033</v>
+        <v>-0.01923076923076916</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3495,14 +3499,10 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MTUM</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>COWZ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3510,38 +3510,38 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Large Cap Cash Flow</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.5788609625148387</v>
+        <v>0.3393160015912671</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2156377354426406</v>
+        <v>0.2436504109489019</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2460841078552054</v>
+        <v>0.2430722933679541</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.2613970580432219</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>-0.03645899704563371</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>-0.02443364153401328</v>
+        <v>0.1413170312751668</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0.1074959590991704</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0.0004650715682685824</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.01283193138710215</v>
+        <v>0.007863883328567356</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PPA</t>
+          <t>VHT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3559,45 +3559,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.4252562909729434</v>
+        <v>0.2226274989655019</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.09251327022794942</v>
+        <v>0.2299232461298379</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2454421718450501</v>
-      </c>
-      <c r="I55" s="5" t="n">
-        <v>-0.0695102616472606</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>-0.08158109610287967</v>
+        <v>0.2375153649331088</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>0.1440829352440294</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0.1009066565759524</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.1227908489645452</v>
+        <v>-0.006134969325153561</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.007032611401543321</v>
+        <v>0.01139216064877369</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3607,53 +3607,49 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ARGT</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XLI</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2133211222115738</v>
+        <v>0.327301484029503</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.3026884862784323</v>
+        <v>0.1233242689548151</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2443815697542298</v>
+        <v>0.2315733266205304</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1047077292564342</v>
+        <v>0.03464477993975756</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.02271085800039419</v>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>0.04685613958081869</v>
+        <v>-0.03577637053719507</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>-0.08789493514182667</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.01527663088356723</v>
+        <v>-0.01688228810117764</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3663,10 +3659,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>XLI</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D57" s="18" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -3674,29 +3674,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.3499906033863192</v>
+        <v>0.4089955498295821</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1534846023622358</v>
+        <v>0.07382373335350745</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2438923123924837</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>0.04865419874505861</v>
+        <v>0.2293064876737918</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>-0.07488393953934769</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.01345082211132131</v>
+        <v>-0.07991563448041672</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.07268129976328808</v>
-      </c>
-      <c r="L57" s="3" t="n">
-        <v>0.01067135737320424</v>
+        <v>-0.1264800567468762</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>-0.01062975094246332</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3715,49 +3715,49 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>COWZ</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Large Cap Cash Flow</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3167191481091121</v>
+        <v>0.1876725257844196</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2451331504327969</v>
+        <v>0.2185997269643705</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2378834438893416</v>
+        <v>0.2261731924600257</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1287846303503339</v>
+        <v>0.1267038928518893</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.1078517764174258</v>
-      </c>
-      <c r="K58" s="3" t="n">
-        <v>0.00585653405354325</v>
+        <v>0.09276392417583468</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>-0.006176505523221243</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.01010976314269207</v>
+        <v>0.01197387518142223</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VBK</t>
+          <t>ONEQ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3778,38 +3778,38 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3605688068567818</v>
+        <v>0.4947880329763561</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.157310566302127</v>
+        <v>0.1922311841915336</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.234319667062552</v>
+        <v>0.2235051004192332</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1296613887775309</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>-0.02462797750569168</v>
+        <v>0.185179646134225</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0.01013108566124288</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.06238991633641566</v>
-      </c>
-      <c r="L59" s="3" t="n">
-        <v>0.008018225930528367</v>
+        <v>-0.02556092019312683</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>-0.00819040277510108</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3819,14 +3819,10 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>XMMO</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>VBK</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3834,29 +3830,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3656964132043186</v>
+        <v>0.343452005092858</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1434722404349746</v>
+        <v>0.128767074461076</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2289114161841082</v>
+        <v>0.2205731513728775</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.06646093335431491</v>
+        <v>0.1220185684751689</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.09323024370185828</v>
+        <v>-0.0358999348155693</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.06952427540662842</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>0.008884174235894493</v>
+        <v>-0.07521554673600661</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>-0.008277319557368878</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3865,7 +3861,7 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3875,10 +3871,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ONEQ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>XMMO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3886,38 +3886,38 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.524026311157211</v>
+        <v>0.3328107524522248</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.2112826619165993</v>
+        <v>0.1026276564724091</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2221372858863664</v>
+        <v>0.2066882340667311</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.184358291733963</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>0.0218777242996826</v>
+        <v>0.04629697429798862</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>-0.1207150471550053</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.008881673192627226</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>0.008846116457664976</v>
+        <v>-0.08623650637880276</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>-0.02096339620161658</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3927,40 +3927,40 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IAU</t>
+          <t>QUAL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gold Bullion</t>
+          <t>Quality Factor</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.483747957145451</v>
+        <v>0.3039800780171629</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1904137529137528</v>
+        <v>0.159552735357184</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.208916083916084</v>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>-0.1457396759017252</v>
+        <v>0.1971242463914793</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>0.1320180157230959</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.03260457475041068</v>
+        <v>0.01628457633395497</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.01530489274523994</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>0.005414051925679786</v>
+        <v>-0.03138480500044016</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>-0.0006811989100816707</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -3969,50 +3969,50 @@
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
-      <c r="A63" s="15" t="n">
+      <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C63" s="15" t="inlineStr"/>
-      <c r="D63" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E63" s="15" t="inlineStr">
-        <is>
-          <t>Gold Bullion</t>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.4815351463813342</v>
+        <v>0.3853665103365629</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1894350653224364</v>
+        <v>0.1695977579101065</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.2077790371651853</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>-0.1458833104866347</v>
+        <v>0.1965427731527949</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0.1543408568911269</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.03222716918616686</v>
+        <v>0.02776617803670778</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.01518818532055721</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>0.00608033101221106</v>
+        <v>-0.02251905727673265</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>-0.005280687770439441</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>QUAL</t>
+          <t>IVV</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -4042,29 +4042,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Quality Factor</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3076201919156223</v>
+        <v>0.3853758486457015</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1725849624825191</v>
+        <v>0.1695010670551322</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.2005416884272659</v>
+        <v>0.1964783646940815</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1266124939517614</v>
+        <v>0.1544506997142359</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.02173483839105761</v>
+        <v>0.0278626630239589</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>-0.02328675981370587</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>0.008149436864755888</v>
+        <v>-0.02254725069420449</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>-0.00530003125325551</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4073,50 +4073,50 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
-      <c r="A65" t="n">
+      <c r="A65" s="15" t="n">
         <v>64</v>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>RSP</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr"/>
       <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Equal Weight</t>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2821651155885614</v>
+        <v>0.3835865890936403</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1648555272414511</v>
+        <v>0.1688237077181842</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1985212452298601</v>
+        <v>0.1959598881388804</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1193386590688088</v>
+        <v>0.1539809758323334</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.02837736108103739</v>
+        <v>0.02755446556412844</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.02808937941016831</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0.007974855748932752</v>
+        <v>-0.02268987504499409</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>-0.005312119745122801</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4135,40 +4135,44 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IVV</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D66" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3998384551799237</v>
+        <v>0.3714346828858759</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1855259011094481</v>
+        <v>0.1454617410605656</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1982932456273345</v>
+        <v>0.1955191892594998</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1540957947818076</v>
+        <v>0.1966325683049919</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.03904263932367802</v>
+        <v>0.02759837291466849</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.0106546077635632</v>
+        <v>-0.04187088643047188</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.008391002324268149</v>
+        <v>0.005584950029394298</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4187,40 +4191,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VOO</t>
+          <t>IAU</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3994765629879853</v>
+        <v>0.4520795660036168</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1853947881640585</v>
+        <v>0.1717495987158908</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1982347653018524</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>0.1540082545864605</v>
+        <v>0.1933459798628339</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>-0.1491841491841491</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.03888938505152728</v>
+        <v>0.01401692132845045</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.01071574411760567</v>
-      </c>
-      <c r="L67" s="3" t="n">
-        <v>0.008483456542022427</v>
+        <v>-0.01809733431156768</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>-0.01725614979806633</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4229,7 +4233,7 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4239,40 +4243,40 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr"/>
-      <c r="D68" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3983569388879287</v>
+        <v>0.4495986387008473</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1848309671521442</v>
+        <v>0.1705998327159757</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1975429140972143</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>0.1535772612630477</v>
+        <v>0.1917791850878241</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>-0.14966148771808</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.03862907051471698</v>
+        <v>0.01378899984477666</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.01061502414270743</v>
-      </c>
-      <c r="L68" s="3" t="n">
-        <v>0.008524339231753775</v>
+        <v>-0.01777120513334662</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>-0.01730320736264002</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4281,7 +4285,7 @@
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4291,44 +4295,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D69" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>RSP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.37791339717299</v>
+        <v>0.2887757354467084</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1464090882536739</v>
+        <v>0.1481385516313509</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1966192452641962</v>
+        <v>0.1896394659697189</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1848635090681803</v>
+        <v>0.1198653065611734</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.03660244604406726</v>
+        <v>0.01957237982187743</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.04196001126443238</v>
+        <v>-0.03488528711893313</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.001177163037080931</v>
+        <v>0.0004188579140875781</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4347,49 +4347,53 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EWZ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>OEF</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Brazil Equity</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.6672854789796419</v>
+        <v>0.4102743749428397</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.3395267041089065</v>
+        <v>0.1675945045629892</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.187650542056234</v>
+        <v>0.1844132968184888</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.06737450505136167</v>
+        <v>0.1674816201806828</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.1075427912059146</v>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>0.1278795038393383</v>
+        <v>0.04036917858951616</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>-0.01420010422094842</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.00959543568464738</v>
+        <v>-0.005258314710135381</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4399,53 +4403,49 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OEF</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>EWZ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>Brazil Equity</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.4282835957153377</v>
+        <v>0.6265609610578255</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1796444022939223</v>
+        <v>0.300814685370935</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1826838436354445</v>
+        <v>0.1742451730814349</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.1632932922731403</v>
+        <v>0.06413477523375333</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.048342779058691</v>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>-0.002569952534550057</v>
-      </c>
-      <c r="L71" s="3" t="n">
-        <v>0.008351007423117895</v>
+        <v>0.07595839081146227</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0.1077879774948176</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>-0.0204241948153967</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4455,44 +4455,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>XHE</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D72" s="13" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>MGK</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.07414823274586513</v>
+        <v>0.432397782297663</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1177227939705541</v>
+        <v>0.1422555581233211</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1809292046061513</v>
+        <v>0.1651390214589759</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1279448621553885</v>
+        <v>0.1806646598465587</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.0970140158439976</v>
+        <v>0.02945526682871202</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.05352260778128271</v>
-      </c>
-      <c r="L72" s="3" t="n">
-        <v>0.005361331397297109</v>
+        <v>-0.01964011411016031</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>-0.006117908787541815</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4501,7 +4497,7 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4511,40 +4507,44 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VWO</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XHE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.373956728378845</v>
+        <v>0.1046737453574231</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1702390145119903</v>
+        <v>0.108289211502256</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.171402466721944</v>
+        <v>0.1596281848561474</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1125341100746424</v>
+        <v>0.1476442428823381</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.02236421464102967</v>
+        <v>0.1126038104543234</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.0009932130441978604</v>
+        <v>-0.0442719261435166</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.006840173506840186</v>
+        <v>0.01210976558160182</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -4563,49 +4563,49 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MGK</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.4605366088710081</v>
+        <v>0.34915164766785</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1548766085449917</v>
+        <v>0.1389701624167168</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1588589416779054</v>
+        <v>0.1556324129851134</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.1746091350024359</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>0.03806229443785347</v>
+        <v>0.1021969353045211</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>-0.0001565223955933837</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.003436426116838365</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>0.009091929509484897</v>
+        <v>-0.01441829632084857</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>-0.01458160729080371</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4630,25 +4630,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.4105964210639947</v>
+        <v>0.3888080218720666</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1349079101057367</v>
+        <v>0.125374563843162</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1494331819927557</v>
+        <v>0.1523066046872716</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.165325794027507</v>
+        <v>0.1761723293530455</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.05441104109248651</v>
+        <v>0.05135187092515103</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.01263689974726212</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>0.008605851979345935</v>
+        <v>-0.02337228714524198</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>-0.00170648464163814</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4682,25 +4682,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.4300018628016369</v>
+        <v>0.4015177450510616</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1352166083763857</v>
+        <v>0.1213849288763165</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1461792772825428</v>
+        <v>0.1506217229053388</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1625601107472603</v>
+        <v>0.1679610453825562</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.03521630978762036</v>
+        <v>0.026703200532189</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.009564532463148478</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>0.009287925696594534</v>
+        <v>-0.02540956201939149</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>-0.006475800954328537</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4738,25 +4738,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.267808400720406</v>
+        <v>0.2724092250263885</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1002946808242238</v>
+        <v>0.09031755447671341</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1457028129910174</v>
+        <v>0.1424735716607293</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1362033504845761</v>
+        <v>0.1456672664737277</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.02954411469852847</v>
+        <v>0.02532251606586744</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.03963342993655516</v>
+        <v>-0.04565183692450792</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>0.01005025125628145</v>
+        <v>0.004241089633798101</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -4790,25 +4790,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2714059859723621</v>
+        <v>0.261999603601818</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.0935583599351193</v>
+        <v>0.07523147828534826</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1283883217503832</v>
+        <v>0.1158445652838507</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>-0.0246071794610434</v>
+        <v>-0.03106423703498251</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>-0.02840077398027863</v>
+        <v>-0.04258207292996341</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.03086699954607364</v>
+        <v>-0.03639672429481344</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.0001561036528255899</v>
+        <v>-0.007962529274004648</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -4827,49 +4827,53 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BOTZ</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>IAK</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D79" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.177502524229626</v>
+        <v>0.1476690670691039</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.05099482294746394</v>
+        <v>0.1191814601188499</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1263637827563384</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>-0.008214616121666074</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>-0.05266659892022219</v>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>-0.0669135149431368</v>
+        <v>0.1143554209684401</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0.1361642375440277</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.08081313948100588</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0.004330789853578043</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.01495972382048349</v>
+        <v>0.01444243855020133</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4879,53 +4883,49 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IAK</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>BOTZ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Robotics &amp; AI</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1221391017312754</v>
+        <v>0.1412608087471929</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1219895528596942</v>
+        <v>0.01833138300226511</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.1247162320952233</v>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>0.1199888671532574</v>
-      </c>
-      <c r="J80" s="3" t="n">
-        <v>0.07262572424373115</v>
+        <v>0.1108535594215652</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>-0.004095924024359987</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>-0.06553505642492841</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.002424326383597686</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>0.005164712451144693</v>
+        <v>-0.08328926493918554</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>-0.01729024943310653</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4935,49 +4935,49 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VFH</t>
+          <t>VONG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D81" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.2512826745639731</v>
+        <v>0.3238838940041839</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.09135233194523362</v>
+        <v>0.05953014548110236</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.1069787971792719</v>
+        <v>0.101594590700717</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.1837931557311847</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>0.08776498999710292</v>
+        <v>0.1058102937351713</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>-0.00488794235468526</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.01411631846414452</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>0.00554315744006928</v>
+        <v>-0.03818505062997601</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>-0.01167593328038119</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4987,49 +4987,49 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>IWF</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D82" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Russell 1000 Growth</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.2297750420895845</v>
+        <v>0.3213272968505194</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.09365020267433666</v>
+        <v>0.0578038930725886</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.1064492530811805</v>
+        <v>0.09999699771186243</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1825898941031974</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>0.09180052354380441</v>
+        <v>0.1047992278283407</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>-0.005456636910661117</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.01156767955801108</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>0.006681906101635438</v>
+        <v>-0.03835747254496258</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>-0.0116954281508137</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N82" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5039,49 +5039,49 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>VFH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>U.S. Equity REITs</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1105499232747178</v>
+        <v>0.2521347524694777</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.07536799607963141</v>
+        <v>0.07877759486023406</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.1038402921783643</v>
+        <v>0.09840012761502126</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.05051526666233075</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>-0.02022781314528987</v>
+        <v>0.1871189310939154</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0.07731574139753983</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.02579385469119311</v>
+        <v>-0.01786464901219009</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>0.007224819379515468</v>
+        <v>0.00365120274914088</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5091,49 +5091,49 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VONG</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>U.S. Equity REITs</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.3574417211547898</v>
+        <v>0.1088275988874807</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.07752582226056948</v>
+        <v>0.05120563884836771</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.09644029459731174</v>
+        <v>0.09821801481212455</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.1065152818288555</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>0.007914777925980943</v>
+        <v>0.04393757786161601</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>-0.03368503107843568</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.01725080009366953</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>0.008490868311438637</v>
+        <v>-0.04280787177926559</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>-0.004641350210970452</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5143,49 +5143,49 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IWF</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Russell 1000 Growth</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.3550844416025001</v>
+        <v>0.103569455867798</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.07595202679193047</v>
+        <v>0.0782350027426395</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.09487160524619265</v>
+        <v>0.09672631857914848</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1051644239664777</v>
-      </c>
-      <c r="J85" s="3" t="n">
-        <v>0.006643701153147941</v>
+        <v>0.010336016038617</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>-0.007962469490038315</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.01728018003536413</v>
+        <v>-0.01686046511627914</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>0.007830530827563464</v>
+        <v>0.01403214200047964</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5195,49 +5195,49 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" s="13" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D86" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.06465415772303817</v>
+        <v>0.2320450115153443</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.07196034950878816</v>
+        <v>0.07961118927284261</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.09381610141769858</v>
+        <v>0.09502346599992717</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.002149805705260466</v>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>-0.01538007680777609</v>
+        <v>0.1850584040773597</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0.08063760257766184</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.01998119417019284</v>
+        <v>-0.01407483693786471</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.003490191358767492</v>
+        <v>0.003318777292576458</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N86" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5322,34 +5322,34 @@
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.04817749603803489</v>
+        <v>-0.0428481411468179</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.06754354781372207</v>
+        <v>0.08655221745350494</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.07820831852115173</v>
+        <v>0.0829756795422032</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.006704659738518304</v>
+        <v>0.004629629629629539</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.0165876777251186</v>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>-0.009891196834816873</v>
+        <v>0.0198053037932191</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>0.003302509907529672</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.002671118530884975</v>
+        <v>0.01165501165501159</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N88" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5378,142 +5378,142 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.2338265096994658</v>
+        <v>0.2172153292158792</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.02227561809154532</v>
+        <v>0.0008572646439883869</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0.07446542387634714</v>
+        <v>0.07338910911521168</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.1229962615649864</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>0.001592130534236125</v>
+        <v>0.1140407286531109</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.01519072778653796</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.04857281083696174</v>
-      </c>
-      <c r="L89" s="3" t="n">
-        <v>0.007651579846285284</v>
+        <v>-0.06757274119448697</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>-0.009254551001728895</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
-      <c r="A90" t="n">
+      <c r="A90" s="15" t="n">
         <v>89</v>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>US Dollar Index Bullish</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.03086598136418761</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.06742685608971266</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.06553626654651445</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0.01219074937253506</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0.01001788908765655</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>0.001774308019872217</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0.005700035625222588</v>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="21" customHeight="1">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
         <is>
           <t>XLU</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" s="13" t="inlineStr">
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" s="14" t="inlineStr">
         <is>
           <t>Defensive Equity</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="F90" s="3" t="n">
-        <v>0.1414632687928854</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0.02983016121088022</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>0.06505671779865518</v>
-      </c>
-      <c r="I90" s="5" t="n">
-        <v>-0.07615190527573446</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>-0.03153961243079439</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>-0.03307481751824826</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>-0.003057384760112969</v>
-      </c>
-      <c r="M90" s="6" t="inlineStr">
+      <c r="F91" s="3" t="n">
+        <v>0.1352886416621983</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0.01556347472222375</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0.06413075010151625</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>-0.09297043970572816</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>-0.05011489856715035</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>-0.04564032697547682</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>-0.00849256900212314</v>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
         <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N90" s="7" t="inlineStr">
+      <c r="N91" s="7" t="inlineStr">
         <is>
           <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="21" customHeight="1">
-      <c r="A91" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="16" t="inlineStr">
-        <is>
-          <t>UUP</t>
-        </is>
-      </c>
-      <c r="C91" s="15" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D91" s="22" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E91" s="15" t="inlineStr">
-        <is>
-          <t>US Dollar Index Bullish</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>0.0275631929721567</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>0.05789575411833114</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>0.06279516445090616</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>0.01408959537572252</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>0.004293381037567157</v>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>-0.004609929078014163</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>0.001427042454513083</v>
-      </c>
-      <c r="M91" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="N91" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5542,34 +5542,34 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.01116266470177751</v>
+        <v>0.01730325493989193</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.03808599582343963</v>
+        <v>0.04560468470233081</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.04480116398515888</v>
+        <v>0.04718773494412076</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.004971319311663613</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>-0.002656546489563594</v>
+        <v>0.004562737642585635</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0.004180919802356575</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.006427221172022657</v>
+        <v>-0.001511715797430035</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.0007616146230007281</v>
+        <v>0.005327245053272422</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5594,25 +5594,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.08856486859704615</v>
+        <v>0.08621731903256702</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.0314718913748151</v>
+        <v>0.02787904160939392</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03903199568235749</v>
+        <v>0.03881117741771867</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.02082067101867247</v>
+        <v>0.02171307728601346</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.001969320616498793</v>
+        <v>-0.002985127923759379</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.007276103468380146</v>
+        <v>-0.01052369867207237</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.0002543881963877892</v>
+        <v>-0.001017811704834615</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5626,49 +5626,45 @@
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
-      <c r="A94" t="n">
+      <c r="A94" s="15" t="n">
         <v>93</v>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>XRT</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr"/>
       <c r="D94" s="23" t="inlineStr">
         <is>
-          <t>Consumer</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Retail</t>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>1-3 Year Treasury</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.2449238253855912</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>-0.01120709605380221</v>
+        <v>0.04287028501670442</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0.01643096723479043</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.0353229627590923</v>
+        <v>0.02212459389040711</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.06158254881591496</v>
+        <v>0.002971174981437397</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.03076363698898266</v>
+        <v>-0.0001050800105854011</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.04494255462942098</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>0.01387062059069732</v>
+        <v>-0.005570384168084197</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>-0.0004915816640039816</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -5677,7 +5673,7 @@
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5683,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VCR</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5695,36 +5691,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D95" s="23" t="inlineStr">
+      <c r="D95" s="24" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1866218179026031</v>
+        <v>0.2669503414588925</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.01146446294142323</v>
+        <v>-0.02592476154536183</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.0310970865750253</v>
+        <v>0.02095525345245508</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.04300659100779725</v>
+        <v>0.06978950901133452</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-0.02826116238786736</v>
+        <v>-0.02685722648799738</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.04127792626960514</v>
+        <v>-0.0459177959457947</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>0.01039064576136051</v>
+        <v>0.004717537445453335</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -5743,101 +5739,105 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>VCR</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D96" s="24" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.1731348396070262</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>-0.03274030267362205</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0.01713159405536668</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.04578360050460972</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>-0.0328436140958005</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>-0.0490319020866774</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>-0.002735330475263531</v>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N96" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="21" customHeight="1">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>IWP</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" s="19" t="inlineStr">
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>Russell Midcap Growth</t>
         </is>
       </c>
-      <c r="F96" s="3" t="n">
-        <v>0.1903887272276956</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>-0.0347931696864876</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>0.02255969994083706</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0.06418056632938796</v>
-      </c>
-      <c r="J96" s="5" t="n">
-        <v>-0.01819951458526348</v>
-      </c>
-      <c r="K96" s="5" t="n">
-        <v>-0.05608755129958953</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>0.009657594381035972</v>
-      </c>
-      <c r="M96" s="6" t="inlineStr">
+      <c r="F97" s="3" t="n">
+        <v>0.1660070707932022</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>-0.05629266725339066</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>0.01631614729395103</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0.05541600052886175</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>-0.02871199472074737</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>-0.07144313778804989</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>-0.01014492753623197</v>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
         <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N96" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="21" customHeight="1">
-      <c r="A97" s="15" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="16" t="inlineStr">
-        <is>
-          <t>SHY</t>
-        </is>
-      </c>
-      <c r="C97" s="15" t="inlineStr"/>
-      <c r="D97" s="24" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E97" s="15" t="inlineStr">
-        <is>
-          <t>1-3 Year Treasury</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>0.04262407763400011</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>0.01729909378610239</v>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>0.02112356260409443</v>
-      </c>
-      <c r="I97" s="3" t="n">
-        <v>0.004072618997297051</v>
-      </c>
-      <c r="J97" s="3" t="n">
-        <v>0.0001430225417717867</v>
-      </c>
-      <c r="K97" s="5" t="n">
-        <v>-0.003745353606608326</v>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v>-0.0006140997297960915</v>
-      </c>
-      <c r="M97" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
       <c r="N97" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5866,25 +5866,25 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03321069553401301</v>
+        <v>0.03512117142504345</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.008660983258572008</v>
+        <v>-0.009602130150173638</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0.001454720993891545</v>
+        <v>0.002087014758827221</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.01325635234597888</v>
+        <v>-0.01064165052737787</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.0177237279192145</v>
+        <v>-0.01716375835171013</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.01010101010101006</v>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v>-0.004608294930875556</v>
+        <v>-0.01166480029861894</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>0.000661375661375585</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5903,49 +5903,49 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FXE</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="22" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D99" s="23" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Euro Currency</t>
+          <t>7-10 Year Treasury</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.07427164098302175</v>
+        <v>0.01992104875187617</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.001208176450858467</v>
+        <v>-0.02882098050513671</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.00822985080442229</v>
-      </c>
-      <c r="I99" s="3" t="n">
-        <v>0.01130739704125716</v>
-      </c>
-      <c r="J99" s="3" t="n">
-        <v>0.003439445758174564</v>
-      </c>
-      <c r="K99" s="3" t="n">
-        <v>0.007079941213454566</v>
+        <v>-0.00631056919306483</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>-0.03000930033801774</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>-0.02525615475435683</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>-0.0226533669516763</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.001120134416129792</v>
+        <v>-0.00164817053071098</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
-          <t>RECOVERY</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N99" s="7" t="inlineStr">
         <is>
-          <t>Weak long trend; 3m and 1m now positive; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5955,40 +5955,40 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>LQD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" s="24" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
+      <c r="D100" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>7-10 Year Treasury</t>
+          <t>Investment Grade Corporate Bonds</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.01858454521482167</v>
+        <v>0.03653421212524055</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.02571525525183649</v>
+        <v>-0.02790392607948255</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.008402582135218495</v>
+        <v>-0.0100408261382825</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>-0.02942339534283345</v>
+        <v>-0.01358111301565068</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>-0.02530292993915439</v>
+        <v>-0.0326607216756275</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.01745937696560118</v>
+        <v>-0.01804427941358244</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>-0.001864443957008133</v>
+        <v>-0.001246165644171682</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6007,49 +6007,49 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LQD</t>
+          <t>FXE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D101" s="22" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Investment Grade Corporate Bonds</t>
+          <t>Euro Currency</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.03475193716326985</v>
+        <v>0.07071959216679269</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.02215955975437756</v>
+        <v>-0.01030022223197458</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.009445560272062448</v>
-      </c>
-      <c r="I101" s="5" t="n">
-        <v>-0.01598907960307394</v>
+        <v>-0.01069424160794796</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>0.01327139312817605</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>-0.03207527123923926</v>
-      </c>
-      <c r="K101" s="5" t="n">
-        <v>-0.01283523547257737</v>
+        <v>-0.002188817387284048</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>0.0003982786642360292</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>-0.0003832886163281923</v>
+        <v>-0.00607419867302128</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>REBOUND</t>
         </is>
       </c>
       <c r="N101" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Weak long trend; 1m rebound not yet confirmed by 3m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr"/>
-      <c r="D102" s="24" t="inlineStr">
+      <c r="D102" s="23" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -6074,25 +6074,25 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.04332721963109898</v>
+        <v>-0.03936328631511998</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.05755354177200045</v>
+        <v>-0.06554960800261411</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.04675553650660935</v>
+        <v>-0.04755136048099529</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.04838040706433888</v>
+        <v>-0.04542597362361322</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-0.04852363407068816</v>
+        <v>-0.04796321315204533</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>-0.01132763491310429</v>
-      </c>
-      <c r="L102" s="3" t="n">
-        <v>0.001114137162664175</v>
+        <v>-0.01889681687267475</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>-0.001854828737479997</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6130,25 +6130,25 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.001849568434031945</v>
+        <v>-0.009234557767289098</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.08634311512415338</v>
+        <v>-0.09316303531179571</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>-0.06038374717832951</v>
+        <v>-0.06123215627347867</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0.001030502885408069</v>
-      </c>
-      <c r="J103" s="3" t="n">
-        <v>0.01632140615191457</v>
+        <v>0.004577611319184438</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>-0.001034554107179786</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>-0.02762762762762772</v>
-      </c>
-      <c r="L103" s="3" t="n">
-        <v>0.009561421741841603</v>
+        <v>-0.0340136054421768</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>-0.005970763845995486</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="N103" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6186,25 +6186,25 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.0513320043740243</v>
+        <v>-0.04051881591672923</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.1500673073910234</v>
+        <v>-0.1454190390179692</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>-0.1333884744589839</v>
+        <v>-0.1103924417313996</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.1326764436296974</v>
+        <v>0.1588655752824533</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.1452734012974977</v>
+        <v>0.1480127912288716</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>-0.01924603174603168</v>
+        <v>-0.03937308868501532</v>
       </c>
       <c r="L104" s="3" t="n">
-        <v>0.01042518397383474</v>
+        <v>0.01679142221323082</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -206,9 +206,6 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -690,25 +687,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.240075533726315</v>
+        <v>2.220339033013261</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.328310111130494</v>
+        <v>1.314127511468786</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.345644399605916</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.4281111558598469</v>
+        <v>0.4194120016109544</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1020511521904278</v>
+        <v>-0.1075208913649025</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.00738998992274098</v>
+        <v>-0.01343634531407456</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>-0.06051292920729112</v>
+        <v>-0.06623569309029254</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -746,25 +743,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.851639896671285</v>
+        <v>1.839045903436774</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.122198294465897</v>
+        <v>1.112825809884659</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>1.293293956872363</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4993447168279066</v>
+        <v>0.4927230051447549</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.178100060546436</v>
+        <v>-0.1817299025503319</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.07460694774594434</v>
+        <v>-0.07869385712498433</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>-0.05369098895475288</v>
+        <v>-0.05787027165337555</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -802,25 +799,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.596346696792424</v>
+        <v>1.552912088659186</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9517026292359907</v>
+        <v>0.9190524974047569</v>
       </c>
       <c r="H4" s="10" t="n">
         <v>1.260313464353132</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.4218712336233688</v>
+        <v>0.3980846779619589</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.2201932448630207</v>
+        <v>-0.2332386714442596</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.1365345293846053</v>
+        <v>-0.1509794868412375</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>-0.06292054402290614</v>
+        <v>-0.0785969935576234</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -858,25 +855,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.895399305555555</v>
+        <v>1.875868055555556</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.016626360338573</v>
+        <v>1.003022974607013</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>1.17956469165659</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.541002541002541</v>
+        <v>0.5306075306075309</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1316063525123665</v>
+        <v>-0.1374642020307211</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.07475728155339811</v>
+        <v>-0.08099861303744782</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-0.06777529346003364</v>
+        <v>-0.07406372275013973</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -910,25 +907,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.568510688323379</v>
+        <v>1.554731345212028</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9667350459873336</v>
+        <v>0.956184061274294</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>1.168227358529634</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.5094324824203698</v>
+        <v>0.5013346599151638</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1617656400756099</v>
+        <v>-0.1662625335110278</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.09292951301884733</v>
+        <v>-0.09779569306750924</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-0.05219420570322741</v>
+        <v>-0.05727891930863083</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -966,25 +963,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.518463104640253</v>
+        <v>1.501910893456296</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.876909905464766</v>
+        <v>0.8645744069359325</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.086400699445819</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4679430069726984</v>
+        <v>0.4582953362186568</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1612660453952527</v>
+        <v>-0.1667784045303321</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.100407747196738</v>
+        <v>-0.1063200815494393</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-0.05209452201933396</v>
+        <v>-0.05832438238453264</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1022,25 +1019,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.468522396073779</v>
+        <v>1.463200245957859</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7910656403878054</v>
+        <v>0.7872040913814964</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.944372436407511</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4010533653473782</v>
+        <v>0.3980326853071026</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1246693335053876</v>
+        <v>-0.1265565520356152</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.0788464149918523</v>
+        <v>-0.08083242802824553</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>-0.04548572634689463</v>
+        <v>-0.04754366524193965</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1078,25 +1075,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.210577917775439</v>
+        <v>1.213054987064196</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.7853042063953255</v>
+        <v>0.7873047340334562</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.7921393424922727</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5300757251035864</v>
+        <v>0.5317902557508216</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.04355876047554075</v>
+        <v>0.04472812317287067</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.003813953488372102</v>
+        <v>-0.00269767441860469</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-0.03444234063655205</v>
+        <v>-0.03336038229194849</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -1134,25 +1131,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.145658263305322</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8866995073891628</v>
+        <v>0.8842364532019706</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.7105911330049264</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.4604385128693995</v>
+        <v>0.4585319351763584</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.2435064935064934</v>
+        <v>0.2418831168831168</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1029517638588913</v>
+        <v>0.1015118790496761</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-0.04309806371018121</v>
+        <v>-0.04434728294815748</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -1190,34 +1187,34 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.209185013743035</v>
+        <v>1.233708324004235</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.6407556313874108</v>
+        <v>0.6589690264453247</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.6570314312263976</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.1122890874663018</v>
+        <v>0.1246361793677935</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-0.01165794760284222</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>-0.009822263797941821</v>
+        <v>-0.0006867439035823653</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.001169317118802748</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.04348808313566022</v>
+        <v>-0.03287021348695351</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1242,34 +1239,34 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8058442697184656</v>
+        <v>0.8169117524746563</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.6442729697987886</v>
+        <v>0.6543502300835615</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.6465823419473826</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.2869881359430653</v>
+        <v>0.2948757036812251</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.1719393867856704</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>-0.001402524544179662</v>
+        <v>0.1791218549375744</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.004717582557694611</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.0028169014084507</v>
+        <v>0.008962868117797784</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1298,34 +1295,34 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.6790386905469414</v>
+        <v>0.6395645211087173</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6100494267389664</v>
+        <v>0.572197193652958</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.6054743117895212</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1094225743001105</v>
+        <v>0.08334006951741979</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-0.03837260901043982</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0.002849696763036702</v>
+        <v>-0.06098045168974942</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>-0.02072728158413906</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.02122804098224262</v>
+        <v>-0.0442389521477643</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1354,25 +1351,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.242686079498196</v>
+        <v>1.244710392782184</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5719225991675372</v>
+        <v>0.5733413554976203</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.56216791757505</v>
+        <v>0.5621678118840088</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1251797246164066</v>
+        <v>0.1261953443610677</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.0289302865907255</v>
+        <v>0.02985902881037195</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.00624432334241587</v>
+        <v>0.007152588555858319</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-0.02303791887125228</v>
+        <v>-0.02215608465608476</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -1406,25 +1403,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.8788881535407016</v>
+        <v>0.8808735936465919</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.5025138925641706</v>
+        <v>0.5041016141836465</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.5390314898121196</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.2188746732700508</v>
+        <v>-0.2180492502407483</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.07358459781367266</v>
+        <v>-0.07260564529286995</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.02372764786795045</v>
+        <v>-0.02269601100412644</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>-0.02305574673090149</v>
+        <v>-0.02202339986235369</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1462,25 +1459,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.7604938650807305</v>
+        <v>0.7696810476773683</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4825291918781633</v>
+        <v>0.4902658086655249</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0.5045301958672228</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.1169612151304087</v>
+        <v>0.1227901060117154</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.04986209966941169</v>
+        <v>-0.04490378055483579</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.01462317210348696</v>
+        <v>-0.009480957737425633</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.03204419889502763</v>
+        <v>-0.02699289660615634</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1518,25 +1515,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.7143534943040648</v>
+        <v>0.7260165295464791</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.3937053353613504</v>
+        <v>0.4031869472330367</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.4982778952795142</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.3869086041791963</v>
+        <v>0.3963439767451769</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.04837343710121089</v>
+        <v>-0.04189936149336093</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.06979516967288302</v>
+        <v>-0.0634668297156834</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.0138074093281042</v>
+        <v>-0.007098175217969072</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1574,25 +1571,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.7542041075899208</v>
+        <v>0.7607466593828269</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.3934054805656257</v>
+        <v>0.3986025172167098</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.4923490629612628</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.005544605100627709</v>
+        <v>-0.001835547538242888</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.1500587176030883</v>
+        <v>-0.146888659743051</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.06630056255022776</v>
+        <v>-0.06281810875971061</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-0.02489858721499516</v>
+        <v>-0.02126171492516427</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1630,25 +1627,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.142077413592747</v>
+        <v>1.166485016412749</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.697023681202972</v>
+        <v>0.7163600739421008</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.4898937147062012</v>
+        <v>0.4898936215659329</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.4039955477823676</v>
+        <v>0.4199931795550906</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.2515750071788669</v>
+        <v>0.265835904325169</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.1390233172019357</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>-0.00423076923076926</v>
+        <v>0.1520017597888252</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0.007115384615384635</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1657,7 +1654,7 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1686,25 +1683,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.6630991703688478</v>
+        <v>0.6572068438324503</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.3889272890244726</v>
+        <v>0.384006611595894</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.4265756386651089</v>
+        <v>0.4265758086905247</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.1501619868067132</v>
+        <v>0.1460870680591695</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.04580952792948989</v>
+        <v>0.04210432040167778</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.02639071397284276</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0.00338562239024931</v>
+        <v>-0.02984012264564162</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>-0.0001692811195125321</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1713,7 +1710,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1738,25 +1735,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.7501354768038586</v>
+        <v>0.7562348380821993</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.3620876944098592</v>
+        <v>0.3668346783154481</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0.4149720619830586</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.3456693274152582</v>
+        <v>0.3503590920065554</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.005092142716405901</v>
+        <v>-0.001624809735238819</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.0373748492949626</v>
+        <v>-0.03402002411280602</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-0.02147386369691484</v>
+        <v>-0.01806362231576697</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1794,25 +1791,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.5891877958846365</v>
+        <v>0.5584597790914039</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.5187455596562893</v>
+        <v>0.4893794977541974</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.4133397781732577</v>
+        <v>0.4133396897232375</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.1516509613081432</v>
+        <v>0.1293830140141483</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.1481680276558059</v>
+        <v>0.125967425230703</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.07457922228670921</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>0.008387342737323555</v>
+        <v>0.05380150899593716</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>-0.01111050596372753</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1821,7 +1818,7 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1846,25 +1843,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.570886584954402</v>
+        <v>0.5403328080341847</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.5225623711919263</v>
+        <v>0.4929487689592091</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.4126676551432764</v>
+        <v>0.4126677798334002</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.1562858408736478</v>
+        <v>0.1337961603339384</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.1517741828127546</v>
+        <v>0.1293722537138284</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.07779233540779562</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>0.01028553883942274</v>
+        <v>0.05682934818211582</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>-0.009364445809026734</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1873,7 +1870,7 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1902,25 +1899,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6546065515020687</v>
+        <v>0.6091120429876642</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.5495342215953742</v>
+        <v>0.5069286511111746</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0.395546629552846</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.1955359314723468</v>
+        <v>0.1626638014574995</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.2091149325734156</v>
+        <v>0.1758694380465402</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1103421331696155</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>0.01645207439198848</v>
+        <v>0.07981246860523528</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>-0.01149601471489881</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1929,7 +1926,7 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1958,25 +1955,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5169278624682669</v>
+        <v>0.5292604349051877</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4149271274911202</v>
+        <v>0.4264306000723488</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.3869702032179523</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.2272781071517227</v>
+        <v>0.2372559779415742</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1893738863286207</v>
+        <v>0.1990435927215364</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.02015683120538858</v>
+        <v>0.02845078918266819</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>9.855615236764592e-05</v>
+        <v>0.008229438722712201</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -2010,25 +2007,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.5808856733514705</v>
+        <v>0.5625032818008719</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.5602531148817178</v>
+        <v>0.5421106368016977</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.3853410185204995</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.168234064785789</v>
+        <v>0.154649947753396</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.1747810858143608</v>
+        <v>0.1611208406304727</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.1262592343854936</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>0.01145958986730999</v>
+        <v>0.1131631967763598</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>-0.0003015681544028537</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2037,7 +2034,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2066,25 +2063,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.6493195437453771</v>
+        <v>0.6328367570625735</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.2521206094681121</v>
+        <v>0.2396072242391989</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.3835111543716991</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.03349730063685286</v>
+        <v>0.0231687829540359</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>-0.2188973816880794</v>
+        <v>-0.2267035290291105</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>-0.09496890898812882</v>
+        <v>-0.1040135669869984</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>-0.02950090927460092</v>
+        <v>-0.03919983835118213</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -2122,25 +2119,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.723392124056216</v>
+        <v>0.7297775354336784</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3307078354230755</v>
+        <v>0.3356383917141161</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3778993868045706</v>
+        <v>0.3778994855315365</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.3331546362079096</v>
+        <v>0.3380941625427074</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.01707882858655241</v>
+        <v>0.02084724938480176</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.03424890948745918</v>
+        <v>-0.03067066521264994</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-0.01947962078748877</v>
+        <v>-0.01584665421078124</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -2174,25 +2171,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.7194325805735347</v>
+        <v>0.7247877157150517</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3280289745893044</v>
+        <v>0.3321650917660555</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.3748677069422435</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.3331660201418016</v>
+        <v>0.337318136534499</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.0188573859765131</v>
+        <v>0.02203059500691151</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>-0.03406781039108864</v>
+        <v>-0.03105943572648173</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.01874948376971997</v>
+        <v>-0.01569340051210033</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -2226,25 +2223,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1.407555798725963</v>
+        <v>1.440260045068144</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.4241427388450694</v>
+        <v>0.4434882987620041</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.3724514027470198</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.02283234545119628</v>
+        <v>-0.00955849663370012</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.1281453377299329</v>
+        <v>0.1434700679207872</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.03766350924672968</v>
+        <v>0.05175913396481713</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.04503943545039435</v>
+        <v>-0.0320672478206725</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2282,25 +2279,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.7315569901636605</v>
+        <v>0.7396629465454132</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3317249724468088</v>
+        <v>0.337959299681547</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3672120620978938</v>
+        <v>0.3672121732588138</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.3356959984385284</v>
+        <v>0.3419488064974769</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.02113110238108473</v>
+        <v>0.02591133440519489</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.02595580498070837</v>
+        <v>-0.02139600140301645</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>-0.01310957551826253</v>
+        <v>-0.008489634748272468</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2338,25 +2335,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5145644925141428</v>
+        <v>0.5132049193610779</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.2731522151902905</v>
+        <v>0.2720093496470317</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3622957275644758</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.1110444707564924</v>
+        <v>0.1100471238348077</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>-0.157774607974429</v>
+        <v>-0.1585306451306459</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.06543624161073813</v>
+        <v>-0.06627516778523479</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>-0.02309266296404555</v>
+        <v>-0.02396959953230049</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2394,25 +2391,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.9928133460564925</v>
+        <v>0.9888419372604327</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2876978795858327</v>
+        <v>0.2851315825162715</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.3446230145833766</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.01379411632433514</v>
+        <v>0.0117736914163602</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.08281696638329872</v>
+        <v>-0.08464485176599346</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.04233538648390733</v>
+        <v>-0.04424394898932937</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>-0.02851359676141862</v>
+        <v>-0.03044970518349022</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2450,25 +2447,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5323398749294579</v>
+        <v>0.534488398816942</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1020977017856126</v>
+        <v>0.1036429746571006</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.3275711934165428</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.08507270689784863</v>
+        <v>-0.08378986933896071</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.133682529342915</v>
+        <v>-0.1324678485724774</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.1698390961999315</v>
+        <v>-0.1686751112632661</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-0.01410798503821764</v>
+        <v>-0.0127256464465767</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2506,25 +2503,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.7782824200007499</v>
+        <v>0.7838008675005423</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.2074357831072569</v>
+        <v>0.2111827531630288</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.3175156871781777</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.01671356698217785</v>
+        <v>0.01986867911656853</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.07866470906421441</v>
+        <v>-0.07580557916698871</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.08355111452728659</v>
+        <v>-0.0807071483474251</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-0.01755108767303881</v>
+        <v>-0.01450230718523404</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2558,25 +2555,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5368071802630852</v>
+        <v>0.5347563701209368</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.1243549959202865</v>
+        <v>0.1228547128529127</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.3157482500866637</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>-0.03295910176436545</v>
+        <v>-0.03424947276849233</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.1894940131324835</v>
+        <v>-0.1905755117806102</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.1454634305261443</v>
+        <v>-0.1466036813813325</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.02208966352875386</v>
+        <v>-0.02339453816758319</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2614,25 +2611,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.5523915116936424</v>
+        <v>0.5537624775009724</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.3003507488370594</v>
+        <v>0.3014992656616815</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.307935429216279</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.286482345537405</v>
+        <v>0.2876186132865106</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.1245042012930848</v>
+        <v>0.125497404085253</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.005798971577491763</v>
+        <v>-0.00492085726162661</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.01197711834107973</v>
+        <v>0.01287093314265286</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2670,25 +2667,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4176786931152972</v>
+        <v>0.4220911284200264</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.1847246737783101</v>
+        <v>0.1884120544255257</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.3061009534158234</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1037789865445176</v>
+        <v>0.1072144288577153</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.07096385542168671</v>
+        <v>-0.06807228915662655</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.09293024350076473</v>
+        <v>-0.09010704622985544</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.02528125395019598</v>
+        <v>-0.02224750347617244</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2722,25 +2719,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.3254433995732973</v>
+        <v>0.3219786912967479</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2876767986120823</v>
+        <v>0.2843108122085074</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0.2876767986120823</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1362909703441519</v>
+        <v>0.1333207064077311</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.05741032644568711</v>
-      </c>
-      <c r="K39" s="20" t="n">
-        <v>0</v>
+        <v>0.05464625646659593</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>-0.002613999419111113</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.009085580304806662</v>
+        <v>0.006447831184056341</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2774,25 +2771,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.5685911471849954</v>
+        <v>0.5705517499660058</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.208863038942213</v>
+        <v>0.2103740903286491</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2819773856485994</v>
+        <v>0.2819774677508238</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.2449564600516696</v>
+        <v>0.2465125475651015</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>-0.0540989747699786</v>
+        <v>-0.05291668059220334</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.05703247773703513</v>
+        <v>-0.0558538501833421</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.02899332479266414</v>
+        <v>-0.02777965073157573</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2826,25 +2823,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4447070470966654</v>
+        <v>0.4429794452466242</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.211048733731108</v>
+        <v>0.2096006274440427</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2794757025428209</v>
+        <v>0.2794757908971111</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1699724476358928</v>
+        <v>0.1685733774443998</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.03713377032069864</v>
+        <v>-0.03828517986291613</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.0534804753820034</v>
+        <v>-0.05461233729485027</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.01006214856466403</v>
+        <v>-0.01124593074874236</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2878,25 +2875,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4561738178807442</v>
+        <v>0.4536491816034112</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2100300578895733</v>
+        <v>0.2079320794273194</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2734729265881319</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1743379616041814</v>
+        <v>0.1723018669346408</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.01325894442000697</v>
+        <v>-0.0149697791789708</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.04981878088962111</v>
+        <v>-0.05146622734761119</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.001765377825469816</v>
+        <v>-0.003496140399460002</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -2930,25 +2927,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.3521716305175431</v>
+        <v>0.3507154904889866</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2301881853174532</v>
+        <v>0.2288634080341048</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.2707263701879186</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1130828339141201</v>
+        <v>0.1118841662058345</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.02318560231030098</v>
+        <v>0.02208374402652935</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.03190158465387827</v>
+        <v>-0.03294412010008341</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>-0.002577873254564933</v>
+        <v>-0.003651987110633637</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2982,25 +2979,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4332331500530524</v>
+        <v>0.4301423823234247</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2614608403647247</v>
+        <v>0.258740499673858</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.2688446222399339</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.1742851675009072</v>
+        <v>0.1717528211754278</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.04102587495139032</v>
+        <v>0.03878090233134723</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.005819295558958548</v>
-      </c>
-      <c r="L44" s="20" t="n">
-        <v>0</v>
+        <v>-0.007963246554364423</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>-0.002156500308071463</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3009,7 +3006,7 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d flat.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3034,25 +3031,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.4748477593057197</v>
+        <v>0.4759065157732758</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2507144336800791</v>
+        <v>0.2516122904163891</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>0.263027897492333</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1761012269839763</v>
+        <v>0.1769455207578341</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.05748895904234774</v>
+        <v>0.0582481040237135</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.009749162181375004</v>
+        <v>-0.009038285772316468</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>-0.01065340909090906</v>
+        <v>-0.009943181818181879</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -3086,25 +3083,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4925201116659261</v>
+        <v>0.499090902071659</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2151873519079543</v>
+        <v>0.2205372080642829</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2597840673404985</v>
+        <v>0.2597839869962866</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1923722963773591</v>
+        <v>0.1976217857471156</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-0.01997756307574861</v>
+        <v>-0.01566295648820293</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.03540028532563622</v>
+        <v>-0.03115357818254216</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.0123985189714324</v>
+        <v>-0.008050545195149361</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3138,25 +3135,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.4480732898169368</v>
+        <v>0.4478715229842014</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2286352379341288</v>
+        <v>0.228463951828185</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.2596380231099376</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1317811087306213</v>
+        <v>0.1316233252218062</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.007792604258085367</v>
+        <v>0.007652106195313868</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.02461245580636395</v>
+        <v>-0.02474843622518363</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.01320676846884017</v>
+        <v>-0.013344338973724</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3190,25 +3187,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4914584847821535</v>
+        <v>0.498239281802408</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2146460675070427</v>
+        <v>0.2201683589548122</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.259409314694258</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1920049227397247</v>
+        <v>0.1974242780290025</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.02012097361776322</v>
+        <v>-0.01566603179397308</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.03554304916196549</v>
+        <v>-0.03115822257434409</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.01235172336615942</v>
+        <v>-0.007861459265890769</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3246,25 +3243,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.1721139624853809</v>
+        <v>0.1711323952604378</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.3172698808099992</v>
+        <v>0.3161667551901435</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.255356955395607</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1212196012054356</v>
+        <v>0.1202806546117328</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-0.02077939000367623</v>
+        <v>-0.02159942191825492</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.04931898066783824</v>
+        <v>0.04844024604569408</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.001362683438155043</v>
+        <v>0.0005241090146750338</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3298,25 +3295,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4559913206509885</v>
+        <v>0.4628068505692728</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.08390806540947748</v>
+        <v>0.08898197691329468</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0.2543613498891937</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-0.05794190077834704</v>
+        <v>-0.05353200700649918</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.07647264706337131</v>
+        <v>-0.07214949807159332</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.1358885017421603</v>
+        <v>-0.1318434859225439</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>-0.01483950504543174</v>
+        <v>-0.01022784347746675</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3354,25 +3351,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.5169097467126098</v>
+        <v>0.517213258781664</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1882548364972194</v>
+        <v>0.1884927729883081</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>0.2532511546462963</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.2333220955852053</v>
+        <v>0.2335690563572488</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.07530504815265393</v>
+        <v>-0.07511988696886396</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.05186216498433693</v>
+        <v>-0.05167230959086155</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>-0.02410109431995844</v>
+        <v>-0.02390568004168847</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3410,25 +3407,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4213173949600446</v>
+        <v>0.4217453316529409</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.1633282572897696</v>
+        <v>0.163678266306269</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2499357209162836</v>
+        <v>0.2499355995034787</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.1613488214115184</v>
+        <v>0.1616983477196399</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.03802726763131514</v>
+        <v>-0.03773774671265639</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.06928953399541626</v>
+        <v>-0.06900942195059834</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>-0.005821070097652536</v>
+        <v>-0.005521856214128262</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3462,25 +3459,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.4134775592222828</v>
+        <v>0.4129445737172972</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.134732567648965</v>
+        <v>0.1343046896068651</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.2474784317422918</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.05905945227660125</v>
+        <v>0.05866010859173088</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.08010712348235804</v>
+        <v>-0.08045399108285478</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>-0.09037900874635574</v>
+        <v>-0.090722003086949</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.01923076923076916</v>
+        <v>-0.01960059171597628</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3514,25 +3511,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.3393160015912671</v>
+        <v>0.3406460075511395</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2436504109489019</v>
+        <v>0.2448854163222376</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.2430722933679541</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.1413170312751668</v>
+        <v>0.1424504146230072</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.1074959590991704</v>
+        <v>0.1085957564766276</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.0004650715682685824</v>
+        <v>0.001458582066350411</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.007863883328567356</v>
+        <v>0.008864741206748628</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3570,25 +3567,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2226274989655019</v>
+        <v>0.2255064288206527</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2299232461298379</v>
+        <v>0.2328190617374617</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2375153649331088</v>
+        <v>0.2375152171373887</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1440829352440294</v>
+        <v>0.1467767794978176</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.1009066565759524</v>
+        <v>0.1034988384706521</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.006134969325153561</v>
+        <v>-0.003794826386692929</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.01139216064877369</v>
+        <v>0.01377357276179425</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3622,25 +3619,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.327301484029503</v>
+        <v>0.3309829348374158</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1233242689548151</v>
+        <v>0.1264398266463573</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0.2315733266205304</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.03464477993975756</v>
+        <v>0.03751438366082249</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.03577637053719507</v>
+        <v>-0.0331020809948398</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.08789493514182667</v>
+        <v>-0.08536519726573</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.01688228810117764</v>
+        <v>-0.01415559552126233</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3678,25 +3675,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4089955498295821</v>
+        <v>0.4139243567961899</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.07382373335350745</v>
+        <v>0.07758000351827699</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0.2293064876737918</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>-0.07488393953934769</v>
+        <v>-0.07164785362606163</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.07991563448041672</v>
+        <v>-0.07669714959884411</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.1264800567468762</v>
+        <v>-0.1234244557210673</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.01062975094246332</v>
+        <v>-0.007168901798405569</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3730,25 +3727,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1876725257844196</v>
+        <v>0.1905825730644324</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2185997269643705</v>
+        <v>0.2215855558316593</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2261731924600257</v>
+        <v>0.2261733287090002</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1267038928518893</v>
+        <v>0.1294644318507494</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.09276392417583468</v>
+        <v>0.09544130680349161</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.006176505523221243</v>
+        <v>-0.003741536999643635</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.01197387518142223</v>
+        <v>0.01445331398161587</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3782,25 +3779,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.4947880329763561</v>
+        <v>0.4985636843749994</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1922311841915336</v>
+        <v>0.1952427464949416</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>0.2235051004192332</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.185179646134225</v>
+        <v>0.188173500712101</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.01013108566124288</v>
+        <v>0.01268266520337735</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.02556092019312683</v>
+        <v>-0.02309949824860358</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.00819040277510108</v>
+        <v>-0.005685103102717304</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -3834,25 +3831,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.343452005092858</v>
+        <v>0.3460365607009626</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.128767074461076</v>
+        <v>0.1309386155816243</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.2205731513728775</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1220185684751689</v>
+        <v>0.1241771267061715</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.0358999348155693</v>
+        <v>-0.03404518286254044</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.07521554673600661</v>
+        <v>-0.07343643081976203</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>-0.008277319557368878</v>
+        <v>-0.006369426751592355</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3890,25 +3887,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3328107524522248</v>
+        <v>0.3200177201434939</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1026276564724091</v>
+        <v>0.09204397041551893</v>
       </c>
       <c r="H61" s="3" t="n">
         <v>0.2066882340667311</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.04629697429798862</v>
+        <v>0.03625398414329606</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>-0.1207150471550053</v>
+        <v>-0.1291549550793463</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.08623650637880276</v>
+        <v>-0.09500736015701661</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.02096339620161658</v>
+        <v>-0.0303607807057894</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -3942,25 +3939,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3039800780171629</v>
+        <v>0.3045727795172355</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.159552735357184</v>
+        <v>0.1600797782985897</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1971242463914793</v>
+        <v>0.1971243426476204</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1320180157230959</v>
+        <v>0.1325324524491687</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.01628457633395497</v>
+        <v>0.01674641890443174</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.03138480500044016</v>
+        <v>-0.03094462540716614</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.0006811989100816707</v>
+        <v>-0.0002270663033605569</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -3994,25 +3991,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3853665103365629</v>
+        <v>0.3862585686175264</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1695977579101065</v>
+        <v>0.1703508794541568</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0.1965427731527949</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1543408568911269</v>
+        <v>0.1550841542877084</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.02776617803670778</v>
+        <v>0.02842797209854719</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.02251905727673265</v>
+        <v>-0.02188964263235205</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.005280687770439441</v>
+        <v>-0.004640173081302601</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -4046,25 +4043,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3853758486457015</v>
+        <v>0.3865183105867593</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1695010670551322</v>
+        <v>0.1704655262076105</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.1964783646940815</v>
+        <v>0.1964782528849172</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1544506997142359</v>
+        <v>0.1554028551646778</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.0278626630239589</v>
+        <v>0.0287104125529305</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>-0.02254725069420449</v>
+        <v>-0.02174107771251621</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>-0.00530003125325551</v>
+        <v>-0.004479633295134788</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4098,25 +4095,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.3835865890936403</v>
+        <v>0.3844239235082487</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1688237077181842</v>
+        <v>0.1695310493636335</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1959598881388804</v>
+        <v>0.1959600003667503</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1539809758323334</v>
+        <v>0.154679226689157</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.02755446556412844</v>
+        <v>0.02817621826286354</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.02268987504499409</v>
+        <v>-0.02209852419396297</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.005312119745122801</v>
+        <v>-0.004710253961192623</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4143,7 +4140,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D66" s="21" t="inlineStr">
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4154,25 +4151,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3714346828858759</v>
+        <v>0.3658221594036459</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1454617410605656</v>
+        <v>0.1407741599032766</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1955191892594998</v>
+        <v>0.1955192656104046</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1966325683049919</v>
+        <v>0.1917355043014051</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.02759837291466849</v>
+        <v>0.02339305949145731</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.04187088643047188</v>
+        <v>-0.04579190589553284</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.005584950029394298</v>
+        <v>0.001469723691945868</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4206,25 +4203,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.4520795660036168</v>
+        <v>0.4564195298372515</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1717495987158908</v>
+        <v>0.1752517145775574</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.1933459798628339</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>-0.1491841491841491</v>
+        <v>-0.1466412375503283</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.01401692132845045</v>
+        <v>0.01704760702108854</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.01809733431156768</v>
+        <v>-0.01516263145023222</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.01725614979806633</v>
+        <v>-0.01431893281116126</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4258,25 +4255,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.4495986387008473</v>
+        <v>0.4531868457070987</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1705998327159757</v>
+        <v>0.1734974309953399</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.1917791850878241</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>-0.14966148771808</v>
+        <v>-0.1475566357087058</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.01378899984477666</v>
+        <v>0.0162984425932633</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.01777120513334662</v>
+        <v>-0.01533988369761385</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>-0.01730320736264002</v>
+        <v>-0.01487072748702256</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4310,25 +4307,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.2887757354467084</v>
+        <v>0.2890755065053814</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1481385516313509</v>
+        <v>0.1484056102821769</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0.1896394659697189</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1198653065611734</v>
+        <v>0.1201257888152116</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.01957237982187743</v>
+        <v>0.01980953379932027</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.03488528711893313</v>
+        <v>-0.03466080007183581</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.0004188579140875781</v>
+        <v>0.0006515567552471957</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4366,25 +4363,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.4102743749428397</v>
+        <v>0.4118771712458007</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1675945045629892</v>
+        <v>0.1689214918418633</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0.1844132968184888</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1674816201806828</v>
+        <v>0.1688084791648976</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.04036917858951616</v>
+        <v>0.04155157252844432</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.01420010422094842</v>
+        <v>-0.01307972902553423</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.005258314710135381</v>
+        <v>-0.004127777047456371</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4418,25 +4415,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.6265609610578255</v>
+        <v>0.6400395469420257</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.300814685370935</v>
+        <v>0.3115939570219639</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0.1742451730814349</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.06413477523375333</v>
+        <v>0.07295278593470123</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.07595839081146227</v>
+        <v>0.08487437854606683</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.1077879774948176</v>
+        <v>0.1169677228309149</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.0204241948153967</v>
+        <v>-0.01230688661953383</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4470,25 +4467,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.432397782297663</v>
+        <v>0.4365660114362195</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1422555581233211</v>
+        <v>0.1455794131329693</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>0.1651390214589759</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1806646598465587</v>
+        <v>0.1841002816883057</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.02945526682871202</v>
+        <v>0.03245088372155447</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.01964011411016031</v>
+        <v>-0.01678736010533244</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.006117908787541815</v>
+        <v>-0.003225806451612967</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4526,25 +4523,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.1046737453574231</v>
+        <v>0.1079477509693498</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.108289211502256</v>
+        <v>0.1115739325462255</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0.1596281848561474</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1476442428823381</v>
+        <v>0.1510456034265559</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.1126038104543234</v>
+        <v>0.1159013190034197</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.0442719261435166</v>
+        <v>-0.04143936214855215</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.01210976558160182</v>
+        <v>0.01510943228530159</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -4578,34 +4575,34 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.34915164766785</v>
+        <v>0.3523277235157314</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1389701624167168</v>
+        <v>0.1416514441173784</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0.1556324129851134</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.1021969353045211</v>
-      </c>
-      <c r="J74" s="5" t="n">
-        <v>-0.0001565223955933837</v>
+        <v>0.1047916481167397</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0.002197237262463014</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.01441829632084857</v>
+        <v>-0.01209811070599942</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.01458160729080371</v>
+        <v>-0.01226180613090311</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4630,25 +4627,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3888080218720666</v>
+        <v>0.3947429936295834</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.125374563843162</v>
+        <v>0.1301838568510387</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0.1523066046872716</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1761723293530455</v>
+        <v>0.1811987068289131</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.05135187092515103</v>
+        <v>0.0558448276385064</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.02337228714524198</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>-0.00170648464163814</v>
+        <v>-0.01919866444073448</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0.002559726962457542</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4657,7 +4654,7 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4682,25 +4679,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.4015177450510616</v>
+        <v>0.4056846360026141</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1213849288763165</v>
+        <v>0.1247189492480469</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>0.1506217229053388</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1679610453825562</v>
+        <v>0.1714335424871811</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.026703200532189</v>
+        <v>0.0297557200534968</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.02540956201939149</v>
+        <v>-0.02251198038560132</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.006475800954328537</v>
+        <v>-0.003521926834810341</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4738,25 +4735,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2724092250263885</v>
+        <v>0.2750958297691828</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.09031755447671341</v>
+        <v>0.09261985744239154</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>0.1424735716607293</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1456672664737277</v>
+        <v>0.1480864453032833</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.02532251606586744</v>
+        <v>0.02748757619887421</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.04565183692450792</v>
+        <v>-0.04363664548132085</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>0.004241089633798101</v>
+        <v>0.006361634450697373</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -4790,25 +4787,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.261999603601818</v>
+        <v>0.2590203788529941</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.07523147828534826</v>
+        <v>0.07269316034794193</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0.1158445652838507</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>-0.03106423703498251</v>
+        <v>-0.03335162080024456</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>-0.04258207292996341</v>
+        <v>-0.04484226633664434</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.03639672429481344</v>
+        <v>-0.03867151956323922</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.007962529274004648</v>
+        <v>-0.01030444964871191</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -4835,7 +4832,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D79" s="21" t="inlineStr">
+      <c r="D79" s="20" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4846,25 +4843,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1476690670691039</v>
+        <v>0.1442127743192039</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1191814601188499</v>
+        <v>0.1158108930931669</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0.1143554209684401</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.1361642375440277</v>
+        <v>0.1327425245767495</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.08081313948100588</v>
+        <v>0.07755812386586802</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.004330789853578043</v>
+        <v>0.001306111225682249</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.01444243855020133</v>
+        <v>0.01138730731842785</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -4898,25 +4895,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1412608087471929</v>
+        <v>0.1442234125195392</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.01833138300226511</v>
+        <v>0.02097475936122262</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.1108535594215652</v>
+        <v>0.1108534349551622</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.004095924024359987</v>
+        <v>-0.001510652410924629</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-0.06553505642492841</v>
+        <v>-0.06310927491579221</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.08328926493918554</v>
+        <v>-0.08090957165520896</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.01729024943310653</v>
+        <v>-0.0147392290249434</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4950,25 +4947,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.3238838940041839</v>
+        <v>0.3279269373194744</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05953014548110236</v>
+        <v>0.06276587203645745</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0.101594590700717</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.1058102937351713</v>
+        <v>0.1091873564340331</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>-0.00488794235468526</v>
+        <v>-0.001848943866336716</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.03818505062997601</v>
+        <v>-0.03524773904305478</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.01167593328038119</v>
+        <v>-0.008657664813343957</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -5002,25 +4999,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.3213272968505194</v>
+        <v>0.3259196842899255</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.0578038930725886</v>
+        <v>0.06148039976338548</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.09999699771186243</v>
+        <v>0.09999692424762507</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1047992278283407</v>
+        <v>0.1086391457006339</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.005456636910661117</v>
+        <v>-0.001999932073707078</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.03835747254496258</v>
+        <v>-0.03501512016552599</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-0.0116954281508137</v>
+        <v>-0.008260407295329952</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5043,7 +5040,7 @@
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" s="21" t="inlineStr">
+      <c r="D83" s="20" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -5054,25 +5051,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.2521347524694777</v>
+        <v>0.2440963089832584</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.07877759486023406</v>
+        <v>0.07185199506442697</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0.09840012761502126</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1871189310939154</v>
+        <v>0.1794977952212815</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.07731574139753983</v>
+        <v>0.07039952649449543</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.01786464901219009</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>0.00365120274914088</v>
+        <v>-0.02416981925178663</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>-0.002792096219931373</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
@@ -5081,7 +5078,7 @@
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5106,25 +5103,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1088275988874807</v>
+        <v>0.1084752666146165</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05120563884836771</v>
+        <v>0.05087142764483388</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0.09821801481212455</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.04393757786161601</v>
+        <v>0.0436055893151055</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>-0.03368503107843568</v>
+        <v>-0.03399225287864394</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.04280787177926559</v>
+        <v>-0.04311219314262527</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.004641350210970452</v>
+        <v>-0.004957805907172985</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
@@ -5158,25 +5155,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.103569455867798</v>
+        <v>0.1018726607257185</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.0782350027426395</v>
+        <v>0.07657726537859633</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.09672631857914848</v>
+        <v>0.09672642528499509</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.010336016038617</v>
+        <v>0.008782572134595545</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>-0.007962469490038315</v>
+        <v>-0.00948777852571292</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.01686046511627914</v>
+        <v>-0.01837209302325582</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>0.01403214200047964</v>
+        <v>0.01247301511153753</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5195,40 +5192,44 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLF</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>EDEN</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Denmark Equity</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.2320450115153443</v>
+        <v>0.09987131606021826</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.07961118927284261</v>
+        <v>0.08606859210408024</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.09502346599992717</v>
+        <v>0.09535690016117071</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.1850584040773597</v>
+        <v>0.1590411915485337</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.08063760257766184</v>
+        <v>0.05042670408354932</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.01407483693786471</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>0.003318777292576458</v>
+        <v>-0.008479709267110724</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>-0.005467800729040073</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5237,7 +5238,7 @@
       </c>
       <c r="N86" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5247,53 +5248,49 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EDEN</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XLF</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.05663703459910518</v>
+        <v>0.2232507182728078</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.09103697474365813</v>
+        <v>0.07190512776381475</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.08535547687136003</v>
+        <v>0.09502354451200845</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.1480634437640767</v>
+        <v>0.1765995958309858</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.05610669332592599</v>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>0.00523468853603215</v>
+        <v>0.07292413779603168</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>-0.02111225540679706</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>-0.009286328460877069</v>
+        <v>-0.003842794759825297</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5308,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D88" s="22" t="inlineStr">
+      <c r="D88" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5322,34 +5319,34 @@
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.0428481411468179</v>
+        <v>-0.04631379962192816</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.08655221745350494</v>
+        <v>0.08261802575107291</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>0.0829756795422032</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.004629629629629539</v>
+        <v>0.0009920634920634885</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.0198053037932191</v>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>0.003302509907529672</v>
+        <v>0.01611278952668682</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>-0.0003302509907530116</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.01165501165501159</v>
+        <v>0.007992007992007943</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N88" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5378,25 +5375,25 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.2172153292158792</v>
+        <v>0.2205055506285958</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.0008572646439883869</v>
+        <v>0.003562759380278724</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0.07338910911521168</v>
+        <v>0.07338922129382208</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.1140407286531109</v>
+        <v>0.1170520616293511</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>-0.01519072778653796</v>
+        <v>-0.01252871682010859</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.06757274119448697</v>
+        <v>-0.0650523226135783</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.009254551001728895</v>
+        <v>-0.006576494118444631</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -5423,7 +5420,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D90" s="22" t="inlineStr">
+      <c r="D90" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5434,34 +5431,34 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.03086598136418761</v>
+        <v>0.02867498034109706</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.06742685608971266</v>
+        <v>0.06515814863787495</v>
       </c>
       <c r="H90" s="3" t="n">
         <v>0.06553626654651445</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.01219074937253506</v>
+        <v>0.01003944065973461</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.01001788908765655</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>0.001774308019872217</v>
+        <v>0.007871198568873083</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>-0.0003548616039743546</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0.005700035625222588</v>
+        <v>0.003562522265764256</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N90" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5486,25 +5483,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1352886416621983</v>
+        <v>0.1296163665731609</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.01556347472222375</v>
+        <v>0.01048937492380064</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.06413075010151625</v>
+        <v>0.06413084819809134</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.09297043970572816</v>
+        <v>-0.09750235042811217</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.05011489856715035</v>
+        <v>-0.05486093404897052</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.04564032697547682</v>
+        <v>-0.05040871934604907</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>-0.00849256900212314</v>
+        <v>-0.01344656758669494</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -5531,7 +5528,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D92" s="22" t="inlineStr">
+      <c r="D92" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5542,25 +5539,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.01730325493989193</v>
+        <v>0.01576305319130755</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.04560468470233081</v>
+        <v>0.04402163446054064</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0.04718773494412076</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.004562737642585635</v>
+        <v>0.003041825095057016</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.004180919802356575</v>
+        <v>0.002660585328772447</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.001511715797430035</v>
+        <v>-0.003023431594860182</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.005327245053272422</v>
+        <v>0.003805175038051667</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -5583,7 +5580,7 @@
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr"/>
-      <c r="D93" s="21" t="inlineStr">
+      <c r="D93" s="20" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -5594,25 +5591,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.08621731903256702</v>
+        <v>0.08635577007710027</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02787904160939392</v>
+        <v>0.02800994826268099</v>
       </c>
       <c r="H93" s="3" t="n">
         <v>0.03881117741771867</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.02171307728601346</v>
+        <v>0.02184330010943447</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.002985127923759379</v>
+        <v>-0.002858152010351778</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.01052369867207237</v>
+        <v>-0.01039768284154152</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.001017811704834615</v>
+        <v>-0.0008905852417302462</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5635,7 +5632,7 @@
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr"/>
-      <c r="D94" s="23" t="inlineStr">
+      <c r="D94" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -5646,34 +5643,34 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.04287028501670442</v>
+        <v>0.04299851202826432</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01643096723479043</v>
+        <v>0.01655604030515789</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.02212459389040711</v>
+        <v>0.02212469134920636</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.002971174981437397</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>-0.0001050800105854011</v>
+        <v>0.003094401785922241</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>1.786292805849854e-05</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.005570384168084197</v>
+        <v>-0.005448113220607009</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>-0.0004915816640039816</v>
+        <v>-0.000368686248003014</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5688,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D95" s="24" t="inlineStr">
+      <c r="D95" s="23" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -5702,25 +5699,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.2669503414588925</v>
+        <v>0.2721557049551857</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.02592476154536183</v>
+        <v>-0.02192289436872819</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.02095525345245508</v>
+        <v>0.0209551643887802</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.06978950901133452</v>
+        <v>0.07418470009190714</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-0.02685722648799738</v>
+        <v>-0.02285910498630461</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.0459177959457947</v>
+        <v>-0.04199798409676336</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>0.004717537445453335</v>
+        <v>0.00884538271022528</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -5747,7 +5744,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D96" s="24" t="inlineStr">
+      <c r="D96" s="23" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -5758,25 +5755,25 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.1731348396070262</v>
+        <v>0.1737843484565225</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.03274030267362205</v>
+        <v>-0.03220466966297864</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.01713159405536668</v>
+        <v>0.0171315148715725</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.04578360050460972</v>
+        <v>0.04636279863765269</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-0.0328436140958005</v>
+        <v>-0.03230796296032079</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.0490319020866774</v>
+        <v>-0.04850521669341901</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.002735330475263531</v>
+        <v>-0.00218300412929695</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5810,25 +5807,25 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.1660070707932022</v>
+        <v>0.1691653622733889</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.05629266725339066</v>
+        <v>-0.05373650537113406</v>
       </c>
       <c r="H97" s="3" t="n">
         <v>0.01631614729395103</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>0.05541600052886175</v>
+        <v>0.05827474079383732</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.02871199472074737</v>
+        <v>-0.02608112677086938</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.07144313778804989</v>
+        <v>-0.06892801305145824</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>-0.01014492753623197</v>
+        <v>-0.007463768115942071</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -5866,25 +5863,25 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03512117142504345</v>
+        <v>0.03424147098888897</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.009602130150173638</v>
+        <v>-0.01044374858362174</v>
       </c>
       <c r="H98" s="3" t="n">
         <v>0.002087014758827221</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.01064165052737787</v>
+        <v>-0.01148231514750964</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.01716375835171013</v>
+        <v>-0.01799888155316975</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.01166480029861894</v>
-      </c>
-      <c r="L98" s="3" t="n">
-        <v>0.000661375661375585</v>
+        <v>-0.01250466592011945</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>-0.0001889644746788655</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5893,7 +5890,7 @@
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5904,7 @@
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="23" t="inlineStr">
+      <c r="D99" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -5918,25 +5915,25 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.01992104875187617</v>
+        <v>0.02070655002741972</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.02882098050513671</v>
+        <v>-0.02807284788503006</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.00631056919306483</v>
+        <v>-0.006310650227061343</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.03000930033801774</v>
+        <v>-0.02926208302471511</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.02525615475435683</v>
+        <v>-0.02450527631829724</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.0226533669516763</v>
+        <v>-0.02190040344393485</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.00164817053071098</v>
+        <v>-0.0008790242830457595</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5959,7 +5956,7 @@
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" s="21" t="inlineStr">
+      <c r="D100" s="20" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -5970,25 +5967,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.03653421212524055</v>
+        <v>0.03762846836513711</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.02790392607948255</v>
+        <v>-0.02687755324813323</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.0100408261382825</v>
+        <v>-0.01004075567050999</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>-0.01358111301565068</v>
+        <v>-0.01253961662466418</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>-0.0326607216756275</v>
+        <v>-0.03163937157174768</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.01804427941358244</v>
+        <v>-0.01700756639635903</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>-0.001246165644171682</v>
+        <v>-0.000191717791411028</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6011,7 +6008,7 @@
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" s="22" t="inlineStr">
+      <c r="D101" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -6022,25 +6019,25 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.07071959216679269</v>
+        <v>0.07263231050556374</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.01030022223197458</v>
+        <v>-0.008532306931187117</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01069424160794796</v>
+        <v>-0.01069431184167569</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.01327139312817605</v>
+        <v>0.01508156059650867</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>-0.002188817387284048</v>
+        <v>-0.0004063416003677878</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0.0003982786642360292</v>
+        <v>0.002185376002955541</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>-0.00607419867302128</v>
+        <v>-0.004298663676292058</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6063,7 +6060,7 @@
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr"/>
-      <c r="D102" s="23" t="inlineStr">
+      <c r="D102" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -6074,25 +6071,25 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03936328631511998</v>
+        <v>-0.03686445734710986</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.06554960800261411</v>
+        <v>-0.06311830695917853</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.04755136048099529</v>
+        <v>-0.04755110811657592</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.04542597362361322</v>
+        <v>-0.04294256745984903</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-0.04796321315204533</v>
+        <v>-0.0454864937248517</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>-0.01889681687267475</v>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v>-0.001854828737479997</v>
+        <v>-0.01634439283331957</v>
+      </c>
+      <c r="L102" s="3" t="n">
+        <v>0.0007419314949919098</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6101,7 +6098,7 @@
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6130,25 +6127,25 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.009234557767289098</v>
+        <v>-0.005540734660373414</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.09316303531179571</v>
+        <v>-0.08978211870773856</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>-0.06123215627347867</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0.004577611319184438</v>
-      </c>
-      <c r="J103" s="5" t="n">
-        <v>-0.001034554107179786</v>
+        <v>0.00832292967124415</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>0.00268984067866751</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>-0.0340136054421768</v>
+        <v>-0.03041216486594633</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>-0.005970763845995486</v>
+        <v>-0.002264772493308587</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6186,25 +6183,25 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.04051881591672923</v>
+        <v>-0.04395507960823308</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.1454190390179692</v>
+        <v>-0.1484796154799024</v>
       </c>
       <c r="H104" s="5" t="n">
         <v>-0.1103924417313996</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.1588655752824533</v>
+        <v>0.1547152409499655</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.1480127912288716</v>
+        <v>0.1439013248058474</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>-0.03937308868501532</v>
+        <v>-0.04281345565749239</v>
       </c>
       <c r="L104" s="3" t="n">
-        <v>0.01679142221323082</v>
+        <v>0.01314990896216872</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -210,6 +210,9 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -799,13 +802,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.552912088659186</v>
+        <v>1.552912281805216</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9190524974047569</v>
+        <v>0.9190527156866941</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.260313464353132</v>
+        <v>1.260313721451676</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.3980846779619589</v>
@@ -907,25 +910,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.554731345212028</v>
+        <v>1.557404949099305</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.956184061274294</v>
+        <v>0.9582311496268574</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.168227358529634</v>
+        <v>1.168227228278037</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.5013346599151638</v>
+        <v>0.5029058522013412</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1662625335110278</v>
+        <v>-0.1653900019489318</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.09779569306750924</v>
+        <v>-0.09685150887896288</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-0.05727891930863083</v>
+        <v>-0.05629233308668691</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -963,7 +966,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.501910893456296</v>
+        <v>1.501911438188204</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.8645744069359325</v>
@@ -1354,10 +1357,10 @@
         <v>1.244710392782184</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5733413554976203</v>
+        <v>0.5733414619446262</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.5621678118840088</v>
+        <v>0.56216791757505</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.1261953443610677</v>
@@ -1571,7 +1574,7 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.7607466593828269</v>
+        <v>0.7607468284043433</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0.3986025172167098</v>
@@ -1630,10 +1633,10 @@
         <v>1.166485016412749</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.7163600739421008</v>
+        <v>0.7163601812398539</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.4898936215659329</v>
+        <v>0.4898937147062012</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>0.4199931795550906</v>
@@ -1686,10 +1689,10 @@
         <v>0.6572068438324503</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.384006611595894</v>
+        <v>0.3840064466440576</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.4265758086905247</v>
+        <v>0.4265756386651089</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>0.1460870680591695</v>
@@ -1843,7 +1846,7 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5403328080341847</v>
+        <v>0.5403329482921677</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0.4929487689592091</v>
@@ -1899,7 +1902,7 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6091120429876642</v>
+        <v>0.6091119408822019</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0.5069286511111746</v>
@@ -1955,13 +1958,13 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5292604349051877</v>
+        <v>0.5292606093176024</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4264306000723488</v>
+        <v>0.4264304483268988</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.3869702032179523</v>
+        <v>0.3869700556703481</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>0.2372559779415742</v>
@@ -2063,7 +2066,7 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.6328367570625735</v>
+        <v>0.6328366501164413</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0.2396072242391989</v>
@@ -2119,13 +2122,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.7297775354336784</v>
+        <v>0.7297776959465778</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3356383917141161</v>
+        <v>0.335638296015172</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3778994855315365</v>
+        <v>0.3778993868045706</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.3380941625427074</v>
@@ -2171,7 +2174,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.7247877157150517</v>
+        <v>0.724787525252333</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.3321650917660555</v>
@@ -2279,13 +2282,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.7396629465454132</v>
+        <v>0.7396625787269775</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.337959299681547</v>
+        <v>0.3379591908990263</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3672121732588138</v>
+        <v>0.3672120620978938</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>0.3419488064974769</v>
@@ -2335,7 +2338,7 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5132049193610779</v>
+        <v>0.5132050501615186</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>0.2720093496470317</v>
@@ -2394,10 +2397,10 @@
         <v>0.9888419372604327</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2851315825162715</v>
+        <v>0.2851314681437027</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3446230145833766</v>
+        <v>0.3446228949162622</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>0.0117736914163602</v>
@@ -2771,13 +2774,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.5705517499660058</v>
+        <v>0.5705518804807144</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2103740903286491</v>
+        <v>0.2103740128121498</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2819774677508238</v>
+        <v>0.2819773856485994</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.2465125475651015</v>
@@ -2823,7 +2826,7 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4429794452466242</v>
+        <v>0.4429796829875632</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.2096006274440427</v>
@@ -2832,7 +2835,7 @@
         <v>0.2794757908971111</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1685733774443998</v>
+        <v>0.1685734554032861</v>
       </c>
       <c r="J41" s="5" t="n">
         <v>-0.03828517986291613</v>
@@ -2875,25 +2878,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4536491816034112</v>
+        <v>0.4538005544976944</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2079320794273194</v>
+        <v>0.2080579581350546</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2734729265881319</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1723018669346408</v>
+        <v>0.1724240326148132</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.0149697791789708</v>
+        <v>-0.01486712909343291</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.05146622734761119</v>
+        <v>-0.05136738056013168</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.003496140399460002</v>
+        <v>-0.003392294645020444</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -2979,16 +2982,16 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4301423823234247</v>
+        <v>0.4301422618815076</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.258740499673858</v>
+        <v>0.2587404063717371</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2688446222399339</v>
+        <v>0.2688445281888612</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.1717528211754278</v>
+        <v>0.1717527403233639</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0.03878090233134723</v>
@@ -3083,13 +3086,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.499090902071659</v>
+        <v>0.4990910194974332</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2205372080642829</v>
+        <v>0.2205372859054853</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2597839869962866</v>
+        <v>0.2597840673404985</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>0.1976217857471156</v>
@@ -3135,7 +3138,7 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.4478715229842014</v>
+        <v>0.4478716344854876</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0.228463951828185</v>
@@ -3187,25 +3190,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.498239281802408</v>
+        <v>0.498070483123376</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2201683589548122</v>
+        <v>0.2200308598583485</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.259409314694258</v>
+        <v>0.2594094469337846</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1974242780290025</v>
+        <v>0.1972892162149393</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.01566603179397308</v>
+        <v>-0.01577705838148191</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.03115822257434409</v>
+        <v>-0.03126750174163684</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.007861459265890769</v>
+        <v>-0.007973366159355511</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3304,7 +3307,7 @@
         <v>0.2543613498891937</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-0.05353200700649918</v>
+        <v>-0.05353207006341631</v>
       </c>
       <c r="J50" s="5" t="n">
         <v>-0.07214949807159332</v>
@@ -3351,7 +3354,7 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.517213258781664</v>
+        <v>0.5172133759696664</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0.1884927729883081</v>
@@ -3407,13 +3410,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4217453316529409</v>
+        <v>0.4217451629248197</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.163678266306269</v>
+        <v>0.1636783793404464</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2499355995034787</v>
+        <v>0.2499357209162836</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>0.1616983477196399</v>
@@ -3444,49 +3447,49 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>COWZ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>U.S. Infrastructure Development</t>
+          <t>Large Cap Cash Flow</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.4129445737172972</v>
+        <v>0.3406461047205951</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1343046896068651</v>
+        <v>0.2448854163222376</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2474784317422918</v>
+        <v>0.2430722933679541</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.05866010859173088</v>
-      </c>
-      <c r="J53" s="5" t="n">
-        <v>-0.08045399108285478</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>-0.090722003086949</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>-0.01960059171597628</v>
+        <v>0.1424504146230072</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0.1085957564766276</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0.001458582066350411</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>0.008864741206748628</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3496,49 +3499,53 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>COWZ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>VHT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Large Cap Cash Flow</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.3406460075511395</v>
+        <v>0.2255061378340366</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2448854163222376</v>
+        <v>0.2328192089723227</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2430722933679541</v>
+        <v>0.2375153649331088</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.1424504146230072</v>
+        <v>0.1467767794978176</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.1085957564766276</v>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>0.001458582066350411</v>
+        <v>0.1034988384706521</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>-0.003794826386692929</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.008864741206748628</v>
+        <v>0.01377357276179425</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3548,53 +3555,49 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>XLI</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2255064288206527</v>
+        <v>0.3309829348374158</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2328190617374617</v>
+        <v>0.1264398266463573</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2375152171373887</v>
+        <v>0.2315733266205304</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1467767794978176</v>
-      </c>
-      <c r="J55" s="3" t="n">
-        <v>0.1034988384706521</v>
+        <v>0.03751438366082249</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>-0.0331020809948398</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.003794826386692929</v>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>0.01377357276179425</v>
+        <v>-0.08536519726573</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>-0.01415559552126233</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3604,10 +3607,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>XLI</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D56" s="18" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -3615,29 +3622,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3309829348374158</v>
+        <v>0.4139242618534722</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1264398266463573</v>
+        <v>0.07758000351827699</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2315733266205304</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>0.03751438366082249</v>
+        <v>0.2293064876737918</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>-0.07164785362606163</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.0331020809948398</v>
+        <v>-0.07669714959884411</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.08536519726573</v>
+        <v>-0.1234244557210673</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.01415559552126233</v>
+        <v>-0.007168901798405569</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3656,53 +3663,49 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PPA</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D57" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>XLV</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4139243567961899</v>
+        <v>0.1905825730644324</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.07758000351827699</v>
+        <v>0.2215854200924652</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2293064876737918</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>-0.07164785362606163</v>
-      </c>
-      <c r="J57" s="5" t="n">
-        <v>-0.07669714959884411</v>
+        <v>0.2261731924600257</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0.1294644318507494</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0.09544130680349161</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.1234244557210673</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>-0.007168901798405569</v>
+        <v>-0.003741536999643635</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0.01445331398161587</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3712,40 +3715,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>ONEQ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1905825730644324</v>
+        <v>0.4998706979576504</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2215855558316593</v>
+        <v>0.1962852103691983</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2261733287090002</v>
+        <v>0.2235051004192332</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1294644318507494</v>
+        <v>0.1892096944791875</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.09544130680349161</v>
+        <v>0.01356590427565485</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.003741536999643635</v>
-      </c>
-      <c r="L58" s="3" t="n">
-        <v>0.01445331398161587</v>
+        <v>-0.02224746757549934</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>-0.004817883985353655</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3754,7 +3757,7 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3767,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ONEQ</t>
+          <t>VBK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3775,38 +3778,38 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.4985636843749994</v>
+        <v>0.3460365607009626</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1952427464949416</v>
+        <v>0.1309385002777921</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2235051004192332</v>
+        <v>0.2205730269304365</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.188173500712101</v>
-      </c>
-      <c r="J59" s="3" t="n">
-        <v>0.01268266520337735</v>
+        <v>0.1241770127769368</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>-0.03404518286254044</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.02309949824860358</v>
+        <v>-0.07343643081976203</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.005685103102717304</v>
+        <v>-0.006369426751592355</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3816,10 +3819,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VBK</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>XMMO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D60" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3827,29 +3834,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3460365607009626</v>
+        <v>0.3200175399494947</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1309386155816243</v>
+        <v>0.09204409374337241</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2205731513728775</v>
+        <v>0.2066883703417106</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1241771267061715</v>
+        <v>0.03625398414329606</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.03404518286254044</v>
+        <v>-0.1291549550793463</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.07343643081976203</v>
+        <v>-0.09500736015701661</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>-0.006369426751592355</v>
+        <v>-0.0303607807057894</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3868,14 +3875,10 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>XMMO</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>QUAL</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3883,38 +3886,38 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Quality Factor</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3200177201434939</v>
+        <v>0.3045726615563662</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.09204397041551893</v>
+        <v>0.1600796850210591</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2066882340667311</v>
+        <v>0.1971242463914793</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.03625398414329606</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>-0.1291549550793463</v>
+        <v>0.1325324524491687</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0.01674641890443174</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.09500736015701661</v>
+        <v>-0.03094462540716614</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.0303607807057894</v>
+        <v>-0.0002270663033605569</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3927,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>QUAL</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -3935,29 +3938,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Quality Factor</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3045727795172355</v>
+        <v>0.3862587363453316</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1600797782985897</v>
+        <v>0.1703508794541568</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1971243426476204</v>
+        <v>0.1965427731527949</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1325324524491687</v>
+        <v>0.1550841542877084</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.01674641890443174</v>
+        <v>0.02842797209854719</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.03094462540716614</v>
+        <v>-0.02188964263235205</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.0002270663033605569</v>
+        <v>-0.004640173081302601</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -3976,7 +3979,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VOO</t>
+          <t>IVV</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -3991,25 +3994,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3862585686175264</v>
+        <v>0.3865186175344131</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1703508794541568</v>
+        <v>0.1704656355859233</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1965427731527949</v>
+        <v>0.1964783646940815</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1550841542877084</v>
+        <v>0.1554027485834406</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.02842797209854719</v>
+        <v>0.0287104125529305</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.02188964263235205</v>
+        <v>-0.02174107771251621</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.004640173081302601</v>
+        <v>-0.004479633295134788</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -4023,45 +4026,45 @@
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
-      <c r="A64" t="n">
+      <c r="A64" s="15" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>IVV</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr"/>
       <c r="D64" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3865183105867593</v>
+        <v>0.3847697155463543</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1704655262076105</v>
+        <v>0.1698230571387764</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.1964782528849172</v>
+        <v>0.1959598881388804</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1554028551646778</v>
+        <v>0.1549676346517579</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.0287104125529305</v>
+        <v>0.02843302916016732</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>-0.02174107771251621</v>
+        <v>-0.02185427058158074</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>-0.004479633295134788</v>
+        <v>-0.004461657224351989</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4075,45 +4078,49 @@
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
-      <c r="A65" s="15" t="n">
+      <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="inlineStr"/>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.3844239235082487</v>
+        <v>0.3658221594036459</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1695310493636335</v>
+        <v>0.1407740870486252</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1959600003667503</v>
+        <v>0.1955191892594998</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.154679226689157</v>
+        <v>0.1917355838106696</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.02817621826286354</v>
+        <v>0.02339305949145731</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.02209852419396297</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>-0.004710253961192623</v>
+        <v>-0.04579190589553284</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.001469723691945868</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4122,7 +4129,7 @@
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4132,44 +4139,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D66" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3658221594036459</v>
+        <v>0.4564195298372515</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1407741599032766</v>
+        <v>0.1752517145775574</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1955192656104046</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>0.1917355043014051</v>
+        <v>0.1933459798628339</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>-0.1466412375503283</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.02339305949145731</v>
+        <v>0.01704760702108854</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.04579190589553284</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>0.001469723691945868</v>
+        <v>-0.01516263145023222</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>-0.01431893281116126</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4178,111 +4181,111 @@
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
+      <c r="A67" s="15" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr"/>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>Gold Bullion</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0.4531868457070987</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0.1734974309953399</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0.1917791850878241</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>-0.1475566357087058</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0.0162984425932633</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>-0.01533988369761385</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>-0.01487072748702256</v>
+      </c>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="21" customHeight="1">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RSP</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Equal Weight</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0.2890755065053814</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0.1484056102821769</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>0.1896394659697189</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>0.1201258778572365</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>0.01980953379932027</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>-0.03466080007183581</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>0.0006515567552471957</v>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
           <t>Established trend; positive 3m but negative 1m; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="21" customHeight="1">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>IAU</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Gold Bullion</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>0.4564195298372515</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>0.1752517145775574</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>0.1933459798628339</v>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>-0.1466412375503283</v>
-      </c>
-      <c r="J67" s="3" t="n">
-        <v>0.01704760702108854</v>
-      </c>
-      <c r="K67" s="5" t="n">
-        <v>-0.01516263145023222</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>-0.01431893281116126</v>
-      </c>
-      <c r="M67" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="N67" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="21" customHeight="1">
-      <c r="A68" s="15" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr"/>
-      <c r="D68" s="13" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="inlineStr">
-        <is>
-          <t>Gold Bullion</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>0.4531868457070987</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>0.1734974309953399</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>0.1917791850878241</v>
-      </c>
-      <c r="I68" s="5" t="n">
-        <v>-0.1475566357087058</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>0.0162984425932633</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>-0.01533988369761385</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>-0.01487072748702256</v>
-      </c>
-      <c r="M68" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="N68" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4292,10 +4295,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RSP</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>OEF</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -4303,29 +4310,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Equal Weight</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.2890755065053814</v>
+        <v>0.4118771712458007</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1484056102821769</v>
+        <v>0.1689214918418633</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1896394659697189</v>
+        <v>0.1844132968184888</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1201257888152116</v>
+        <v>0.1688084791648976</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.01980953379932027</v>
+        <v>0.04155157252844432</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.03466080007183581</v>
-      </c>
-      <c r="L69" s="3" t="n">
-        <v>0.0006515567552471957</v>
+        <v>-0.01307972902553423</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>-0.004127777047456371</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4334,7 +4341,7 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4344,53 +4351,49 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OEF</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D70" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>EWZ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>Brazil Equity</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.4118771712458007</v>
+        <v>0.640039410933225</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1689214918418633</v>
+        <v>0.3115939570219639</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1844132968184888</v>
+        <v>0.1742451730814349</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1688084791648976</v>
+        <v>0.07295278593470123</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.04155157252844432</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>-0.01307972902553423</v>
+        <v>0.08487437854606683</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>0.1169677228309149</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.004127777047456371</v>
+        <v>-0.01230688661953383</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4400,49 +4403,49 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EWZ</t>
+          <t>MGK</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Brazil Equity</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.6400395469420257</v>
+        <v>0.436565923577992</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.3115939570219639</v>
+        <v>0.1455794131329693</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1742451730814349</v>
+        <v>0.1651390214589759</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.07295278593470123</v>
+        <v>0.1841002816883057</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.08487437854606683</v>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>0.1169677228309149</v>
+        <v>0.03245088372155447</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>-0.01678736010533244</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.01230688661953383</v>
+        <v>-0.003225806451612967</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4452,40 +4455,44 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MGK</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XHE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.4365660114362195</v>
+        <v>0.1086753077720002</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1455794131329693</v>
+        <v>0.1123038705559964</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1651390214589759</v>
+        <v>0.1596281848561474</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1841002816883057</v>
+        <v>0.1518014613252709</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.03245088372155447</v>
+        <v>0.1166340986809968</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.01678736010533244</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>-0.003225806451612967</v>
+        <v>-0.04080990348300451</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0.01577602488612384</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4494,7 +4501,7 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4504,44 +4511,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>XHE</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>VWO</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.1079477509693498</v>
+        <v>0.3523277235157314</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1115739325462255</v>
+        <v>0.1416515275254409</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1596281848561474</v>
+        <v>0.1556324974146135</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1510456034265559</v>
+        <v>0.1047916481167397</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.1159013190034197</v>
+        <v>0.002197237262463014</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.04143936214855215</v>
-      </c>
-      <c r="L73" s="3" t="n">
-        <v>0.01510943228530159</v>
+        <v>-0.01209811070599942</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>-0.01226180613090311</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -4550,7 +4553,7 @@
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4560,40 +4563,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>SCHG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D74" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3523277235157314</v>
+        <v>0.3947428883705688</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1416514441173784</v>
+        <v>0.130183925965542</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1556324129851134</v>
+        <v>0.1523066751546547</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.1047916481167397</v>
+        <v>0.181198782323692</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.002197237262463014</v>
+        <v>0.0558448276385064</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.01209811070599942</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>-0.01226180613090311</v>
+        <v>-0.01919866444073448</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>0.002559726962457542</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -4602,7 +4605,7 @@
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4615,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SCHG</t>
+          <t>VUG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -4627,25 +4630,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3947429936295834</v>
+        <v>0.4056845500620376</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1301838568510387</v>
+        <v>0.1247189492480469</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1523066046872716</v>
+        <v>0.1506217229053388</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1811987068289131</v>
+        <v>0.1714335424871811</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.0558448276385064</v>
+        <v>0.0297557200534968</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.01919866444073448</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>0.002559726962457542</v>
+        <v>-0.02251198038560132</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>-0.003521926834810341</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4654,7 +4657,7 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4664,10 +4667,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VUG</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>SPGP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D76" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -4675,29 +4682,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.4056846360026141</v>
+        <v>0.2750959302992106</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1247189492480469</v>
+        <v>0.09261985744239154</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1506217229053388</v>
+        <v>0.1424735716607293</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1714335424871811</v>
+        <v>0.1480864453032833</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.0297557200534968</v>
+        <v>0.02748757619887421</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.02251198038560132</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>-0.003521926834810341</v>
+        <v>-0.04363664548132085</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0.006361634450697373</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4706,7 +4713,7 @@
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4716,53 +4723,49 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SPGP</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D77" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>IGF</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2750958297691828</v>
+        <v>0.2590203788529941</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.09261985744239154</v>
+        <v>0.07269316034794193</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1424735716607293</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0.1480864453032833</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>0.02748757619887421</v>
+        <v>0.1158445652838507</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>-0.03335162080024456</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>-0.04484226633664434</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.04363664548132085</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>0.006361634450697373</v>
+        <v>-0.03867151956323922</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>-0.01030444964871191</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4772,49 +4775,53 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IGF</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>IAK</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2590203788529941</v>
+        <v>0.1442127743192039</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.07269316034794193</v>
+        <v>0.1158108930931669</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1158445652838507</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>-0.03335162080024456</v>
-      </c>
-      <c r="J78" s="5" t="n">
-        <v>-0.04484226633664434</v>
-      </c>
-      <c r="K78" s="5" t="n">
-        <v>-0.03867151956323922</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>-0.01030444964871191</v>
+        <v>0.1143554209684401</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0.1327425245767495</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>0.07755812386586802</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0.001306111225682249</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>0.01138730731842785</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4824,53 +4831,49 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IAK</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D79" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>BOTZ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Robotics &amp; AI</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1442127743192039</v>
+        <v>0.1442234125195392</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1158108930931669</v>
+        <v>0.02097475936122262</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1143554209684401</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>0.1327425245767495</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>0.07755812386586802</v>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>0.001306111225682249</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>0.01138730731842785</v>
+        <v>0.1108534349551622</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>-0.001510652410924629</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>-0.06310927491579221</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>-0.08090957165520896</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>-0.0147392290249434</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4880,40 +4883,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>VONG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D80" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1442234125195392</v>
+        <v>0.3279269373194744</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.02097475936122262</v>
+        <v>0.06276587203645745</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.1108534349551622</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>-0.001510652410924629</v>
+        <v>0.101594590700717</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.109187431639697</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-0.06310927491579221</v>
+        <v>-0.001848943866336716</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.08090957165520896</v>
+        <v>-0.03524773904305478</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.0147392290249434</v>
+        <v>-0.008657664813343957</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4932,49 +4935,49 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VONG</t>
+          <t>VFH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.3279269373194744</v>
+        <v>0.2440962242062454</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.06276587203645745</v>
+        <v>0.0718518692096386</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.101594590700717</v>
+        <v>0.09839999864300264</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.1091873564340331</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>-0.001848943866336716</v>
+        <v>0.1794977952212815</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>0.07039952649449543</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.03524773904305478</v>
+        <v>-0.02416981925178663</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.008657664813343957</v>
+        <v>-0.002792096219931373</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4984,40 +4987,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IWF</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Russell 1000 Growth</t>
+          <t>U.S. Equity REITs</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.3259196842899255</v>
+        <v>0.1084751672361679</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.06148039976338548</v>
+        <v>0.05087142764483388</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.09999692424762507</v>
+        <v>0.09821801481212455</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1086391457006339</v>
+        <v>0.04360567740235521</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.001999932073707078</v>
+        <v>-0.03399225287864394</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.03501512016552599</v>
+        <v>-0.04311219314262527</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-0.008260407295329952</v>
+        <v>-0.004957805907172985</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5036,49 +5039,49 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VFH</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.2440963089832584</v>
+        <v>0.1018727704512268</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.07185199506442697</v>
+        <v>0.07657726537859633</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.09840012761502126</v>
+        <v>0.09672642528499509</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1794977952212815</v>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>0.07039952649449543</v>
+        <v>0.008782480165939743</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>-0.00948777852571292</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.02416981925178663</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>-0.002792096219931373</v>
+        <v>-0.01837209302325582</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>0.01247301511153753</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5088,49 +5091,53 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VNQ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+          <t>EDEN</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>U.S. Equity REITs</t>
+          <t>Denmark Equity</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1084752666146165</v>
+        <v>0.09987147714598676</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05087142764483388</v>
+        <v>0.08606867063811396</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.09821801481212455</v>
+        <v>0.0953569793668454</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.0436055893151055</v>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>-0.03399225287864394</v>
+        <v>0.1590411915485337</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0.05042670408354932</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.04311219314262527</v>
+        <v>-0.008479709267110724</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.004957805907172985</v>
+        <v>-0.005467800729040073</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5140,49 +5147,49 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1018726607257185</v>
+        <v>0.2232508183621185</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.07657726537859633</v>
+        <v>0.07190512776381475</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.09672642528499509</v>
+        <v>0.09502354451200845</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.008782572134595545</v>
-      </c>
-      <c r="J85" s="5" t="n">
-        <v>-0.00948777852571292</v>
+        <v>0.1765995958309858</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0.07292413779603168</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.01837209302325582</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>0.01247301511153753</v>
+        <v>-0.02111225540679706</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>-0.003842794759825297</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5199,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EDEN</t>
+          <t>EUO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5200,45 +5207,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D86" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>0.09987131606021826</v>
+          <t>2x Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>-0.04536862003780706</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.08606859210408024</v>
+        <v>0.08369098712446355</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.09535690016117071</v>
+        <v>0.0829756795422032</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.1590411915485337</v>
+        <v>0.001984126984126977</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.05042670408354932</v>
-      </c>
-      <c r="K86" s="5" t="n">
-        <v>-0.008479709267110724</v>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v>-0.005467800729040073</v>
+        <v>0.01711983887210478</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>0.0006605019815060231</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>0.00899100899100902</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N86" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5248,62 +5255,66 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XLF</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>VOT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Mid Growth</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.2232507182728078</v>
+        <v>0.2205055506285958</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.07190512776381475</v>
+        <v>0.003562654499147389</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.09502354451200845</v>
+        <v>0.07338910911521168</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.1765995958309858</v>
-      </c>
-      <c r="J87" s="3" t="n">
-        <v>0.07292413779603168</v>
+        <v>0.1170520616293511</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>-0.01252871682010859</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.02111225540679706</v>
+        <v>-0.0650523226135783</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>-0.003842794759825297</v>
+        <v>-0.006576494118444631</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
-      <c r="A88" t="n">
+      <c r="A88" s="15" t="n">
         <v>87</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>EUO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
@@ -5313,31 +5324,31 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2x Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>-0.04631379962192816</v>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>US Dollar Index Bullish</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.02867498034109706</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.08261802575107291</v>
+        <v>0.06515814863787495</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.0829756795422032</v>
+        <v>0.06553626654651445</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.0009920634920634885</v>
+        <v>0.01003944065973461</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.01611278952668682</v>
+        <v>0.007871198568873083</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.0003302509907530116</v>
+        <v>-0.0003548616039743546</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.007992007992007943</v>
+        <v>0.003562522265764256</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5356,321 +5367,321 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VOT</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.1296163665731609</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.01048937492380064</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.06413084819809134</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>-0.09750242472458248</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.05486093404897052</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>-0.05040871934604907</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>-0.01344656758669494</v>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>USDU</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D89" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Mid Growth</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>0.2205055506285958</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>0.003562759380278724</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>0.07338922129382208</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>0.1170520616293511</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>-0.01252871682010859</v>
-      </c>
-      <c r="K89" s="5" t="n">
-        <v>-0.0650523226135783</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>-0.006576494118444631</v>
-      </c>
-      <c r="M89" s="6" t="inlineStr">
+      <c r="D90" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Bloomberg Dollar Bullish</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.01576305319130755</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.04402163446054064</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.04718773494412076</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0.003041825095057016</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0.002660585328772447</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>-0.003023431594860182</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0.003805175038051667</v>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="21" customHeight="1">
+      <c r="A91" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="16" t="inlineStr">
+        <is>
+          <t>HYG</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr"/>
+      <c r="D91" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>High Yield Corporate Bonds</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0.08635577007710027</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0.028010050934002</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0.03881128116780008</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0.02184330010943447</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>-0.002858152010351778</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>-0.01039768284154152</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>-0.0008905852417302462</v>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
         <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N89" s="7" t="inlineStr">
+      <c r="N91" s="7" t="inlineStr">
         <is>
           <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="21" customHeight="1">
-      <c r="A90" s="15" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="16" t="inlineStr">
-        <is>
-          <t>UUP</t>
-        </is>
-      </c>
-      <c r="C90" s="15" t="inlineStr">
+    <row r="92" ht="21" customHeight="1">
+      <c r="A92" s="15" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr"/>
+      <c r="D92" s="22" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>1-3 Year Treasury</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.04299861406424332</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.01655604030515789</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0.02212469134920636</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>0.003094401785922241</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>1.786292805849854e-05</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>-0.005448113220607009</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>-0.000368686248003014</v>
+      </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N92" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="21" customHeight="1">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>XRT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D90" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E90" s="15" t="inlineStr">
-        <is>
-          <t>US Dollar Index Bullish</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>0.02867498034109706</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0.06515814863787495</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>0.06553626654651445</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>0.01003944065973461</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>0.007871198568873083</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>-0.0003548616039743546</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>0.003562522265764256</v>
-      </c>
-      <c r="M90" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="N90" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="21" customHeight="1">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>XLU</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>0.1296163665731609</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>0.01048937492380064</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>0.06413084819809134</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>-0.09750235042811217</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>-0.05486093404897052</v>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>-0.05040871934604907</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>-0.01344656758669494</v>
-      </c>
-      <c r="M91" s="6" t="inlineStr">
+      <c r="D93" s="23" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0.2718582638270688</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>-0.02215149204553757</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>0.02095525345245508</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>0.07393364920684364</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>-0.02308756907211573</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>-0.04222197334527955</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>0.008609505837952502</v>
+      </c>
+      <c r="M93" s="6" t="inlineStr">
         <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N91" s="7" t="inlineStr">
+      <c r="N93" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="21" customHeight="1">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>VCR</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D94" s="23" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.1737844592852351</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.03220466966297864</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0.0171315148715725</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0.04636279863765269</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>-0.03230796296032079</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>-0.04850521669341901</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>-0.00218300412929695</v>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N94" s="7" t="inlineStr">
         <is>
           <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="21" customHeight="1">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>USDU</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D92" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Bloomberg Dollar Bullish</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>0.01576305319130755</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>0.04402163446054064</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>0.04718773494412076</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>0.003041825095057016</v>
-      </c>
-      <c r="J92" s="3" t="n">
-        <v>0.002660585328772447</v>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>-0.003023431594860182</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>0.003805175038051667</v>
-      </c>
-      <c r="M92" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="N92" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="21" customHeight="1">
-      <c r="A93" s="15" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="16" t="inlineStr">
-        <is>
-          <t>HYG</t>
-        </is>
-      </c>
-      <c r="C93" s="15" t="inlineStr"/>
-      <c r="D93" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
-        </is>
-      </c>
-      <c r="E93" s="15" t="inlineStr">
-        <is>
-          <t>High Yield Corporate Bonds</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>0.08635577007710027</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>0.02800994826268099</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>0.03881117741771867</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>0.02184330010943447</v>
-      </c>
-      <c r="J93" s="5" t="n">
-        <v>-0.002858152010351778</v>
-      </c>
-      <c r="K93" s="5" t="n">
-        <v>-0.01039768284154152</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>-0.0008905852417302462</v>
-      </c>
-      <c r="M93" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N93" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="21" customHeight="1">
-      <c r="A94" s="15" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="16" t="inlineStr">
-        <is>
-          <t>SHY</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr"/>
-      <c r="D94" s="22" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="inlineStr">
-        <is>
-          <t>1-3 Year Treasury</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>0.04299851202826432</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>0.01655604030515789</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>0.02212469134920636</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>0.003094401785922241</v>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>1.786292805849854e-05</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>-0.005448113220607009</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>-0.000368686248003014</v>
-      </c>
-      <c r="M94" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="N94" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5680,100 +5691,96 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>XRT</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Russell Midcap Growth</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0.1691654384140304</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.05373650537113406</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0.01631614729395103</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0.05827474079383732</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>-0.02608112677086938</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>-0.06892801305145824</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>-0.007463768115942071</v>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="21" customHeight="1">
+      <c r="A96" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D95" s="23" t="inlineStr">
-        <is>
-          <t>Consumer</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>0.2721557049551857</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>-0.02192289436872819</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>0.0209551643887802</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0.07418470009190714</v>
-      </c>
-      <c r="J95" s="5" t="n">
-        <v>-0.02285910498630461</v>
-      </c>
-      <c r="K95" s="5" t="n">
-        <v>-0.04199798409676336</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>0.00884538271022528</v>
-      </c>
-      <c r="M95" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N95" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="21" customHeight="1">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>VCR</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D96" s="23" t="inlineStr">
-        <is>
-          <t>Consumer</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
+      <c r="D96" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>TIPS</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.1737843484565225</v>
+        <v>0.03424154810875368</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.03220466966297864</v>
+        <v>-0.01044374858362174</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.0171315148715725</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0.04636279863765269</v>
+        <v>0.002087014758827221</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>-0.01148231514750964</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-0.03230796296032079</v>
+        <v>-0.01799895107901017</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.04850521669341901</v>
+        <v>-0.01250466592011945</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.00218300412929695</v>
+        <v>-0.0001889644746788655</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5792,105 +5799,101 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IWP</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D97" s="22" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Russell Midcap Growth</t>
+          <t>7-10 Year Treasury</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.1691653622733889</v>
+        <v>0.020706812271716</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.05373650537113406</v>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>0.01631614729395103</v>
-      </c>
-      <c r="I97" s="3" t="n">
-        <v>0.05827474079383732</v>
+        <v>-0.02807300640362997</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>-0.006310812295014956</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>-0.0292620039592334</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.02608112677086938</v>
+        <v>-0.02450527631829724</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.06892801305145824</v>
+        <v>-0.02190040344393485</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>-0.007463768115942071</v>
+        <v>-0.0008790242830457595</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N97" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1">
-      <c r="A98" s="15" t="n">
+      <c r="A98" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="16" t="inlineStr">
-        <is>
-          <t>TIP</t>
-        </is>
-      </c>
-      <c r="C98" s="15" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D98" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="inlineStr">
-        <is>
-          <t>TIPS</t>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>LQD</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Investment Grade Corporate Bonds</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03424147098888897</v>
+        <v>0.03762838960808113</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.01044374858362174</v>
-      </c>
-      <c r="H98" s="3" t="n">
-        <v>0.002087014758827221</v>
+        <v>-0.02687762251742032</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>-0.0100408261382825</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.01148231514750964</v>
+        <v>-0.01253961662466418</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.01799888155316975</v>
+        <v>-0.03163937157174768</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.01250466592011945</v>
+        <v>-0.01700756639635903</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>-0.0001889644746788655</v>
+        <v>-0.000191717791411028</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5900,101 +5903,101 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>FXE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="22" t="inlineStr">
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Euro Currency</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>0.07263239288871293</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>-0.008532095769512416</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>-0.01069410114046232</v>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>0.01508148681653965</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>-0.0004063416003677878</v>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>0.002185376002955541</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>-0.004298663676292058</v>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>REBOUND</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>Weak long trend; 1m rebound not yet confirmed by 3m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="21" customHeight="1">
+      <c r="A100" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="16" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr"/>
+      <c r="D100" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>7-10 Year Treasury</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>0.02070655002741972</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>-0.02807284788503006</v>
-      </c>
-      <c r="H99" s="5" t="n">
-        <v>-0.006310650227061343</v>
-      </c>
-      <c r="I99" s="5" t="n">
-        <v>-0.02926208302471511</v>
-      </c>
-      <c r="J99" s="5" t="n">
-        <v>-0.02450527631829724</v>
-      </c>
-      <c r="K99" s="5" t="n">
-        <v>-0.02190040344393485</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>-0.0008790242830457595</v>
-      </c>
-      <c r="M99" s="6" t="inlineStr">
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>20+ Year Treasury</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>-0.0368641949997347</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>-0.06311830695917853</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>-0.04755110811657592</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>-0.04294248111099697</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>-0.04548640783442792</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>-0.01634439283331957</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>0.0007419314949919098</v>
+      </c>
+      <c r="M100" s="6" t="inlineStr">
         <is>
           <t>BROAD_WEAKNESS</t>
         </is>
       </c>
-      <c r="N99" s="7" t="inlineStr">
-        <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="21" customHeight="1">
-      <c r="A100" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>LQD</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Investment Grade Corporate Bonds</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>0.03762846836513711</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>-0.02687755324813323</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>-0.01004075567050999</v>
-      </c>
-      <c r="I100" s="5" t="n">
-        <v>-0.01253961662466418</v>
-      </c>
-      <c r="J100" s="5" t="n">
-        <v>-0.03163937157174768</v>
-      </c>
-      <c r="K100" s="5" t="n">
-        <v>-0.01700756639635903</v>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v>-0.000191717791411028</v>
-      </c>
-      <c r="M100" s="6" t="inlineStr">
-        <is>
-          <t>BROAD_WEAKNESS</t>
-        </is>
-      </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6004,92 +6007,100 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FXE</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
+          <t>INDA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Euro Currency</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>0.07263231050556374</v>
+          <t>India Equity</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>-0.006156371844859398</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.008532306931187117</v>
+        <v>-0.0903456048084148</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01069431184167569</v>
+        <v>-0.06123215627347867</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.01508156059650867</v>
-      </c>
-      <c r="J101" s="5" t="n">
-        <v>-0.0004063416003677878</v>
-      </c>
-      <c r="K101" s="3" t="n">
-        <v>0.002185376002955541</v>
+        <v>0.007698709945900939</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>0.002069108214359572</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>-0.03101240496198476</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>-0.004298663676292058</v>
+        <v>-0.002882437718756403</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>REBOUND</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N101" s="7" t="inlineStr">
         <is>
-          <t>Weak long trend; 1m rebound not yet confirmed by 3m; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
-      <c r="A102" s="15" t="n">
+      <c r="A102" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="16" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="C102" s="15" t="inlineStr"/>
-      <c r="D102" s="22" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="inlineStr">
-        <is>
-          <t>20+ Year Treasury</t>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>IPAY</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Digital Payments</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03686445734710986</v>
+        <v>-0.04395507960823308</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.06311830695917853</v>
+        <v>-0.1484796154799024</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.04755110811657592</v>
-      </c>
-      <c r="I102" s="5" t="n">
-        <v>-0.04294256745984903</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>-0.0454864937248517</v>
+        <v>-0.1103924417313996</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>0.1547152409499655</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>0.1439013248058474</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>-0.01634439283331957</v>
+        <v>-0.04281345565749239</v>
       </c>
       <c r="L102" s="3" t="n">
-        <v>0.0007419314949919098</v>
+        <v>0.01314990896216872</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6108,53 +6119,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>INDA</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>IWF</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>India Equity</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>-0.005540734660373414</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>-0.08978211870773856</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>-0.06123215627347867</v>
-      </c>
-      <c r="I103" s="3" t="n">
-        <v>0.00832292967124415</v>
-      </c>
-      <c r="J103" s="3" t="n">
-        <v>0.00268984067866751</v>
-      </c>
-      <c r="K103" s="5" t="n">
-        <v>-0.03041216486594633</v>
-      </c>
-      <c r="L103" s="5" t="n">
-        <v>-0.002264772493308587</v>
-      </c>
+          <t>Russell 1000 Growth</t>
+        </is>
+      </c>
+      <c r="F103" s="24" t="n"/>
+      <c r="G103" s="24" t="n"/>
+      <c r="H103" s="24" t="n"/>
+      <c r="I103" s="24" t="n"/>
+      <c r="J103" s="24" t="n"/>
+      <c r="K103" s="24" t="n"/>
+      <c r="L103" s="24" t="n"/>
       <c r="M103" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>INSUFFICIENT_DATA</t>
         </is>
       </c>
       <c r="N103" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Insufficient history for transition assessment.</t>
         </is>
       </c>
     </row>
@@ -6164,53 +6157,35 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IPAY</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>PAVE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Digital Payments</t>
-        </is>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>-0.04395507960823308</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>-0.1484796154799024</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>-0.1103924417313996</v>
-      </c>
-      <c r="I104" s="3" t="n">
-        <v>0.1547152409499655</v>
-      </c>
-      <c r="J104" s="3" t="n">
-        <v>0.1439013248058474</v>
-      </c>
-      <c r="K104" s="5" t="n">
-        <v>-0.04281345565749239</v>
-      </c>
-      <c r="L104" s="3" t="n">
-        <v>0.01314990896216872</v>
-      </c>
+          <t>U.S. Infrastructure Development</t>
+        </is>
+      </c>
+      <c r="F104" s="24" t="n"/>
+      <c r="G104" s="24" t="n"/>
+      <c r="H104" s="24" t="n"/>
+      <c r="I104" s="24" t="n"/>
+      <c r="J104" s="24" t="n"/>
+      <c r="K104" s="24" t="n"/>
+      <c r="L104" s="24" t="n"/>
       <c r="M104" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>INSUFFICIENT_DATA</t>
         </is>
       </c>
       <c r="N104" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Insufficient history for transition assessment.</t>
         </is>
       </c>
     </row>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -210,9 +210,6 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -802,13 +799,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.552912281805216</v>
+        <v>1.552911895513185</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9190527156866941</v>
+        <v>0.9190524974047569</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.260313721451676</v>
+        <v>1.260313464353132</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.3980846779619589</v>
@@ -910,7 +907,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.557404949099305</v>
+        <v>1.557405149737365</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0.9582311496268574</v>
@@ -966,7 +963,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.501911438188204</v>
+        <v>1.50191116582222</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.8645744069359325</v>
@@ -1242,7 +1239,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8169117524746563</v>
+        <v>0.8169115926655646</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.6543502300835615</v>
@@ -1797,10 +1794,10 @@
         <v>0.5584597790914039</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.4893794977541974</v>
+        <v>0.4893795909629621</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.4133396897232375</v>
+        <v>0.4133397781732577</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0.1293830140141483</v>
@@ -1846,13 +1843,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5403329482921677</v>
+        <v>0.5403328080341847</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4929487689592091</v>
+        <v>0.4929486371830269</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.4126677798334002</v>
+        <v>0.4126676551432764</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>0.1337961603339384</v>
@@ -1905,10 +1902,10 @@
         <v>0.6091119408822019</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.5069286511111746</v>
+        <v>0.5069288302096486</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.395546629552846</v>
+        <v>0.3955467954135667</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>0.1626638014574995</v>
@@ -1961,10 +1958,10 @@
         <v>0.5292606093176024</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4264304483268988</v>
+        <v>0.4264306000723488</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.3869700556703481</v>
+        <v>0.3869702032179523</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>0.2372559779415742</v>
@@ -2122,7 +2119,7 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.7297776959465778</v>
+        <v>0.7297775354336784</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.335638296015172</v>
@@ -2174,7 +2171,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.724787525252333</v>
+        <v>0.7247877157150517</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.3321650917660555</v>
@@ -2282,7 +2279,7 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.7396625787269775</v>
+        <v>0.7396627626361758</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0.3379591908990263</v>
@@ -2338,7 +2335,7 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5132050501615186</v>
+        <v>0.5132049193610779</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>0.2720093496470317</v>
@@ -2394,7 +2391,7 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.9888419372604327</v>
+        <v>0.988842074221548</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0.2851314681437027</v>
@@ -2617,10 +2614,10 @@
         <v>0.5537624775009724</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.3014992656616815</v>
+        <v>0.3014991516179761</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.307935429216279</v>
+        <v>0.3079353146086059</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0.2876186132865106</v>
@@ -2774,7 +2771,7 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.5705518804807144</v>
+        <v>0.5705517499660058</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0.2103740128121498</v>
@@ -2878,7 +2875,7 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4538005544976944</v>
+        <v>0.4538004424835325</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>0.2080579581350546</v>
@@ -2930,7 +2927,7 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.3507154904889866</v>
+        <v>0.3507156405462939</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0.2288634080341048</v>
@@ -2982,16 +2979,16 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4301422618815076</v>
+        <v>0.4301423823234247</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2587404063717371</v>
+        <v>0.2587405929759927</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2688445281888612</v>
+        <v>0.2688447162910208</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.1717527403233639</v>
+        <v>0.1717528211754278</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0.03878090233134723</v>
@@ -3086,13 +3083,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4990910194974332</v>
+        <v>0.499090902071659</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2205372859054853</v>
+        <v>0.2205372080642829</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2597840673404985</v>
+        <v>0.2597839869962866</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>0.1976217857471156</v>
@@ -3138,7 +3135,7 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.4478716344854876</v>
+        <v>0.4478714114829319</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0.228463951828185</v>
@@ -3190,13 +3187,13 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.498070483123376</v>
+        <v>0.498070289976358</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2200308598583485</v>
+        <v>0.2200307317536216</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2594094469337846</v>
+        <v>0.259409314694258</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.1972892162149393</v>
@@ -3298,7 +3295,7 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4628068505692728</v>
+        <v>0.462806699945052</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>0.08898197691329468</v>
@@ -3410,7 +3407,7 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4217451629248197</v>
+        <v>0.4217453316529409</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>0.1636783793404464</v>
@@ -3419,7 +3416,7 @@
         <v>0.2499357209162836</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.1616983477196399</v>
+        <v>0.1616984603695042</v>
       </c>
       <c r="J52" s="5" t="n">
         <v>-0.03773774671265639</v>
@@ -3447,49 +3444,49 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COWZ</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Large Cap Cash Flow</t>
+          <t>U.S. Infrastructure Development</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.3406461047205951</v>
+        <v>0.4129445737172972</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2448854163222376</v>
+        <v>0.1343046896068651</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2430722933679541</v>
+        <v>0.2474784317422918</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1424504146230072</v>
-      </c>
-      <c r="J53" s="3" t="n">
-        <v>0.1085957564766276</v>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>0.001458582066350411</v>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>0.008864741206748628</v>
+        <v>0.05866010859173088</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>-0.08045399108285478</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>-0.090722003086949</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>-0.01960059171597628</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3499,53 +3496,49 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D54" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>COWZ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Large Cap Cash Flow</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.2255061378340366</v>
+        <v>0.3406460075511395</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2328192089723227</v>
+        <v>0.2448854163222376</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2375153649331088</v>
+        <v>0.2430722933679541</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.1467767794978176</v>
+        <v>0.1424504146230072</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.1034988384706521</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>-0.003794826386692929</v>
+        <v>0.1085957564766276</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0.001458582066350411</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.01377357276179425</v>
+        <v>0.008864741206748628</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3555,49 +3548,53 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>XLI</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>VHT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3309829348374158</v>
+        <v>0.2255064288206527</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1264398266463573</v>
+        <v>0.2328192089723227</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2315733266205304</v>
+        <v>0.2375153649331088</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.03751438366082249</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>-0.0331020809948398</v>
+        <v>0.1467767794978176</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0.1034988384706521</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.08536519726573</v>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v>-0.01415559552126233</v>
+        <v>-0.003794826386692929</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0.01377357276179425</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3607,14 +3604,10 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PPA</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>XLI</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" s="18" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -3622,29 +3615,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.4139242618534722</v>
+        <v>0.3309827757649795</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.07758000351827699</v>
+        <v>0.1264398266463573</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2293064876737918</v>
-      </c>
-      <c r="I56" s="5" t="n">
-        <v>-0.07164785362606163</v>
+        <v>0.2315733266205304</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>0.03751438366082249</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.07669714959884411</v>
+        <v>-0.0331020809948398</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.1234244557210673</v>
+        <v>-0.08536519726573</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.007168901798405569</v>
+        <v>-0.01415559552126233</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3663,49 +3656,53 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>XLV</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.1905825730644324</v>
+        <v>0.4139242618534722</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2215854200924652</v>
+        <v>0.07758000351827699</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2261731924600257</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>0.1294644318507494</v>
-      </c>
-      <c r="J57" s="3" t="n">
-        <v>0.09544130680349161</v>
+        <v>0.2293064876737918</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>-0.07164785362606163</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-0.07669714959884411</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.003741536999643635</v>
-      </c>
-      <c r="L57" s="3" t="n">
-        <v>0.01445331398161587</v>
+        <v>-0.1234244557210673</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>-0.007168901798405569</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3715,40 +3712,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ONEQ</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.4998706979576504</v>
+        <v>0.1905825730644324</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.1962852103691983</v>
+        <v>0.2215855558316593</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2235051004192332</v>
+        <v>0.2261733287090002</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1892096944791875</v>
+        <v>0.1294644318507494</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.01356590427565485</v>
+        <v>0.09544130680349161</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.02224746757549934</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>-0.004817883985353655</v>
+        <v>-0.003741536999643635</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>0.01445331398161587</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3757,7 +3754,7 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3764,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VBK</t>
+          <t>ONEQ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3778,38 +3775,38 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3460365607009626</v>
+        <v>0.4998708641387162</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1309385002777921</v>
+        <v>0.1962851046525729</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2205730269304365</v>
+        <v>0.2235049922971657</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1241770127769368</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>-0.03404518286254044</v>
+        <v>0.1892097989489854</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0.01356590427565485</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.07343643081976203</v>
+        <v>-0.02224746757549934</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.006369426751592355</v>
+        <v>-0.004817883985353655</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3819,14 +3816,10 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>XMMO</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>VBK</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3834,29 +3827,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3200175399494947</v>
+        <v>0.3460365607009626</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.09204409374337241</v>
+        <v>0.1309386155816243</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2066883703417106</v>
+        <v>0.2205731513728775</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.03625398414329606</v>
+        <v>0.1241770127769368</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.1291549550793463</v>
+        <v>-0.03404518286254044</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.09500736015701661</v>
+        <v>-0.07343643081976203</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>-0.0303607807057894</v>
+        <v>-0.006369426751592355</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3875,10 +3868,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>QUAL</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>XMMO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3886,38 +3883,38 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quality Factor</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3045726615563662</v>
+        <v>0.3200176300464881</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1600796850210591</v>
+        <v>0.0920438470876932</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.1971242463914793</v>
+        <v>0.2066880977917822</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1325324524491687</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>0.01674641890443174</v>
+        <v>0.03625398414329606</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>-0.1291549550793463</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.03094462540716614</v>
+        <v>-0.09500736015701661</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.0002270663033605569</v>
+        <v>-0.0303607807057894</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3924,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VOO</t>
+          <t>QUAL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -3938,29 +3935,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Quality Factor</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3862587363453316</v>
+        <v>0.3045726615563662</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1703508794541568</v>
+        <v>0.1600797782985897</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1965427731527949</v>
+        <v>0.1971243426476204</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1550841542877084</v>
+        <v>0.1325324524491687</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.02842797209854719</v>
+        <v>0.01674641890443174</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.02188964263235205</v>
+        <v>-0.03094462540716614</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.004640173081302601</v>
+        <v>-0.0002270663033605569</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -3979,7 +3976,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IVV</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -3994,142 +3991,138 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3865186175344131</v>
+        <v>0.3862585686175264</v>
       </c>
       <c r="G63" s="3" t="n">
+        <v>0.1703508794541568</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0.1965427731527949</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0.1550841542877084</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0.02842797209854719</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>-0.02188964263235205</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>-0.004640173081302601</v>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="21" customHeight="1">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>IVV</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.3865184640605692</v>
+      </c>
+      <c r="G64" s="3" t="n">
         <v>0.1704656355859233</v>
       </c>
-      <c r="H63" s="3" t="n">
+      <c r="H64" s="3" t="n">
         <v>0.1964783646940815</v>
       </c>
-      <c r="I63" s="3" t="n">
-        <v>0.1554027485834406</v>
-      </c>
-      <c r="J63" s="3" t="n">
+      <c r="I64" s="3" t="n">
+        <v>0.1554028551646778</v>
+      </c>
+      <c r="J64" s="3" t="n">
         <v>0.0287104125529305</v>
       </c>
-      <c r="K63" s="5" t="n">
+      <c r="K64" s="5" t="n">
         <v>-0.02174107771251621</v>
       </c>
-      <c r="L63" s="5" t="n">
+      <c r="L64" s="5" t="n">
         <v>-0.004479633295134788</v>
       </c>
-      <c r="M63" s="6" t="inlineStr">
+      <c r="M64" s="6" t="inlineStr">
         <is>
           <t>CORRECTION</t>
         </is>
       </c>
-      <c r="N63" s="7" t="inlineStr">
+      <c r="N64" s="7" t="inlineStr">
         <is>
           <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="21" customHeight="1">
-      <c r="A64" s="15" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
+    <row r="65" ht="21" customHeight="1">
+      <c r="A65" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="C64" s="15" t="inlineStr"/>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="C65" s="15" t="inlineStr"/>
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr">
+      <c r="E65" s="15" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
-      <c r="F64" s="3" t="n">
+      <c r="F65" s="3" t="n">
         <v>0.3847697155463543</v>
       </c>
-      <c r="G64" s="3" t="n">
+      <c r="G65" s="3" t="n">
         <v>0.1698230571387764</v>
       </c>
-      <c r="H64" s="3" t="n">
+      <c r="H65" s="3" t="n">
         <v>0.1959598881388804</v>
       </c>
-      <c r="I64" s="3" t="n">
+      <c r="I65" s="3" t="n">
         <v>0.1549676346517579</v>
       </c>
-      <c r="J64" s="3" t="n">
+      <c r="J65" s="3" t="n">
         <v>0.02843302916016732</v>
       </c>
-      <c r="K64" s="5" t="n">
+      <c r="K65" s="5" t="n">
         <v>-0.02185427058158074</v>
       </c>
-      <c r="L64" s="5" t="n">
+      <c r="L65" s="5" t="n">
         <v>-0.004461657224351989</v>
       </c>
-      <c r="M64" s="6" t="inlineStr">
+      <c r="M65" s="6" t="inlineStr">
         <is>
           <t>CORRECTION</t>
         </is>
       </c>
-      <c r="N64" s="7" t="inlineStr">
+      <c r="N65" s="7" t="inlineStr">
         <is>
           <t>Established trend; positive 3m but negative 1m; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="21" customHeight="1">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D65" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0.3658221594036459</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>0.1407740870486252</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>0.1955191892594998</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>0.1917355838106696</v>
-      </c>
-      <c r="J65" s="3" t="n">
-        <v>0.02339305949145731</v>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>-0.04579190589553284</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0.001469723691945868</v>
-      </c>
-      <c r="M65" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4139,153 +4132,157 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0.3658220549686115</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0.1407740870486252</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0.1955191892594998</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>0.1917355043014051</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0.02339305949145731</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>-0.04579190589553284</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0.001469723691945868</v>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>IAU</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Gold Bullion</t>
         </is>
       </c>
-      <c r="F66" s="3" t="n">
+      <c r="F67" s="3" t="n">
         <v>0.4564195298372515</v>
       </c>
-      <c r="G66" s="3" t="n">
+      <c r="G67" s="3" t="n">
         <v>0.1752517145775574</v>
       </c>
-      <c r="H66" s="3" t="n">
+      <c r="H67" s="3" t="n">
         <v>0.1933459798628339</v>
       </c>
-      <c r="I66" s="5" t="n">
+      <c r="I67" s="5" t="n">
         <v>-0.1466412375503283</v>
       </c>
-      <c r="J66" s="3" t="n">
+      <c r="J67" s="3" t="n">
         <v>0.01704760702108854</v>
       </c>
-      <c r="K66" s="5" t="n">
+      <c r="K67" s="5" t="n">
         <v>-0.01516263145023222</v>
       </c>
-      <c r="L66" s="5" t="n">
+      <c r="L67" s="5" t="n">
         <v>-0.01431893281116126</v>
       </c>
-      <c r="M66" s="6" t="inlineStr">
+      <c r="M67" s="6" t="inlineStr">
         <is>
           <t>CORRECTION</t>
         </is>
       </c>
-      <c r="N66" s="7" t="inlineStr">
+      <c r="N67" s="7" t="inlineStr">
         <is>
           <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="21" customHeight="1">
-      <c r="A67" s="15" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
+    <row r="68" ht="21" customHeight="1">
+      <c r="A68" s="15" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="C67" s="15" t="inlineStr"/>
-      <c r="D67" s="13" t="inlineStr">
+      <c r="C68" s="15" t="inlineStr"/>
+      <c r="D68" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E67" s="15" t="inlineStr">
+      <c r="E68" s="15" t="inlineStr">
         <is>
           <t>Gold Bullion</t>
         </is>
       </c>
-      <c r="F67" s="3" t="n">
+      <c r="F68" s="3" t="n">
         <v>0.4531868457070987</v>
       </c>
-      <c r="G67" s="3" t="n">
+      <c r="G68" s="3" t="n">
         <v>0.1734974309953399</v>
       </c>
-      <c r="H67" s="3" t="n">
+      <c r="H68" s="3" t="n">
         <v>0.1917791850878241</v>
       </c>
-      <c r="I67" s="5" t="n">
+      <c r="I68" s="5" t="n">
         <v>-0.1475566357087058</v>
       </c>
-      <c r="J67" s="3" t="n">
+      <c r="J68" s="3" t="n">
         <v>0.0162984425932633</v>
       </c>
-      <c r="K67" s="5" t="n">
+      <c r="K68" s="5" t="n">
         <v>-0.01533988369761385</v>
       </c>
-      <c r="L67" s="5" t="n">
+      <c r="L68" s="5" t="n">
         <v>-0.01487072748702256</v>
       </c>
-      <c r="M67" s="6" t="inlineStr">
+      <c r="M68" s="6" t="inlineStr">
         <is>
           <t>CORRECTION</t>
         </is>
       </c>
-      <c r="N67" s="7" t="inlineStr">
+      <c r="N68" s="7" t="inlineStr">
         <is>
           <t>Established trend; positive 3m but negative 1m; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="21" customHeight="1">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>RSP</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Equal Weight</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>0.2890755065053814</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>0.1484056102821769</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>0.1896394659697189</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>0.1201258778572365</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>0.01980953379932027</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>-0.03466080007183581</v>
-      </c>
-      <c r="L68" s="3" t="n">
-        <v>0.0006515567552471957</v>
-      </c>
-      <c r="M68" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="N68" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4295,14 +4292,10 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OEF</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>RSP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -4310,29 +4303,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.4118771712458007</v>
+        <v>0.2890753885770738</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1689214918418633</v>
+        <v>0.1484056102821769</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1844132968184888</v>
+        <v>0.1896394659697189</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1688084791648976</v>
+        <v>0.1201258778572365</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.04155157252844432</v>
+        <v>0.01980953379932027</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.01307972902553423</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>-0.004127777047456371</v>
+        <v>-0.03466080007183581</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>0.0006515567552471957</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4341,7 +4334,7 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4351,49 +4344,53 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EWZ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>OEF</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Brazil Equity</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.640039410933225</v>
+        <v>0.4118771712458007</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.3115939570219639</v>
+        <v>0.1689214918418633</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1742451730814349</v>
+        <v>0.1844132968184888</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.07295278593470123</v>
+        <v>0.1688084791648976</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.08487437854606683</v>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>0.1169677228309149</v>
+        <v>0.04155157252844432</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>-0.01307972902553423</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.01230688661953383</v>
+        <v>-0.004127777047456371</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4403,49 +4400,49 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MGK</t>
+          <t>EWZ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>Brazil Equity</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.436565923577992</v>
+        <v>0.640039410933225</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1455794131329693</v>
+        <v>0.3115938700343948</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1651390214589759</v>
+        <v>0.1742450952031154</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.1841002816883057</v>
+        <v>0.07295278593470123</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.03245088372155447</v>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>-0.01678736010533244</v>
+        <v>0.08487437854606683</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0.1169677228309149</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.003225806451612967</v>
+        <v>-0.01230688661953383</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4455,44 +4452,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>XHE</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>MGK</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.1086753077720002</v>
+        <v>0.4365660114362195</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1123038705559964</v>
+        <v>0.1455793013993303</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1596281848561474</v>
+        <v>0.165138907817598</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1518014613252709</v>
+        <v>0.1841002816883057</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.1166340986809968</v>
+        <v>0.03245088372155447</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.04080990348300451</v>
-      </c>
-      <c r="L72" s="3" t="n">
-        <v>0.01577602488612384</v>
+        <v>-0.01678736010533244</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>-0.003225806451612967</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4501,7 +4494,7 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4511,40 +4504,44 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VWO</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XHE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.3523277235157314</v>
+        <v>0.1086753077720002</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1416515275254409</v>
+        <v>0.1123038705559964</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1556324974146135</v>
+        <v>0.1596281848561474</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1047916481167397</v>
+        <v>0.1518014613252709</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.002197237262463014</v>
+        <v>0.1166340986809968</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.01209811070599942</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>-0.01226180613090311</v>
+        <v>-0.04080990348300451</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0.01577602488612384</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -4553,7 +4550,7 @@
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4563,40 +4560,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SCHG</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3947428883705688</v>
+        <v>0.3523277235157314</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.130183925965542</v>
+        <v>0.1416514441173784</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1523066751546547</v>
+        <v>0.1556324129851134</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.181198782323692</v>
+        <v>0.1047916481167397</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.0558448276385064</v>
+        <v>0.002197237262463014</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.01919866444073448</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>0.002559726962457542</v>
+        <v>-0.01209811070599942</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>-0.01226180613090311</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -4605,7 +4602,7 @@
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4612,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VUG</t>
+          <t>SCHG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -4630,25 +4627,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.4056845500620376</v>
+        <v>0.3947432041476604</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1247189492480469</v>
+        <v>0.130183925965542</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1506217229053388</v>
+        <v>0.1523066751546547</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1714335424871811</v>
+        <v>0.181198782323692</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.0297557200534968</v>
+        <v>0.0558448276385064</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.02251198038560132</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>-0.003521926834810341</v>
+        <v>-0.01919866444073448</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0.002559726962457542</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4657,7 +4654,7 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4667,14 +4664,10 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SPGP</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>VUG</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -4682,29 +4675,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.2750959302992106</v>
+        <v>0.4056846360026141</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.09261985744239154</v>
+        <v>0.1247189492480469</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1424735716607293</v>
+        <v>0.1506217229053388</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1480864453032833</v>
+        <v>0.1714335424871811</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.02748757619887421</v>
+        <v>0.0297557200534968</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.04363664548132085</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>0.006361634450697373</v>
+        <v>-0.02251198038560132</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>-0.003521926834810341</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4713,7 +4706,7 @@
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4723,49 +4716,53 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IGF</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>SPGP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2590203788529941</v>
+        <v>0.2750960308292543</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.07269316034794193</v>
+        <v>0.09261985744239154</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1158445652838507</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>-0.03335162080024456</v>
-      </c>
-      <c r="J77" s="5" t="n">
-        <v>-0.04484226633664434</v>
+        <v>0.1424735716607293</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0.1480864453032833</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0.02748757619887421</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.03867151956323922</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>-0.01030444964871191</v>
+        <v>-0.04363664548132085</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>0.006361634450697373</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4775,53 +4772,49 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IAK</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D78" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>IGF</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1442127743192039</v>
+        <v>0.2590203788529941</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1158108930931669</v>
+        <v>0.07269316034794193</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1143554209684401</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>0.1327425245767495</v>
-      </c>
-      <c r="J78" s="3" t="n">
-        <v>0.07755812386586802</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>0.001306111225682249</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>0.01138730731842785</v>
+        <v>0.1158445652838507</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>-0.03335162080024456</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>-0.04484226633664434</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>-0.03867151956323922</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>-0.01030444964871191</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4831,49 +4824,53 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BOTZ</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>IAK</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1442234125195392</v>
+        <v>0.1442127057445972</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.02097475936122262</v>
+        <v>0.1158108930931669</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1108534349551622</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>-0.001510652410924629</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>-0.06310927491579221</v>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>-0.08090957165520896</v>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v>-0.0147392290249434</v>
+        <v>0.1143554209684401</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0.1327425245767495</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.07755812386586802</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0.001306111225682249</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0.01138730731842785</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4883,40 +4880,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VONG</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Robotics &amp; AI</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.3279269373194744</v>
+        <v>0.1442234125195392</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.06276587203645745</v>
+        <v>0.02097487375710227</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.101594590700717</v>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>0.109187431639697</v>
+        <v>0.1108535594215652</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>-0.001510652410924629</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-0.001848943866336716</v>
+        <v>-0.06310927491579221</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.03524773904305478</v>
+        <v>-0.08090957165520896</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.008657664813343957</v>
+        <v>-0.0147392290249434</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4935,49 +4932,49 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VFH</t>
+          <t>VONG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D81" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.2440962242062454</v>
+        <v>0.3279268295268538</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.0718518692096386</v>
+        <v>0.06276594107886213</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.09839999864300264</v>
+        <v>0.101594662265623</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.1794977952212815</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>0.07039952649449543</v>
+        <v>0.109187431639697</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>-0.001848943866336716</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.02416981925178663</v>
+        <v>-0.03524773904305478</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.002792096219931373</v>
+        <v>-0.008657664813343957</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4987,40 +4984,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>IWF</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+      <c r="D82" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>U.S. Equity REITs</t>
+          <t>Russell 1000 Growth</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1084751672361679</v>
+        <v>0.3259197949031281</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.05087142764483388</v>
+        <v>0.06148039976338548</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.09821801481212455</v>
+        <v>0.09999692424762507</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.04360567740235521</v>
+        <v>0.1086391457006339</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.03399225287864394</v>
+        <v>-0.001999932073707078</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.04311219314262527</v>
+        <v>-0.03501512016552599</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-0.004957805907172985</v>
+        <v>-0.008260407295329952</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5039,49 +5036,49 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>VFH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D83" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1018727704512268</v>
+        <v>0.2440963089832584</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.07657726537859633</v>
+        <v>0.07185199506442697</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.09672642528499509</v>
+        <v>0.09840012761502126</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.008782480165939743</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>-0.00948777852571292</v>
+        <v>0.1794977952212815</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0.07039952649449543</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.01837209302325582</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>0.01247301511153753</v>
+        <v>-0.02416981925178663</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>-0.002792096219931373</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5091,53 +5088,49 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EDEN</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>VNQ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
+          <t>U.S. Equity REITs</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.09987147714598676</v>
+        <v>0.1084751672361679</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.08606867063811396</v>
+        <v>0.05087133832675339</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.0953569793668454</v>
+        <v>0.09821792146985442</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.1590411915485337</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>0.05042670408354932</v>
+        <v>0.04360567740235521</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>-0.03399225287864394</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.008479709267110724</v>
+        <v>-0.04311219314262527</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.005467800729040073</v>
+        <v>-0.004957805907172985</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5147,49 +5140,49 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.2232508183621185</v>
+        <v>0.1018726607257185</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.07190512776381475</v>
+        <v>0.07657716063315956</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.09502354451200845</v>
+        <v>0.09672631857914848</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1765995958309858</v>
-      </c>
-      <c r="J85" s="3" t="n">
-        <v>0.07292413779603168</v>
+        <v>0.008782480165939743</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>-0.00948777852571292</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.02111225540679706</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>-0.003842794759825297</v>
+        <v>-0.01837209302325582</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>0.01247301511153753</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5192,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EUO</t>
+          <t>EDEN</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5207,45 +5200,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D86" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2x Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>-0.04536862003780706</v>
+          <t>Denmark Equity</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.09987139660309685</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.08369098712446355</v>
+        <v>0.08606867063811396</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.0829756795422032</v>
+        <v>0.0953569793668454</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.001984126984126977</v>
+        <v>0.1590411915485337</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.01711983887210478</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>0.0006605019815060231</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>0.00899100899100902</v>
+        <v>0.05042670408354932</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>-0.008479709267110724</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>-0.005467800729040073</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N86" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5255,109 +5248,105 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VOT</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
+          <t>XLF</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.2232507182728078</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.07190512776381475</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0.09502354451200845</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0.1765995958309858</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0.07292413779603168</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>-0.02111225540679706</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>-0.003842794759825297</v>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N87" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="21" customHeight="1">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EUO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D87" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Mid Growth</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>0.2205055506285958</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>0.003562654499147389</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>0.07338910911521168</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>0.1170520616293511</v>
-      </c>
-      <c r="J87" s="5" t="n">
-        <v>-0.01252871682010859</v>
-      </c>
-      <c r="K87" s="5" t="n">
-        <v>-0.0650523226135783</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>-0.006576494118444631</v>
-      </c>
-      <c r="M87" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N87" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="21" customHeight="1">
-      <c r="A88" s="15" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="16" t="inlineStr">
-        <is>
-          <t>UUP</t>
-        </is>
-      </c>
-      <c r="C88" s="15" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
       <c r="D88" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E88" s="15" t="inlineStr">
-        <is>
-          <t>US Dollar Index Bullish</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>0.02867498034109706</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2x Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-0.04536862003780706</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.06515814863787495</v>
+        <v>0.08369098712446355</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.06553626654651445</v>
+        <v>0.0829756795422032</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.01003944065973461</v>
+        <v>0.001984126984126977</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.007871198568873083</v>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>-0.0003548616039743546</v>
+        <v>0.01711983887210478</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>0.0006605019815060231</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.003562522265764256</v>
+        <v>0.00899100899100902</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N88" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5367,321 +5356,321 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>VOT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Mid Growth</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.2205055506285958</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.003562759380278724</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.07338922129382208</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0.1170520616293511</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.01252871682010859</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>-0.0650523226135783</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>-0.006576494118444631</v>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" s="15" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D90" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>US Dollar Index Bullish</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.02867498034109706</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.06515814863787495</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.06553626654651445</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0.01003944065973461</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0.007871198568873083</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>-0.0003548616039743546</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0.003562522265764256</v>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="21" customHeight="1">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>XLU</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" s="14" t="inlineStr">
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" s="14" t="inlineStr">
         <is>
           <t>Defensive Equity</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="F89" s="3" t="n">
+      <c r="F91" s="3" t="n">
         <v>0.1296163665731609</v>
       </c>
-      <c r="G89" s="3" t="n">
+      <c r="G91" s="3" t="n">
         <v>0.01048937492380064</v>
       </c>
-      <c r="H89" s="3" t="n">
+      <c r="H91" s="3" t="n">
         <v>0.06413084819809134</v>
       </c>
-      <c r="I89" s="5" t="n">
+      <c r="I91" s="5" t="n">
         <v>-0.09750242472458248</v>
       </c>
-      <c r="J89" s="5" t="n">
+      <c r="J91" s="5" t="n">
         <v>-0.05486093404897052</v>
       </c>
-      <c r="K89" s="5" t="n">
+      <c r="K91" s="5" t="n">
         <v>-0.05040871934604907</v>
       </c>
-      <c r="L89" s="5" t="n">
+      <c r="L91" s="5" t="n">
         <v>-0.01344656758669494</v>
       </c>
-      <c r="M89" s="6" t="inlineStr">
+      <c r="M91" s="6" t="inlineStr">
         <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N89" s="7" t="inlineStr">
+      <c r="N91" s="7" t="inlineStr">
         <is>
           <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="21" customHeight="1">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
+    <row r="92" ht="21" customHeight="1">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>USDU</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D90" s="21" t="inlineStr">
+      <c r="D92" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Bloomberg Dollar Bullish</t>
         </is>
       </c>
-      <c r="F90" s="3" t="n">
+      <c r="F92" s="3" t="n">
         <v>0.01576305319130755</v>
       </c>
-      <c r="G90" s="3" t="n">
+      <c r="G92" s="3" t="n">
         <v>0.04402163446054064</v>
       </c>
-      <c r="H90" s="3" t="n">
+      <c r="H92" s="3" t="n">
         <v>0.04718773494412076</v>
       </c>
-      <c r="I90" s="3" t="n">
+      <c r="I92" s="3" t="n">
         <v>0.003041825095057016</v>
       </c>
-      <c r="J90" s="3" t="n">
+      <c r="J92" s="3" t="n">
         <v>0.002660585328772447</v>
       </c>
-      <c r="K90" s="5" t="n">
+      <c r="K92" s="5" t="n">
         <v>-0.003023431594860182</v>
       </c>
-      <c r="L90" s="3" t="n">
+      <c r="L92" s="3" t="n">
         <v>0.003805175038051667</v>
       </c>
-      <c r="M90" s="6" t="inlineStr">
+      <c r="M92" s="6" t="inlineStr">
         <is>
           <t>CORRECTION</t>
         </is>
       </c>
-      <c r="N90" s="7" t="inlineStr">
+      <c r="N92" s="7" t="inlineStr">
         <is>
           <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="21" customHeight="1">
-      <c r="A91" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="16" t="inlineStr">
+    <row r="93" ht="21" customHeight="1">
+      <c r="A93" s="15" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>HYG</t>
         </is>
       </c>
-      <c r="C91" s="15" t="inlineStr"/>
-      <c r="D91" s="20" t="inlineStr">
+      <c r="C93" s="15" t="inlineStr"/>
+      <c r="D93" s="20" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
       </c>
-      <c r="E91" s="15" t="inlineStr">
+      <c r="E93" s="15" t="inlineStr">
         <is>
           <t>High Yield Corporate Bonds</t>
         </is>
       </c>
-      <c r="F91" s="3" t="n">
+      <c r="F93" s="3" t="n">
         <v>0.08635577007710027</v>
       </c>
-      <c r="G91" s="3" t="n">
+      <c r="G93" s="3" t="n">
         <v>0.028010050934002</v>
       </c>
-      <c r="H91" s="3" t="n">
+      <c r="H93" s="3" t="n">
         <v>0.03881128116780008</v>
       </c>
-      <c r="I91" s="3" t="n">
-        <v>0.02184330010943447</v>
-      </c>
-      <c r="J91" s="5" t="n">
+      <c r="I93" s="3" t="n">
+        <v>0.02184340155268072</v>
+      </c>
+      <c r="J93" s="5" t="n">
         <v>-0.002858152010351778</v>
       </c>
-      <c r="K91" s="5" t="n">
+      <c r="K93" s="5" t="n">
         <v>-0.01039768284154152</v>
       </c>
-      <c r="L91" s="5" t="n">
+      <c r="L93" s="5" t="n">
         <v>-0.0008905852417302462</v>
       </c>
-      <c r="M91" s="6" t="inlineStr">
+      <c r="M93" s="6" t="inlineStr">
         <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N91" s="7" t="inlineStr">
+      <c r="N93" s="7" t="inlineStr">
         <is>
           <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="21" customHeight="1">
-      <c r="A92" s="15" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="16" t="inlineStr">
+    <row r="94" ht="21" customHeight="1">
+      <c r="A94" s="15" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
         <is>
           <t>SHY</t>
         </is>
       </c>
-      <c r="C92" s="15" t="inlineStr"/>
-      <c r="D92" s="22" t="inlineStr">
+      <c r="C94" s="15" t="inlineStr"/>
+      <c r="D94" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
       </c>
-      <c r="E92" s="15" t="inlineStr">
+      <c r="E94" s="15" t="inlineStr">
         <is>
           <t>1-3 Year Treasury</t>
         </is>
       </c>
-      <c r="F92" s="3" t="n">
+      <c r="F94" s="3" t="n">
         <v>0.04299861406424332</v>
       </c>
-      <c r="G92" s="3" t="n">
-        <v>0.01655604030515789</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>0.02212469134920636</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>0.003094401785922241</v>
-      </c>
-      <c r="J92" s="3" t="n">
+      <c r="G94" s="3" t="n">
+        <v>0.01655613723300919</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0.02212478880802426</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0.003094496163655647</v>
+      </c>
+      <c r="J94" s="3" t="n">
         <v>1.786292805849854e-05</v>
       </c>
-      <c r="K92" s="5" t="n">
+      <c r="K94" s="5" t="n">
         <v>-0.005448113220607009</v>
       </c>
-      <c r="L92" s="5" t="n">
+      <c r="L94" s="5" t="n">
         <v>-0.000368686248003014</v>
       </c>
-      <c r="M92" s="6" t="inlineStr">
+      <c r="M94" s="6" t="inlineStr">
         <is>
           <t>CORRECTION</t>
         </is>
       </c>
-      <c r="N92" s="7" t="inlineStr">
+      <c r="N94" s="7" t="inlineStr">
         <is>
           <t>Established trend; positive 3m but negative 1m; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="21" customHeight="1">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>XRT</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D93" s="23" t="inlineStr">
-        <is>
-          <t>Consumer</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>0.2718582638270688</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>-0.02215149204553757</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>0.02095525345245508</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>0.07393364920684364</v>
-      </c>
-      <c r="J93" s="5" t="n">
-        <v>-0.02308756907211573</v>
-      </c>
-      <c r="K93" s="5" t="n">
-        <v>-0.04222197334527955</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>0.008609505837952502</v>
-      </c>
-      <c r="M93" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N93" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="21" customHeight="1">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>VCR</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D94" s="23" t="inlineStr">
-        <is>
-          <t>Consumer</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>0.1737844592852351</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>-0.03220466966297864</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>0.0171315148715725</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>0.04636279863765269</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>-0.03230796296032079</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>-0.04850521669341901</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>-0.00218300412929695</v>
-      </c>
-      <c r="M94" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N94" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5691,40 +5680,44 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IWP</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XRT</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D95" s="23" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Russell Midcap Growth</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1691654384140304</v>
+        <v>0.2718582638270688</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.05373650537113406</v>
+        <v>-0.02215149204553757</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.01631614729395103</v>
+        <v>0.02095525345245508</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.05827474079383732</v>
+        <v>0.07393354631587434</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-0.02608112677086938</v>
+        <v>-0.02308756907211573</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.06892801305145824</v>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v>-0.007463768115942071</v>
+        <v>-0.04222197334527955</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0.008609505837952502</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -5733,54 +5726,54 @@
       </c>
       <c r="N95" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
-      <c r="A96" s="15" t="n">
+      <c r="A96" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="16" t="inlineStr">
-        <is>
-          <t>TIP</t>
-        </is>
-      </c>
-      <c r="C96" s="15" t="inlineStr">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>VCR</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D96" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="inlineStr">
-        <is>
-          <t>TIPS</t>
+      <c r="D96" s="23" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.03424154810875368</v>
+        <v>0.1737844592852351</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.01044374858362174</v>
+        <v>-0.03220466966297864</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.002087014758827221</v>
-      </c>
-      <c r="I96" s="5" t="n">
-        <v>-0.01148231514750964</v>
+        <v>0.0171315148715725</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.04636279863765269</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-0.01799895107901017</v>
+        <v>-0.03230796296032079</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.01250466592011945</v>
+        <v>-0.04850521669341901</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.0001889644746788655</v>
+        <v>-0.00218300412929695</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5799,101 +5792,105 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>IWP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" s="22" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>7-10 Year Treasury</t>
+          <t>Russell Midcap Growth</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.020706812271716</v>
+        <v>0.1691653622733889</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.02807300640362997</v>
-      </c>
-      <c r="H97" s="5" t="n">
-        <v>-0.006310812295014956</v>
-      </c>
-      <c r="I97" s="5" t="n">
-        <v>-0.0292620039592334</v>
+        <v>-0.05373650537113406</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>0.01631614729395103</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0.05827474079383732</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.02450527631829724</v>
+        <v>-0.02608112677086938</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.02190040344393485</v>
+        <v>-0.06892801305145824</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>-0.0008790242830457595</v>
+        <v>-0.007463768115942071</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N97" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1">
-      <c r="A98" t="n">
+      <c r="A98" s="15" t="n">
         <v>97</v>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>LQD</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Investment Grade Corporate Bonds</t>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>TIPS</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03762838960808113</v>
+        <v>0.03424154810875368</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.02687762251742032</v>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>-0.0100408261382825</v>
+        <v>-0.01044367798384582</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>0.002087086252609005</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.01253961662466418</v>
+        <v>-0.01148231514750964</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.03163937157174768</v>
+        <v>-0.01799888155316975</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.01700756639635903</v>
+        <v>-0.01250466592011945</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>-0.000191717791411028</v>
+        <v>-0.0001889644746788655</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5903,92 +5900,92 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FXE</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D99" s="22" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Euro Currency</t>
+          <t>7-10 Year Treasury</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.07263239288871293</v>
+        <v>0.02070672485693548</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.008532095769512416</v>
+        <v>-0.0280729271443364</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.01069410114046232</v>
-      </c>
-      <c r="I99" s="3" t="n">
-        <v>0.01508148681653965</v>
+        <v>-0.006310731261044644</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>-0.0292620039592334</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.0004063416003677878</v>
-      </c>
-      <c r="K99" s="3" t="n">
-        <v>0.002185376002955541</v>
+        <v>-0.02450527631829724</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>-0.02190040344393485</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.004298663676292058</v>
+        <v>-0.0008790242830457595</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
-          <t>REBOUND</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N99" s="7" t="inlineStr">
         <is>
-          <t>Weak long trend; 1m rebound not yet confirmed by 3m; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
-      <c r="A100" s="15" t="n">
+      <c r="A100" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="16" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="C100" s="15" t="inlineStr"/>
-      <c r="D100" s="22" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="inlineStr">
-        <is>
-          <t>20+ Year Treasury</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>-0.0368641949997347</v>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>LQD</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Investment Grade Corporate Bonds</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0.03762823209400445</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.06311830695917853</v>
+        <v>-0.02687762251742032</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.04755110811657592</v>
+        <v>-0.0100408261382825</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>-0.04294248111099697</v>
+        <v>-0.01253968795020988</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>-0.04548640783442792</v>
+        <v>-0.03163937157174768</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.01634439283331957</v>
-      </c>
-      <c r="L100" s="3" t="n">
-        <v>0.0007419314949919098</v>
+        <v>-0.01700756639635903</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>-0.000191717791411028</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -5997,7 +5994,7 @@
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6007,100 +6004,92 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INDA</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>FXE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>India Equity</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>-0.006156371844859398</v>
+          <t>Euro Currency</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0.07263222812242698</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.0903456048084148</v>
+        <v>-0.008532306931187117</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.06123215627347867</v>
+        <v>-0.01069431184167569</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.007698709945900939</v>
-      </c>
-      <c r="J101" s="3" t="n">
-        <v>0.002069108214359572</v>
-      </c>
-      <c r="K101" s="5" t="n">
-        <v>-0.03101240496198476</v>
+        <v>0.01508163437648835</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>-0.0004063416003677878</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>0.002185376002955541</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>-0.002882437718756403</v>
+        <v>-0.004298663676292058</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>REBOUND</t>
         </is>
       </c>
       <c r="N101" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Weak long trend; 1m rebound not yet confirmed by 3m; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
-      <c r="A102" t="n">
+      <c r="A102" s="15" t="n">
         <v>101</v>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>IPAY</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Digital Payments</t>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr"/>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>20+ Year Treasury</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.04395507960823308</v>
+        <v>-0.03686410755057801</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.1484796154799024</v>
+        <v>-0.06311830695917853</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.1103924417313996</v>
-      </c>
-      <c r="I102" s="3" t="n">
-        <v>0.1547152409499655</v>
-      </c>
-      <c r="J102" s="3" t="n">
-        <v>0.1439013248058474</v>
+        <v>-0.04755110811657592</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>-0.04294248111099697</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>-0.0454864937248517</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>-0.04281345565749239</v>
+        <v>-0.01634439283331957</v>
       </c>
       <c r="L102" s="3" t="n">
-        <v>0.01314990896216872</v>
+        <v>0.0007419314949919098</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6119,35 +6108,53 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IWF</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>INDA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Russell 1000 Growth</t>
-        </is>
-      </c>
-      <c r="F103" s="24" t="n"/>
-      <c r="G103" s="24" t="n"/>
-      <c r="H103" s="24" t="n"/>
-      <c r="I103" s="24" t="n"/>
-      <c r="J103" s="24" t="n"/>
-      <c r="K103" s="24" t="n"/>
-      <c r="L103" s="24" t="n"/>
+          <t>India Equity</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>-0.006156371844859398</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>-0.0903456048084148</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>-0.06123215627347867</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>0.007698709945900939</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>0.002069108214359572</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>-0.03101240496198476</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>-0.002882437718756403</v>
+      </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_DATA</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N103" s="7" t="inlineStr">
         <is>
-          <t>Insufficient history for transition assessment.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6157,35 +6164,53 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PAVE</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>IPAY</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>U.S. Infrastructure Development</t>
-        </is>
-      </c>
-      <c r="F104" s="24" t="n"/>
-      <c r="G104" s="24" t="n"/>
-      <c r="H104" s="24" t="n"/>
-      <c r="I104" s="24" t="n"/>
-      <c r="J104" s="24" t="n"/>
-      <c r="K104" s="24" t="n"/>
-      <c r="L104" s="24" t="n"/>
+          <t>Digital Payments</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>-0.04395507960823308</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>-0.1484796154799024</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>-0.1103924417313996</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>0.1547152409499655</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>0.1439013248058474</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>-0.04281345565749239</v>
+      </c>
+      <c r="L104" s="3" t="n">
+        <v>0.01314990896216872</v>
+      </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_DATA</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N104" s="7" t="inlineStr">
         <is>
-          <t>Insufficient history for transition assessment.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.839045903436774</v>
+        <v>1.839045625081257</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>1.112825809884659</v>
@@ -799,13 +799,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.552911895513185</v>
+        <v>1.552912281805216</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9190524974047569</v>
+        <v>0.9190527156866941</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.260313464353132</v>
+        <v>1.260313721451676</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.3980846779619589</v>
@@ -907,16 +907,16 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.557405149737365</v>
+        <v>1.557404949099305</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9582311496268574</v>
+        <v>0.9582312672633913</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.168227228278037</v>
+        <v>1.168227358529634</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.5029058522013412</v>
+        <v>0.5029059907836733</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>-0.1653900019489318</v>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.50191116582222</v>
+        <v>1.501910893456296</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.8645744069359325</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8169115926655646</v>
+        <v>0.8169117524746563</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.6543502300835615</v>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.5584597790914039</v>
+        <v>0.5584596770357342</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0.4893795909629621</v>
@@ -1902,10 +1902,10 @@
         <v>0.6091119408822019</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.5069288302096486</v>
+        <v>0.5069286511111746</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.3955467954135667</v>
+        <v>0.395546629552846</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>0.1626638014574995</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5292606093176024</v>
+        <v>0.5292607837300569</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0.4264306000723488</v>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.7297775354336784</v>
+        <v>0.7297778564595072</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.335638296015172</v>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.7247877157150517</v>
+        <v>0.724787906177812</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3321650917660555</v>
+        <v>0.332164978145395</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3748677069422435</v>
+        <v>0.3748675896794673</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.337318136534499</v>
@@ -2282,10 +2282,10 @@
         <v>0.7396627626361758</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3379591908990263</v>
+        <v>0.337959299681547</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3672120620978938</v>
+        <v>0.3672121732588138</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>0.3419488064974769</v>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.988842074221548</v>
+        <v>0.9888419372604327</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2851314681437027</v>
+        <v>0.2851315825162715</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3446228949162622</v>
+        <v>0.3446230145833766</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>0.0117736914163602</v>
@@ -2447,13 +2447,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.534488398816942</v>
+        <v>0.5344885467771676</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1036429746571006</v>
+        <v>0.1036428981194886</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3275711934165428</v>
+        <v>0.3275711013495146</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>-0.08378986933896071</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5347563701209368</v>
+        <v>0.534756198610516</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.1228547128529127</v>
@@ -2614,10 +2614,10 @@
         <v>0.5537624775009724</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.3014991516179761</v>
+        <v>0.3014992656616815</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.3079353146086059</v>
+        <v>0.307935429216279</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0.2876186132865106</v>
@@ -2722,10 +2722,10 @@
         <v>0.3219786912967479</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2843108122085074</v>
+        <v>0.2843107205927771</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2876767986120823</v>
+        <v>0.2876767067562409</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>0.1333207064077311</v>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4429796829875632</v>
+        <v>0.4429795641170839</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2096006274440427</v>
+        <v>0.2096005439149868</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2794757908971111</v>
+        <v>0.2794757025428209</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0.1685734554032861</v>
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4538004424835325</v>
+        <v>0.4538005544976944</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2080579581350546</v>
+        <v>0.208057880788882</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2734729265881319</v>
+        <v>0.2734728450537518</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0.1724240326148132</v>
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.3507156405462939</v>
+        <v>0.3507154904889866</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2288634080341048</v>
+        <v>0.2288632838298326</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2707263701879186</v>
+        <v>0.2707262417524527</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>0.1118841662058345</v>
@@ -2982,10 +2982,10 @@
         <v>0.4301423823234247</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2587405929759927</v>
+        <v>0.258740499673858</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2688447162910208</v>
+        <v>0.2688446222399339</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>0.1717528211754278</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.4478714114829319</v>
+        <v>0.4478716344854876</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0.228463951828185</v>
@@ -3190,10 +3190,10 @@
         <v>0.498070289976358</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2200307317536216</v>
+        <v>0.2200308598583485</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.259409314694258</v>
+        <v>0.2594094469337846</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.1972892162149393</v>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.462806699945052</v>
+        <v>0.4628068505692728</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>0.08898197691329468</v>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.5172133759696664</v>
+        <v>0.517213258781664</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0.1884927729883081</v>
@@ -3570,10 +3570,10 @@
         <v>0.2255064288206527</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2328192089723227</v>
+        <v>0.2328190617374617</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2375153649331088</v>
+        <v>0.2375152171373887</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>0.1467767794978176</v>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3309827757649795</v>
+        <v>0.3309830939098899</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0.1264398266463573</v>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4139242618534722</v>
+        <v>0.4139241669107674</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0.07758000351827699</v>
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1905825730644324</v>
+        <v>0.1905824441277422</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2215855558316593</v>
+        <v>0.2215854200924652</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2261733287090002</v>
+        <v>0.2261731924600257</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0.1294644318507494</v>
@@ -3779,13 +3779,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.4998708641387162</v>
+        <v>0.4998706979576504</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1962851046525729</v>
+        <v>0.1962853160858424</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2235049922971657</v>
+        <v>0.2235052085413201</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>0.1892097989489854</v>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3460365607009626</v>
+        <v>0.346036479033432</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1309386155816243</v>
+        <v>0.1309385002777921</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2205731513728775</v>
+        <v>0.2205730269304365</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>0.1241770127769368</v>
@@ -3890,10 +3890,10 @@
         <v>0.3200176300464881</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.0920438470876932</v>
+        <v>0.09204409374337241</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2066880977917822</v>
+        <v>0.2066883703417106</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>0.03625398414329606</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3862585686175264</v>
+        <v>0.386258484753639</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1703508794541568</v>
+        <v>0.1703509990039265</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1965427731527949</v>
+        <v>0.1965428953780313</v>
       </c>
       <c r="I63" s="3" t="n">
         <v>0.1550841542877084</v>
@@ -4043,13 +4043,13 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3865184640605692</v>
+        <v>0.3865183105867593</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1704656355859233</v>
+        <v>0.1704655262076105</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.1964783646940815</v>
+        <v>0.1964782528849172</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>0.1554028551646778</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.3847697155463543</v>
+        <v>0.3847695617241742</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>0.1698230571387764</v>
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3658220549686115</v>
+        <v>0.3658222638386961</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0.1407740870486252</v>
@@ -4307,13 +4307,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.2890753885770738</v>
+        <v>0.2890755065053814</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1484056102821769</v>
+        <v>0.1484057038770483</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1896394659697189</v>
+        <v>0.1896395629251431</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>0.1201258778572365</v>
@@ -4418,10 +4418,10 @@
         <v>0.640039410933225</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.3115938700343948</v>
+        <v>0.3115939570219639</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1742450952031154</v>
+        <v>0.1742451730814349</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>0.07295278593470123</v>
@@ -4627,13 +4627,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3947432041476604</v>
+        <v>0.3947429936295834</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.130183925965542</v>
+        <v>0.1301838568510387</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1523066751546547</v>
+        <v>0.1523066046872716</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0.181198782323692</v>
@@ -4682,10 +4682,10 @@
         <v>0.4056846360026141</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1247189492480469</v>
+        <v>0.1247188392065075</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1506217229053388</v>
+        <v>0.1506216103294939</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>0.1714335424871811</v>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2750960308292543</v>
+        <v>0.2750957292391709</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0.09261985744239154</v>
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2590203788529941</v>
+        <v>0.2590202834625599</v>
       </c>
       <c r="G78" s="3" t="n">
         <v>0.07269316034794193</v>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1442127057445972</v>
+        <v>0.1442127743192039</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>0.1158108930931669</v>
@@ -4950,13 +4950,13 @@
         <v>0.3279268295268538</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.06276594107886213</v>
+        <v>0.06276587203645745</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.101594662265623</v>
+        <v>0.101594590700717</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.109187431639697</v>
+        <v>0.1091873564340331</v>
       </c>
       <c r="J81" s="5" t="n">
         <v>-0.001848943866336716</v>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.3259197949031281</v>
+        <v>0.3259196842899255</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.06148039976338548</v>
+        <v>0.06148047065526385</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.09999692424762507</v>
+        <v>0.09999699771186243</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>0.1086391457006339</v>
@@ -5103,16 +5103,16 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1084751672361679</v>
+        <v>0.1084750678577369</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05087133832675339</v>
+        <v>0.05087142764483388</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.09821792146985442</v>
+        <v>0.09821801481212455</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.04360567740235521</v>
+        <v>0.0436055893151055</v>
       </c>
       <c r="J84" s="5" t="n">
         <v>-0.03399225287864394</v>
@@ -5214,10 +5214,10 @@
         <v>0.09987139660309685</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.08606867063811396</v>
+        <v>0.08606859210408024</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.0953569793668454</v>
+        <v>0.09535690016117071</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>0.1590411915485337</v>
@@ -5263,13 +5263,13 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.2232507182728078</v>
+        <v>0.2232508183621185</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.07190512776381475</v>
+        <v>0.07190505090930044</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.09502354451200845</v>
+        <v>0.09502346599992717</v>
       </c>
       <c r="I87" s="3" t="n">
         <v>0.1765995958309858</v>
@@ -5375,13 +5375,13 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.2205055506285958</v>
+        <v>0.2205056281921831</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.003562759380278724</v>
+        <v>0.003562654499147389</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0.07338922129382208</v>
+        <v>0.07338910911521168</v>
       </c>
       <c r="I89" s="3" t="n">
         <v>0.1170520616293511</v>
@@ -5483,7 +5483,7 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1296163665731609</v>
+        <v>0.1296162501621017</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0.01048937492380064</v>
@@ -5591,16 +5591,16 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.08635577007710027</v>
+        <v>0.08635565542062529</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.028010050934002</v>
+        <v>0.02800994826268099</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03881128116780008</v>
+        <v>0.03881117741771867</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.02184340155268072</v>
+        <v>0.02184319866620799</v>
       </c>
       <c r="J93" s="5" t="n">
         <v>-0.002858152010351778</v>
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.04299861406424332</v>
+        <v>0.04299871610024231</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01655613723300919</v>
+        <v>0.01655604030515789</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.02212478880802426</v>
+        <v>0.02212469134920636</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>0.003094496163655647</v>
@@ -5708,7 +5708,7 @@
         <v>0.02095525345245508</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.07393354631587434</v>
+        <v>0.07393364920684364</v>
       </c>
       <c r="J95" s="5" t="n">
         <v>-0.02308756907211573</v>
@@ -5755,13 +5755,13 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.1737844592852351</v>
+        <v>0.1737846809427237</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.03220466966297864</v>
+        <v>-0.03220459432001155</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.0171315148715725</v>
+        <v>0.01713159405536668</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>0.04636279863765269</v>
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.1691653622733889</v>
+        <v>0.1691652861327571</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>-0.05373650537113406</v>
@@ -5863,19 +5863,19 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03424154810875368</v>
+        <v>0.03424162522862995</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.01044367798384582</v>
+        <v>-0.01044374858362174</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0.002087086252609005</v>
+        <v>0.002087014758827221</v>
       </c>
       <c r="I98" s="5" t="n">
         <v>-0.01148231514750964</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.01799888155316975</v>
+        <v>-0.01799895107901017</v>
       </c>
       <c r="K98" s="5" t="n">
         <v>-0.01250466592011945</v>
@@ -5918,16 +5918,16 @@
         <v>0.02070672485693548</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.0280729271443364</v>
+        <v>-0.02807300640362997</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.006310731261044644</v>
+        <v>-0.006310812295014956</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.0292620039592334</v>
+        <v>-0.02926216209018406</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.02450527631829724</v>
+        <v>-0.02450519647604732</v>
       </c>
       <c r="K99" s="5" t="n">
         <v>-0.02190040344393485</v>
@@ -5967,13 +5967,13 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.03762823209400445</v>
+        <v>0.03762838960808113</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.02687762251742032</v>
+        <v>-0.02687755324813323</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.0100408261382825</v>
+        <v>-0.01004075567050999</v>
       </c>
       <c r="I100" s="5" t="n">
         <v>-0.01253968795020988</v>
@@ -6019,16 +6019,16 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.07263222812242698</v>
+        <v>0.07263239288871293</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.008532306931187117</v>
+        <v>-0.008532236543972282</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01069431184167569</v>
+        <v>-0.01069424160794796</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.01508163437648835</v>
+        <v>0.01508148681653965</v>
       </c>
       <c r="J101" s="5" t="n">
         <v>-0.0004063416003677878</v>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03686410755057801</v>
+        <v>-0.0368641949997347</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>-0.06311830695917853</v>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -101,12 +101,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -141,12 +141,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E7FF"/>
+        <fgColor rgb="00FAE8FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAE8FF"/>
+        <fgColor rgb="00E0E7FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -687,25 +687,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.220339033013261</v>
+        <v>2.30049909090986</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.314127511468786</v>
+        <v>1.316978834405198</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.345644399605916</v>
+        <v>1.336346567719441</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.4194120016109544</v>
+        <v>0.3392186326070623</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1075208913649025</v>
+        <v>-0.1570111137384724</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.01343634531407456</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>-0.06623569309029254</v>
+        <v>-0.008289751863803319</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.01151969129497221</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -743,25 +743,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.839045625081257</v>
+        <v>1.872529739391047</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.112825809884659</v>
+        <v>1.14590592186771</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>1.293293956872363</v>
+        <v>1.284108740004862</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4927230051447549</v>
+        <v>0.4922770101315888</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.1817299025503319</v>
+        <v>-0.2070875499822753</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.07869385712498433</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>-0.05787027165337555</v>
+        <v>-0.0605062341019974</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.01982618142313974</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -799,25 +799,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.552912281805216</v>
+        <v>1.61465878354213</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9190527156866941</v>
+        <v>0.9380428960509377</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.260313721451676</v>
+        <v>1.279147978823718</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3980846779619589</v>
+        <v>0.3713331045046533</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.2332386714442596</v>
+        <v>-0.2589881544864966</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.1509794868412375</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>-0.0785969935576234</v>
+        <v>-0.1496634206914579</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.0107986326911127</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -855,25 +855,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.875868055555556</v>
+        <v>1.963420008814455</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.003022974607013</v>
+        <v>1.030193236714976</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>1.17956469165659</v>
+        <v>1.203200483091788</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.5306075306075309</v>
+        <v>0.4800792427911071</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1374642020307211</v>
+        <v>-0.172736220472441</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.08099861303744782</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>-0.07406372275013973</v>
+        <v>-0.07852542140605734</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.01479022034409883</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -907,25 +907,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.557404949099305</v>
+        <v>1.606629564617812</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9582312672633913</v>
+        <v>0.9824514506925397</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.168227358529634</v>
+        <v>1.163153055844476</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.5029059907836733</v>
+        <v>0.4948064733723698</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1653900019489318</v>
+        <v>-0.1973267563051954</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.09685150887896288</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>-0.05629233308668691</v>
+        <v>-0.08353620871334611</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.01415359871330923</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -963,25 +963,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.501910893456296</v>
+        <v>1.552604146609794</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.8645744069359325</v>
+        <v>0.8891851675965174</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.086400699445819</v>
+        <v>1.076107019123945</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4582953362186568</v>
+        <v>0.4509931347755709</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1667784045303321</v>
+        <v>-0.1978299576933991</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.1063200815494393</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>-0.05832438238453264</v>
+        <v>-0.09003478616738281</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.01448614121136083</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1019,25 +1019,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.463200245957859</v>
+        <v>1.500034612763686</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7872040913814964</v>
+        <v>0.8036362314644352</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.944372436407511</v>
+        <v>0.9375953974549958</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3980326853071026</v>
+        <v>0.3890637692932573</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1265565520356152</v>
+        <v>-0.1544119919641478</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.08083242802824553</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>-0.04754366524193965</v>
+        <v>-0.06913681058827548</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.01048938134810706</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.213054987064196</v>
+        <v>1.257954484494167</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.7873047340334562</v>
+        <v>0.7835791949662092</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.7921393424922727</v>
+        <v>0.7824138921507562</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5317902557508216</v>
+        <v>0.4874357906427877</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.04472812317287067</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>-0.00269767441860469</v>
+        <v>0.007238883143743546</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.0006537779023070289</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-0.03336038229194849</v>
+        <v>-0.0006529241675216069</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1131,34 +1131,34 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.142857142857143</v>
+        <v>1.197080291970803</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8842364532019706</v>
+        <v>0.8580246913580249</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7105911330049264</v>
+        <v>0.7641975308641975</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.4585319351763584</v>
+        <v>0.4104967197750704</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.2418831168831168</v>
+        <v>0.2552126772310259</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1015118790496761</v>
+        <v>0.05318404478656413</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-0.04434728294815748</v>
+        <v>-0.0163398692810458</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1168,53 +1168,49 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COPX</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Natural Resources</t>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.233708324004235</v>
+        <v>0.8004787562734055</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.6589690264453247</v>
+        <v>0.6443381728435096</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.6570314312263976</v>
+        <v>0.680093936046325</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.1246361793677935</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>-0.0006867439035823653</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0.001169317118802748</v>
+        <v>0.2445422364028342</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.1305808273691522</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>-0.02128200241407785</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.03287021348695351</v>
+        <v>-0.02246192893401011</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1224,49 +1220,53 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>OIH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Defensive Equity</t>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Oil Services</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8169117524746563</v>
+        <v>0.6819278374830311</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.6543502300835615</v>
+        <v>0.6086103293236047</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6465823419473826</v>
+        <v>0.663857686585934</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.2948757036812251</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0.1791218549375744</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.004717582557694611</v>
+        <v>0.09332474434334492</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>-0.01921409997110668</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>-0.03320437661690367</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.008962868117797784</v>
+        <v>0.01313236830323827</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1284,36 +1284,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oil Services</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.6395645211087173</v>
+        <v>1.182077254901352</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.572197193652958</v>
+        <v>0.633272991741072</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.6054743117895212</v>
+        <v>0.6480807181468253</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.08334006951741979</v>
+        <v>0.08337929947690315</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-0.06098045168974942</v>
+        <v>-0.05112335658957967</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.02072728158413906</v>
+        <v>-0.008984830805134125</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.0442389521477643</v>
+        <v>-0.008058864751226302</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1351,25 +1351,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.244710392782184</v>
+        <v>1.214246559253477</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5733414619446262</v>
+        <v>0.570530002401598</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.56216791757505</v>
+        <v>0.5669963540667984</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1261953443610677</v>
+        <v>0.109224579761442</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02985902881037195</v>
+        <v>0.0155375299897178</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.007152588555858319</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>-0.02215608465608476</v>
+        <v>0.002255045664674826</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.00202908353060538</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1403,25 +1403,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.8808735936465919</v>
+        <v>0.8750813272608979</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.5041016141836465</v>
+        <v>0.5033907146583201</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5390314898121196</v>
+        <v>0.525299947835159</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.2180492502407483</v>
+        <v>-0.2127833925157061</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.07260564529286995</v>
+        <v>-0.09185441941074524</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.02269601100412644</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>-0.02202339986235369</v>
+        <v>-0.01436388508891928</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0.01407459535538358</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PICK</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1448,36 +1448,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Global Metals &amp; Mining</t>
+          <t>Lithium &amp; Battery</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.7696810476773683</v>
+        <v>0.775965631512022</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4902658086655249</v>
+        <v>0.4101582637393668</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5045301958672228</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.1227901060117154</v>
+        <v>0.5148680020150302</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>-0.01799721413696487</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.04490378055483579</v>
+        <v>-0.1635223987491038</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.009480957737425633</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>-0.02699289660615634</v>
+        <v>-0.06912136115911205</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0.0008575103615835467</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>QTEC</t>
+          <t>BOAT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1504,45 +1504,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Global Shipping</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.7260165295464791</v>
+        <v>1.176270047039389</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.4031869472330367</v>
+        <v>0.7012797948276588</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.4982778952795142</v>
+        <v>0.5110907825421778</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.3963439767451769</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>-0.04189936149336093</v>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>-0.0634668297156834</v>
+        <v>0.3744270259679694</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0.2609114130576813</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0.1258620689655172</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.007098175217969072</v>
+        <v>-0.002482337215963248</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>PICK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1560,36 +1560,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Global Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.7607468284043433</v>
+        <v>0.7597635442407662</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.3986025172167098</v>
+        <v>0.4867483103797461</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4923490629612628</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>-0.001835547538242888</v>
+        <v>0.5002905851652479</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.09727995219973917</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.146888659743051</v>
+        <v>-0.06593740504405954</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.06281810875971061</v>
+        <v>-0.009026434558349505</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-0.02126171492516427</v>
+        <v>-0.002595717066839809</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BOAT</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1616,45 +1616,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Global Shipping</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.166485016412749</v>
+        <v>0.7517022878794402</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.7163601812398539</v>
+        <v>0.4054323819360943</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.4898937147062012</v>
+        <v>0.4991462313324342</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.4199931795550906</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0.265835904325169</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>0.1520017597888252</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>0.007115384615384635</v>
+        <v>0.3707730105555855</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>-0.08422487769164466</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>-0.06251147982611893</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>-0.0003264346804203733</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DXJ</t>
+          <t>VDE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1672,97 +1672,97 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Japan Hedged Equity</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.6572068438324503</v>
+        <v>0.5923281556448163</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.3840064466440576</v>
+        <v>0.520079065350147</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.4265756386651089</v>
+        <v>0.4415951524803936</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.1460870680591695</v>
+        <v>0.1427311182428161</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.04210432040167778</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>-0.02984012264564162</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>-0.0001692811195125321</v>
+        <v>0.1828728428954471</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.05444240897641395</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0.01442969653577131</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="A21" t="n">
+      <c r="A21" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>XLK</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Technology</t>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr"/>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.7562348380821993</v>
+        <v>0.5730456087544327</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.3668346783154481</v>
+        <v>0.5234623598626429</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.4149720619830586</v>
+        <v>0.4410627150358475</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.3503590920065554</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>-0.001624809735238819</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>-0.03402002411280602</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>-0.01806362231576697</v>
+        <v>0.1459883654802612</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0.1867148115735211</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.05717977709578426</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0.0142569347590269</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VDE</t>
+          <t>DXJ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1780,97 +1780,101 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Japan Hedged Equity</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.6580066323222324</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.3854395240179331</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0.430756905274075</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0.1223010199975405</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0.02076049226192089</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>-0.03167371136850183</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>-0.004458490885490107</v>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>XOP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0.5584596770357342</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0.4893795909629621</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>0.4133397781732577</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>0.1293830140141483</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>0.125967425230703</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0.05380150899593716</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>-0.01111050596372753</v>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas E&amp;P</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.6686282970486948</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.5548638716094128</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0.4192241336440927</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>0.1920164839087275</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0.2547940366316168</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0.09557316194803045</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0.02207060526179783</v>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
         <is>
           <t>STEADY_POSITIVE</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr"/>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>0.5403328080341847</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0.4929486371830269</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>0.4126676551432764</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>0.1337961603339384</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>0.1293722537138284</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>0.05682934818211582</v>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>-0.009364445809026734</v>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>STEADY_POSITIVE</t>
-        </is>
-      </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1880,53 +1884,49 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>XOP</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>XLK</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6091119408822019</v>
+        <v>0.7957705098658592</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.5069286511111746</v>
+        <v>0.3719735006319762</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.395546629552846</v>
+        <v>0.4102714896136423</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.1626638014574995</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>0.1758694380465402</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0.07981246860523528</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>-0.01149601471489881</v>
+        <v>0.3352104275227572</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>-0.03503620499932436</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>-0.02715646544918682</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.003093119166485803</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Defensive Equity</t>
         </is>
@@ -1955,25 +1955,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5292607837300569</v>
+        <v>0.5197767622774105</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4264306000723488</v>
+        <v>0.4339850755932984</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.3869702032179523</v>
+        <v>0.4098779126562229</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.2372559779415742</v>
+        <v>0.2075246345460502</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1990435927215364</v>
+        <v>0.171226113724807</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.02845078918266819</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>0.008229438722712201</v>
+        <v>0.01709875920508441</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>-0.01441837732160312</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1992,49 +1992,53 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DBC</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+          <t>QCLN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Broad Commodity Futures</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.5625032818008719</v>
+        <v>0.6680331221524942</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.5421106368016977</v>
+        <v>0.2454131448724162</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3853410185204995</v>
+        <v>0.391549261641591</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.154649947753396</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>0.1611208406304727</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>0.1131631967763598</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>-0.0003015681544028537</v>
+        <v>0.01135620313047836</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>-0.247323677581864</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>-0.1050168476226132</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.005467928496319718</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2044,53 +2048,49 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>QCLN</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>DBC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Broad Commodity Futures</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.6328366501164413</v>
+        <v>0.5857276278510641</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.2396072242391989</v>
+        <v>0.5502528125975523</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3835111543716991</v>
+        <v>0.3874577678379048</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.0231687829540359</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>-0.2267035290291105</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>-0.1040135669869984</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>-0.03919983835118213</v>
+        <v>0.1840339102790536</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.1878100637845501</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.1173333333333335</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.01116138763197605</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FTEC</t>
+          <t>DRIV</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2115,38 +2115,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Autonomous &amp; Electric Vehicles</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.7297778564595072</v>
+        <v>0.5305079570069677</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.335638296015172</v>
+        <v>0.2794136500571267</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3778993868045706</v>
+        <v>0.3799471994939432</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.3380941625427074</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>0.02084724938480176</v>
+        <v>0.09240982713233992</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>-0.1751848871566442</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.03067066521264994</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>-0.01584665421078124</v>
+        <v>-0.07285318559556797</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.002395926924228853</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2156,49 +2156,49 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VGT</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.724787906177812</v>
+        <v>1.396799339683054</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.332164978145395</v>
+        <v>0.4251701055879027</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3748675896794673</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>0.337318136534499</v>
+        <v>0.3764450275603612</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>-0.02439975989465004</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.02203059500691151</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>-0.03105943572648173</v>
+        <v>0.06783063560558045</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0.03539921831379123</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.01569340051210033</v>
+        <v>-0.005896858582609577</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2208,49 +2208,53 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SIL</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" s="13" t="inlineStr">
+          <t>XME</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1.440260045068144</v>
+        <v>0.9688345848166877</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.4434882987620041</v>
+        <v>0.2853873436907342</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3724514027470198</v>
+        <v>0.3739417231493074</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.00955849663370012</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>0.1434700679207872</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>0.05175913396481713</v>
+        <v>-0.006762015358798723</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>-0.09089797679571954</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>-0.06445279153150074</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.0320672478206725</v>
+        <v>-0.005264591086502679</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2264,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IYW</t>
+          <t>FTEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2279,34 +2283,34 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.7396627626361758</v>
+        <v>0.7692025828993831</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.337959299681547</v>
+        <v>0.3374558262616099</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3672121732588138</v>
+        <v>0.3718818529300072</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.3419488064974769</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>0.02591133440519489</v>
+        <v>0.3221771388311856</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>-0.01007263270969194</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.02139600140301645</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>-0.008489634748272468</v>
+        <v>-0.02509401709401704</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.002531289551399363</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2316,14 +2320,10 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DRIV</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>VGT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -2331,29 +2331,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Autonomous &amp; Electric Vehicles</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5132049193610779</v>
+        <v>0.7600338755169549</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.2720093496470317</v>
+        <v>0.3334755964026048</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3622957275644758</v>
+        <v>0.3685376745528659</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.1100471238348077</v>
+        <v>0.3207509078635586</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>-0.1585306451306459</v>
+        <v>-0.009673230060119442</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.06627516778523479</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>-0.02396959953230049</v>
+        <v>-0.02562010443864227</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.002097843416967393</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>IYW</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2380,36 +2380,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.9888419372604327</v>
+        <v>0.7790718117893196</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2851315825162715</v>
+        <v>0.3341441258384972</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3446230145833766</v>
+        <v>0.3558483121265503</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.0117736914163602</v>
+        <v>0.3249944480658717</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.08464485176599346</v>
+        <v>-0.01007993070047641</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.04424394898932937</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>-0.03044970518349022</v>
+        <v>-0.01600782778864973</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0.001234567901234662</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2428,14 +2428,10 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XAR</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>AIRR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" s="18" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -2443,29 +2439,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>U.S. Industrial Renaissance</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5344885467771676</v>
+        <v>0.5720786266535529</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1036428981194886</v>
+        <v>0.1396250093099527</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3275711013495146</v>
+        <v>0.3488445911899107</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.08378986933896071</v>
+        <v>-0.04584956323314926</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.1324678485724774</v>
+        <v>-0.1915317941244151</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.1686751112632661</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>-0.0127256464465767</v>
+        <v>-0.1551102204408817</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.00591715976331364</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2474,7 +2470,7 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2480,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ARKQ</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2492,36 +2488,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.7838008675005423</v>
+        <v>0.5235976782248355</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.2111827531630288</v>
+        <v>0.09025035700961848</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.3175156871781777</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>0.01986867911656853</v>
+        <v>0.345323692915807</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>-0.1115218761304897</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.07580557916698871</v>
+        <v>-0.1494661850009392</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.0807071483474251</v>
+        <v>-0.1895999730394635</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-0.01450230718523404</v>
+        <v>-0.009718733270189128</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2540,49 +2536,53 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AIRR</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>CALF</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>U.S. Industrial Renaissance</t>
+          <t>Small Cap Cash Flow</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.534756198610516</v>
+        <v>0.5713639192089242</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.1228547128529127</v>
+        <v>0.3145125201513366</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.3157482500866637</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>-0.03424947276849233</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>-0.1905755117806102</v>
+        <v>0.3205800079126468</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0.2773342714219709</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.1296998958616897</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.1466036813813325</v>
+        <v>-0.004594562786771839</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.02339453816758319</v>
+        <v>-0.002823861630780078</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CALF</t>
+          <t>ROBO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2600,45 +2600,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Small Cap Cash Flow</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.5537624775009724</v>
+        <v>0.4505271599103216</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.3014992656616815</v>
+        <v>0.2002357235393644</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.307935429216279</v>
+        <v>0.3135852977402176</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.2876186132865106</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>0.125497404085253</v>
+        <v>0.09000140627197317</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>-0.09036498063607545</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.00492085726162661</v>
+        <v>-0.08629022751385118</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.01287093314265286</v>
+        <v>0.002068519715578754</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2648,44 +2648,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ROBO</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SCHA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4220911284200264</v>
+        <v>0.4639471969072151</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.1884120544255257</v>
+        <v>0.2172297074566689</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.3061009534158234</v>
+        <v>0.3023481113694551</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1072144288577153</v>
+        <v>0.1525789063123784</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.06807228915662655</v>
+        <v>-0.05041533532160769</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.09010704622985544</v>
+        <v>-0.06535764375876574</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.02224750347617244</v>
+        <v>-0.002693804250224363</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2719,25 +2715,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.3219786912967479</v>
+        <v>0.3276966585867671</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2843107205927771</v>
+        <v>0.2940183697883518</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2876767067562409</v>
+        <v>0.3023181960668779</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1333207064077311</v>
+        <v>0.1294336664522422</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.05464625646659593</v>
+        <v>0.05955175487588682</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>-0.002613999419111113</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>0.006447831184056341</v>
+        <v>-0.006373117033603881</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>-0.001164822364589591</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2746,7 +2742,7 @@
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2756,40 +2752,44 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SPMO</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>ARKQ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.5705517499660058</v>
+        <v>0.8241670341643736</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2103740128121498</v>
+        <v>0.1906424410608729</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2819773856485994</v>
+        <v>0.2975166559960483</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.2465125475651015</v>
+        <v>0.003354297693920483</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>-0.05291668059220334</v>
+        <v>-0.1116638206251391</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.0558538501833421</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>-0.02777965073157573</v>
+        <v>-0.08236827977605632</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0.0004180602006689238</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SCHA</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2823,25 +2823,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4429795641170839</v>
+        <v>0.4642831902279723</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2096005439149868</v>
+        <v>0.2109883919818296</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2794757025428209</v>
+        <v>0.2933573076725349</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1685734554032861</v>
+        <v>0.1523729146634831</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.03828517986291613</v>
+        <v>-0.03047787130057</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.05461233729485027</v>
+        <v>-0.06368612540561791</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.01124593074874236</v>
+        <v>-0.007814942169427908</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2860,49 +2860,53 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>ARGT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4538005544976944</v>
+        <v>0.1813844227428318</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.208057880788882</v>
+        <v>0.3479622363533508</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2734728450537518</v>
+        <v>0.2890163422796628</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1724240326148132</v>
+        <v>0.1146998297884214</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.01486712909343291</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>-0.05136738056013168</v>
+        <v>-0.02706568848931545</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0.04572936132791017</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.003392294645020444</v>
+        <v>-0.003352540597171383</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2912,49 +2916,49 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HEFA</t>
+          <t>SPMO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Developed ex-US Currency-Hedged</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.3507154904889866</v>
+        <v>0.5921826667377852</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2288632838298326</v>
+        <v>0.20794594952784</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2707262417524527</v>
+        <v>0.283191473961427</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1118841662058345</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>0.02208374402652935</v>
+        <v>0.2351972403782541</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>-0.08425328795815512</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.03294412010008341</v>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>-0.003651987110633637</v>
+        <v>-0.05863935816319876</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0.000901588182259383</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2964,49 +2968,49 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FNDX</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fundamental Large Cap</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4301423823234247</v>
+        <v>0.4481283873265185</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.258740499673858</v>
+        <v>0.0786712094382267</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2688446222399339</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0.1717528211754278</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>0.03878090233134723</v>
+        <v>0.2762411160356404</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>-0.07946720640353511</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>-0.09848357203032854</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.007963246554364423</v>
+        <v>-0.1548060974646552</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>-0.002156500308071463</v>
+        <v>-0.01268625732343032</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3016,40 +3020,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EWJ</t>
+          <t>FNDX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Japan Equity</t>
+          <t>Fundamental Large Cap</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.4759065157732758</v>
+        <v>0.4407807907944996</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2516122904163891</v>
+        <v>0.2620100897326796</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.263027897492333</v>
+        <v>0.2752738742924663</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1769455207578341</v>
+        <v>0.1623785440206873</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.0582481040237135</v>
+        <v>0.03320681134017311</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.009038285772316468</v>
+        <v>-0.01040073416947063</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>-0.009943181818181879</v>
+        <v>-0.001234949058351309</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -3068,40 +3072,44 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>QQQM</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>IWO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Russell 2000 Growth</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.499090902071659</v>
+        <v>0.4334206595863168</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2205372080642829</v>
+        <v>0.1633212084485638</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2597839869962866</v>
+        <v>0.2707565878593987</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1976217857471156</v>
+        <v>0.138147624301971</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-0.01566295648820293</v>
+        <v>-0.06207110857912324</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.03115357818254216</v>
+        <v>-0.08454442057373934</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.008050545195149361</v>
+        <v>-0.009299781181619338</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3120,7 +3128,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>HEFA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -3131,29 +3139,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Developed Markets</t>
+          <t>Developed ex-US Currency-Hedged</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.4478716344854876</v>
+        <v>0.3531834438914816</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.228463951828185</v>
+        <v>0.2277852884171887</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2596380231099376</v>
+        <v>0.270296789422761</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1316233252218062</v>
+        <v>0.09667110268668311</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.007652106195313868</v>
+        <v>0.01305881162752276</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.02474843622518363</v>
+        <v>-0.03346580213344497</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.013344338973724</v>
+        <v>-0.003665373005605876</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3167,45 +3175,45 @@
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
-      <c r="A48" s="15" t="n">
+      <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr"/>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>Nasdaq-100</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PAVE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>U.S. Infrastructure Development</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.498070289976358</v>
+        <v>0.4343639555671133</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2200308598583485</v>
+        <v>0.1474711578368721</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2594094469337846</v>
+        <v>0.2701744783234903</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1972892162149393</v>
+        <v>0.04622769656045</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.01577705838148191</v>
+        <v>-0.08848514472862234</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.03126750174163684</v>
+        <v>-0.0966035159583547</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.007973366159355511</v>
+        <v>-0.001697472651829512</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3224,14 +3232,10 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ARGT</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>EWJ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>International</t>
@@ -3239,38 +3243,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>Japan Equity</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.1711323952604378</v>
+        <v>0.4724897126474985</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.3161667551901435</v>
+        <v>0.2526710835898267</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.255356955395607</v>
+        <v>0.2684279525657993</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1202806546117328</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>-0.02159942191825492</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>0.04844024604569408</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>0.0005241090146750338</v>
+        <v>0.1463144618410037</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0.03115032957686581</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>-0.01242236024844723</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>-0.006046320967411423</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3280,40 +3284,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Developed Markets</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4628068505692728</v>
+        <v>0.4560480938450344</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.08898197691329468</v>
+        <v>0.2311899069765964</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2543613498891937</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>-0.05353207006341631</v>
+        <v>0.2655902955481695</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>0.1056791298760524</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.07214949807159332</v>
+        <v>-0.005984595110815949</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.1318434859225439</v>
+        <v>-0.02718129926610491</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>-0.01022784347746675</v>
+        <v>-0.001952035694366971</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3351,25 +3355,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.517213258781664</v>
+        <v>0.546059684426758</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1884927729883081</v>
+        <v>0.1941306798821245</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2532511546462963</v>
+        <v>0.2601137490532559</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.2335690563572488</v>
+        <v>0.2205277816154014</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.07511988696886396</v>
+        <v>-0.0990018883193956</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.05167230959086155</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>-0.02390568004168847</v>
+        <v>-0.0523627880583839</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0.003003003003003046</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3388,14 +3392,10 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IWO</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>COWZ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3403,38 +3403,38 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Russell 2000 Growth</t>
+          <t>Large Cap Cash Flow</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4217453316529409</v>
+        <v>0.3523870876287789</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.1636783793404464</v>
+        <v>0.2562105894620479</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2499357209162836</v>
+        <v>0.2540397762870876</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.1616984603695042</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>-0.03773774671265639</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>-0.06900942195059834</v>
+        <v>0.1338682367832629</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>0.1083481890645546</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>0.001731056076536452</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>-0.005521856214128262</v>
+        <v>-0.002409297052154202</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3444,40 +3444,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>QQQM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>U.S. Infrastructure Development</t>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.4129445737172972</v>
+        <v>0.5260365501284441</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1343046896068651</v>
+        <v>0.2146984766172428</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2474784317422918</v>
+        <v>0.2526942183313561</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.05866010859173088</v>
+        <v>0.1838745711195309</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.08045399108285478</v>
+        <v>-0.04578838319526723</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>-0.090722003086949</v>
+        <v>-0.03033121823195239</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.01960059171597628</v>
+        <v>-0.0004794192178617651</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3491,54 +3491,54 @@
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
-      <c r="A54" t="n">
+      <c r="A54" s="15" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>COWZ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Large Cap Cash Flow</t>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.3406460075511395</v>
+        <v>0.5248051745528219</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2448854163222376</v>
+        <v>0.21410014298452</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2430722933679541</v>
+        <v>0.2521579904517077</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.1424504146230072</v>
-      </c>
-      <c r="J54" s="3" t="n">
-        <v>0.1085957564766276</v>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>0.001458582066350411</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>0.008864741206748628</v>
+        <v>0.1834567619569536</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>-0.04619760576167742</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>-0.03039380633865429</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>-0.0004653261513295481</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3548,53 +3548,49 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>XLI</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2255064288206527</v>
+        <v>0.3395060331617559</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2328190617374617</v>
+        <v>0.1310958245437939</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2375152171373887</v>
+        <v>0.2462969352848288</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1467767794978176</v>
-      </c>
-      <c r="J55" s="3" t="n">
-        <v>0.1034988384706521</v>
+        <v>0.02470949729411087</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>-0.05033319556715332</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.003794826386692929</v>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>0.01377357276179425</v>
+        <v>-0.0924347219988203</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>-0.003883952215618214</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3604,49 +3600,53 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>XLI</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>VHT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3309830939098899</v>
+        <v>0.2262754895403778</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1264398266463573</v>
+        <v>0.2395184749519443</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2315733266205304</v>
+        <v>0.2460914390089983</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.03751438366082249</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>-0.0331020809948398</v>
+        <v>0.1302141086603497</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0.09978804965466104</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.08536519726573</v>
+        <v>-0.005274864950746694</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.01415559552126233</v>
+        <v>-0.006285315218081289</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3675,25 +3675,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4139241669107674</v>
+        <v>0.4074979440701867</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.07758000351827699</v>
+        <v>0.0722939448455342</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2293064876737918</v>
+        <v>0.2454247380237193</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>-0.07164785362606163</v>
+        <v>-0.09008044039483554</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.07669714959884411</v>
+        <v>-0.09286321546451215</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.1234244557210673</v>
+        <v>-0.1390134529147982</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.007168901798405569</v>
+        <v>-0.008029878618113884</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="14" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>Defensive Equity</t>
         </is>
@@ -3727,25 +3727,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1905824441277422</v>
+        <v>0.1896783600244283</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2215854200924652</v>
+        <v>0.2283116607461635</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2261731924600257</v>
+        <v>0.2330265858518887</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1294644318507494</v>
+        <v>0.1135273659540397</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.09544130680349161</v>
+        <v>0.09533209871717552</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.003741536999643635</v>
-      </c>
-      <c r="L58" s="3" t="n">
-        <v>0.01445331398161587</v>
+        <v>-0.00382386329688722</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>-0.006080476900149123</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ONEQ</t>
+          <t>VBK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3775,38 +3775,38 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.4998706979576504</v>
+        <v>0.3710954401164008</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1962853160858424</v>
+        <v>0.1355458647508767</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2235052085413201</v>
+        <v>0.2317962539392182</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1892097989489854</v>
-      </c>
-      <c r="J59" s="3" t="n">
-        <v>0.01356590427565485</v>
+        <v>0.1033800140883068</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>-0.05368459042477713</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.02224746757549934</v>
+        <v>-0.07813823826833199</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.004817883985353655</v>
+        <v>-0.003603922958761552</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3816,10 +3816,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VBK</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>XMMO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D60" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3827,29 +3831,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.346036479033432</v>
+        <v>0.3411857363130528</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1309385002777921</v>
+        <v>0.0958694830280733</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2205730269304365</v>
+        <v>0.2311758171570499</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1241770127769368</v>
+        <v>0.02414652436456155</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.03404518286254044</v>
+        <v>-0.1406059963134003</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.07343643081976203</v>
+        <v>-0.1099000908265214</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>-0.006369426751592355</v>
+        <v>-0.003727549983056688</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3868,14 +3872,10 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>XMMO</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>ONEQ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3883,29 +3883,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3200176300464881</v>
+        <v>0.524484791185545</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.09204409374337241</v>
+        <v>0.1873412808018635</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2066883703417106</v>
+        <v>0.2143210690818824</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.03625398414329606</v>
+        <v>0.1721601038881431</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>-0.1291549550793463</v>
+        <v>-0.01926922196723846</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.09500736015701661</v>
+        <v>-0.02221800227876936</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.0303607807057894</v>
+        <v>-0.002904725019364784</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -3924,40 +3924,44 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>QUAL</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Quality Factor</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3045726615563662</v>
+        <v>0.3869584999548787</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1600797782985897</v>
+        <v>0.1501856083311661</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1971243426476204</v>
+        <v>0.2034131758991924</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1325324524491687</v>
+        <v>0.1910281052718821</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.01674641890443174</v>
+        <v>0.04203155777468082</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.03094462540716614</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>-0.0002270663033605569</v>
+        <v>-0.04423050090693459</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>0.00528324038743766</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -3966,7 +3970,7 @@
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3980,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VOO</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -3987,29 +3991,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.386258484753639</v>
+        <v>0.2963471071801052</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1703509990039265</v>
+        <v>0.152105159094766</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1965428953780313</v>
+        <v>0.1984798799511605</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1550841542877084</v>
+        <v>0.1074052066662872</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.02842797209854719</v>
+        <v>0.009861694507613539</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.02188964263235205</v>
+        <v>-0.03869461776720384</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.004640173081302601</v>
+        <v>-0.003999813962141219</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -4028,49 +4032,49 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IVV</t>
+          <t>IAU</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3865183105867593</v>
+        <v>0.4350453172205437</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1704655262076105</v>
+        <v>0.1757425742574257</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.1964782528849172</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>0.1554028551646778</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>0.0287104125529305</v>
+        <v>0.198019801980198</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>-0.1439626841937878</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>-0.006276150627615107</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>-0.02174107771251621</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>-0.004479633295134788</v>
+        <v>-0.01859504132231404</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0.002607400049664754</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4080,49 +4084,49 @@
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr"/>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.3847695617241742</v>
+        <v>0.43125068149602</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1698230571387764</v>
+        <v>0.1739908174825591</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1959598881388804</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>0.1549676346517579</v>
-      </c>
-      <c r="J65" s="3" t="n">
-        <v>0.02843302916016732</v>
+        <v>0.1969471110846104</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>-0.1447559889668354</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>-0.006985247761946867</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.02185427058158074</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>-0.004461657224351989</v>
+        <v>-0.01917903756102435</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.002392831687200836</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4132,53 +4136,49 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D66" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>QUAL</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Quality Factor</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3658222638386961</v>
+        <v>0.3193185120827722</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1407740870486252</v>
+        <v>0.1575583019465987</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1955191892594998</v>
+        <v>0.1948033222651731</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1917355043014051</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>0.02339305949145731</v>
+        <v>0.1151305568797893</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>-0.001824817518248034</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.04579190589553284</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>0.001469723691945868</v>
+        <v>-0.03117251151257527</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>-0.006132182602770819</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4188,40 +4188,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IAU</t>
+          <t>IVV</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D67" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gold Bullion</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.4564195298372515</v>
+        <v>0.3981772535345818</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1752517145775574</v>
+        <v>0.1651142350430475</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1933459798628339</v>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>-0.1466412375503283</v>
+        <v>0.1947046323259263</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0.1382384571306829</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.01704760702108854</v>
+        <v>0.005777748396906146</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.01516263145023222</v>
+        <v>-0.02476796061740416</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.01431893281116126</v>
+        <v>-0.004918375889493509</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4235,45 +4235,45 @@
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
-      <c r="A68" s="15" t="n">
+      <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr"/>
-      <c r="D68" s="13" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="inlineStr">
-        <is>
-          <t>Gold Bullion</t>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.4531868457070987</v>
+        <v>0.4016911179676794</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1734974309953399</v>
+        <v>0.1681754488464464</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1917791850878241</v>
-      </c>
-      <c r="I68" s="5" t="n">
-        <v>-0.1475566357087058</v>
+        <v>0.1945571140665079</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>0.1412594672587981</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.0162984425932633</v>
+        <v>0.008722917717588041</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.01533988369761385</v>
+        <v>-0.02208489230812349</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>-0.01487072748702256</v>
+        <v>-0.002073502073501987</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4287,45 +4287,45 @@
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
-      <c r="A69" t="n">
+      <c r="A69" s="15" t="n">
         <v>68</v>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>RSP</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr"/>
       <c r="D69" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Equal Weight</t>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.2890755065053814</v>
+        <v>0.4002874464692965</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1484057038770483</v>
+        <v>0.1675538929113474</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1896395629251431</v>
+        <v>0.1939916870484035</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1201258778572365</v>
+        <v>0.1407326111508613</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.01980953379932027</v>
+        <v>0.008314140394689806</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.03466080007183581</v>
-      </c>
-      <c r="L69" s="3" t="n">
-        <v>0.0006515567552471957</v>
+        <v>-0.02214236030605155</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>-0.002273683103774626</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>XHE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4352,36 +4352,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D70" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.4118771712458007</v>
+        <v>0.1232527893724016</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1689214918418633</v>
+        <v>0.1289592232231322</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1844132968184888</v>
+        <v>0.1823291073464774</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1688084791648976</v>
+        <v>0.1296572280178838</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.04155157252844432</v>
+        <v>0.1080521378974295</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.01307972902553423</v>
+        <v>-0.0451396178878859</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.004127777047456371</v>
+        <v>-0.0051405446789895</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4415,25 +4415,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.640039410933225</v>
+        <v>0.6210235439400584</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.3115939570219639</v>
+        <v>0.3142072721817388</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1742451730814349</v>
+        <v>0.1805944597597668</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.07295278593470123</v>
+        <v>0.04378775101031862</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.08487437854606683</v>
+        <v>0.09035796766743664</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.1169677228309149</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>-0.01230688661953383</v>
+        <v>0.1131741821396994</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>0.001325556733828392</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4452,10 +4452,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MGK</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>OEF</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D72" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -4463,29 +4467,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.4365660114362195</v>
+        <v>0.4258292884868091</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1455793013993303</v>
+        <v>0.1618261480846455</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.165138907817598</v>
+        <v>0.1776500607509988</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1841002816883057</v>
+        <v>0.1531169983137477</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.03245088372155447</v>
+        <v>0.01708664600458154</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.01678736010533244</v>
+        <v>-0.01343685462578093</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.003225806451612967</v>
+        <v>-0.003669676329267624</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4504,44 +4508,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>XHE</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>MGK</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.1086753077720002</v>
+        <v>0.4624976395501155</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1123038705559964</v>
+        <v>0.1367963127375591</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1596281848561474</v>
+        <v>0.1534522032384673</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1518014613252709</v>
+        <v>0.1674456454707312</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.1166340986809968</v>
+        <v>0.002342130764978689</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.04080990348300451</v>
-      </c>
-      <c r="L73" s="3" t="n">
-        <v>0.01577602488612384</v>
+        <v>-0.01444003527336868</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>-0.002231893761856951</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4575,34 +4575,34 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3523277235157314</v>
+        <v>0.3499104252055334</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1416514441173784</v>
+        <v>0.1382217363168823</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1556324129851134</v>
+        <v>0.1533801174984455</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.1047916481167397</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>0.002197237262463014</v>
+        <v>0.0794348155317901</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>-0.02382473778249961</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.01209811070599942</v>
+        <v>-0.01314257195142243</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.01226180613090311</v>
+        <v>-0.004864955544371719</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4612,10 +4612,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SCHG</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>SPGP</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -4623,29 +4627,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3947429936295834</v>
+        <v>0.2883311154372921</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1301838568510387</v>
+        <v>0.09728040929442106</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1523066046872716</v>
+        <v>0.1526272617514979</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.181198782323692</v>
+        <v>0.1311769763254778</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.0558448276385064</v>
+        <v>0.01173969225282812</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.01919866444073448</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>0.002559726962457542</v>
+        <v>-0.048017997052207</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>-0.005429937596239554</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4654,7 +4658,7 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4668,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VUG</t>
+          <t>SCHG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -4679,25 +4683,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.4056846360026141</v>
+        <v>0.4190112957158045</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1247188392065075</v>
+        <v>0.1223944865800395</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1506216103294939</v>
+        <v>0.1434813172416627</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1714335424871811</v>
+        <v>0.1631775087477616</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.0297557200534968</v>
+        <v>0.0276508086253755</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.02251198038560132</v>
+        <v>-0.01844090528080455</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.003521926834810341</v>
+        <v>-0.003404255319148897</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4716,14 +4720,10 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SPGP</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>VUG</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -4731,38 +4731,38 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2750957292391709</v>
+        <v>0.4309700037894306</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.09261985744239154</v>
+        <v>0.1174044689097726</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1424735716607293</v>
+        <v>0.1416847581472906</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1480864453032833</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>0.02748757619887421</v>
+        <v>0.1541390761058821</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>-0.001517426704891189</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.04363664548132085</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>0.006361634450697373</v>
+        <v>-0.02126706962167013</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>-0.003078326302587975</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4772,49 +4772,53 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IGF</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>IAK</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2590202834625599</v>
+        <v>0.1291711591662315</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.07269316034794193</v>
+        <v>0.1116384144321763</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1158445652838507</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>-0.03335162080024456</v>
-      </c>
-      <c r="J78" s="5" t="n">
-        <v>-0.04484226633664434</v>
+        <v>0.1200919384962993</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0.1184822201879701</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>0.07132276699748186</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.03867151956323922</v>
+        <v>-0.007547169811320753</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.01030444964871191</v>
+        <v>-0.006933955787450152</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4824,53 +4828,49 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IAK</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D79" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>BOTZ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Robotics &amp; AI</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1442127743192039</v>
+        <v>0.1748840230427899</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1158108930931669</v>
+        <v>0.02430259531063639</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1143554209684401</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>0.1327425245767495</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>0.07755812386586802</v>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>0.001306111225682249</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>0.01138730731842785</v>
+        <v>0.114039767925747</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>-0.01900670961961048</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>-0.09235677204421144</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>-0.08055113937466873</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>-0.001726121979286344</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4880,40 +4880,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>IGF</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1442234125195392</v>
+        <v>0.2602925440726733</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.02097487375710227</v>
+        <v>0.07003169860384273</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.1108535594215652</v>
+        <v>0.1120367266587625</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.001510652410924629</v>
+        <v>-0.0435289502318269</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-0.06310927491579221</v>
+        <v>-0.04831207801950499</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.08090957165520896</v>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v>-0.0147392290249434</v>
+        <v>-0.03777305825242716</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.0006310143555765535</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4932,40 +4932,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VONG</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>U.S. Equity REITs</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.3279268295268538</v>
+        <v>0.1244415371812848</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.06276587203645745</v>
+        <v>0.04980843408799962</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.101594590700717</v>
+        <v>0.1061041315662792</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.1091873564340331</v>
+        <v>0.02914349220145218</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>-0.001848943866336716</v>
+        <v>-0.03264411123290578</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.03524773904305478</v>
+        <v>-0.05089547708185771</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.008657664813343957</v>
+        <v>-0.005618573094455681</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -4984,49 +4984,53 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IWF</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>EDEN</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Russell 1000 Growth</t>
+          <t>Denmark Equity</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.3259196842899255</v>
+        <v>0.09370043758648761</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.06148047065526385</v>
+        <v>0.0789838175331905</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.09999699771186243</v>
+        <v>0.1043526691782559</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1086391457006339</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>-0.001999932073707078</v>
+        <v>0.1274373779221336</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0.04711848778238825</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.03501512016552599</v>
+        <v>-0.02297169405489119</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-0.008260407295329952</v>
+        <v>-0.008988567937865399</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N82" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5051,25 +5055,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.2440963089832584</v>
+        <v>0.24980099164709</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.07185199506442697</v>
+        <v>0.07419730102685196</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.09840012761502126</v>
+        <v>0.1028054491143735</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1794977952212815</v>
+        <v>0.1671497471498877</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.07039952649449543</v>
+        <v>0.0643011905658224</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.02416981925178663</v>
+        <v>-0.02594124658206542</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.002792096219931373</v>
+        <v>-0.002584535860434944</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
@@ -5088,40 +5092,40 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>U.S. Equity REITs</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1084750678577369</v>
+        <v>0.09639023026426918</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05087142764483388</v>
+        <v>0.0698317787232785</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.09821801481212455</v>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>0.0436055893151055</v>
+        <v>0.1015646194269473</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>-0.003718297771432511</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>-0.03399225287864394</v>
+        <v>-0.01508970969592727</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.04311219314262527</v>
+        <v>-0.0288070623765827</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.004957805907172985</v>
+        <v>-0.009594882729211163</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
@@ -5140,49 +5144,49 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1018726607257185</v>
+        <v>0.2267225592014359</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.07657716063315956</v>
+        <v>0.07365627868656088</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.09672631857914848</v>
+        <v>0.09781732011973232</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.008782480165939743</v>
-      </c>
-      <c r="J85" s="5" t="n">
-        <v>-0.00948777852571292</v>
+        <v>0.1637456369929713</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0.0657067000067515</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.01837209302325582</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>0.01247301511153753</v>
+        <v>-0.0220082530949105</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>-0.002630194634402949</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5192,53 +5196,49 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EDEN</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>VONG</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.09987139660309685</v>
+        <v>0.3553436244148844</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.08606859210408024</v>
+        <v>0.05814843206205356</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.09535690016117071</v>
+        <v>0.09454853448805167</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.1590411915485337</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>0.05042670408354932</v>
+        <v>0.09538442065521102</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>-0.02545546136584598</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.008479709267110724</v>
+        <v>-0.03325581395348842</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.005467800729040073</v>
+        <v>-0.0008012178511337398</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N86" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5248,49 +5248,49 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>IWF</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Russell 1000 Growth</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.2232508183621185</v>
+        <v>0.3519957491731682</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.07190505090930044</v>
+        <v>0.05579287610477834</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.09502346599992717</v>
+        <v>0.09313519086990896</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.1765995958309858</v>
-      </c>
-      <c r="J87" s="3" t="n">
-        <v>0.07292413779603168</v>
+        <v>0.09318374494394255</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>-0.02693792216146662</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.02111225540679706</v>
+        <v>-0.03416074706680505</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>-0.003842794759825297</v>
+        <v>-0.002061685634174526</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EUO</t>
+          <t>VOT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5308,45 +5308,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D88" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D88" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2x Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>-0.04536862003780706</v>
+          <t>Mid Growth</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.2383445789466412</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.08369098712446355</v>
+        <v>0.005955343832266813</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.0829756795422032</v>
+        <v>0.08441502598767059</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.001984126984126977</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>0.01711983887210478</v>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>0.0006605019815060231</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>0.00899100899100902</v>
+        <v>0.09556359238051759</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>-0.045159521228336</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>-0.07235207948538303</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>-0.005971677188193136</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N88" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VOT</t>
+          <t>EUO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5364,153 +5364,153 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D89" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D89" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mid Growth</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>0.2205056281921831</v>
+          <t>2x Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>-0.05552089831565821</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.003562654499147389</v>
+        <v>0.08220157255182281</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0.07338910911521168</v>
+        <v>0.07612580414581838</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.1170520616293511</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>-0.01252871682010859</v>
-      </c>
-      <c r="K89" s="5" t="n">
-        <v>-0.0650523226135783</v>
+        <v>0.01576652130157674</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0.01884253028263805</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>0.00564596479574897</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.006576494118444631</v>
+        <v>-0.0006600660066006236</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.1224067089001413</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.001438149992964988</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.06539554444629725</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>-0.1068766489178258</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>-0.06312123396805158</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>-0.0600315955766193</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>-0.004065040650406582</v>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N89" s="7" t="inlineStr">
+      <c r="N90" s="7" t="inlineStr">
         <is>
           <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="21" customHeight="1">
-      <c r="A90" s="15" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="16" t="inlineStr">
+    <row r="91" ht="21" customHeight="1">
+      <c r="A91" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="16" t="inlineStr">
         <is>
           <t>UUP</t>
         </is>
       </c>
-      <c r="C90" s="15" t="inlineStr">
+      <c r="C91" s="15" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D90" s="21" t="inlineStr">
+      <c r="D91" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E90" s="15" t="inlineStr">
+      <c r="E91" s="15" t="inlineStr">
         <is>
           <t>US Dollar Index Bullish</t>
         </is>
       </c>
-      <c r="F90" s="3" t="n">
-        <v>0.02867498034109706</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0.06515814863787495</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>0.06553626654651445</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>0.01003944065973461</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>0.007871198568873083</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>-0.0003548616039743546</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>0.003562522265764256</v>
-      </c>
-      <c r="M90" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="N90" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="21" customHeight="1">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>XLU</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
       <c r="F91" s="3" t="n">
-        <v>0.1296162501621017</v>
+        <v>0.02578316635720967</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.01048937492380064</v>
+        <v>0.06435777074081095</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.06413084819809134</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>-0.09750242472458248</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>-0.05486093404897052</v>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>-0.05040871934604907</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>-0.01344656758669494</v>
+        <v>0.06133724496361093</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0.01658853227551393</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0.00786557025384349</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>0.00284596229099976</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0.0007099751508696794</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N91" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5539,34 +5539,34 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.01576305319130755</v>
+        <v>0.01465204891993421</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.04402163446054064</v>
+        <v>0.04362000916011111</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.04718773494412076</v>
+        <v>0.0428293879410504</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.003041825095057016</v>
+        <v>0.008403361344537785</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.002660585328772447</v>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>-0.003023431594860182</v>
+        <v>0.002658564375237482</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>0.0007581501137225999</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.003805175038051667</v>
+        <v>0.0007581501137225999</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5591,25 +5591,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.08635565542062529</v>
+        <v>0.09188684533728142</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02800994826268099</v>
+        <v>0.02850179262403141</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03881117741771867</v>
+        <v>0.03879525088789815</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.02184319866620799</v>
+        <v>0.01810901187204195</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.002858152010351778</v>
+        <v>-0.00461125225800274</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.01039768284154152</v>
+        <v>-0.009909034773761705</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.0008905852417302462</v>
+        <v>-0.0005093594804533863</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5623,54 +5623,58 @@
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
-      <c r="A94" s="15" t="n">
+      <c r="A94" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="16" t="inlineStr">
-        <is>
-          <t>SHY</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>XRT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="inlineStr">
-        <is>
-          <t>1-3 Year Treasury</t>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.04299871610024231</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>0.01655604030515789</v>
+        <v>0.2809500210640206</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.01683351198639704</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.02212469134920636</v>
+        <v>0.03850681758472851</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.003094496163655647</v>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>1.786292805849854e-05</v>
+        <v>0.05550437646814066</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>-0.03486162187819075</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.005448113220607009</v>
+        <v>-0.0532883642495785</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>-0.000368686248003014</v>
+        <v>-0.01531805425631438</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5680,44 +5684,40 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>XRT</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D95" s="23" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Russell Midcap Growth</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.2718582638270688</v>
+        <v>0.1894584315122145</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.02215149204553757</v>
+        <v>-0.05414562521253796</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.02095525345245508</v>
+        <v>0.02454801153048258</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.07393364920684364</v>
+        <v>0.03640526658293974</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-0.02308756907211573</v>
+        <v>-0.04897159647404503</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.04222197334527955</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>0.008609505837952502</v>
+        <v>-0.07680814940577252</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>-0.007519894867489274</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -5726,63 +5726,59 @@
       </c>
       <c r="N95" s="7" t="inlineStr">
         <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="21" customHeight="1">
+      <c r="A96" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr"/>
+      <c r="D96" s="23" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>1-3 Year Treasury</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.04236811589479195</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0.01680382778437783</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0.02187433087107848</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.002004006326828955</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>-0.0003463886641877911</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>-0.004961963456287743</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>0.0001229407425620277</v>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N96" s="7" t="inlineStr">
+        <is>
           <t>Established trend; 3m and 1m now negative; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="21" customHeight="1">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>VCR</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D96" s="23" t="inlineStr">
-        <is>
-          <t>Consumer</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>0.1737846809427237</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>-0.03220459432001155</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>0.01713159405536668</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0.04636279863765269</v>
-      </c>
-      <c r="J96" s="5" t="n">
-        <v>-0.03230796296032079</v>
-      </c>
-      <c r="K96" s="5" t="n">
-        <v>-0.04850521669341901</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v>-0.00218300412929695</v>
-      </c>
-      <c r="M96" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N96" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5792,40 +5788,44 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IWP</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>VCR</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Russell Midcap Growth</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.1691652861327571</v>
+        <v>0.1965006817223245</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.05373650537113406</v>
+        <v>-0.04096338172826219</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.01631614729395103</v>
+        <v>0.01423590115630846</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>0.05827474079383732</v>
+        <v>0.026284065875263</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.02608112677086938</v>
+        <v>-0.05060534777774828</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.06892801305145824</v>
+        <v>-0.054424501066901</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>-0.007463768115942071</v>
+        <v>-0.007143233697084694</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -5863,25 +5863,25 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03424162522862995</v>
+        <v>0.03156173402345575</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.01044374858362174</v>
+        <v>-0.01023801529441204</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0.002087014758827221</v>
+        <v>0.001841388303224667</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.01148231514750964</v>
+        <v>-0.01571502216979437</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.01799895107901017</v>
+        <v>-0.02045303422661027</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.01250466592011945</v>
+        <v>-0.0120572016076268</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>-0.0001889644746788655</v>
+        <v>-0.001134001134001084</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="22" t="inlineStr">
+      <c r="D99" s="23" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -5915,25 +5915,25 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.02070672485693548</v>
+        <v>0.01516211328349337</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.02807300640362997</v>
+        <v>-0.02666045228201785</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.006310812295014956</v>
+        <v>-0.006218997628379963</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.02926216209018406</v>
+        <v>-0.03499093123777308</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.02450519647604732</v>
+        <v>-0.0269331442547831</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.02190040344393485</v>
+        <v>-0.02056937555140936</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.0008790242830457595</v>
+        <v>-0.001429671175629754</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5952,40 +5952,40 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LQD</t>
+          <t>FXE</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D100" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Investment Grade Corporate Bonds</t>
+          <t>Euro Currency</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.03762838960808113</v>
+        <v>0.07721983515743513</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.02687755324813323</v>
+        <v>-0.008527744264326342</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.01004075567050999</v>
-      </c>
-      <c r="I100" s="5" t="n">
-        <v>-0.01253968795020988</v>
+        <v>-0.007343049622224318</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>0.007812857006041174</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>-0.03163937157174768</v>
+        <v>-0.000686182914871436</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.01700756639635903</v>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v>-0.000191717791411028</v>
+        <v>-0.001193458265366654</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>0.0002815579540123014</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6004,49 +6004,49 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FXE</t>
+          <t>LQD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D101" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Euro Currency</t>
+          <t>Investment Grade Corporate Bonds</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.07263239288871293</v>
+        <v>0.03327093582864848</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.008532236543972282</v>
+        <v>-0.02616820162105649</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01069424160794796</v>
-      </c>
-      <c r="I101" s="3" t="n">
-        <v>0.01508148681653965</v>
+        <v>-0.01227545458995671</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>-0.01830038091157193</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>-0.0004063416003677878</v>
-      </c>
-      <c r="K101" s="3" t="n">
-        <v>0.002185376002955541</v>
+        <v>-0.03248318992460952</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>-0.01406540628726838</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>-0.004298663676292058</v>
+        <v>-0.001054650047938588</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>REBOUND</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N101" s="7" t="inlineStr">
         <is>
-          <t>Weak long trend; 1m rebound not yet confirmed by 3m; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr"/>
-      <c r="D102" s="22" t="inlineStr">
+      <c r="D102" s="23" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -6071,25 +6071,25 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.0368641949997347</v>
+        <v>-0.04950479989813084</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.06311830695917853</v>
+        <v>-0.06324178393108493</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.04755110811657592</v>
+        <v>-0.04979175648478162</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.04294248111099697</v>
+        <v>-0.05451973318800496</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-0.0454864937248517</v>
+        <v>-0.04917806278068193</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>-0.01634439283331957</v>
-      </c>
-      <c r="L102" s="3" t="n">
-        <v>0.0007419314949919098</v>
+        <v>-0.01415482083858377</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>-0.004448288644507747</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6127,25 +6127,25 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.006156371844859398</v>
+        <v>-0.01566687280972989</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.0903456048084148</v>
+        <v>-0.1015992474129821</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>-0.06123215627347867</v>
-      </c>
-      <c r="I103" s="3" t="n">
-        <v>0.007698709945900939</v>
-      </c>
-      <c r="J103" s="3" t="n">
-        <v>0.002069108214359572</v>
+        <v>-0.06340545625587957</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>-0.01668039538714994</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>-0.03065367438083633</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>-0.03101240496198476</v>
+        <v>-0.04077942948975499</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>-0.002882437718756403</v>
+        <v>-0.01404088374974188</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6183,25 +6183,25 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.04395507960823308</v>
+        <v>-0.03531919964195296</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.1484796154799024</v>
+        <v>-0.1458881189666406</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>-0.1103924417313996</v>
+        <v>-0.1042912030459175</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.1547152409499655</v>
+        <v>0.1373311970702678</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.1439013248058474</v>
+        <v>0.1209113467177982</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>-0.04281345565749239</v>
-      </c>
-      <c r="L104" s="3" t="n">
-        <v>0.01314990896216872</v>
+        <v>-0.04644022260602576</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>-0.007787539936102261</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="N104" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -210,6 +210,9 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -687,25 +690,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.30049909090986</v>
+        <v>2.285130708046156</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.316978834405198</v>
+        <v>1.306190097055653</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.336346567719441</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.3392186326070623</v>
+        <v>0.3329827197595792</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1570111137384724</v>
+        <v>-0.1609363915819343</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.008289751863803319</v>
+        <v>-0.01290753310337167</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.01151969129497221</v>
+        <v>0.006809669731018042</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -743,25 +746,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.872529739391047</v>
+        <v>1.863349884032141</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.14590592186771</v>
+        <v>1.139048322030492</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>1.284108740004862</v>
+        <v>1.284108905985093</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4922770101315888</v>
+        <v>0.4875080822696503</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.2070875499822753</v>
+        <v>-0.2096214912339964</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.0605062341019974</v>
+        <v>-0.06350861098369542</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.01982618142313974</v>
+        <v>0.01656708310700727</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -799,25 +802,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.61465878354213</v>
+        <v>1.597376433577898</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9380428960509377</v>
+        <v>0.9252328361738811</v>
       </c>
       <c r="H4" s="10" t="n">
         <v>1.279147978823718</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3713331045046533</v>
+        <v>0.3622688783124004</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.2589881544864966</v>
+        <v>-0.2638860884434686</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.1496634206914579</v>
+        <v>-0.1552839683680804</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.0107986326911127</v>
+        <v>0.004117464263517778</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -855,25 +858,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.963420008814455</v>
+        <v>1.946672542970471</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.030193236714976</v>
+        <v>1.018719806763285</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>1.203200483091788</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.4800792427911071</v>
+        <v>0.471714725952014</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.172736220472441</v>
+        <v>-0.1774114173228347</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.07852542140605734</v>
+        <v>-0.08373304097574341</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.01479022034409883</v>
+        <v>0.009055236945366696</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -907,25 +910,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.606629564617812</v>
+        <v>1.593866153657924</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9824514506925397</v>
+        <v>0.9727442213722131</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.163153055844476</v>
+        <v>1.163152926126449</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4948064733723698</v>
+        <v>0.487487125205631</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1973267563051954</v>
+        <v>-0.2012570610231522</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.08353620871334611</v>
+        <v>-0.08802369099960017</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.01415359871330923</v>
+        <v>0.009187776437475037</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -963,25 +966,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.552604146609794</v>
+        <v>1.541124307227399</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.8891851675965174</v>
+        <v>0.8806887197998163</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.076107019123945</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4509931347755709</v>
+        <v>0.4444675078513665</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1978299576933991</v>
+        <v>-0.201437648461587</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.09003478616738281</v>
+        <v>-0.09412727644771834</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.01448614121136083</v>
+        <v>0.009923577050302335</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1019,25 +1022,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.500034612763686</v>
+        <v>1.490211383812625</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8036362314644352</v>
+        <v>0.7965493169250726</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.9375953974549958</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3890637692932573</v>
+        <v>0.3836058082859464</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1544119919641478</v>
+        <v>-0.1577345078040489</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.06913681058827548</v>
+        <v>-0.07279439284134614</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.01048938134810706</v>
+        <v>0.006518928901200427</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1075,34 +1078,34 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.257954484494167</v>
+        <v>1.250999799223651</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.7835791949662092</v>
+        <v>0.7780856245505023</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.7824138921507562</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.4874357906427877</v>
+        <v>0.4828543662362905</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.007238883143743546</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.0006537779023070289</v>
+        <v>0.004136504653567741</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>-0.00242831792285414</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-0.0006529241675216069</v>
+        <v>-0.003730995242981039</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1183,25 +1186,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8004787562734055</v>
+        <v>0.7988427552610584</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.6443381728435096</v>
+        <v>0.6428439021424961</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.680093936046325</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.2445422364028342</v>
+        <v>0.2434112750040518</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.1305808273691522</v>
+        <v>0.1295534269028942</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.02128200241407785</v>
+        <v>-0.02217139952989011</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.02246192893401011</v>
+        <v>-0.02335025380710665</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -1239,25 +1242,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.6819278374830311</v>
+        <v>0.6819691279980182</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.6086103293236047</v>
+        <v>0.6086498199292247</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.663857686585934</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.09332474434334492</v>
+        <v>0.09335158493705897</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.01921409997110668</v>
+        <v>-0.01919002215159393</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.03320437661690367</v>
+        <v>-0.03318064225191641</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.01313236830323827</v>
+        <v>0.01315724021290365</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1295,25 +1298,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.182077254901352</v>
+        <v>1.166661873790738</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.633272991741072</v>
+        <v>0.6217345036326927</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.6480807181468253</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.08337929947690315</v>
+        <v>0.07572561315067983</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-0.05112335658957967</v>
+        <v>-0.05782682987400523</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.008984830805134125</v>
+        <v>-0.01598599766627773</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.008058864751226302</v>
+        <v>-0.01506657323055371</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1351,34 +1354,34 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.214246559253477</v>
+        <v>1.202788185859292</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.570530002401598</v>
+        <v>0.5624026112315594</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.5669963540667984</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.109224579761442</v>
+        <v>0.1034844143132447</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.0155375299897178</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.002255045664674826</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0.00202908353060538</v>
+        <v>0.01028218896378386</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>-0.002931559364077074</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>-0.003156352158719233</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1403,25 +1406,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.8750813272608979</v>
+        <v>0.8614183474300585</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.5033907146583201</v>
+        <v>0.4924360980699007</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.525299947835159</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.2127833925157061</v>
+        <v>-0.2185195301830101</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.09185441941074524</v>
+        <v>-0.09847171892232554</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.01436388508891928</v>
+        <v>-0.02154582763337887</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.01407459535538358</v>
+        <v>0.006685432793807067</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1459,25 +1462,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.775965631512022</v>
+        <v>0.7754584301321816</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4101582637393668</v>
+        <v>0.4097555339767682</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0.5148680020150302</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.01799721413696487</v>
+        <v>-0.0182776661677696</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.1635223987491038</v>
+        <v>-0.1637612899675104</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.06912136115911205</v>
+        <v>-0.06938721254818558</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.0008575103615835467</v>
+        <v>0.0005716735743890311</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1515,25 +1518,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.176270047039389</v>
+        <v>1.183352089688637</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.7012797948276588</v>
+        <v>0.7068162248358181</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.5110907825421778</v>
+        <v>0.511090876404922</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.3744270259679694</v>
+        <v>0.3788997019713105</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.2609114130576813</v>
+        <v>0.2650146852670956</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1258620689655172</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>-0.002482337215963248</v>
+        <v>0.1295258620689654</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0.000763796066450162</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1542,7 +1545,7 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1574,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.7597635442407662</v>
+        <v>0.7543251077832884</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.4867483103797461</v>
+        <v>0.4821536100060937</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.5002905851652479</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.09727995219973917</v>
+        <v>0.09388887882761909</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.06593740504405954</v>
+        <v>-0.06882406563354593</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.009026434558349505</v>
+        <v>-0.01208897485493232</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-0.002595717066839809</v>
+        <v>-0.005678131083711846</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1627,25 +1630,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.7517022878794402</v>
+        <v>0.7436942445048604</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.4054323819360943</v>
+        <v>0.3990073383927604</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.4991462313324342</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3707730105555855</v>
+        <v>0.3645064150266608</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.08422487769164466</v>
+        <v>-0.08841141495402616</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.06251147982611893</v>
+        <v>-0.06679728157717524</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-0.0003264346804203733</v>
+        <v>-0.004896520206306709</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1683,25 +1686,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.5923281556448163</v>
+        <v>0.584807083695293</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.520079065350147</v>
+        <v>0.5128991490308321</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0.4415951524803936</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.1427311182428161</v>
+        <v>0.1373336686443973</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.1828728428954471</v>
+        <v>0.1772856808708039</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.05444240897641395</v>
+        <v>0.04946187313945494</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.01442969653577131</v>
+        <v>0.009638156083053406</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1735,25 +1738,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.5730456087544327</v>
+        <v>0.567277374283828</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.5234623598626429</v>
+        <v>0.5178760780420519</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.4410627150358475</v>
+        <v>0.441062842993152</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1459883654802612</v>
+        <v>0.1417861163173082</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.1867148115735211</v>
+        <v>0.1823632217373461</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.05717977709578426</v>
+        <v>0.05330318203844286</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.0142569347590269</v>
+        <v>0.0105377343871067</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1791,25 +1794,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.6580066323222324</v>
+        <v>0.6551868931516165</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.3854395240179331</v>
+        <v>0.383083251475504</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.430756905274075</v>
+        <v>0.4307568195416953</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.1223010199975405</v>
+        <v>0.1203923447934629</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.02076049226192089</v>
+        <v>0.01902450503018294</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.03167371136850183</v>
+        <v>-0.03332052478454184</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-0.004458490885490107</v>
+        <v>-0.00615158869010668</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1847,25 +1850,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6686282970486948</v>
+        <v>0.6616244519337195</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.5548638716094128</v>
+        <v>0.5483373449539559</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.4192241336440927</v>
+        <v>0.41922404850307</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.1920164839087275</v>
+        <v>0.1870130770024654</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.2547940366316168</v>
+        <v>0.2495271252813374</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.09557316194803045</v>
+        <v>0.09097456922821201</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.02207060526179783</v>
+        <v>0.01778053444978545</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1899,25 +1902,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.7957705098658592</v>
+        <v>0.7907189754805113</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3719735006319762</v>
+        <v>0.3681138584284667</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.4102714896136423</v>
+        <v>0.4102713298974281</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.3352104275227572</v>
+        <v>0.3314543581567209</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-0.03503620499932436</v>
+        <v>-0.03775073663795214</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.02715646544918682</v>
+        <v>-0.02989316351770943</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.003093119166485803</v>
+        <v>0.0002713262426743412</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1955,25 +1958,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5197767622774105</v>
+        <v>0.5180433199004018</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4339850755932984</v>
+        <v>0.4323493309444255</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.4098779126562229</v>
+        <v>0.4098777596715413</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.2075246345460502</v>
+        <v>0.2061473438644452</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.171226113724807</v>
+        <v>0.1698902247778358</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.01709875920508441</v>
+        <v>0.01593866639765973</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.01441837732160312</v>
+        <v>-0.01554252199413497</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -2011,25 +2014,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.6680331221524942</v>
+        <v>0.6610552533151763</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.2454131448724162</v>
+        <v>0.2402033011373297</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.391549261641591</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.01135620313047836</v>
+        <v>0.007125472307928815</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-0.247323677581864</v>
+        <v>-0.2504722921914359</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>-0.1050168476226132</v>
+        <v>-0.1087607637588919</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.005467928496319718</v>
+        <v>0.001261829652996926</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2063,25 +2066,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.5857276278510641</v>
+        <v>0.5871468351552265</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.5502528125975523</v>
+        <v>0.55164027036539</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.3874577678379048</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.1840339102790536</v>
+        <v>0.1850936064994702</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.1878100637845501</v>
+        <v>0.1888731396172927</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.1173333333333335</v>
+        <v>0.1183333333333332</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.01116138763197605</v>
+        <v>0.01206636500754144</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -2119,25 +2122,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.5305079570069677</v>
+        <v>0.5254779039663116</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.2794136500571267</v>
+        <v>0.2752088247955109</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.3799471994939432</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.09240982713233992</v>
+        <v>0.08881959465595646</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.1751848871566442</v>
+        <v>-0.1778956628486897</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.07285318559556797</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>0.002395926924228853</v>
+        <v>-0.07590027700831026</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>-0.0008984725965858198</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -2146,7 +2149,7 @@
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2171,25 +2174,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.396799339683054</v>
+        <v>1.366296734143532</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.4251701055879027</v>
+        <v>0.4070325298381281</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3764450275603612</v>
+        <v>0.3764448661459949</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.02439975989465004</v>
+        <v>-0.03681572498658603</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.06783063560558045</v>
+        <v>0.05424090145960792</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.03539921831379123</v>
+        <v>0.02222222222222237</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.005896858582609577</v>
+        <v>-0.01854830063257196</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -2227,25 +2230,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.9688345848166877</v>
+        <v>0.9611094377095504</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.2853873436907342</v>
+        <v>0.2803439638038554</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3739417231493074</v>
+        <v>0.3739418460973216</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.006762015358798723</v>
+        <v>-0.01065919880067956</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>-0.09089797679571954</v>
+        <v>-0.0944650346475111</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>-0.06445279153150074</v>
+        <v>-0.06812361277104328</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.005264591086502679</v>
+        <v>-0.009167649995461602</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2283,25 +2286,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.7692025828993831</v>
+        <v>0.7628740858278804</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3374558262616099</v>
+        <v>0.3326718280052383</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.3718818529300072</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.3221771388311856</v>
+        <v>0.3174477915117584</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>-0.01007263270969194</v>
+        <v>-0.013613542776448</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.02509401709401704</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>0.002531289551399363</v>
+        <v>-0.02858119658119662</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>-0.001054703979749716</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2310,7 +2313,7 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2335,25 +2338,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.7600338755169549</v>
+        <v>0.7545807476159225</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.3334755964026048</v>
+        <v>0.3293440776396759</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3685376745528659</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.3207509078635586</v>
+        <v>0.3166588141111759</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>-0.009673230060119442</v>
+        <v>-0.01274156790032843</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.02562010443864227</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>0.002097843416967393</v>
+        <v>-0.02863903394255873</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>-0.001006964840144398</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2362,7 +2365,7 @@
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2391,25 +2394,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.7790718117893196</v>
+        <v>0.772207535242504</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.3341441258384972</v>
+        <v>0.3289965706218758</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3558483121265503</v>
+        <v>0.3558482023394396</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.3249944480658717</v>
+        <v>0.3198823021105641</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.01007993070047641</v>
+        <v>-0.01389927944245384</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.01600782778864973</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>0.001234567901234662</v>
+        <v>-0.01980430528375732</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>-0.002628434886499442</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2418,7 +2421,7 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2443,25 +2446,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5720786266535529</v>
+        <v>0.5653667160084477</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1396250093099527</v>
+        <v>0.1347594376383257</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.3488445911899107</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.04584956323314926</v>
+        <v>-0.04992326054382368</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.1915317941244151</v>
+        <v>-0.1949835084758763</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.1551102204408817</v>
+        <v>-0.1587174348697394</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.00591715976331364</v>
+        <v>0.001622447031876417</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2499,25 +2502,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5235976782248355</v>
+        <v>0.517325121558962</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.09025035700961848</v>
+        <v>0.08576178913810151</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.345323692915807</v>
+        <v>0.345323599845285</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.1115218761304897</v>
+        <v>-0.1151796851820588</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1494661850009392</v>
+        <v>-0.152967779698195</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.1895999730394635</v>
+        <v>-0.1929363394331548</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-0.009718733270189128</v>
+        <v>-0.01379565951488704</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2555,25 +2558,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5713639192089242</v>
+        <v>0.5652451679745836</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.3145125201513366</v>
+        <v>0.3093940643206587</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.3205800079126468</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.2773342714219709</v>
+        <v>0.272360580453602</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.1296998958616897</v>
+        <v>0.1253010644087769</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.004594562786771839</v>
+        <v>-0.00847047776353127</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.002823861630780078</v>
+        <v>-0.006706671373102657</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2611,25 +2614,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.4505271599103216</v>
+        <v>0.4458486437191516</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2002357235393644</v>
+        <v>0.196364494912286</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.3135852977402176</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.09000140627197317</v>
+        <v>0.08648572633947404</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.09036498063607545</v>
+        <v>-0.09329890857880518</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.08629022751385118</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>0.002068519715578754</v>
+        <v>-0.08923729812566306</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>-0.001163542340012813</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2638,7 +2641,7 @@
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2663,25 +2666,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4639471969072151</v>
+        <v>0.4595537201893096</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2172297074566689</v>
+        <v>0.2135766416341176</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.3023481113694551</v>
+        <v>0.3023482021148793</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1525789063123784</v>
+        <v>0.149119861761331</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.05041533532160769</v>
+        <v>-0.05326522927322364</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.06535764375876574</v>
+        <v>-0.06816269284712484</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.002693804250224363</v>
+        <v>-0.005686920083807223</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2715,25 +2718,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.3276966585867671</v>
+        <v>0.3265354078649714</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2940183697883518</v>
+        <v>0.2928866683287923</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.3023181960668779</v>
+        <v>0.3023182897785208</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1294336664522422</v>
+        <v>0.128445823595287</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.05955175487588682</v>
+        <v>0.05862503322439205</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>-0.006373117033603881</v>
+        <v>-0.007242178447276926</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.001164822364589591</v>
+        <v>-0.002038439138031478</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2771,25 +2774,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.8241670341643736</v>
+        <v>0.8121228055225862</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.1906424410608729</v>
+        <v>0.1827811161261625</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.2975166559960483</v>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>0.003354297693920483</v>
+      <c r="I40" s="5" t="n">
+        <v>-0.003270440251572304</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>-0.1116638206251391</v>
+        <v>-0.1175291409904224</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.08236827977605632</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>0.0004180602006689238</v>
+        <v>-0.08842702661247015</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>-0.006187290969899673</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2798,7 +2801,7 @@
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2823,25 +2826,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4642831902279723</v>
+        <v>0.4619767346333434</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2109883919818296</v>
+        <v>0.2090807228073148</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.2933573076725349</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1523729146634831</v>
+        <v>0.1505575824097598</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.03047787130057</v>
+        <v>-0.03200515883790389</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.06368612540561791</v>
+        <v>-0.06516110000327768</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.007814942169427908</v>
+        <v>-0.009377930603313711</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2879,25 +2882,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.1813844227428318</v>
+        <v>0.1692142745680194</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.3479622363533508</v>
+        <v>0.3340759439994534</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2890163422796628</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1146998297884214</v>
+        <v>0.1032165350003142</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.02706568848931545</v>
+        <v>-0.03708855851223636</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0.04572936132791017</v>
+        <v>0.03495657909200833</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.003352540597171383</v>
+        <v>-0.01361969617600833</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -2931,25 +2934,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.5921826667377852</v>
+        <v>0.5893144004730206</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.20794594952784</v>
+        <v>0.2057697719580143</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.283191473961427</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2351972403782541</v>
+        <v>0.2329720486986016</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.08425328795815512</v>
+        <v>-0.08590305337619053</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.05863935816319876</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>0.000901588182259383</v>
+        <v>-0.06033526841041026</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>-0.000901588182259494</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2958,7 +2961,7 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2983,25 +2986,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4481283873265185</v>
+        <v>0.4458276883278622</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.0786712094382267</v>
+        <v>0.07695759290141235</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.2762411160356404</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.07946720640353511</v>
+        <v>-0.08092959846886916</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-0.09848357203032854</v>
+        <v>-0.09991575400168495</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.1548060974646552</v>
+        <v>-0.1561488034120527</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>-0.01268625732343032</v>
+        <v>-0.01425474004705451</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3035,25 +3038,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.4407807907944996</v>
+        <v>0.4381084322327677</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2620100897326796</v>
+        <v>0.2596695155984614</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2752738742924663</v>
+        <v>0.2752739691828336</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1623785440206873</v>
+        <v>0.1602225846721337</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.03320681134017311</v>
+        <v>0.03129050813521439</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.01040073416947063</v>
+        <v>-0.01223615784643617</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>-0.001234949058351309</v>
+        <v>-0.003087372645878439</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -3091,25 +3094,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4334206595863168</v>
+        <v>0.4290673665837081</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.1633212084485638</v>
+        <v>0.1597882064350535</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.2707565878593987</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.138147624301971</v>
+        <v>0.1346910743662115</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-0.06207110857912324</v>
+        <v>-0.06491959499702205</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.08454442057373934</v>
+        <v>-0.08732465562997593</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.009299781181619338</v>
+        <v>-0.01230853391684905</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3143,25 +3146,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3531834438914816</v>
+        <v>0.3528904592985438</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2277852884171887</v>
+        <v>0.2275195915359038</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.270296789422761</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.09667110268668311</v>
+        <v>0.09643377935781783</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.01305881162752276</v>
+        <v>0.01283958228070881</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.03346580213344497</v>
+        <v>-0.03367496339677889</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.003665373005605876</v>
+        <v>-0.00388098318240615</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3195,25 +3198,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4343639555671133</v>
+        <v>0.4316540293332816</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.1474711578368721</v>
+        <v>0.1453032546480626</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.2701744783234903</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.04622769656045</v>
+        <v>0.04425107140163553</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.08848514472862234</v>
+        <v>-0.09020725856816769</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.0966035159583547</v>
+        <v>-0.09831029185867901</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.001697472651829512</v>
+        <v>-0.003583553376084625</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3247,25 +3250,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4724897126474985</v>
+        <v>0.4711233442163381</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2526710835898267</v>
+        <v>0.2515086916161895</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2684279525657993</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1463144618410037</v>
+        <v>0.1452507614433785</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.03115032957686581</v>
+        <v>0.03019349351477785</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.01242236024844723</v>
+        <v>-0.01333876387333255</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.006046320967411423</v>
+        <v>-0.006968641114982521</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3299,25 +3302,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4560480938450344</v>
+        <v>0.4536073335282</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.2311899069765964</v>
+        <v>0.229125883662302</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0.2655902955481695</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1056791298760524</v>
+        <v>0.1038255185937789</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.005984595110815949</v>
+        <v>-0.007651008195290743</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.02718129926610491</v>
+        <v>-0.0288121772220713</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>-0.001952035694366971</v>
+        <v>-0.003625209146681629</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3355,25 +3358,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.546059684426758</v>
+        <v>0.5436424800378161</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1941306798821245</v>
+        <v>0.1922636815610248</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2601137490532559</v>
+        <v>0.2601138254355535</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.2205277816154014</v>
+        <v>0.2186194381112123</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.0990018883193956</v>
+        <v>-0.1004106345352637</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.0523627880583839</v>
+        <v>-0.05384445635383495</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.003003003003003046</v>
+        <v>0.001434768101434836</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3407,34 +3410,34 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.3523870876287789</v>
+        <v>0.3491209162280557</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2562105894620479</v>
+        <v>0.2531766101253548</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2540397762870876</v>
+        <v>0.2540396909136367</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.1338682367832629</v>
+        <v>0.1311298137082073</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.1083481890645546</v>
-      </c>
-      <c r="K52" s="3" t="n">
-        <v>0.001731056076536452</v>
+        <v>0.10567139985954</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>-0.0006882404078080162</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>-0.002409297052154202</v>
+        <v>-0.004818594104308405</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3459,25 +3462,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.5260365501284441</v>
+        <v>0.5215402111086054</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2146984766172428</v>
+        <v>0.2111194691830547</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.2526942183313561</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1838745711195309</v>
+        <v>0.1803863837440245</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.04578838319526723</v>
+        <v>-0.04859988789052583</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>-0.03033121823195239</v>
+        <v>-0.03318826617055914</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.0004794192178617651</v>
+        <v>-0.003424422984727116</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3511,25 +3514,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.5248051745528219</v>
+        <v>0.5202878706569893</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.21410014298452</v>
+        <v>0.210503316716244</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.2521579904517077</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.1834567619569536</v>
+        <v>0.1799507180829185</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.04619760576167742</v>
+        <v>-0.04902328824443192</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>-0.03039380633865429</v>
+        <v>-0.03326630828785215</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>-0.0004653261513295481</v>
+        <v>-0.003426492568882278</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3563,25 +3566,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3395060331617559</v>
+        <v>0.3367362525004258</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1310958245437939</v>
+        <v>0.128756939803566</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2462969352848288</v>
+        <v>0.2462968082095851</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.02470949729411087</v>
+        <v>0.02259070291794885</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>-0.05033319556715332</v>
+        <v>-0.05229682398064373</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.0924347219988203</v>
+        <v>-0.09431129698139518</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>-0.003883952215618214</v>
+        <v>-0.005943623845112822</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3619,25 +3622,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2262754895403778</v>
+        <v>0.2256487195482795</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2395184749519443</v>
+        <v>0.2388848613955201</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2460914390089983</v>
+        <v>0.2460913637214592</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1302141086603497</v>
+        <v>0.1296364372529077</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.09978804965466104</v>
+        <v>0.09922592951683584</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.005274864950746694</v>
+        <v>-0.00578328566889097</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.006285315218081289</v>
+        <v>-0.006793219478128276</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3675,25 +3678,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4074979440701867</v>
+        <v>0.4043182607121536</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.0722939448455342</v>
+        <v>0.06987159406651555</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0.2454247380237193</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>-0.09008044039483554</v>
+        <v>-0.09213598156864244</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.09286321546451215</v>
+        <v>-0.09491247024885441</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.1390134529147982</v>
+        <v>-0.1409584526446593</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.008029878618113884</v>
+        <v>-0.0102707749766574</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3727,25 +3730,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1896783600244283</v>
+        <v>0.1908912413468948</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2283116607461635</v>
+        <v>0.2295640627273718</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0.2330265858518887</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1135273659540397</v>
+        <v>0.1146627324280527</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.09533209871717552</v>
+        <v>0.09644891306841363</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.00382386329688722</v>
+        <v>-0.0028081496086515</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.006080476900149123</v>
+        <v>-0.005067064083457473</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3779,25 +3782,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3710954401164008</v>
+        <v>0.365404476042462</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1355458647508767</v>
+        <v>0.1308326592642142</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>0.2317962539392182</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1033800140883068</v>
+        <v>0.09880031643125475</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>-0.05368459042477713</v>
+        <v>-0.05761237451432744</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.07813823826833199</v>
+        <v>-0.08196452485719752</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.003603922958761552</v>
+        <v>-0.007739572255701321</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -3835,25 +3838,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3411857363130528</v>
+        <v>0.3377186324496659</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.0958694830280733</v>
+        <v>0.09303662313997374</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.2311758171570499</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.02414652436456155</v>
+        <v>0.02149907076416335</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.1406059963134003</v>
+        <v>-0.1428275590440187</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.1099000908265214</v>
+        <v>-0.1122010293672419</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>-0.003727549983056688</v>
+        <v>-0.006302948153168453</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3887,25 +3890,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.524484791185545</v>
+        <v>0.5198954732304686</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1873412808018635</v>
+        <v>0.1837668270844957</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2143210690818824</v>
+        <v>0.2143208554450089</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1721601038881431</v>
+        <v>0.1686315582267979</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>-0.01926922196723846</v>
+        <v>-0.02222150921903654</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.02221800227876936</v>
+        <v>-0.02516141283706785</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.002904725019364784</v>
+        <v>-0.005906274206041839</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -3943,25 +3946,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3869584999548787</v>
+        <v>0.3849338499906381</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1501856083311661</v>
+        <v>0.1485065788182549</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.2034131758991924</v>
+        <v>0.2034132529810573</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1910281052718821</v>
+        <v>0.1892893781109013</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.04203155777468082</v>
+        <v>0.04051034382172514</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.04423050090693459</v>
+        <v>-0.04562578484721636</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.00528324038743766</v>
+        <v>0.003815673613149384</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -3995,25 +3998,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.2963471071801052</v>
+        <v>0.2941073293157268</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.152105159094766</v>
+        <v>0.1501145968306283</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0.1984798799511605</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1074052066662872</v>
+        <v>0.1054918752328688</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.009861694507613539</v>
+        <v>0.00811689494203871</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.03869461776720384</v>
+        <v>-0.04035552363424166</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.003999813962141219</v>
+        <v>-0.005720664155155486</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -4047,25 +4050,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.4350453172205437</v>
+        <v>0.4311355962324506</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1757425742574257</v>
+        <v>0.1725393127548047</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.198019801980198</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>-0.1439626841937878</v>
+        <v>-0.1462949220820523</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>-0.006276150627615107</v>
+        <v>-0.008983509721880445</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>-0.01859504132231404</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>0.002607400049664754</v>
+        <v>-0.0212688381137579</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>-0.0001241619071269406</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4074,7 +4077,7 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4099,25 +4102,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.43125068149602</v>
+        <v>0.4277250754188928</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1739908174825591</v>
+        <v>0.1710989207560669</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.1969471110846104</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>-0.1447559889668354</v>
+        <v>-0.1468627152878831</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>-0.006985247761946867</v>
+        <v>-0.009431345353675513</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.01917903756102435</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0.002392831687200836</v>
+        <v>-0.02159509813689353</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>-7.636696874036009e-05</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4126,7 +4129,7 @@
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4151,25 +4154,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3193185120827722</v>
+        <v>0.316484388668272</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1575583019465987</v>
+        <v>0.1550717736014666</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0.1948033222651731</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1151305568797893</v>
+        <v>0.1127351667438958</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>-0.001824817518248034</v>
+        <v>-0.003968978102189658</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.03117251151257527</v>
+        <v>-0.03325363088912503</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>-0.006132182602770819</v>
+        <v>-0.008267090620031725</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4203,25 +4206,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3981772535345818</v>
+        <v>0.3950527118753526</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1651142350430475</v>
+        <v>0.1625104164644668</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1947046323259263</v>
+        <v>0.1947045206436493</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1382384571306829</v>
+        <v>0.1356948071975639</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.005777748396906146</v>
+        <v>0.003530111720764229</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.02476796061740416</v>
+        <v>-0.02694733603404953</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.004918375889493509</v>
+        <v>-0.00714210966931772</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4255,25 +4258,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.4016911179676794</v>
+        <v>0.3986380686027575</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1681754488464464</v>
+        <v>0.1656309051888369</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1945571140665079</v>
+        <v>0.1945569920178736</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1412594672587981</v>
+        <v>0.1387737825604742</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.008722917717588041</v>
+        <v>0.006525799662231213</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.02208489230812349</v>
+        <v>-0.02421490730230791</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>-0.002073502073501987</v>
+        <v>-0.004247104247104172</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4307,25 +4310,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.4002874464692965</v>
+        <v>0.3972439448073399</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1675538929113474</v>
+        <v>0.1650163431489831</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1939916870484035</v>
+        <v>0.1939917991290847</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1407326111508613</v>
+        <v>0.1382532476411478</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.008314140394689806</v>
+        <v>0.006122586246430251</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.02214236030605155</v>
+        <v>-0.02426771775253111</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.002273683103774626</v>
+        <v>-0.004442224792345684</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4363,7 +4366,7 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.1232527893724016</v>
+        <v>0.1232528951989564</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>0.1289592232231322</v>
@@ -4415,25 +4418,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.6210235439400584</v>
+        <v>0.6163025328245324</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.3142072721817388</v>
+        <v>0.3103798218259008</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0.1805944597597668</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.04378775101031862</v>
+        <v>0.04074786081674842</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.09035796766743664</v>
+        <v>0.08718244803695141</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.1131741821396994</v>
-      </c>
-      <c r="L71" s="3" t="n">
-        <v>0.001325556733828392</v>
+        <v>0.1099322133804892</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>-0.001590668080593938</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4442,7 +4445,7 @@
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4471,25 +4474,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.4258292884868091</v>
+        <v>0.4223157895883989</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1618261480846455</v>
+        <v>0.1589631754955927</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1776500607509988</v>
+        <v>0.1776501713922569</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1531169983137477</v>
+        <v>0.1502754860059314</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.01708664600458154</v>
+        <v>0.01458024524996615</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.01343685462578093</v>
+        <v>-0.0158680364938697</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.003669676329267624</v>
+        <v>-0.00612492739848991</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4523,34 +4526,34 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.4624976395501155</v>
+        <v>0.45824494841748</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1367963127375591</v>
+        <v>0.1334905634778369</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0.1534522032384673</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1674456454707312</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>0.002342130764978689</v>
+        <v>0.1640507694185851</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>-0.0005726321698035219</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.01444003527336868</v>
+        <v>-0.01730599647266307</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.002231893761856951</v>
+        <v>-0.00513335565227091</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4575,25 +4578,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3499104252055334</v>
+        <v>0.3476349008819457</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1382217363168823</v>
+        <v>0.1363029538888361</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0.1533801174984455</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.0794348155317901</v>
+        <v>0.07761513445368529</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>-0.02382473778249961</v>
+        <v>-0.02547034678826077</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.01314257195142243</v>
+        <v>-0.01480618865413408</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.004864955544371719</v>
+        <v>-0.006542526421741357</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -4631,25 +4634,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.2883311154372921</v>
+        <v>0.283606851920684</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.09728040929442106</v>
+        <v>0.09325673477947127</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1526272617514979</v>
+        <v>0.1526271831227746</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1311769763254778</v>
+        <v>0.1270290816111159</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.01173969225282812</v>
+        <v>0.008029760200075842</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.048017997052207</v>
+        <v>-0.0515088045923513</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-0.005429937596239554</v>
+        <v>-0.009076910608639355</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4683,25 +4686,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.4190112957158045</v>
+        <v>0.4145681583992569</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1223944865800395</v>
+        <v>0.1188800829868701</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1434813172416627</v>
+        <v>0.1434813869246168</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1631775087477616</v>
+        <v>0.1595353360759069</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.0276508086253755</v>
+        <v>0.02443300079876609</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.01844090528080455</v>
+        <v>-0.02151438949427198</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.003404255319148897</v>
+        <v>-0.006524822695035404</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4735,25 +4738,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.4309700037894306</v>
+        <v>0.4270423642547845</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1174044689097726</v>
+        <v>0.1143375936573414</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1416847581472906</v>
+        <v>0.141684869464987</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1541390761058821</v>
+        <v>0.1509712652839994</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.001517426704891189</v>
+        <v>-0.004258001014026846</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.02126706962167013</v>
+        <v>-0.02395343631072311</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.003078326302587975</v>
+        <v>-0.005814616349332891</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -4791,25 +4794,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1291711591662315</v>
+        <v>0.1283906705800659</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1116384144321763</v>
+        <v>0.1108699122445287</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0.1200919384962993</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1184822201879701</v>
+        <v>0.1177089867139376</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.07132276699748186</v>
+        <v>0.07058213597985485</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.007547169811320753</v>
+        <v>-0.008233276157804337</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.006933955787450152</v>
+        <v>-0.00762048606343535</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -4843,25 +4846,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1748840230427899</v>
+        <v>0.171159606831415</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.02430259531063639</v>
+        <v>0.021055526564695</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0.114039767925747</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>-0.01900670961961048</v>
+        <v>-0.02211648662081633</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>-0.09235677204421144</v>
+        <v>-0.09523402723369667</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.08055113937466873</v>
+        <v>-0.08346581875993642</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>-0.001726121979286344</v>
+        <v>-0.004890678941311677</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -4895,25 +4898,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.2602925440726733</v>
+        <v>0.2585043314135762</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.07003169860384273</v>
+        <v>0.06851344457776132</v>
       </c>
       <c r="H80" s="3" t="n">
         <v>0.1120367266587625</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.0435289502318269</v>
+        <v>-0.04488607453387849</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-0.04831207801950499</v>
+        <v>-0.04966241560390106</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.03777305825242716</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>0.0006310143555765535</v>
+        <v>-0.03913834951456308</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>-0.0007887679444706919</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4922,7 +4925,7 @@
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4947,25 +4950,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.1244415371812848</v>
+        <v>0.1269590466778021</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.04980843408799962</v>
+        <v>0.0521586616359293</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.1061041315662792</v>
+        <v>0.1061040371181672</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.02914349220145218</v>
+        <v>0.03144754479593304</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>-0.03264411123290578</v>
+        <v>-0.0304783890938749</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.05089547708185771</v>
+        <v>-0.04877061620965284</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.005618573094455681</v>
+        <v>-0.003392346019293946</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -5055,25 +5058,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.24980099164709</v>
+        <v>0.2450332477911845</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.07419730102685196</v>
+        <v>0.07009937711161252</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0.1028054491143735</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1671497471498877</v>
+        <v>0.1626972216623079</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.0643011905658224</v>
+        <v>0.06024101903339685</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.02594124658206542</v>
+        <v>-0.0296571548762532</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.002584535860434944</v>
+        <v>-0.006389546988297745</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
@@ -5107,25 +5110,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.09639023026426918</v>
+        <v>0.09704577786565527</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.0698317787232785</v>
+        <v>0.07047165823896417</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.1015646194269473</v>
+        <v>0.1015647269638111</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>-0.003718297771432511</v>
+        <v>-0.003122506776199629</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>-0.01508970969592727</v>
+        <v>-0.01450071897095184</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.0288070623765827</v>
+        <v>-0.0282262748286678</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.009594882729211163</v>
+        <v>-0.009002606017531445</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
@@ -5159,25 +5162,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.2267225592014359</v>
+        <v>0.2221937213192802</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.07365627868656088</v>
+        <v>0.06969235782643124</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>0.09781732011973232</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1637456369929713</v>
+        <v>0.159449017250463</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.0657067000067515</v>
+        <v>0.0617721288569375</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.0220082530949105</v>
+        <v>-0.02561898211829428</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.002630194634402949</v>
+        <v>-0.006312467122567056</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5211,25 +5214,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.3553436244148844</v>
+        <v>0.3517573088164863</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.05814843206205356</v>
+        <v>0.05534842418313057</v>
       </c>
       <c r="H86" s="3" t="n">
         <v>0.09454853448805167</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.09538442065521102</v>
+        <v>0.09248588117308265</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.02545546136584598</v>
+        <v>-0.02803424171825775</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.03325581395348842</v>
+        <v>-0.03581395348837213</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.0008012178511337398</v>
+        <v>-0.00344523675987507</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5263,25 +5266,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.3519957491731682</v>
+        <v>0.3484205186985345</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.05579287610477834</v>
+        <v>0.05300099743360653</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.09313519086990896</v>
+        <v>0.09313526363788682</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.09318374494394255</v>
+        <v>0.09029299455159023</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>-0.02693792216146662</v>
+        <v>-0.02951109681569641</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.03416074706680505</v>
+        <v>-0.03671482161385597</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>-0.002061685634174526</v>
+        <v>-0.004700643245917902</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
@@ -5319,25 +5322,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.2383445789466412</v>
+        <v>0.2360489063460078</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.005955343832266813</v>
+        <v>0.004090439230259424</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.08441502598767059</v>
+        <v>0.08441491170410664</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.09556359238051759</v>
+        <v>0.09353255598849186</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>-0.045159521228336</v>
+        <v>-0.04692956537024029</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.07235207948538303</v>
+        <v>-0.07407171517737721</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>-0.005971677188193136</v>
+        <v>-0.007814366149121343</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5427,25 +5430,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.1224067089001413</v>
+        <v>0.1221373388521485</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.001438149992964988</v>
+        <v>0.001197616829497594</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.06539554444629725</v>
+        <v>0.06539544672706632</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>-0.1068766489178258</v>
+        <v>-0.1070910842962368</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>-0.06312123396805158</v>
+        <v>-0.06334617484825134</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>-0.0600315955766193</v>
+        <v>-0.06025727826675698</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.004065040650406582</v>
+        <v>-0.004304160688665681</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -5483,25 +5486,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.02578316635720967</v>
+        <v>0.02614704828922698</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.06435777074081095</v>
+        <v>0.06473533646296081</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>0.06133724496361093</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.01658853227551393</v>
+        <v>0.01694915254237284</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.00786557025384349</v>
+        <v>0.008223096174472699</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.00284596229099976</v>
+        <v>0.003201707577374702</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.0007099751508696794</v>
+        <v>0.001064962726304408</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -5539,34 +5542,34 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.01465204891993421</v>
+        <v>0.0150363868172525</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.04362000916011111</v>
+        <v>0.04401531976964135</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0.0428293879410504</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.008403361344537785</v>
+        <v>0.008785332314743988</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.002658564375237482</v>
+        <v>0.003038359285985726</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.0007581501137225999</v>
+        <v>0.0011372251705839</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.0007581501137225999</v>
+        <v>0.0011372251705839</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5591,25 +5594,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.09188684533728142</v>
+        <v>0.09119105577859732</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02850179262403141</v>
+        <v>0.02784640696552443</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03879525088789815</v>
+        <v>0.03879504318590365</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.01810901187204195</v>
+        <v>0.01746045217534675</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.00461125225800274</v>
+        <v>-0.005245338605143757</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.009909034773761705</v>
+        <v>-0.0105397463072221</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.0005093594804533863</v>
+        <v>-0.001146058831020036</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5647,25 +5650,25 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.2809500210640206</v>
+        <v>0.2772992906869232</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.01683351198639704</v>
+        <v>-0.01963555398999828</v>
       </c>
       <c r="H94" s="3" t="n">
         <v>0.03850681758472851</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.05550437646814066</v>
+        <v>0.05249617019391728</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.03486162187819075</v>
+        <v>-0.03761228344747269</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.0532883642495785</v>
+        <v>-0.05598650927487359</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>-0.01531805425631438</v>
+        <v>-0.0181244153414406</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -5699,25 +5702,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1894584315122145</v>
+        <v>0.1845584206888078</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.05414562521253796</v>
+        <v>-0.05804203870290858</v>
       </c>
       <c r="H95" s="3" t="n">
         <v>0.02454801153048258</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.03640526658293974</v>
+        <v>0.03213583191112535</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-0.04897159647404503</v>
+        <v>-0.05288932419196868</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.07680814940577252</v>
+        <v>-0.08061120543293721</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.007519894867489274</v>
+        <v>-0.01160838139738629</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -5751,25 +5754,25 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04236811589479195</v>
+        <v>0.04223998213746016</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.01680382778437783</v>
+        <v>0.0166787395820136</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.02187433087107848</v>
+        <v>0.02187423342437844</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.002004006326828955</v>
+        <v>0.001880740203600073</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-0.0003463886641877911</v>
+        <v>-0.0004692717141367986</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.004961963456287743</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>0.0001229407425620277</v>
+        <v>-0.005084279133797609</v>
+      </c>
+      <c r="L96" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5778,7 +5781,7 @@
       </c>
       <c r="N96" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
         </is>
       </c>
     </row>
@@ -5807,25 +5810,25 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.1965006817223245</v>
+        <v>0.1899570456367643</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.04096338172826219</v>
+        <v>-0.04620840614940325</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.01423590115630846</v>
+        <v>0.01423582234960419</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>0.026284065875263</v>
+        <v>0.02067134074264554</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.05060534777774828</v>
+        <v>-0.05579756638708233</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.054424501066901</v>
+        <v>-0.05959583281034264</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>-0.007143233697084694</v>
+        <v>-0.01257314565870626</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -5863,25 +5866,25 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03156173402345575</v>
+        <v>0.03146398707001863</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.01023801529441204</v>
+        <v>-0.01033179548722174</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0.001841388303224667</v>
+        <v>0.001841245158691773</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.01571502216979437</v>
+        <v>-0.01580807286979824</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.02045303422661027</v>
+        <v>-0.02054570659801747</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.0120572016076268</v>
+        <v>-0.01215066828675571</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>-0.001134001134001084</v>
+        <v>-0.001228501228501155</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5915,25 +5918,25 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.01516211328349337</v>
+        <v>0.01493868243857754</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.02666045228201785</v>
+        <v>-0.02687484425288078</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>-0.006218997628379963</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.03499093123777308</v>
+        <v>-0.03520341007172578</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.0269331442547831</v>
+        <v>-0.02714747616133484</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.02056937555140936</v>
+        <v>-0.02078510916912935</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.001429671175629754</v>
+        <v>-0.001649620587265033</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5967,25 +5970,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.07721983515743513</v>
+        <v>0.07691645463195318</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.008527744264326342</v>
+        <v>-0.008806822587389518</v>
       </c>
       <c r="H100" s="5" t="n">
         <v>-0.007343049622224318</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0.007812857006041174</v>
+        <v>0.007529106465570257</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>-0.000686182914871436</v>
+        <v>-0.0009674684704406022</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.001193458265366654</v>
-      </c>
-      <c r="L100" s="3" t="n">
-        <v>0.0002815579540123014</v>
+        <v>-0.001474601033728873</v>
+      </c>
+      <c r="L100" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -5994,7 +5997,7 @@
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d flat.</t>
         </is>
       </c>
     </row>
@@ -6019,16 +6022,16 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.03327093582864848</v>
+        <v>0.03327109218751878</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.02616820162105649</v>
+        <v>-0.02616813217749892</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01227545458995671</v>
+        <v>-0.01227538415571294</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>-0.01830038091157193</v>
+        <v>-0.01830031034137936</v>
       </c>
       <c r="J101" s="5" t="n">
         <v>-0.03248318992460952</v>
@@ -6071,25 +6074,25 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.04950479989813084</v>
+        <v>-0.04903291448167213</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.06324178393108493</v>
+        <v>-0.06277663527919464</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.04979175648478162</v>
+        <v>-0.04979167219730185</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.05451973318800496</v>
+        <v>-0.05405050688083401</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-0.04917806278068193</v>
+        <v>-0.04870601515143058</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>-0.01415482083858377</v>
+        <v>-0.01366538547596174</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>-0.004448288644507747</v>
+        <v>-0.003954034350673541</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6127,25 +6130,25 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.01566687280972989</v>
+        <v>-0.01710987425273136</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.1015992474129821</v>
+        <v>-0.1029162746942615</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>-0.06340545625587957</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>-0.01668039538714994</v>
+        <v>-0.01812191103789129</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>-0.03065367438083633</v>
+        <v>-0.0320747056435241</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>-0.04077942948975499</v>
+        <v>-0.0421856167135396</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>-0.01404088374974188</v>
+        <v>-0.01548626884162707</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6183,25 +6186,25 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.03531919964195296</v>
+        <v>-0.04056097497092603</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.1458881189666406</v>
+        <v>-0.1505290971892006</v>
       </c>
       <c r="H104" s="5" t="n">
         <v>-0.1042912030459175</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.1373311970702678</v>
+        <v>0.1311512932021059</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.1209113467177982</v>
+        <v>0.11482066320776</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>-0.04644022260602576</v>
+        <v>-0.05162156975628474</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>-0.007787539936102261</v>
+        <v>-0.01317891373801905</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -210,9 +210,6 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -690,25 +687,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.285130708046156</v>
+        <v>2.267910712789236</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.306190097055653</v>
+        <v>1.29410151183267</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.336346567719441</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.3329827197595792</v>
+        <v>0.3259954921111947</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1609363915819343</v>
+        <v>-0.1653345944667769</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.01290753310337167</v>
+        <v>-0.01808167352842993</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.006809669731018042</v>
+        <v>0.001532175689479054</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -746,25 +743,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.863349884032141</v>
+        <v>1.845882382423783</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.139048322030492</v>
+        <v>1.125999536737137</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>1.284108905985093</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4875080822696503</v>
+        <v>0.4784338723101282</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.2096214912339964</v>
+        <v>-0.2144430183379658</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.06350861098369542</v>
+        <v>-0.06922146699470411</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.01656708310700727</v>
+        <v>0.01036574325547712</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -802,25 +799,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.597376433577898</v>
+        <v>1.583912475291135</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9252328361738811</v>
+        <v>0.9152526881494336</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.279147978823718</v>
+        <v>1.279147719814472</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3622688783124004</v>
+        <v>0.3552072137207618</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.2638860884434686</v>
+        <v>-0.2677019207122723</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.1552839683680804</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.004117464263517778</v>
+        <v>-0.1596627671394025</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>-0.00108763206960838</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -829,7 +826,7 @@
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -858,25 +855,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.946672542970471</v>
+        <v>1.924636403702071</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.018719806763285</v>
+        <v>1.003623188405797</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>1.203200483091788</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.471714725952014</v>
+        <v>0.460708782742681</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1774114173228347</v>
+        <v>-0.1835629921259843</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.08373304097574341</v>
+        <v>-0.09058517198848837</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.009055236945366696</v>
+        <v>0.001509206157561005</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -910,25 +907,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.593866153657924</v>
+        <v>1.577743747090618</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9727442213722131</v>
+        <v>0.9604827257512756</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.163152926126449</v>
+        <v>1.163153055844476</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.487487125205631</v>
+        <v>0.4782416327844872</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.2012570610231522</v>
+        <v>-0.2062216564563609</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.08802369099960017</v>
+        <v>-0.09369208967697384</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.009187776437475037</v>
+        <v>0.002915158825894659</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -966,25 +963,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.541124307227399</v>
+        <v>1.525626146781242</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.8806887197998163</v>
+        <v>0.8692185152742697</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.076107019123945</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4444675078513665</v>
+        <v>0.4356577002501714</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.201437648461587</v>
+        <v>-0.2063080309986408</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.09412727644771834</v>
+        <v>-0.09965213832617148</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.009923577050302335</v>
+        <v>0.003764115432873361</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1022,25 +1019,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.490211383812625</v>
+        <v>1.476870068213974</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7965493169250726</v>
+        <v>0.7869242981088218</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.9375953974549958</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3836058082859464</v>
+        <v>0.3761931356620634</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1577345078040489</v>
+        <v>-0.162246947921496</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.07279439284134614</v>
+        <v>-0.07776189990133042</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.006518928901200427</v>
+        <v>0.001126500461680502</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1078,25 +1075,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.250999799223651</v>
+        <v>1.248049326684645</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.7780856245505023</v>
+        <v>0.7757550189195963</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.7824138921507562</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.4828543662362905</v>
+        <v>0.4809107316395946</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.004136504653567741</v>
+        <v>0.002820344081978066</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.00242831792285414</v>
+        <v>-0.003735873727467975</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-0.003730995242981039</v>
+        <v>-0.005036843578024364</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -1134,25 +1131,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.197080291970803</v>
+        <v>1.237956204379562</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8580246913580249</v>
+        <v>0.8925925925925926</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.7641975308641975</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.4104967197750704</v>
+        <v>0.436738519212746</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.2552126772310259</v>
+        <v>0.2785654712260217</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.05318404478656413</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>-0.0163398692810458</v>
+        <v>0.07277816655003511</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.001960784313725483</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -1161,7 +1158,7 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1186,25 +1183,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.7988427552610584</v>
+        <v>0.8001283107644286</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.6428439021424961</v>
+        <v>0.6440179719790067</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.680093936046325</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.2434112750040518</v>
+        <v>0.2442998875316666</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.1295534269028942</v>
+        <v>0.1303606701263826</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.02217139952989011</v>
+        <v>-0.02147258751032333</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.02335025380710665</v>
+        <v>-0.02265228426395938</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -1242,25 +1239,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.6819691279980182</v>
+        <v>0.6991459822326365</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.6086498199292247</v>
+        <v>0.6250779118671297</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.663857686585934</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.09335158493705897</v>
+        <v>0.1045172719220548</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.01919002215159393</v>
+        <v>-0.009173649234325398</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.03318064225191641</v>
+        <v>-0.02330714641729759</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.01315724021290365</v>
+        <v>0.02350395463363664</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1298,25 +1295,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.166661873790738</v>
+        <v>1.17334175193813</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6217345036326927</v>
+        <v>0.6267345151463237</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.6480807181468253</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.07572561315067983</v>
+        <v>0.07904221055870986</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-0.05782682987400523</v>
+        <v>-0.05492199145075416</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.01598599766627773</v>
+        <v>-0.0129521586931155</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.01506657323055371</v>
+        <v>-0.0120298995561785</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1354,25 +1351,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.202788185859292</v>
+        <v>1.205030082689862</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5624026112315594</v>
+        <v>0.5639927529822188</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.5669963540667984</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1034844143132447</v>
+        <v>0.1046074901618048</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.01028218896378386</v>
+        <v>0.01131040786016224</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-0.002931559364077074</v>
+        <v>-0.00191678881497348</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-0.003156352158719233</v>
+        <v>-0.002141810393416765</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -1406,25 +1403,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.8614183474300585</v>
+        <v>0.8715029277813924</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.4924360980699007</v>
+        <v>0.5005216484089723</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.525299947835159</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.2185195301830101</v>
+        <v>-0.2142857142857143</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.09847171892232554</v>
+        <v>-0.09358752166377815</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.02154582763337887</v>
+        <v>-0.01624487004103958</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.006685432793807067</v>
+        <v>0.01213933849401827</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1462,25 +1459,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.7754584301321816</v>
+        <v>0.7757122026062571</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4097555339767682</v>
+        <v>0.4099568988580673</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0.5148680020150302</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.0182776661677696</v>
+        <v>-0.01813744015236729</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.1637612899675104</v>
+        <v>-0.1636418443583072</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.06938721254818558</v>
+        <v>-0.06925428685364887</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.0005716735743890311</v>
+        <v>0.0007145919679862889</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1518,25 +1515,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.183352089688637</v>
+        <v>1.18001919054084</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.7068162248358181</v>
+        <v>0.7042106840214517</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.511090876404922</v>
+        <v>0.5110906886794451</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.3788997019713105</v>
+        <v>0.3767949132638559</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.2650146852670956</v>
+        <v>0.2630837336391358</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1295258620689654</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>0.000763796066450162</v>
+        <v>0.127801724137931</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>-0.000763796066450273</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1545,7 +1542,7 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1574,25 +1571,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.7543251077832884</v>
+        <v>0.7583323767519563</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.4821536100060937</v>
+        <v>0.485539178702469</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.5002905851652479</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.09388887882761909</v>
+        <v>0.09638756447023389</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.06882406563354593</v>
+        <v>-0.06669705256760849</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.01208897485493232</v>
+        <v>-0.00983236621534489</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-0.005678131083711846</v>
+        <v>-0.003406878650227152</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1630,25 +1627,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.7436942445048604</v>
+        <v>0.7376882119739261</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.3990073383927604</v>
+        <v>0.3941885557352605</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.4991462313324342</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3645064150266608</v>
+        <v>0.3598064683799678</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.08841141495402616</v>
+        <v>-0.09155131790081217</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.06679728157717524</v>
+        <v>-0.07001163289046719</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-0.004896520206306709</v>
+        <v>-0.008324084350721295</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1686,25 +1683,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.584807083695293</v>
+        <v>0.604604204694978</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.5128991490308321</v>
+        <v>0.53179800922765</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0.4415951524803936</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.1373336686443973</v>
+        <v>0.1515409243555519</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.1772856808708039</v>
+        <v>0.1919921188437155</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.04946187313945494</v>
+        <v>0.06257155942294479</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.009638156083053406</v>
+        <v>0.02225037175744893</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1738,25 +1735,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.567277374283828</v>
+        <v>0.5848222754963444</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.5178760780420519</v>
+        <v>0.5348679604177642</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.441062842993152</v>
+        <v>0.4410627150358475</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1417861163173082</v>
+        <v>0.1545679575212897</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.1823632217373461</v>
+        <v>0.1955993074890447</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.05330318203844286</v>
+        <v>0.06509449200452266</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.0105377343871067</v>
+        <v>0.02185030218503026</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1794,25 +1791,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.6551868931516165</v>
+        <v>0.6612023367155975</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.383083251475504</v>
+        <v>0.3881098723068566</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.4307568195416953</v>
+        <v>0.430756905274075</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.1203923447934629</v>
+        <v>0.1244641852288284</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01902450503018294</v>
+        <v>0.0227279444578905</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.03332052478454184</v>
+        <v>-0.02980732283032317</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-0.00615158869010668</v>
+        <v>-0.002539646706924747</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1850,25 +1847,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6616244519337195</v>
+        <v>0.685167858672306</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.5483373449539559</v>
+        <v>0.5702755969087654</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0.41922404850307</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.1870130770024654</v>
+        <v>0.2038317580488158</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.2495271252813374</v>
+        <v>0.2672315622298667</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.09097456922821201</v>
+        <v>0.1064324893345892</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.01778053444978545</v>
+        <v>0.03220137489016373</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1902,25 +1899,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.7907189754805113</v>
+        <v>0.7849871435366675</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3681138584284667</v>
+        <v>0.3637351341922765</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.4102713298974281</v>
+        <v>0.4102716493298924</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.3314543581567209</v>
+        <v>0.3271926640683334</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-0.03775073663795214</v>
+        <v>-0.04083068599716444</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.02989316351770943</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>0.0002713262426743412</v>
+        <v>-0.03299826324930255</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>-0.002930323420881176</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1929,7 +1926,7 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1958,25 +1955,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5180433199004018</v>
+        <v>0.5224147844520923</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4323493309444255</v>
+        <v>0.4364738598489424</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.4098777596715413</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.2061473438644452</v>
+        <v>0.2096205116702312</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1698902247778358</v>
+        <v>0.1732589882093281</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.01593866639765973</v>
+        <v>0.01886411782507813</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.01554252199413497</v>
+        <v>-0.01270772238514173</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -2014,25 +2011,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.6610552533151763</v>
+        <v>0.646401961855559</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.2402033011373297</v>
+        <v>0.2292627514453471</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.391549261641591</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>0.007125472307928815</v>
+        <v>0.3915493999196957</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-0.001759062419425361</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-0.2504722921914359</v>
+        <v>-0.2570843828715366</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>-0.1087607637588919</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>0.001261829652996926</v>
+        <v>-0.1166229876450768</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>-0.007570977917981114</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2041,7 +2038,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2066,25 +2063,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.5871468351552265</v>
+        <v>0.5932967334732648</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.55164027036539</v>
+        <v>0.5576525873593543</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.3874577678379048</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.1850936064994702</v>
+        <v>0.1896856234546098</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.1888731396172927</v>
+        <v>0.1934798015591779</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.1183333333333332</v>
+        <v>0.1226666666666667</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.01206636500754144</v>
+        <v>0.0159879336349924</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -2122,25 +2119,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.5254779039663116</v>
+        <v>0.5195331632955409</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.2752088247955109</v>
+        <v>0.2702394858499646</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.3799471994939432</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.08881959465595646</v>
+        <v>0.08457659263841211</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.1778956628486897</v>
+        <v>-0.1810993068483802</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.07590027700831026</v>
+        <v>-0.07950138504155135</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-0.0008984725965858198</v>
+        <v>-0.004791853848457706</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -2174,25 +2171,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.366296734143532</v>
+        <v>1.396541077369968</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.4070325298381281</v>
+        <v>0.4250163987171534</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3764448661459949</v>
+        <v>0.3764450275603612</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.03681572498658603</v>
+        <v>-0.0245049799378021</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.05424090145960792</v>
+        <v>0.06771546836705511</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.02222222222222237</v>
+        <v>0.0352875488553881</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.01854830063257196</v>
+        <v>-0.006004074193202591</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -2230,25 +2227,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.9611094377095504</v>
+        <v>0.966139900803431</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.2803439638038554</v>
+        <v>0.2836279851584445</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3739418460973216</v>
+        <v>0.3739417231493074</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.01065919880067956</v>
+        <v>-0.008121497954803658</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>-0.0944650346475111</v>
+        <v>-0.09214229930215845</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>-0.06812361277104328</v>
+        <v>-0.06573331056855047</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.009167649995461602</v>
+        <v>-0.006626123264046546</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2286,25 +2283,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.7628740858278804</v>
+        <v>0.7587796173381105</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3326718280052383</v>
+        <v>0.3295763948750792</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3718818529300072</v>
+        <v>0.3718819511110505</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.3174477915117584</v>
+        <v>0.314387625599188</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>-0.013613542776448</v>
+        <v>-0.01590471987846642</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.02858119658119662</v>
+        <v>-0.03083760683760672</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>-0.001054703979749716</v>
+        <v>-0.003375052735198891</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2338,25 +2335,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.7545807476159225</v>
+        <v>0.7507488199016839</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.3293440776396759</v>
+        <v>0.3264408482386991</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3685376745528659</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.3166588141111759</v>
+        <v>0.3137832887716641</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>-0.01274156790032843</v>
+        <v>-0.01489769719344824</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.02863903394255873</v>
+        <v>-0.03076044386422971</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>-0.001006964840144398</v>
+        <v>-0.003188721993790389</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2394,25 +2391,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.772207535242504</v>
+        <v>0.769660039983411</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.3289965706218758</v>
+        <v>0.3270862853096193</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3558482023394396</v>
+        <v>0.3558483121265503</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.3198823021105641</v>
+        <v>0.3179850108281819</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.01389927944245384</v>
+        <v>-0.0153167696972083</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.01980430528375732</v>
+        <v>-0.02121330724070447</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>-0.002628434886499442</v>
+        <v>-0.004062126642771724</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2446,25 +2443,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5653667160084477</v>
+        <v>0.5668582517073597</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1347594376383257</v>
+        <v>0.1358406757875761</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.3488445911899107</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.04992326054382368</v>
+        <v>-0.04901799447478494</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.1949835084758763</v>
+        <v>-0.1942164608422183</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.1587174348697394</v>
+        <v>-0.1579158316633267</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.001622447031876417</v>
+        <v>0.002576827638862245</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2502,25 +2499,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.517325121558962</v>
+        <v>0.5303138969466974</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.08576178913810151</v>
+        <v>0.09505614218525826</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.345323599845285</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.1151796851820588</v>
+        <v>-0.1076054341156784</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.152967779698195</v>
+        <v>-0.1457170027998372</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.1929363394331548</v>
+        <v>-0.1860277019512688</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-0.01379565951488704</v>
+        <v>-0.005353539513239802</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2558,25 +2555,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5652451679745836</v>
+        <v>0.5766481518575912</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.3093940643206587</v>
+        <v>0.3189331217898479</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.3205800079126468</v>
+        <v>0.3205801251162927</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.272360580453602</v>
+        <v>0.2816297318037437</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.1253010644087769</v>
+        <v>0.1334988866619324</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.00847047776353127</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>-0.006706671373102657</v>
+        <v>-0.001247181670479658</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0.0005294740557713062</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2585,7 +2582,7 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2614,25 +2611,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.4458486437191516</v>
+        <v>0.4456615030715048</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.196364494912286</v>
+        <v>0.1962096457672027</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.3135852977402176</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.08648572633947404</v>
+        <v>0.08634509914217414</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.09329890857880518</v>
+        <v>-0.0934162656965144</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.08923729812566306</v>
+        <v>-0.0893551809501355</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-0.001163542340012813</v>
+        <v>-0.001292824822236471</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2666,25 +2663,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4595537201893096</v>
+        <v>0.4564780785556475</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2135766416341176</v>
+        <v>0.2110192674246012</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.3023482021148793</v>
+        <v>0.3023480206240432</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.149119861761331</v>
+        <v>0.1466984773446154</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.05326522927322364</v>
+        <v>-0.05526015503935466</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.06816269284712484</v>
+        <v>-0.07012622720897621</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.005686920083807223</v>
+        <v>-0.007782101167315147</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2718,25 +2715,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.3265354078649714</v>
+        <v>0.3288581055286284</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2928866683287923</v>
+        <v>0.2951502574767269</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0.3023182897785208</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.128445823595287</v>
+        <v>0.1304215093091974</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.05862503322439205</v>
+        <v>0.06047847652738181</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>-0.007242178447276926</v>
+        <v>-0.005504055619930615</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.002038439138031478</v>
+        <v>-0.0002912055911474809</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2774,25 +2771,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.8121228055225862</v>
+        <v>0.8134949328362076</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.1827811161261625</v>
+        <v>0.1836767101060661</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.2975166559960483</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>-0.003270440251572304</v>
+        <v>-0.002515723270440251</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>-0.1175291409904224</v>
+        <v>-0.1168609399361497</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.08842702661247015</v>
+        <v>-0.08773678963110654</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.006187290969899673</v>
+        <v>-0.005434782608695565</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2826,25 +2823,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4619767346333434</v>
+        <v>0.4620791395933384</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2090807228073148</v>
+        <v>0.2091655863201043</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2933573076725349</v>
+        <v>0.2933573913347143</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1505575824097598</v>
+        <v>0.1506382638432586</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.03200515883790389</v>
+        <v>-0.03193727939180002</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.06516110000327768</v>
+        <v>-0.06509554557671493</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.009377930603313711</v>
+        <v>-0.009308464450696441</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2882,25 +2879,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.1692142745680194</v>
+        <v>0.1735607960348149</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.3340759439994534</v>
+        <v>0.3390353341258452</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2890163422796628</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1032165350003142</v>
+        <v>0.1073177117103525</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.03708855851223636</v>
+        <v>-0.03350896207547893</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0.03495657909200833</v>
+        <v>0.03880400131911621</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.01361969617600833</v>
+        <v>-0.009952854897852359</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -2934,25 +2931,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.5893144004730206</v>
+        <v>0.5852323128017762</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2057697719580143</v>
+        <v>0.2026729038778778</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.283191473961427</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2329720486986016</v>
+        <v>0.2298052346864699</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.08590305337619053</v>
+        <v>-0.08825079647108713</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.06033526841041026</v>
+        <v>-0.06274867914682669</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>-0.000901588182259494</v>
+        <v>-0.003467646854844353</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2986,25 +2983,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4458276883278622</v>
+        <v>0.4479930608722313</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.07695759290141235</v>
+        <v>0.07857040846547281</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.2762411160356404</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.08092959846886916</v>
+        <v>-0.0795532294662018</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-0.09991575400168495</v>
+        <v>-0.09856781802864367</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.1561488034120527</v>
+        <v>-0.1548850801674433</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>-0.01425474004705451</v>
+        <v>-0.01277852101305532</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3038,25 +3035,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.4381084322327677</v>
+        <v>0.4394445503178399</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2596695155984614</v>
+        <v>0.2608398496172892</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>0.2752739691828336</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1602225846721337</v>
+        <v>0.161300524515434</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.03129050813521439</v>
+        <v>0.03224865973769364</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.01223615784643617</v>
+        <v>-0.0113184460079534</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>-0.003087372645878439</v>
+        <v>-0.002161160852114818</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -3094,25 +3091,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4290673665837081</v>
+        <v>0.4295026958839687</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.1597882064350535</v>
+        <v>0.1601413929228606</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2707565878593987</v>
+        <v>0.270756463303701</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1346910743662115</v>
+        <v>0.1350367293597874</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-0.06491959499702205</v>
+        <v>-0.06463474635523225</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.08732465562997593</v>
+        <v>-0.08704663212435237</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.01230853391684905</v>
+        <v>-0.0120076586433262</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3146,25 +3143,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3528904592985438</v>
+        <v>0.3578686276552698</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2275195915359038</v>
+        <v>0.2320363136443193</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.270296789422761</v>
+        <v>0.2702966606714452</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.09643377935781783</v>
+        <v>0.1004682759485285</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.01283958228070881</v>
+        <v>0.01656648117654669</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.03367496339677889</v>
+        <v>-0.03011922192010053</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.00388098318240615</v>
+        <v>-0.0002156101768004959</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3198,25 +3195,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4316540293332816</v>
+        <v>0.4319250219566648</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.1453032546480626</v>
+        <v>0.1455200449669436</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.2701744783234903</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.04425107140163553</v>
+        <v>0.04444873391751725</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.09020725856816769</v>
+        <v>-0.09003504718421307</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.09831029185867901</v>
+        <v>-0.09813961426864648</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.003583553376084625</v>
+        <v>-0.003394945303659025</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3250,25 +3247,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4711233442163381</v>
+        <v>0.4717306190746315</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2515086916161895</v>
+        <v>0.2520253102711394</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2684279525657993</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1452507614433785</v>
+        <v>0.1457235171756563</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.03019349351477785</v>
+        <v>0.03061875398681679</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.01333876387333255</v>
+        <v>-0.01293147337338352</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.006968641114982521</v>
+        <v>-0.006558721049395366</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3302,25 +3299,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4536073335282</v>
+        <v>0.455031129289394</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.229125883662302</v>
+        <v>0.2303298972623071</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0.2655902955481695</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1038255185937789</v>
+        <v>0.1049067918417719</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.007651008195290743</v>
+        <v>-0.006678933896013706</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.0288121772220713</v>
+        <v>-0.02786083174775755</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>-0.003625209146681629</v>
+        <v>-0.002649191299498033</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3358,25 +3355,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.5436424800378161</v>
+        <v>0.5404535465158291</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1922636815610248</v>
+        <v>0.1898006651081008</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2601138254355535</v>
+        <v>0.2601137490532559</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.2186194381112123</v>
+        <v>0.2161020488078138</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.1004106345352637</v>
+        <v>-0.1022689806072595</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.05384445635383495</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>0.001434768101434836</v>
+        <v>-0.05579899750953621</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>-0.0006339673006339197</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3385,7 +3382,7 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3410,34 +3407,34 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.3491209162280557</v>
+        <v>0.3539240102340844</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2531766101253548</v>
+        <v>0.2576382186774957</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0.2540396909136367</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.1311298137082073</v>
+        <v>0.1351569064656419</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.10567139985954</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>-0.0006882404078080162</v>
+        <v>0.1096078545727968</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>0.002869548539757405</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>-0.004818594104308405</v>
+        <v>-0.001275510204081676</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3462,25 +3459,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.5215402111086054</v>
+        <v>0.5166778910057568</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2111194691830547</v>
+        <v>0.2072491471902698</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.2526942183313561</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1803863837440245</v>
+        <v>0.1766142741402792</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.04859988789052583</v>
+        <v>-0.05164023599121237</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>-0.03318826617055914</v>
+        <v>-0.03627786452277337</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.003424422984727116</v>
+        <v>-0.006609136360523293</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3514,25 +3511,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.5202878706569893</v>
+        <v>0.5155340455700621</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.210503316716244</v>
+        <v>0.2067180852624866</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.2521579904517077</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.1799507180829185</v>
+        <v>0.1762610242916725</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.04902328824443192</v>
+        <v>-0.05199698266675923</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>-0.03326630828785215</v>
+        <v>-0.03628927462486509</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>-0.003426492568882278</v>
+        <v>-0.006542767703544894</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3566,25 +3563,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3367362525004258</v>
+        <v>0.3361823125426053</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.128756939803566</v>
+        <v>0.1282893009642558</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2462968082095851</v>
+        <v>0.2462969352848288</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.02259070291794885</v>
+        <v>0.02216694404271635</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>-0.05229682398064373</v>
+        <v>-0.05268954966334172</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.09431129698139518</v>
+        <v>-0.09468661197791006</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>-0.005943623845112822</v>
+        <v>-0.006355558171011633</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3622,25 +3619,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2256487195482795</v>
+        <v>0.2322298044653119</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2388848613955201</v>
+        <v>0.2455370926427409</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2460913637214592</v>
+        <v>0.2460914390089983</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1296364372529077</v>
+        <v>0.1357019870310492</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.09922592951683584</v>
+        <v>0.1051281909639987</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.00578328566889097</v>
+        <v>-0.0004448681283761857</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.006793219478128276</v>
+        <v>-0.001460224747634964</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3678,25 +3675,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4043182607121536</v>
+        <v>0.4084693901620573</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.06987159406651555</v>
+        <v>0.07303410758356743</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0.2454247380237193</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>-0.09213598156864244</v>
+        <v>-0.08945243770113365</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.09491247024885441</v>
+        <v>-0.09223705428040763</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.1409584526446593</v>
+        <v>-0.1384191474417851</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.0102707749766574</v>
+        <v>-0.007345160286336805</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3730,34 +3727,34 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1908912413468948</v>
+        <v>0.1963141133865811</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2295640627273718</v>
+        <v>0.2351628974425797</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2330265858518887</v>
+        <v>0.2330264472442121</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1146627324280527</v>
+        <v>0.1197384884295225</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.09644891306841363</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>-0.0028081496086515</v>
+        <v>0.1014417301680661</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>0.001732688056401921</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.005067064083457473</v>
+        <v>-0.0005365126676601939</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3782,13 +3779,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.365404476042462</v>
+        <v>0.3654045607325793</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1308326592642142</v>
+        <v>0.1308325430827848</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2317962539392182</v>
+        <v>0.2317961273848173</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>0.09880031643125475</v>
@@ -3838,25 +3835,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3377186324496659</v>
+        <v>0.3352553231933013</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.09303662313997374</v>
+        <v>0.09102380164053425</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.2311758171570499</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.02149907076416335</v>
+        <v>0.01961798531124881</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.1428275590440187</v>
+        <v>-0.1444060378263002</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.1122010293672419</v>
+        <v>-0.1138359067514382</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>-0.006302948153168453</v>
+        <v>-0.008132836326669057</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3890,25 +3887,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.5198954732304686</v>
+        <v>0.5169350766760241</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1837668270844957</v>
+        <v>0.1814610705357054</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2143208554450089</v>
+        <v>0.2143210690818824</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1686315582267979</v>
+        <v>0.1663550771549624</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>-0.02222150921903654</v>
+        <v>-0.02412621067180942</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.02516141283706785</v>
+        <v>-0.02706038739080896</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.005906274206041839</v>
+        <v>-0.007842757552285029</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -3946,25 +3943,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3849338499906381</v>
+        <v>0.375822336816555</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1485065788182549</v>
+        <v>0.1409506144839241</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.2034132529810573</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1892893781109013</v>
+        <v>0.1814651058864873</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.04051034382172514</v>
+        <v>0.03366488103342435</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.04562578484721636</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>0.003815673613149384</v>
+        <v>-0.05190456257848475</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>-0.002788376871147635</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -3973,7 +3970,7 @@
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3998,25 +3995,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.2941073293157268</v>
+        <v>0.2951969509794785</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1501145968306283</v>
+        <v>0.1510829784726413</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0.1984798799511605</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1054918752328688</v>
+        <v>0.1064226851193966</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.00811689494203871</v>
+        <v>0.008965716352318465</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.04035552363424166</v>
+        <v>-0.03954751537460166</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.005720664155155486</v>
+        <v>-0.004883493790986404</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -4050,25 +4047,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.4311355962324506</v>
+        <v>0.4355784609916473</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1725393127548047</v>
+        <v>0.1761793826441467</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.198019801980198</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>-0.1462949220820523</v>
+        <v>-0.1436446517544789</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>-0.008983509721880445</v>
+        <v>-0.00590696529657897</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>-0.0212688381137579</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>-0.0001241619071269406</v>
+        <v>-0.01823043266893531</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0.002979885771045465</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4077,7 +4074,7 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4102,25 +4099,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.4277250754188928</v>
+        <v>0.4325955003089448</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1710989207560669</v>
+        <v>0.17509391211019</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.1969471110846104</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>-0.1468627152878831</v>
+        <v>-0.14395239232891</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>-0.009431345353675513</v>
+        <v>-0.006052200226957627</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.02159509813689353</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>-7.636696874036009e-05</v>
+        <v>-0.01825744744445557</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.003334690968333165</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4129,7 +4126,7 @@
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4154,25 +4151,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.316484388668272</v>
+        <v>0.3185946943897038</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1550717736014666</v>
+        <v>0.1569233502514471</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1948033222651731</v>
+        <v>0.1948032258129999</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1127351667438958</v>
+        <v>0.1145189679089229</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>-0.003968978102189658</v>
+        <v>-0.0023722627737226</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.03325363088912503</v>
+        <v>-0.03170386114063051</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>-0.008267090620031725</v>
+        <v>-0.006677265500794949</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4206,25 +4203,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3950527118753526</v>
+        <v>0.3947402577094297</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1625104164644668</v>
+        <v>0.1622500454982223</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.1947045206436493</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1356948071975639</v>
+        <v>0.1354404422042521</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.003530111720764229</v>
+        <v>0.00330534805314997</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.02694733603404953</v>
+        <v>-0.02716527357571397</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.00714210966931772</v>
+        <v>-0.007364483047300086</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4258,25 +4255,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3986380686027575</v>
+        <v>0.3983769525386522</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1656309051888369</v>
+        <v>0.1654132899522758</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.1945569920178736</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1387737825604742</v>
+        <v>0.1385611813631498</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.006525799662231213</v>
+        <v>0.00633788824960213</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.02421490730230791</v>
+        <v>-0.02439707963733684</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>-0.004247104247104172</v>
+        <v>-0.004433004433004317</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4310,25 +4307,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3972439448073399</v>
+        <v>0.3971332720196326</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1650163431489831</v>
+        <v>0.1649239552746771</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1939917991290847</v>
+        <v>0.1939916870484035</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1382532476411478</v>
+        <v>0.1381630889680674</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.006122586246430251</v>
+        <v>0.006042893368311875</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.02426771775253111</v>
+        <v>-0.02434500347785762</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.004442224792345684</v>
+        <v>-0.004521080853748249</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4366,25 +4363,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.1232528951989564</v>
+        <v>0.1248582478416111</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1289592232231322</v>
+        <v>0.1305727313477918</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0.1823291073464774</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1296572280178838</v>
+        <v>0.1312717337307503</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.1080521378974295</v>
+        <v>0.1096357656230966</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.0451396178878859</v>
+        <v>-0.04377493176569391</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.0051405446789895</v>
+        <v>-0.003718691895439163</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4418,25 +4415,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.6163025328245324</v>
+        <v>0.6214528595010855</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.3103798218259008</v>
+        <v>0.3145552222140875</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0.1805944597597668</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.04074786081674842</v>
+        <v>0.04406410466427935</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.08718244803695141</v>
+        <v>0.09064665127020777</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.1099322133804892</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>-0.001590668080593938</v>
+        <v>0.1134689065723549</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>0.001590668080593938</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4445,7 +4442,7 @@
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4474,25 +4471,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.4223157895883989</v>
+        <v>0.4217868510277487</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1589631754955927</v>
+        <v>0.1585321739427865</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>0.1776501713922569</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1502754860059314</v>
+        <v>0.1498477152785214</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.01458024524996615</v>
+        <v>0.01420293760948654</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.0158680364938697</v>
+        <v>-0.01623402086110892</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.00612492739848991</v>
+        <v>-0.006494535086329689</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4526,25 +4523,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.45824494841748</v>
+        <v>0.456609227779883</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1334905634778369</v>
+        <v>0.1322191214548667</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0.1534522032384673</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1640507694185851</v>
+        <v>0.1627450478600672</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>-0.0005726321698035219</v>
+        <v>-0.001693694837027637</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.01730599647266307</v>
+        <v>-0.01840828924162263</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.00513335565227091</v>
+        <v>-0.006249302533199441</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -4578,7 +4575,7 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3476349008819457</v>
+        <v>0.3476350178685694</v>
       </c>
       <c r="G74" s="3" t="n">
         <v>0.1363029538888361</v>
@@ -4634,25 +4631,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.283606851920684</v>
+        <v>0.2850765906895472</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.09325673477947127</v>
+        <v>0.09450859600497119</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1526271831227746</v>
+        <v>0.1526272617514979</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1270290816111159</v>
+        <v>0.128319537744473</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.008029760200075842</v>
+        <v>0.009183961283154352</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.0515088045923513</v>
+        <v>-0.05042277557986197</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-0.009076910608639355</v>
+        <v>-0.007942296782559422</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4686,25 +4683,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.4145681583992569</v>
+        <v>0.4141642268862928</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1188800829868701</v>
+        <v>0.1185605173688351</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1434813869246168</v>
+        <v>0.1434813172416627</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1595353360759069</v>
+        <v>0.1592042294693745</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.02443300079876609</v>
+        <v>0.02414047281452869</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.02151438949427198</v>
+        <v>-0.02179379715004193</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.006524822695035404</v>
+        <v>-0.006808510638297904</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4738,25 +4735,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.4270423642547845</v>
+        <v>0.4247511522435103</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1143375936573414</v>
+        <v>0.1125484110622692</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.141684869464987</v>
+        <v>0.1416847581472906</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1509712652839994</v>
+        <v>0.1491233756379013</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.004258001014026846</v>
+        <v>-0.005856669361022693</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.02395343631072311</v>
+        <v>-0.025520483546004</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.005814616349332891</v>
+        <v>-0.007410785543267462</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -4794,25 +4791,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1283906705800659</v>
+        <v>0.1315912252320051</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1108699122445287</v>
+        <v>0.1140209018485747</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1200919384962993</v>
+        <v>0.1200920698429204</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1177089867139376</v>
+        <v>0.1208792439574706</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.07058213597985485</v>
+        <v>0.0736187231521257</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.008233276157804337</v>
+        <v>-0.005420240137221199</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.00762048606343535</v>
+        <v>-0.004805711931896162</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -4846,25 +4843,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.171159606831415</v>
+        <v>0.1725139399991877</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.021055526564695</v>
+        <v>0.02223627883594648</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0.114039767925747</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>-0.02211648662081633</v>
+        <v>-0.02098565862037782</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>-0.09523402723369667</v>
+        <v>-0.09418775261933843</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.08346581875993642</v>
+        <v>-0.08240593534711182</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>-0.004890678941311677</v>
+        <v>-0.003739930955120707</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -4898,25 +4895,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.2585043314135762</v>
+        <v>0.2541332399697496</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.06851344457776132</v>
+        <v>0.06480215695845093</v>
       </c>
       <c r="H80" s="3" t="n">
         <v>0.1120367266587625</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.04488607453387849</v>
+        <v>-0.04820348949444919</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-0.04966241560390106</v>
+        <v>-0.05296324081020265</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.03913834951456308</v>
+        <v>-0.04247572815533984</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.0007887679444706919</v>
+        <v>-0.004259346900142069</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4950,25 +4947,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.1269590466778021</v>
+        <v>0.1280379352449863</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.0521586616359293</v>
+        <v>0.05316612028691448</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.1061040371181672</v>
+        <v>0.1061042260144076</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.03144754479593304</v>
+        <v>0.03243499590785337</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>-0.0304783890938749</v>
+        <v>-0.02955022246286176</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.04877061620965284</v>
+        <v>-0.04785996155013661</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.003392346019293946</v>
+        <v>-0.002438248701367551</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -5006,25 +5003,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.09370043758648761</v>
+        <v>0.106413323685471</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.0789838175331905</v>
+        <v>0.09152572171726781</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>0.1043526691782559</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1274373779221336</v>
+        <v>0.1405424971441942</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>0.04711848778238825</v>
+        <v>0.05928999538958046</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.02297169405489119</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>-0.008988567937865399</v>
+        <v>-0.01161490148842814</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>0.002530761846583296</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5033,7 +5030,7 @@
       </c>
       <c r="N82" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5058,25 +5055,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.2450332477911845</v>
+        <v>0.2473720974720039</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.07009937711161252</v>
+        <v>0.07210980589707816</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.1028054491143735</v>
+        <v>0.1028055792232818</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1626972216623079</v>
+        <v>0.1648814047862017</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.06024101903339685</v>
+        <v>0.06223280129458653</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.0296571548762532</v>
+        <v>-0.02783425646778381</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.006389546988297745</v>
+        <v>-0.004522937755761292</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
@@ -5110,25 +5107,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.09704577786565527</v>
+        <v>0.09796380791803916</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.07047165823896417</v>
+        <v>0.0713672387573272</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.1015647269638111</v>
+        <v>0.1015646194269473</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>-0.003122506776199629</v>
+        <v>-0.002288399382873396</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>-0.01450071897095184</v>
+        <v>-0.01367613195598605</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.0282262748286678</v>
+        <v>-0.02741317226158668</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.009002606017531445</v>
+        <v>-0.008173418621179818</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
@@ -5162,25 +5159,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.2221937213192802</v>
+        <v>0.226075553632237</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.06969235782643124</v>
+        <v>0.07309000427797097</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>0.09781732011973232</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.159449017250463</v>
+        <v>0.1631318471000425</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.0617721288569375</v>
+        <v>0.06514461841392083</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.02561898211829428</v>
+        <v>-0.02252407152682245</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.006312467122567056</v>
+        <v>-0.003156233561283583</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5214,25 +5211,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.3517573088164863</v>
+        <v>0.3490403179240267</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.05534842418313057</v>
+        <v>0.05322713791297007</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.09454853448805167</v>
+        <v>0.09454846363307112</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.09248588117308265</v>
+        <v>0.09029001792904601</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.02803424171825775</v>
+        <v>-0.02998786319735758</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.03581395348837213</v>
+        <v>-0.03775193798449616</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.00344523675987507</v>
+        <v>-0.005448281387709364</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5266,25 +5263,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.3484205186985345</v>
+        <v>0.3457390958425595</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.05300099743360653</v>
+        <v>0.05090703571860056</v>
       </c>
       <c r="H87" s="3" t="n">
         <v>0.09313526363788682</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.09029299455159023</v>
+        <v>0.08812480025202785</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>-0.02951109681569641</v>
+        <v>-0.03144097780636856</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.03671482161385597</v>
+        <v>-0.038630377524144</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>-0.004700643245917902</v>
+        <v>-0.006679861454725433</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
@@ -5322,25 +5319,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.2360489063460078</v>
+        <v>0.2317127876072786</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.004090439230259424</v>
+        <v>0.0005680418990761105</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>0.08441491170410664</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.09353255598849186</v>
+        <v>0.08969651649959198</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>-0.04692956537024029</v>
+        <v>-0.05027298208272601</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.07407171517737721</v>
+        <v>-0.07731991592892162</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>-0.007814366149121343</v>
+        <v>-0.01129500085309676</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5378,25 +5375,25 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-0.05552089831565821</v>
+        <v>-0.05333749220212103</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.08220157255182281</v>
+        <v>0.08470335954253039</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>0.07612580414581838</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01576652130157674</v>
+        <v>0.01811472660181157</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0.01884253028263805</v>
+        <v>0.02119784656796786</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>0.00564596479574897</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>-0.0006600660066006236</v>
+        <v>0.007970773829292677</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>0.001650165016501726</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -5405,7 +5402,7 @@
       </c>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5430,25 +5427,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.1221373388521485</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0.001197616829497594</v>
+        <v>0.1135136905583154</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>-0.00649641398056866</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.06539544672706632</v>
+        <v>0.06539554444629725</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>-0.1070910842962368</v>
+        <v>-0.1139530888845677</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>-0.06334617484825134</v>
+        <v>-0.07054428301464322</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>-0.06025727826675698</v>
+        <v>-0.06747912435116232</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.004304160688665681</v>
+        <v>-0.01195600191296031</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -5486,34 +5483,34 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.02614704828922698</v>
+        <v>0.02687481215326204</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.06473533646296081</v>
+        <v>0.06549046790726076</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>0.06133724496361093</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.01694915254237284</v>
+        <v>0.01767039307609086</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.008223096174472699</v>
+        <v>0.008938148015731118</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.003201707577374702</v>
+        <v>0.003913198150124586</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.001064962726304408</v>
+        <v>0.001774937877174088</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N91" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5542,25 +5539,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.0150363868172525</v>
+        <v>0.01542072471457079</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.04401531976964135</v>
+        <v>0.04441063037917181</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0.0428293879410504</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.008785332314743988</v>
+        <v>0.009167303284950412</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.003038359285985726</v>
+        <v>0.003418154196733969</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.0011372251705839</v>
+        <v>0.0015163002274452</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.0011372251705839</v>
+        <v>0.0015163002274452</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -5594,25 +5591,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.09119105577859732</v>
+        <v>0.09035661788171878</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02784640696552443</v>
+        <v>0.02706019094795775</v>
       </c>
       <c r="H93" s="3" t="n">
         <v>0.03879504318590365</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.01746045217534675</v>
+        <v>0.01668228115259041</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.005245338605143757</v>
+        <v>-0.006006146048934013</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.0105397463072221</v>
+        <v>-0.01129660014737466</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.001146058831020036</v>
+        <v>-0.00191009805170006</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5650,25 +5647,25 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.2772992906869232</v>
+        <v>0.2658907582584942</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.01963555398999828</v>
+        <v>-0.02839193525125228</v>
       </c>
       <c r="H94" s="3" t="n">
         <v>0.03850681758472851</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.05249617019391728</v>
+        <v>0.04309552558696916</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.03761228344747269</v>
+        <v>-0.04620810085147886</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.05598650927487359</v>
+        <v>-0.06441821247892077</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>-0.0181244153414406</v>
+        <v>-0.02689429373246022</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -5702,25 +5699,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1845584206888078</v>
+        <v>0.1838585095159821</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.05804203870290858</v>
+        <v>-0.05859856925402995</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.02454801153048258</v>
+        <v>0.0245481203055733</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.03213583191112535</v>
+        <v>0.03152591267229488</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-0.05288932419196868</v>
+        <v>-0.05344899958024341</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.08061120543293721</v>
+        <v>-0.08115449915110351</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.01160838139738629</v>
+        <v>-0.01219245090165721</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -5754,25 +5751,25 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04223998213746016</v>
+        <v>0.04185578456555428</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.0166787395820136</v>
+        <v>0.0163036689489624</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.02187423342437844</v>
+        <v>0.02187413597769727</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.001880740203600073</v>
+        <v>0.001511318431892672</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-0.0004692717141367986</v>
+        <v>-0.000837920863984043</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.005084279133797609</v>
-      </c>
-      <c r="L96" s="24" t="n">
-        <v>0</v>
+        <v>-0.005451226166327539</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>-0.0003688222276863051</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5781,7 +5778,7 @@
       </c>
       <c r="N96" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5810,25 +5807,25 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.1899570456367643</v>
+        <v>0.1828097556392922</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.04620840614940325</v>
+        <v>-0.05193711356822239</v>
       </c>
       <c r="H97" s="3" t="n">
         <v>0.01423582234960419</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>0.02067134074264554</v>
+        <v>0.01454093707837867</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.05579756638708233</v>
+        <v>-0.06146867894582086</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.05959583281034264</v>
+        <v>-0.06524413204468438</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>-0.01257314565870626</v>
+        <v>-0.01850387474300175</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -5866,25 +5863,25 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03146398707001863</v>
+        <v>0.0324400741943367</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.01033179548722174</v>
+        <v>-0.00939540774522829</v>
       </c>
       <c r="H98" s="3" t="n">
         <v>0.001841245158691773</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.01580807286979824</v>
+        <v>-0.0148769365689928</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.02054570659801747</v>
+        <v>-0.01961898288394603</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.01215066828675571</v>
+        <v>-0.01121600149546675</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>-0.001228501228501155</v>
+        <v>-0.0002835002835002154</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5918,25 +5915,25 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.01493868243857754</v>
+        <v>0.01538597710485456</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.02687484425288078</v>
+        <v>-0.02644590106877309</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.006218997628379963</v>
+        <v>-0.006218835077495655</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.03520341007172578</v>
+        <v>-0.03477829591004789</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.02714747616133484</v>
+        <v>-0.02671873277165027</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.02078510916912935</v>
+        <v>-0.02035364193368949</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.001649620587265033</v>
+        <v>-0.001209721763994476</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5970,25 +5967,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.07691645463195318</v>
+        <v>0.07631002584473667</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.008806822587389518</v>
+        <v>-0.009364979233515869</v>
       </c>
       <c r="H100" s="5" t="n">
         <v>-0.007343049622224318</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0.007529106465570257</v>
+        <v>0.006961678152682005</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>-0.0009674684704406022</v>
+        <v>-0.001530039581578824</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.001474601033728873</v>
-      </c>
-      <c r="L100" s="24" t="n">
-        <v>0</v>
+        <v>-0.0020368865704532</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>-0.0005631159080243808</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -5997,7 +5994,7 @@
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d flat.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6022,25 +6019,25 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.03327109218751878</v>
+        <v>0.03416340373991567</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.02616813217749892</v>
+        <v>-0.02532706888009317</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01227538415571294</v>
+        <v>-0.01227552502419049</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>-0.01830031034137936</v>
+        <v>-0.01745231176119633</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>-0.03248318992460952</v>
+        <v>-0.03164744260810326</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>-0.01406540628726838</v>
+        <v>-0.01321374956940535</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>-0.001054650047938588</v>
+        <v>-0.0001917545541706422</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6074,25 +6071,25 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.04903291448167213</v>
+        <v>-0.04785328663848942</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.06277663527919464</v>
+        <v>-0.06161405462427538</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.04979167219730185</v>
+        <v>-0.04979175648478162</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.05405050688083401</v>
+        <v>-0.05287684827608152</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-0.04870601515143058</v>
+        <v>-0.04752598183519485</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>-0.01366538547596174</v>
+        <v>-0.01244179706940673</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>-0.003954034350673541</v>
+        <v>-0.002718398616088136</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6130,25 +6127,25 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.01710987425273136</v>
+        <v>-0.01896516182230457</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.1029162746942615</v>
+        <v>-0.1046095954844778</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>-0.06340545625587957</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>-0.01812191103789129</v>
+        <v>-0.01997528830313011</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>-0.0320747056435241</v>
+        <v>-0.03390174583840833</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>-0.0421856167135396</v>
+        <v>-0.04399357171554841</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>-0.01548626884162707</v>
+        <v>-0.01734462110262225</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6186,25 +6183,25 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.04056097497092603</v>
+        <v>-0.04580275029989911</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.1505290971892006</v>
+        <v>-0.1551700754117606</v>
       </c>
       <c r="H104" s="5" t="n">
         <v>-0.1042912030459175</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.1311512932021059</v>
+        <v>0.1249713893339437</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.11482066320776</v>
+        <v>0.1087299796977217</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>-0.05162156975628474</v>
+        <v>-0.05680291690654382</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>-0.01317891373801905</v>
+        <v>-0.01857028753993606</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.845882382423783</v>
+        <v>1.845882936080272</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.125999536737137</v>
+        <v>1.1259993822463</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>1.284108905985093</v>
+        <v>1.284108740004862</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0.4784338723101282</v>
@@ -799,13 +799,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.583912475291135</v>
+        <v>1.583912277210415</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9152526881494336</v>
+        <v>0.9152529058045467</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.279147719814472</v>
+        <v>1.279147978823718</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.3552072137207618</v>
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.577743747090618</v>
+        <v>1.57774395034017</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9604827257512756</v>
+        <v>0.960482608186801</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.163153055844476</v>
+        <v>1.163152926126449</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.4782416327844872</v>
@@ -963,16 +963,16 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.525626146781242</v>
+        <v>1.525625870268292</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.8692185152742697</v>
+        <v>0.869218363814424</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.076107019123945</v>
+        <v>1.076106850900247</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4356577002501714</v>
+        <v>0.4356577895970211</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>-0.2063080309986408</v>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8001283107644286</v>
+        <v>0.8001279897521867</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.6440179719790067</v>
+        <v>0.6440181058535195</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.680093936046325</v>
+        <v>0.6800940728585503</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>0.2442998875316666</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.17334175193813</v>
+        <v>1.17334196494674</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0.6267345151463237</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.205030082689862</v>
+        <v>1.20502987315916</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0.5639927529822188</v>
@@ -1515,13 +1515,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.18001919054084</v>
+        <v>1.180019363736049</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.7042106840214517</v>
+        <v>0.7042107898800034</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.5110906886794451</v>
+        <v>0.5110907825421778</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>0.3767949132638559</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.7583323767519563</v>
+        <v>0.7583325677482149</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0.485539178702469</v>
@@ -1686,13 +1686,13 @@
         <v>0.604604204694978</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.53179800922765</v>
+        <v>0.5317981056753205</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.4415951524803936</v>
+        <v>0.4415952432485586</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.1515409243555519</v>
+        <v>0.1515410333683538</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.1919921188437155</v>
@@ -1735,25 +1735,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.5848222754963444</v>
+        <v>0.5845822229758721</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.5348679604177642</v>
+        <v>0.5346354655914249</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.4410627150358475</v>
+        <v>0.4410629709504794</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1545679575212897</v>
+        <v>0.1543927867008672</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.1955993074890447</v>
+        <v>0.1954179912458711</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.06509449200452266</v>
+        <v>0.06493296721046704</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.02185030218503026</v>
+        <v>0.02169533550286706</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.685167858672306</v>
+        <v>0.685167641688023</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.5702755969087654</v>
+        <v>0.5702757853143636</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.41922404850307</v>
+        <v>0.4192242187851254</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>0.2038317580488158</v>
@@ -1902,10 +1902,10 @@
         <v>0.7849871435366675</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3637351341922765</v>
+        <v>0.3637348253005288</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.4102716493298924</v>
+        <v>0.4102713298974281</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>0.3271926640683334</v>
@@ -1958,10 +1958,10 @@
         <v>0.5224147844520923</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4364738598489424</v>
+        <v>0.4364740157195452</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.4098777596715413</v>
+        <v>0.4098779126562229</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>0.2096205116702312</v>
@@ -2014,10 +2014,10 @@
         <v>0.646401961855559</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.2292627514453471</v>
+        <v>0.2292625071419732</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3915493999196957</v>
+        <v>0.3915491233635138</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>-0.001759062419425361</v>
@@ -2119,25 +2119,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.5195331632955409</v>
+        <v>0.518618740729053</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.2702394858499646</v>
+        <v>0.2694749721660346</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.3799471994939432</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.08457659263841211</v>
+        <v>0.08392382309725166</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.1810993068483802</v>
+        <v>-0.1815921751560248</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.07950138504155135</v>
+        <v>-0.08005540166204983</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-0.004791853848457706</v>
+        <v>-0.005390835579514808</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -2174,10 +2174,10 @@
         <v>1.396541077369968</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.4250163987171534</v>
+        <v>0.4250162316068697</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3764450275603612</v>
+        <v>0.3764448661459949</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>-0.0245049799378021</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.966139900803431</v>
+        <v>0.9661400355484966</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>0.2836279851584445</v>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.7587796173381105</v>
+        <v>0.7587792843333834</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3295763948750792</v>
+        <v>0.3295762997217042</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3718819511110505</v>
+        <v>0.3718818529300072</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>0.314387625599188</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.769660039983411</v>
+        <v>0.7696602310658807</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0.3270862853096193</v>
@@ -2443,13 +2443,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5668582517073597</v>
+        <v>0.5668584300082449</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1358406757875761</v>
+        <v>0.1358407694852648</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3488445911899107</v>
+        <v>0.3488447024587034</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>-0.04901799447478494</v>
@@ -2508,7 +2508,7 @@
         <v>0.345323599845285</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.1076054341156784</v>
+        <v>-0.1076053334936915</v>
       </c>
       <c r="J35" s="5" t="n">
         <v>-0.1457170027998372</v>
@@ -2558,10 +2558,10 @@
         <v>0.5766481518575912</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.3189331217898479</v>
+        <v>0.3189328876749256</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.3205801251162927</v>
+        <v>0.320579890709022</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.2816297318037437</v>
@@ -2663,16 +2663,16 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4564780785556475</v>
+        <v>0.4564779565009718</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2110192674246012</v>
+        <v>0.2110193518063797</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.3023480206240432</v>
+        <v>0.3023481113694551</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1466984773446154</v>
+        <v>0.1466984016883355</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>-0.05526015503935466</v>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.3288581055286284</v>
+        <v>0.3288578111985523</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0.2951502574767269</v>
@@ -2823,25 +2823,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4620791395933384</v>
+        <v>0.4616179170202712</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2091655863201043</v>
+        <v>0.2087839742690569</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2933573913347143</v>
+        <v>0.2933573076725349</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1506382638432586</v>
+        <v>0.150275197392514</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.03193727939180002</v>
+        <v>-0.03224273689926693</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.06509554557671493</v>
+        <v>-0.06539054049624693</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.009308464450696441</v>
+        <v>-0.009621062137473602</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.1735607960348149</v>
+        <v>0.1735606848438727</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>0.3390353341258452</v>
@@ -2931,16 +2931,16 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.5852323128017762</v>
+        <v>0.5852324462305174</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2026729038778778</v>
+        <v>0.2026728270783513</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.283191473961427</v>
+        <v>0.2831913920201967</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2298052346864699</v>
+        <v>0.2298053149902961</v>
       </c>
       <c r="J43" s="5" t="n">
         <v>-0.08825079647108713</v>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4295026958839687</v>
+        <v>0.4295026095602319</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>0.1601413929228606</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3578686276552698</v>
+        <v>0.3578687793388442</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0.2320363136443193</v>
@@ -3247,25 +3247,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4717306190746315</v>
+        <v>0.4714269816454848</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2520253102711394</v>
+        <v>0.2517670009436646</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2684279525657993</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1457235171756563</v>
+        <v>0.1454871393095174</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.03061875398681679</v>
+        <v>0.03040612375079732</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.01293147337338352</v>
+        <v>-0.01313511862335803</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.006558721049395366</v>
+        <v>-0.006763681082188944</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3302,10 +3302,10 @@
         <v>0.455031129289394</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.2303298972623071</v>
+        <v>0.2303299779886057</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2655902955481695</v>
+        <v>0.2655903785880274</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>0.1049067918417719</v>
@@ -3355,13 +3355,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.5404535465158291</v>
+        <v>0.5404534256337956</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1898006651081008</v>
+        <v>0.1898005929878674</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2601137490532559</v>
+        <v>0.2601136726709674</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>0.2161020488078138</v>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.3539240102340844</v>
+        <v>0.3539241094644132</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2576382186774957</v>
+        <v>0.25763830429593</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2540396909136367</v>
+        <v>0.2540397762870876</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>0.1351569064656419</v>
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.5155340455700621</v>
+        <v>0.5155338465917485</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2067180852624866</v>
+        <v>0.2067182114121551</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2521579904517077</v>
+        <v>0.25215812135164</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>0.1762610242916725</v>
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3361823125426053</v>
+        <v>0.3361824738857431</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1282893009642558</v>
+        <v>0.1282891859213364</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2462969352848288</v>
+        <v>0.2462968082095851</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>0.02216694404271635</v>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2322298044653119</v>
+        <v>0.2322296571560873</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2455370926427409</v>
+        <v>0.2455370173886948</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2460914390089983</v>
+        <v>0.2460913637214592</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0.1357019870310492</v>
@@ -3678,10 +3678,10 @@
         <v>0.4084693901620573</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.07303410758356743</v>
+        <v>0.07303421775479024</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2454247380237193</v>
+        <v>0.2454248658947398</v>
       </c>
       <c r="I57" s="5" t="n">
         <v>-0.08945243770113365</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1963141133865811</v>
+        <v>0.1963142436375918</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0.2351628974425797</v>
@@ -3887,16 +3887,16 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.5169350766760241</v>
+        <v>0.5169349053484442</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1814610705357054</v>
+        <v>0.1814608626799286</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2143210690818824</v>
+        <v>0.2143208554450089</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1663550771549624</v>
+        <v>0.1663549758676877</v>
       </c>
       <c r="J61" s="5" t="n">
         <v>-0.02412621067180942</v>
@@ -3946,10 +3946,10 @@
         <v>0.375822336816555</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1409506144839241</v>
+        <v>0.1409505414029597</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.2034132529810573</v>
+        <v>0.2034131758991924</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>0.1814651058864873</v>
@@ -4151,13 +4151,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3185946943897038</v>
+        <v>0.3185948157100615</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1569233502514471</v>
+        <v>0.1569234436457141</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1948032258129999</v>
+        <v>0.1948033222651731</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>0.1145189679089229</v>
@@ -4203,25 +4203,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3947402577094297</v>
+        <v>0.3947953966798867</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1622500454982223</v>
+        <v>0.1622961019684874</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1947045206436493</v>
+        <v>0.1947046323259263</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1354404422042521</v>
+        <v>0.1354853301442482</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.00330534805314997</v>
+        <v>0.00334501222978778</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.02716527357571397</v>
+        <v>-0.02712681400953798</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.007364483047300086</v>
+        <v>-0.007325240686479773</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4255,16 +4255,16 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3983769525386522</v>
+        <v>0.3983768668221292</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1654132899522758</v>
+        <v>0.1654134090232802</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1945569920178736</v>
+        <v>0.1945571140665079</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1385611813631498</v>
+        <v>0.1385610677159492</v>
       </c>
       <c r="J68" s="3" t="n">
         <v>0.00633788824960213</v>
@@ -4307,25 +4307,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3971332720196326</v>
+        <v>0.3970412019784939</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1649239552746771</v>
+        <v>0.1648471658582287</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1939916870484035</v>
+        <v>0.1939917991290847</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1381630889680674</v>
+        <v>0.1380879567405002</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.006042893368311875</v>
+        <v>0.005976482636546265</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.02434500347785762</v>
+        <v>-0.02440940824896309</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.004521080853748249</v>
+        <v>-0.00458679423825048</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.1248582478416111</v>
+        <v>0.1248581418638091</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>0.1305727313477918</v>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.6214528595010855</v>
+        <v>0.6214527267687424</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0.3145552222140875</v>
@@ -4471,16 +4471,16 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.4217868510277487</v>
+        <v>0.4217865231653308</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1585321739427865</v>
+        <v>0.1585320650976809</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1776501713922569</v>
+        <v>0.1776500607509988</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1498477152785214</v>
+        <v>0.1498476080591153</v>
       </c>
       <c r="J72" s="3" t="n">
         <v>0.01420293760948654</v>
@@ -4532,7 +4532,7 @@
         <v>0.1534522032384673</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1627450478600672</v>
+        <v>0.1627451636941937</v>
       </c>
       <c r="J73" s="5" t="n">
         <v>-0.001693694837027637</v>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3476350178685694</v>
+        <v>0.347634783895342</v>
       </c>
       <c r="G74" s="3" t="n">
         <v>0.1363029538888361</v>
@@ -4631,13 +4631,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.2850765906895472</v>
+        <v>0.2850766936170055</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.09450859600497119</v>
+        <v>0.09450852134092647</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1526272617514979</v>
+        <v>0.1526271831227746</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0.128319537744473</v>
@@ -4686,10 +4686,10 @@
         <v>0.4141642268862928</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1185605173688351</v>
+        <v>0.1185605855331331</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1434813172416627</v>
+        <v>0.1434813869246168</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>0.1592042294693745</v>
@@ -4735,13 +4735,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.4247511522435103</v>
+        <v>0.4247512411929075</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1125484110622692</v>
+        <v>0.1125485195390841</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1416847581472906</v>
+        <v>0.141684869464987</v>
       </c>
       <c r="I77" s="3" t="n">
         <v>0.1491233756379013</v>
@@ -4794,10 +4794,10 @@
         <v>0.1315912252320051</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1140209018485747</v>
+        <v>0.1140207712138837</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1200920698429204</v>
+        <v>0.1200919384962993</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>0.1208792439574706</v>
@@ -4950,13 +4950,13 @@
         <v>0.1280379352449863</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05316612028691448</v>
+        <v>0.05316603035906975</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.1061042260144076</v>
+        <v>0.1061041315662792</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.03243499590785337</v>
+        <v>0.03243508233017312</v>
       </c>
       <c r="J81" s="5" t="n">
         <v>-0.02955022246286176</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.106413323685471</v>
+        <v>0.106413404983583</v>
       </c>
       <c r="G82" s="3" t="n">
         <v>0.09152572171726781</v>
@@ -5064,7 +5064,7 @@
         <v>0.1028055792232818</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1648814047862017</v>
+        <v>0.1648814794486677</v>
       </c>
       <c r="J83" s="3" t="n">
         <v>0.06223280129458653</v>
@@ -5162,10 +5162,10 @@
         <v>0.226075553632237</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.07309000427797097</v>
+        <v>0.0730899270095775</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.09781732011973232</v>
+        <v>0.09781724107083578</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>0.1631318471000425</v>
@@ -5214,10 +5214,10 @@
         <v>0.3490403179240267</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.05322713791297007</v>
+        <v>0.05322720609303744</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.09454846363307112</v>
+        <v>0.09454853448805167</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>0.09029001792904601</v>
@@ -5266,10 +5266,10 @@
         <v>0.3457390958425595</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.05090703571860056</v>
+        <v>0.05090696576167719</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.09313526363788682</v>
+        <v>0.09313519086990896</v>
       </c>
       <c r="I87" s="3" t="n">
         <v>0.08812480025202785</v>
@@ -5328,7 +5328,7 @@
         <v>0.08441491170410664</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.08969651649959198</v>
+        <v>0.08969639142972086</v>
       </c>
       <c r="J88" s="5" t="n">
         <v>-0.05027298208272601</v>
@@ -5375,25 +5375,25 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-0.05333749220212103</v>
+        <v>-0.05396132252027463</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.08470335954253039</v>
+        <v>0.08398856325947102</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>0.07612580414581838</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01811472660181157</v>
+        <v>0.01744381080174429</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0.02119784656796786</v>
+        <v>0.02052489905787347</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>0.007970773829292677</v>
+        <v>0.007306542676851491</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>0.001650165016501726</v>
+        <v>0.000990099009900991</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.1135136905583154</v>
+        <v>0.1135138050281166</v>
       </c>
       <c r="G90" s="5" t="n">
         <v>-0.00649641398056866</v>
@@ -5436,7 +5436,7 @@
         <v>0.06539554444629725</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>-0.1139530888845677</v>
+        <v>-0.1139530164053916</v>
       </c>
       <c r="J90" s="5" t="n">
         <v>-0.07054428301464322</v>
@@ -5591,19 +5591,19 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.09035661788171878</v>
+        <v>0.09035673360533791</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02706019094795775</v>
+        <v>0.02706039630362578</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03879504318590365</v>
+        <v>0.03879525088789815</v>
       </c>
       <c r="I93" s="3" t="n">
         <v>0.01668228115259041</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.006006146048934013</v>
+        <v>-0.006006242221713087</v>
       </c>
       <c r="K93" s="5" t="n">
         <v>-0.01129660014737466</v>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1838585095159821</v>
+        <v>0.1838585885459676</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>-0.05859856925402995</v>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04185578456555428</v>
+        <v>0.0418554790154495</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0.0163036689489624</v>
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.1828097556392922</v>
+        <v>0.182809870300594</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.05193711356822239</v>
+        <v>-0.05193703990319309</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.01423582234960419</v>
+        <v>0.01423590115630846</v>
       </c>
       <c r="I97" s="3" t="n">
         <v>0.01454093707837867</v>
@@ -5875,7 +5875,7 @@
         <v>-0.0148769365689928</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.01961898288394603</v>
+        <v>-0.0196189135676631</v>
       </c>
       <c r="K98" s="5" t="n">
         <v>-0.01121600149546675</v>
@@ -5918,16 +5918,16 @@
         <v>0.01538597710485456</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.02644590106877309</v>
+        <v>-0.02644598068997051</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.006218835077495655</v>
+        <v>-0.00621891635294447</v>
       </c>
       <c r="I99" s="5" t="n">
         <v>-0.03477829591004789</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.02671873277165027</v>
+        <v>-0.02671881234823137</v>
       </c>
       <c r="K99" s="5" t="n">
         <v>-0.02035364193368949</v>
@@ -5967,16 +5967,16 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.07631002584473667</v>
+        <v>0.07631019183632248</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.009364979233515869</v>
+        <v>-0.009364908924886173</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.007343049622224318</v>
+        <v>-0.007342979170091635</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0.006961678152682005</v>
+        <v>0.006961750797921828</v>
       </c>
       <c r="J100" s="5" t="n">
         <v>-0.001530039581578824</v>
@@ -6022,13 +6022,13 @@
         <v>0.03416340373991567</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.02532706888009317</v>
+        <v>-0.0253269993765598</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01227552502419049</v>
+        <v>-0.01227545458995671</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>-0.01745231176119633</v>
+        <v>-0.01745238239234781</v>
       </c>
       <c r="J101" s="5" t="n">
         <v>-0.03164744260810326</v>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.04785328663848942</v>
+        <v>-0.04785345803437091</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>-0.06161405462427538</v>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -96,12 +96,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE7F3"/>
+        <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
+        <fgColor rgb="00FCE7F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -141,12 +141,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAE8FF"/>
+        <fgColor rgb="00E0E7FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E7FF"/>
+        <fgColor rgb="00FAE8FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -687,25 +687,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.267910712789236</v>
+        <v>2.260982016074104</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.29410151183267</v>
+        <v>1.311801027654965</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.336346567719441</v>
+        <v>1.38991549968687</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.3259954921111947</v>
+        <v>0.3319199583426318</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1653345944667769</v>
+        <v>-0.1304453401971735</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.01808167352842993</v>
+        <v>-0.03268503511615339</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.001532175689479054</v>
+        <v>0.0145050711088448</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FTXL</t>
+          <t>PSI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -743,25 +743,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.845882936080272</v>
+        <v>1.539019656450582</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.1259993822463</v>
+        <v>0.9400283117280104</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>1.284108740004862</v>
+        <v>1.320015622747218</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4784338723101282</v>
+        <v>0.3747884639736054</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.2144430183379658</v>
+        <v>-0.210556452686355</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.06922146699470411</v>
+        <v>-0.1637865311308767</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.01036574325547712</v>
+        <v>0.02364286825322748</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PSI</t>
+          <t>FTXL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -799,25 +799,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.583912277210415</v>
+        <v>1.821123410913834</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9152529058045467</v>
+        <v>1.157439387161808</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.279147978823718</v>
+        <v>1.312598998441777</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3552072137207618</v>
+        <v>0.4908218252349743</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.2677019207122723</v>
+        <v>-0.1518094333230472</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.1596627671394025</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>-0.00108763206960838</v>
+        <v>-0.06709317585301844</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.01912996729537197</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -855,25 +855,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.924636403702071</v>
+        <v>1.902459711620017</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.003623188405797</v>
+        <v>1.041766109785203</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>1.203200483091788</v>
+        <v>1.227028639618138</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.460708782742681</v>
+        <v>0.5161719096145325</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1835629921259843</v>
+        <v>-0.1233508389906494</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.09058517198848837</v>
+        <v>-0.08318821165438728</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.001509206157561005</v>
+        <v>0.03134418324291732</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -907,25 +907,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.57774395034017</v>
+        <v>1.553483673620697</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.960482608186801</v>
+        <v>0.9851815911428128</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.163152926126449</v>
+        <v>1.178933257724606</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4782416327844872</v>
+        <v>0.4978537038535247</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.2062216564563609</v>
+        <v>-0.1384161719129451</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.09369208967697384</v>
+        <v>-0.08892042282383739</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.002915158825894659</v>
+        <v>0.02048712037686684</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -963,25 +963,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.525625870268292</v>
+        <v>1.494319805827963</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.869218363814424</v>
+        <v>0.88576272843951</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.076106850900247</v>
+        <v>1.089520989351406</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4356577895970211</v>
+        <v>0.455481484051951</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.2063080309986408</v>
+        <v>-0.1422168333097801</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.09965213832617148</v>
+        <v>-0.09751434034416828</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.003764115432873361</v>
+        <v>0.01909090909090927</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1019,25 +1019,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.476870068213974</v>
+        <v>1.44063773353152</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7869242981088218</v>
+        <v>0.8002255771820876</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.9375953974549958</v>
+        <v>0.940028314473321</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3761931356620634</v>
+        <v>0.3889840757911711</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.162246947921496</v>
+        <v>-0.1050974025974026</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.07776189990133042</v>
+        <v>-0.07206221489050124</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.001126500461680502</v>
+        <v>0.0168784932947188</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.248049326684645</v>
+        <v>1.272901483915839</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.7757550189195963</v>
+        <v>0.8130555683734633</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.7824138921507562</v>
+        <v>0.7891558977541133</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.4809107316395946</v>
+        <v>0.4964383561643835</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.002820344081978066</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>-0.003735873727467975</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>-0.005036843578024364</v>
+        <v>0.05250987571056931</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.01335807050092752</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.02409299709384083</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1112,53 +1112,49 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BDRY</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Transportation &amp; Trade</t>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dry Bulk Freight Futures</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.237956204379562</v>
+        <v>0.7911528677979494</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8925925925925926</v>
+        <v>0.6701372362814395</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7641975308641975</v>
+        <v>0.7152964224810276</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.436738519212746</v>
+        <v>0.25197258446974</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.2785654712260217</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.07277816655003511</v>
+        <v>0.1488286806181713</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>-0.02632733655111885</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.001960784313725483</v>
+        <v>0.008439914302408758</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1168,49 +1164,53 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>BDRY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Defensive Equity</t>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Dry Bulk Freight Futures</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8001279897521867</v>
+        <v>1.2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.6440181058535195</v>
+        <v>0.8623629719853834</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.6800940728585503</v>
+        <v>0.7052375152253347</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.2442998875316666</v>
+        <v>0.4659635666347075</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.1303606701263826</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>-0.02147258751032333</v>
+        <v>0.2605111294311622</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.09214285714285708</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.02265228426395938</v>
+        <v>-0.002609262883235597</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1239,34 +1239,34 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.6991459822326365</v>
+        <v>0.6437770037455095</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.6250779118671297</v>
+        <v>0.6379116185249694</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.663857686585934</v>
+        <v>0.7017781642581455</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.1045172719220548</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>-0.009173649234325398</v>
+        <v>0.06472525477789581</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0.01083236908835761</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.02330714641729759</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>0.02350395463363664</v>
+        <v>-0.0375293014533522</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>-0.00223566863502711</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1295,25 +1295,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.17334196494674</v>
+        <v>1.137146817955403</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6267345151463237</v>
+        <v>0.6191494579722256</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.6480807181468253</v>
+        <v>0.6536075030319715</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.07904221055870986</v>
+        <v>0.1014070095546449</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-0.05492199145075416</v>
+        <v>-0.04431879501948444</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.0129521586931155</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>-0.0120298995561785</v>
+        <v>-0.02083810396152974</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0.01099420735311485</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1351,34 +1351,34 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.20502987315916</v>
+        <v>1.211672993766111</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5639927529822188</v>
+        <v>0.5692914278758947</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.5669963540667984</v>
+        <v>0.5577640784891604</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1046074901618048</v>
+        <v>0.1164073113671125</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.01131040786016224</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>-0.00191678881497348</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>-0.002141810393416765</v>
+        <v>0.0197480422199523</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.007399932727884195</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.01502485314053326</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1403,25 +1403,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.8715029277813924</v>
+        <v>0.8928687723868447</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.5005216484089723</v>
+        <v>0.4997420020639836</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.525299947835159</v>
+        <v>0.5368937048503613</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.2142857142857143</v>
+        <v>-0.1888082612336031</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.09358752166377815</v>
+        <v>-0.08297838775832145</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.01624487004103958</v>
+        <v>-0.02417324156454592</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.01213933849401827</v>
+        <v>0.0104293412132801</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>BOAT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1448,45 +1448,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Global Shipping</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.7757122026062571</v>
+        <v>1.186084730537437</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4099568988580673</v>
+        <v>0.6947419706746465</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5148680020150302</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>-0.01813744015236729</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>-0.1636418443583072</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>-0.06925428685364887</v>
+        <v>0.5337978139154207</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0.3688929921359141</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0.285014969832883</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.1049317943336832</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.0007145919679862889</v>
+        <v>0.006115039174469761</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BOAT</t>
+          <t>PICK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1504,45 +1504,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Global Shipping</t>
+          <t>Global Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.180019363736049</v>
+        <v>0.7187648592956184</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.7042107898800034</v>
+        <v>0.4706063027892593</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.5110907825421778</v>
+        <v>0.5013233061992033</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.3767949132638559</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>0.2630837336391358</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.127801724137931</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>-0.000763796066450273</v>
+        <v>0.100718809143264</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>-0.0585365853658536</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>-0.02045995241871534</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0.005371968093765167</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PICK</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1560,36 +1560,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Global Metals &amp; Mining</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.7583325677482149</v>
+        <v>0.6980937108127421</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.485539178702469</v>
+        <v>0.3926510162873016</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.5002905851652479</v>
+        <v>0.4828750110728948</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.09638756447023389</v>
+        <v>0.3533885254020552</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.06669705256760849</v>
+        <v>-0.05532886925240577</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.00983236621534489</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>-0.003406878650227152</v>
+        <v>-0.0608439646712462</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0.008064781592547421</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>QTEC</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1616,36 +1616,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Lithium &amp; Battery</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.7376882119739261</v>
+        <v>0.7430601722848915</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.3941885557352605</v>
+        <v>0.3678152330546329</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.4991462313324342</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>0.3598064683799678</v>
+        <v>0.4804405645667975</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>-0.01252372494787246</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.09155131790081217</v>
+        <v>-0.1537942454667961</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.07001163289046719</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>-0.008324084350721295</v>
+        <v>-0.0760755508919202</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0.005998286203941827</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1683,25 +1683,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.604604204694978</v>
+        <v>0.5308840075618591</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.5317981056753205</v>
+        <v>0.5084619677587492</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.4415952432485586</v>
+        <v>0.4619433315712811</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.1515410333683538</v>
+        <v>0.117418737665286</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.1919921188437155</v>
+        <v>0.1764286782882509</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.06257155942294479</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0.02225037175744893</v>
+        <v>0.03181972596534943</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>-0.0181563493346264</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1735,25 +1735,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.5845822229758721</v>
+        <v>0.5105568248250847</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.5346354655914249</v>
+        <v>0.5113551912471683</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.4410629709504794</v>
+        <v>0.461607292045245</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1543927867008672</v>
+        <v>0.1212188948342001</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.1954179912458711</v>
+        <v>0.1773243121276991</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.06493296721046704</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>0.02169533550286706</v>
+        <v>0.03403643336529227</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>-0.01850447444259085</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DXJ</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1780,45 +1780,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Japan Hedged Equity</t>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.6612023367155975</v>
+        <v>0.584558309927852</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.3881098723068566</v>
+        <v>0.5373837987199606</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.430756905274075</v>
+        <v>0.4505188056157297</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.1244641852288284</v>
+        <v>0.1527946771691253</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.0227279444578905</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>-0.02980732283032317</v>
+        <v>0.2424920621518849</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0.05988546495773117</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-0.002539646706924747</v>
+        <v>-0.02689033550325481</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1836,36 +1836,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.685167641688023</v>
+        <v>0.5182110626639249</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.5702757853143636</v>
+        <v>0.446472707561582</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.4192242187851254</v>
+        <v>0.4386294013217875</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.2038317580488158</v>
+        <v>0.2146884029528506</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.2672315622298667</v>
+        <v>0.1842680505112915</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.1064324893345892</v>
+        <v>0.005451929616194562</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.03220137489016373</v>
+        <v>0.005049504950495054</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1884,49 +1884,53 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>XLK</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>DXJ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Japan Hedged Equity</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.7849871435366675</v>
+        <v>0.6407794700255223</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3637348253005288</v>
+        <v>0.3928794258100374</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.4102713298974281</v>
+        <v>0.4170762664937646</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.3271926640683334</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>-0.04083068599716444</v>
+        <v>0.1348416385427935</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0.03019510869103192</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.03299826324930255</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>-0.002930323420881176</v>
+        <v>-0.01707518589920143</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.009675229150164055</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1936,44 +1940,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IBB</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>DBC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Broad Commodity Futures</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5224147844520923</v>
+        <v>0.5756550103278046</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4364740157195452</v>
+        <v>0.5351281678287416</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.4098779126562229</v>
+        <v>0.4008216425454265</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.2096205116702312</v>
+        <v>0.1644645340751043</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1732589882093281</v>
+        <v>0.2003584229390682</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.01886411782507813</v>
+        <v>0.09587696335078544</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.01270772238514173</v>
+        <v>-0.005641330166270664</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -1992,14 +1992,10 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>QCLN</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>XLK</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -2007,29 +2003,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.646401961855559</v>
+        <v>0.749375181697769</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.2292625071419732</v>
+        <v>0.3646538749781536</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3915491233635138</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>-0.001759062419425361</v>
+        <v>0.3999618665687914</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>0.3327515733093882</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-0.2570843828715366</v>
+        <v>-0.003748049471527182</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>-0.1166229876450768</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>-0.007570977917981114</v>
+        <v>-0.02522068095838581</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.00968760204636987</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2038,7 +2034,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2048,49 +2044,49 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DBC</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Broad Commodity Futures</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.5932967334732648</v>
+        <v>1.373369003827534</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.5576525873593543</v>
+        <v>0.3932593333806689</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3874577678379048</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>0.1896856234546098</v>
+        <v>0.3627653555179977</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>-0.01413957181763137</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.1934798015591779</v>
+        <v>0.04088210824324845</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.1226666666666667</v>
+        <v>0.02237654320987659</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.0159879336349924</v>
+        <v>0.0004314529177005255</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2096,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DRIV</t>
+          <t>QCLN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2115,29 +2111,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Autonomous &amp; Electric Vehicles</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.518618740729053</v>
+        <v>0.6287193633382655</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.2694749721660346</v>
+        <v>0.21893385047591</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3799471994939432</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>0.08392382309725166</v>
+        <v>0.3624584417851</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>-0.01108340053059376</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.1815921751560248</v>
+        <v>-0.2287984433273877</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.08005540166204983</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>-0.005390835579514808</v>
+        <v>-0.1053423626787057</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.007840644204280656</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -2146,7 +2142,7 @@
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2156,49 +2152,53 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SIL</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>FTEC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.396541077369968</v>
+        <v>0.7202570782424873</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.4250162316068697</v>
+        <v>0.3303442283097238</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3764448661459949</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>-0.0245049799378021</v>
+        <v>0.3587878653878944</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0.3226558825215473</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.06771546836705511</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>0.0352875488553881</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>-0.006004074193202591</v>
+        <v>0.01828987118867476</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>-0.02093309618278838</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.009736136588119004</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2208,53 +2208,49 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>XME</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>VGT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.9661400355484966</v>
+        <v>0.7147052306485704</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.2836279851584445</v>
+        <v>0.3255325199691865</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3739417231493074</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>-0.008121497954803658</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>-0.09214229930215845</v>
+        <v>0.3550576040462512</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>0.3212080461896174</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0.01869694339731165</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>-0.06573331056855047</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>-0.006626123264046546</v>
+        <v>-0.02178880365594904</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0.009091674383365556</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FTEC</t>
+          <t>DRIV</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2279,29 +2275,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Autonomous &amp; Electric Vehicles</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.7587792843333834</v>
+        <v>0.4898766039181861</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3295762997217042</v>
+        <v>0.250986983875344</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3718818529300072</v>
+        <v>0.3537359148051535</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.314387625599188</v>
+        <v>0.08493220931095569</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>-0.01590471987846642</v>
+        <v>-0.1571669252823606</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.03083760683760672</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>-0.003375052735198891</v>
+        <v>-0.07590027700831026</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.004516711833784992</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2310,7 +2306,7 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2320,10 +2316,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VGT</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>IYW</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -2335,34 +2335,34 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.7507488199016839</v>
+        <v>0.7334770963458626</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.3264408482386991</v>
+        <v>0.3263941113174655</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3685376745528659</v>
+        <v>0.3381093666486981</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.3137832887716641</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>-0.01489769719344824</v>
+        <v>0.3240059749912667</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.01809687716022257</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.03076044386422971</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>-0.003188721993790389</v>
+        <v>-0.008755080581024255</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.009716890595009575</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2372,44 +2372,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IYW</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>AIRR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>U.S. Industrial Renaissance</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.7696602310658807</v>
+        <v>0.5380546213373463</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.3270862853096193</v>
+        <v>0.1349641404681428</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3558483121265503</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0.3179850108281819</v>
+        <v>0.3380381699447861</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>-0.04863502014936227</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.0153167696972083</v>
+        <v>-0.1869962385814079</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.02121330724070447</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>-0.004062126642771724</v>
+        <v>-0.151769982380266</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0.008186577820085583</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2418,7 +2414,7 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2428,40 +2424,44 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AIRR</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>XME</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>U.S. Industrial Renaissance</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5668584300082449</v>
+        <v>0.9252945188951376</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1358407694852648</v>
+        <v>0.2437261418055863</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3488447024587034</v>
+        <v>0.3304715339423887</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.04901799447478494</v>
+        <v>-0.002040398151487266</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.1942164608422183</v>
+        <v>-0.07420156148169199</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.1579158316633267</v>
+        <v>-0.0651989839119389</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.002576827638862245</v>
+        <v>0.008771929824561431</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2499,25 +2499,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5303138969466974</v>
+        <v>0.5027586588909818</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.09505614218525826</v>
+        <v>0.08566240452591778</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.345323599845285</v>
+        <v>0.3236139635431958</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.1076053334936915</v>
+        <v>-0.1159501871598974</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1457170027998372</v>
+        <v>-0.1415749587817239</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.1860277019512688</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>-0.005353539513239802</v>
+        <v>-0.1797741377556211</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0.001366289901875595</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CALF</t>
+          <t>ROBO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2544,45 +2544,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Small Cap Cash Flow</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5766481518575912</v>
+        <v>0.4193252839732184</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.3189328876749256</v>
+        <v>0.2010678598309756</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.320579890709022</v>
+        <v>0.3045790225491527</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.2816297318037437</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>0.1334988866619324</v>
+        <v>0.08805907760902887</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-0.07179365268037552</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.001247181670479658</v>
+        <v>-0.07934449422306045</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.0005294740557713062</v>
+        <v>0.01087378640776704</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2592,44 +2592,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ROBO</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SCHA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.4456615030715048</v>
+        <v>0.4294668953560006</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.1962096457672027</v>
+        <v>0.2152545777396218</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.3135852977402176</v>
+        <v>0.3045311509168953</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.08634509914217414</v>
+        <v>0.1437668525698366</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.0934162656965144</v>
+        <v>-0.03890885061845817</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.0893551809501355</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>-0.001292824822236471</v>
+        <v>-0.06843575418994408</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0.006033182503770718</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2638,7 +2634,7 @@
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2648,10 +2644,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SCHA</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>CALF</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -2659,38 +2659,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Small Cap Cash Flow</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4564779565009718</v>
+        <v>0.5394440696424543</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2110193518063797</v>
+        <v>0.3122125814789893</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.3023481113694551</v>
+        <v>0.3039135882829664</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1466984016883355</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>-0.05526015503935466</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>-0.07012622720897621</v>
+        <v>0.2617750273203197</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0.1346050310327658</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.006364680351979013</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.007782101167315147</v>
+        <v>-0.004409948844593448</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2700,49 +2700,53 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SCHD</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>ARGT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.3288578111985523</v>
+        <v>0.1271728912073526</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2951502574767269</v>
+        <v>0.3322492337540661</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.3023182897785208</v>
+        <v>0.3004951102902829</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1304215093091974</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>0.06047847652738181</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>-0.005504055619930615</v>
+        <v>0.07300155969061506</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>-0.03693986925322545</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0.02441694952370521</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.0002912055911474809</v>
+        <v>-0.009947089947089927</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2752,53 +2756,49 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ARKQ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SCHD</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.8134949328362076</v>
+        <v>0.3074446711932053</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.1836767101060661</v>
+        <v>0.297231979975989</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2975166559960483</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>-0.002515723270440251</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>-0.1168609399361497</v>
+        <v>0.3002655537379906</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>0.1235583914409391</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0.06002021278234126</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.08773678963110654</v>
+        <v>-0.002333041703120431</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.005434782608695565</v>
+        <v>-0.003495484998543463</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>SPMO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2819,29 +2819,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4616179170202712</v>
+        <v>0.5617365938548884</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2087839742690569</v>
+        <v>0.2054600020967756</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2933573076725349</v>
+        <v>0.2917070022467936</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.150275197392514</v>
+        <v>0.2393055161152127</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.03224273689926693</v>
+        <v>-0.06207345576063872</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.06539054049624693</v>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>-0.009621062137473602</v>
+        <v>-0.06676978602732653</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>0.00772496346301077</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2860,53 +2860,49 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ARGT</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.1735606848438727</v>
+        <v>0.4376624270100287</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.3390353341258452</v>
+        <v>0.2125830033850131</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2890163422796628</v>
+        <v>0.2835516849073865</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1073177117103525</v>
+        <v>0.1514951987152906</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.03350896207547893</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>0.03880400131911621</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>-0.009952854897852359</v>
+        <v>-0.01654246191383713</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>-0.0552908639027605</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>0.004769586869608045</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2916,10 +2912,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SPMO</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>MTUM</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D43" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -2931,25 +2931,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.5852324462305174</v>
+        <v>0.5191474065868573</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2026728270783513</v>
+        <v>0.1994540455343035</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2831913920201967</v>
+        <v>0.2738927634890074</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2298053149902961</v>
+        <v>0.2229995054449561</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.08825079647108713</v>
+        <v>-0.0699275171868986</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.06274867914682669</v>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>-0.003467646854844353</v>
+        <v>-0.05843405354688347</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0.01045040232379546</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2968,40 +2968,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ITA</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>ARKQ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4479930608722313</v>
+        <v>0.758484687325548</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.07857040846547281</v>
+        <v>0.1674905030998719</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2762411160356404</v>
+        <v>0.2687196896505104</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.0795532294662018</v>
+        <v>-0.01469019286007378</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-0.09856781802864367</v>
+        <v>-0.09285984132980729</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.1548850801674433</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>-0.01277852101305532</v>
+        <v>-0.07978845711657845</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0.009331651954602727</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3010,7 +3014,7 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3020,49 +3024,49 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FNDX</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fundamental Large Cap</t>
+          <t>U.S. Infrastructure Development</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.4394445503178399</v>
+        <v>0.4041075936714134</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2608398496172892</v>
+        <v>0.1485431820952259</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2752739691828336</v>
+        <v>0.2672166275493635</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.161300524515434</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>0.03224865973769364</v>
+        <v>0.04822773715454187</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>-0.08848985134413856</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.0113184460079534</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>-0.002161160852114818</v>
+        <v>-0.09364890175378848</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0.00738077214231625</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3072,14 +3076,10 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IWO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>FNDX</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3087,38 +3087,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Russell 2000 Growth</t>
+          <t>Fundamental Large Cap</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4295026095602319</v>
+        <v>0.4141007352782209</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.1601413929228606</v>
+        <v>0.2588148465515501</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.270756463303701</v>
+        <v>0.2658234043115031</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1350367293597874</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>-0.06463474635523225</v>
+        <v>0.1567113789850034</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>0.03586380506049958</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.08704663212435237</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>-0.0120076586433262</v>
+        <v>-0.00553675792063979</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.0003094059405939209</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3143,25 +3143,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3578687793388442</v>
+        <v>0.3341763788665986</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2320363136443193</v>
+        <v>0.2301410062469862</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2702966606714452</v>
+        <v>0.2627222602884116</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1004682759485285</v>
+        <v>0.1013569727049872</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.01656648117654669</v>
+        <v>0.01612586237822233</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.03011922192010053</v>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>-0.0002156101768004959</v>
+        <v>-0.02580239144115803</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>0.001509596722018447</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3180,40 +3180,44 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PAVE</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>IWO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>U.S. Infrastructure Development</t>
+          <t>Russell 2000 Growth</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4319250219566648</v>
+        <v>0.4055110808164142</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.1455200449669436</v>
+        <v>0.1649264702167323</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2701744783234903</v>
+        <v>0.2616565941168711</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.04444873391751725</v>
+        <v>0.136673745148175</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.09003504718421307</v>
+        <v>-0.04449620667018206</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.09813961426864648</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>-0.003394945303659025</v>
+        <v>-0.07666913829895794</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.007807092826887407</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3222,7 +3226,7 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3247,25 +3251,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4714269816454848</v>
+        <v>0.4601376892904134</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2517670009436646</v>
+        <v>0.2525612082793383</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2684279525657993</v>
+        <v>0.2587156701482509</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1454871393095174</v>
+        <v>0.1544520763239607</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.03040612375079732</v>
+        <v>0.03793030174245637</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.01313511862335803</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>-0.006763681082188944</v>
+        <v>-0.004889477437098999</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0.007944696657036676</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3274,7 +3278,7 @@
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3299,25 +3303,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.455031129289394</v>
+        <v>0.4343010415750324</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.2303299779886057</v>
+        <v>0.2261670941311316</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2655903785880274</v>
+        <v>0.2573928912680641</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1049067918417719</v>
+        <v>0.1062708710943585</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.006678933896013706</v>
+        <v>-0.001130402212035642</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.02786083174775755</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>-0.002649191299498033</v>
+        <v>-0.02483376306147367</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.004613448902558437</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3326,7 +3330,7 @@
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3340,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MTUM</t>
+          <t>VHT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3344,45 +3348,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D51" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.5404534256337956</v>
+        <v>0.2257336654041178</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1898005929878674</v>
+        <v>0.2613764204219609</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2601136726709674</v>
+        <v>0.2554653410025938</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.2161020488078138</v>
-      </c>
-      <c r="J51" s="5" t="n">
-        <v>-0.1022689806072595</v>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>-0.05579899750953621</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>-0.0006339673006339197</v>
+        <v>0.1477806693283723</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0.1111108515069255</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0.004708277661131355</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0.004005595116988836</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3392,49 +3396,49 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>COWZ</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Large Cap Cash Flow</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.3539241094644132</v>
+        <v>0.4367351555346763</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.25763830429593</v>
+        <v>0.07386030785434783</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2540397762870876</v>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>0.1351569064656419</v>
-      </c>
-      <c r="J52" s="3" t="n">
-        <v>0.1096078545727968</v>
-      </c>
-      <c r="K52" s="3" t="n">
-        <v>0.002869548539757405</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>-0.001275510204081676</v>
+        <v>0.2510045642986529</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>-0.07350345841991601</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>-0.09974253908281527</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>-0.141601606820369</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>0.006448598130841088</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3444,101 +3448,105 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>QQQM</t>
+          <t>COWZ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Large Cap Cash Flow</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.5166778910057568</v>
+        <v>0.3252481561665113</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2072491471902698</v>
+        <v>0.2583173827553611</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2526942183313561</v>
+        <v>0.245823015229478</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1766142741402792</v>
-      </c>
-      <c r="J53" s="5" t="n">
-        <v>-0.05164023599121237</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>-0.03627786452277337</v>
+        <v>0.1225536354171952</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0.1095243804731652</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0.01002900682773267</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.006609136360523293</v>
+        <v>-0.003831417624520994</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>XMMO</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Mid Cap Momentum</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0.3080876710443863</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0.1016394573264683</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0.2439600928773975</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>0.01732717285894769</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>-0.1329686488503464</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>-0.1144093258021872</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>0.007037922787837436</v>
+      </c>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N53" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="21" customHeight="1">
-      <c r="A54" s="15" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
-        <is>
-          <t>Nasdaq-100</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>0.5155338465917485</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>0.2067182114121551</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>0.25215812135164</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>0.1762610242916725</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>-0.05199698266675923</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>-0.03628927462486509</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>-0.006542767703544894</v>
-      </c>
-      <c r="M54" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3548,49 +3556,49 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3361824738857431</v>
+        <v>0.1915537912133749</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1282891859213364</v>
+        <v>0.2503396767680126</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2462968082095851</v>
+        <v>0.2412743983128098</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.02216694404271635</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>-0.05268954966334172</v>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>-0.09468661197791006</v>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v>-0.006355558171011633</v>
+        <v>0.1341013214851243</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0.1050876801533993</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0.007303202633941908</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0.003638315638792911</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3600,100 +3608,92 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>QQQM</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2322296571560873</v>
+        <v>0.4927317604670887</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2455370173886948</v>
+        <v>0.2064135525672925</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2460913637214592</v>
+        <v>0.2398734681355723</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1357019870310492</v>
-      </c>
-      <c r="J56" s="3" t="n">
-        <v>0.1051281909639987</v>
+        <v>0.1799139655004163</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>-0.02599020894726445</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.0004448681283761857</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>-0.001460224747634964</v>
+        <v>-0.02698655663516558</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>0.007997518011651827</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
-      <c r="A57" t="n">
+      <c r="A57" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>PPA</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D57" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Aerospace &amp; Defense</t>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4084693901620573</v>
+        <v>0.4914661967790952</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.07303421775479024</v>
+        <v>0.205938966298628</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2454248658947398</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>-0.08945243770113365</v>
+        <v>0.2394962376707548</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0.1798026550248886</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.09223705428040763</v>
+        <v>-0.02599075919399596</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.1384191474417851</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>-0.007345160286336805</v>
+        <v>-0.0270733144258567</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0.007905867658330346</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3712,49 +3712,49 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="13" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1963142436375918</v>
+        <v>0.3158891024316717</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2351628974425797</v>
+        <v>0.1262289023865468</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2330264472442121</v>
+        <v>0.2393040933892123</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1197384884295225</v>
-      </c>
-      <c r="J58" s="3" t="n">
-        <v>0.1014417301680661</v>
-      </c>
-      <c r="K58" s="3" t="n">
-        <v>0.001732688056401921</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>-0.0005365126676601939</v>
+        <v>0.02230340622991611</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>-0.05623250008968705</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>-0.09124087591240881</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>0.002783535682558513</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3779,25 +3779,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3654045607325793</v>
+        <v>0.3362066323407147</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1308325430827848</v>
+        <v>0.1329051409563049</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2317961273848173</v>
+        <v>0.2276686653366782</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.09880031643125475</v>
+        <v>0.09347207319802897</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>-0.05761237451432744</v>
+        <v>-0.03961152471189977</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.08196452485719752</v>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v>-0.007739572255701321</v>
+        <v>-0.07718982088248139</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>0.006162548377493415</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>XMMO</t>
+          <t>PPA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3824,36 +3824,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D60" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3352553231933013</v>
+        <v>0.3919271046315291</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.09102380164053425</v>
+        <v>0.07051629975097984</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2311758171570499</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>0.01961798531124881</v>
+        <v>0.2246123511421001</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>-0.09004365764939393</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.1444060378263002</v>
+        <v>-0.0919920572078825</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.1138359067514382</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>-0.008132836326669057</v>
+        <v>-0.1258325144666449</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0.004138709475136393</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3872,49 +3872,53 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ONEQ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.5169349053484442</v>
+        <v>0.3355208862526571</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1814608626799286</v>
+        <v>0.1490683760315614</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2143208554450089</v>
+        <v>0.2034310803360759</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1663549758676877</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>-0.02412621067180942</v>
+        <v>0.1785106707473885</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0.0262430347973841</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.02706038739080896</v>
+        <v>-0.04517309316070939</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.007842757552285029</v>
+        <v>-0.001471670345842613</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3924,53 +3928,49 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D62" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>ONEQ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.375822336816555</v>
+        <v>0.4884989488888307</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1409505414029597</v>
+        <v>0.1798301752890308</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.2034131758991924</v>
+        <v>0.2006332262387114</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1814651058864873</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>0.03366488103342435</v>
+        <v>0.1693167603152623</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>-0.006877582048748665</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.05190456257848475</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>-0.002788376871147635</v>
+        <v>-0.01732673267326734</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>0.007319215380111155</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3980,153 +3980,153 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Gold Bullion</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0.4485699058447328</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0.1752666474488327</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0.1978956471605651</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>-0.1331986818326777</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0.0004907975460124447</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>-0.0188906268800384</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>0.009408269373607281</v>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="21" customHeight="1">
+      <c r="A64" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr"/>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>Gold Bullion</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.4445938090393837</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0.1732023251010593</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>0.196453335693842</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>-0.1342565375487186</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>-5.029801574318871e-05</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>-0.01943327825593721</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0.008778383864011197</v>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>RSP</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" s="19" t="inlineStr">
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Equal Weight</t>
         </is>
       </c>
-      <c r="F63" s="3" t="n">
-        <v>0.2951969509794785</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0.1510829784726413</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>0.1984798799511605</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>0.1064226851193966</v>
-      </c>
-      <c r="J63" s="3" t="n">
-        <v>0.008965716352318465</v>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>-0.03954751537460166</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>-0.004883493790986404</v>
-      </c>
-      <c r="M63" s="6" t="inlineStr">
+      <c r="F65" s="3" t="n">
+        <v>0.2715614477256438</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0.1536356643046668</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>0.1899057195264289</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>0.1007854375841746</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>0.01281527492204937</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>-0.03048145296435523</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.0004673770798280241</v>
+      </c>
+      <c r="M65" s="6" t="inlineStr">
         <is>
           <t>CORRECTION</t>
         </is>
       </c>
-      <c r="N63" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="21" customHeight="1">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>IAU</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Gold Bullion</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>0.4355784609916473</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>0.1761793826441467</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>0.198019801980198</v>
-      </c>
-      <c r="I64" s="5" t="n">
-        <v>-0.1436446517544789</v>
-      </c>
-      <c r="J64" s="5" t="n">
-        <v>-0.00590696529657897</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>-0.01823043266893531</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>0.002979885771045465</v>
-      </c>
-      <c r="M64" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N64" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="21" customHeight="1">
-      <c r="A65" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="inlineStr"/>
-      <c r="D65" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>Gold Bullion</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0.4325955003089448</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>0.17509391211019</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>0.1969471110846104</v>
-      </c>
-      <c r="I65" s="5" t="n">
-        <v>-0.14395239232891</v>
-      </c>
-      <c r="J65" s="5" t="n">
-        <v>-0.006052200226957627</v>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>-0.01825744744445557</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0.003334690968333165</v>
-      </c>
-      <c r="M65" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4151,34 +4151,34 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3185948157100615</v>
+        <v>0.2986810746393047</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1569234436457141</v>
+        <v>0.1574485295552537</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1948033222651731</v>
+        <v>0.1844909606897531</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1145189679089229</v>
-      </c>
-      <c r="J66" s="5" t="n">
-        <v>-0.0023722627737226</v>
+        <v>0.116888067890075</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0.00799782745037203</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.03170386114063051</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>-0.006677265500794949</v>
+        <v>-0.02283042423451853</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0.001600512163892454</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IVV</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -4203,25 +4203,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3947953966798867</v>
+        <v>0.375204866734334</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1622961019684874</v>
+        <v>0.1635680059140636</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1947046323259263</v>
+        <v>0.1828020488329831</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1354853301442482</v>
+        <v>0.1395333867309287</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.00334501222978778</v>
+        <v>0.01595471088608957</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.02712681400953798</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>-0.007325240686479773</v>
+        <v>-0.01626142171286971</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0.003619649525998359</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VOO</t>
+          <t>IVV</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -4255,25 +4255,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3983768668221292</v>
+        <v>0.375437158110167</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1654134090232802</v>
+        <v>0.1638786064019053</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1945571140665079</v>
+        <v>0.1827849705628419</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1385610677159492</v>
+        <v>0.139798144869955</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.00633788824960213</v>
+        <v>0.01578604325738286</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.02439707963733684</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>-0.004433004433004317</v>
+        <v>-0.01598461650382643</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>0.003689647902171522</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4307,25 +4307,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3970412019784939</v>
+        <v>0.3735752912027084</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1648471658582287</v>
+        <v>0.1627477542281526</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1939917991290847</v>
+        <v>0.1820542165113699</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1380879567405002</v>
+        <v>0.1390884803281527</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.005976482636546265</v>
+        <v>0.01556388160607192</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.02440940824896309</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>-0.00458679423825048</v>
+        <v>-0.01633297526757871</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>0.003512061157395774</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D70" s="12" t="inlineStr">
         <is>
           <t>Defensive Equity</t>
         </is>
@@ -4363,25 +4363,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.1248581418638091</v>
+        <v>0.1113287257679845</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1305727313477918</v>
+        <v>0.1419303734821009</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1823291073464774</v>
+        <v>0.1756045981260685</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1312717337307503</v>
+        <v>0.1220588235294118</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.1096357656230966</v>
+        <v>0.1190417990711319</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.04377493176569391</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>-0.003718691895439163</v>
+        <v>-0.02864417568427757</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>0.005159732133055206</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4415,25 +4415,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.6214527267687424</v>
+        <v>0.5421881810623568</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.3145552222140875</v>
+        <v>0.2822296981562014</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1805944597597668</v>
+        <v>0.1633905674777287</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.04406410466427935</v>
+        <v>0.02959479971926293</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.09064665127020777</v>
+        <v>0.08805579773321703</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.1134689065723549</v>
-      </c>
-      <c r="L71" s="3" t="n">
-        <v>0.001590668080593938</v>
+        <v>0.102148954960259</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>-0.008999470619375449</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4471,25 +4471,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.4217865231653308</v>
+        <v>0.4021147510100656</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1585320650976809</v>
+        <v>0.1566268027388706</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1776500607509988</v>
+        <v>0.1629421035477405</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1498476080591153</v>
+        <v>0.1557767834206549</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.01420293760948654</v>
+        <v>0.02694047523581511</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.01623402086110892</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>-0.006494535086329689</v>
+        <v>-0.005430451601678321</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0.004092261904761862</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4508,40 +4508,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MGK</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.456609227779883</v>
+        <v>0.3290879582406203</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1322191214548667</v>
+        <v>0.1330888397225398</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1534522032384673</v>
+        <v>0.1510047944633168</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1627451636941937</v>
+        <v>0.07710197676224673</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>-0.001693694837027637</v>
+        <v>-0.01062739373465327</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.01840828924162263</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>-0.006249302533199441</v>
+        <v>-0.015565490975327</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0.003883823032759359</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4560,49 +4560,53 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VWO</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>SPGP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D74" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.347634783895342</v>
+        <v>0.2531641889530138</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1363029538888361</v>
+        <v>0.09810631382619772</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1533801174984455</v>
+        <v>0.1405408803314658</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.07761513445368529</v>
-      </c>
-      <c r="J74" s="5" t="n">
-        <v>-0.02547034678826077</v>
+        <v>0.1219852907951933</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0.01483366655839791</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.01480618865413408</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>-0.006542526421741357</v>
+        <v>-0.0372056514913659</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>0.002042316804182764</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4612,14 +4616,10 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SPGP</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>MGK</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -4627,29 +4627,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.2850766936170055</v>
+        <v>0.4319875923469276</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.09450852134092647</v>
+        <v>0.1307574328946068</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1526271831227746</v>
+        <v>0.1361731791203218</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.128319537744473</v>
+        <v>0.1701418064640075</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.009183961283154352</v>
+        <v>0.01788992876329587</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.05042277557986197</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>-0.007942296782559422</v>
+        <v>-0.004766655581421086</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0.00819764177428417</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SCHG</t>
+          <t>VUG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -4683,25 +4683,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.4141642268862928</v>
+        <v>0.4002374710418513</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1185605855331331</v>
+        <v>0.1095867238939743</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1434813869246168</v>
+        <v>0.1245178715070989</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1592042294693745</v>
+        <v>0.1548532455994047</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.02414047281452869</v>
+        <v>0.01149038344291564</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.02179379715004193</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>-0.006808510638297904</v>
+        <v>-0.01327782153707668</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0.007236388697450025</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VUG</t>
+          <t>SCHG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -4735,34 +4735,34 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.4247512411929075</v>
+        <v>0.3862233527733521</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1125485195390841</v>
+        <v>0.1147004433733108</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.141684869464987</v>
+        <v>0.1232507024560034</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1491233756379013</v>
-      </c>
-      <c r="J77" s="5" t="n">
-        <v>-0.005856669361022693</v>
+        <v>0.1628062603113802</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0.03758196545812909</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.025520483546004</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>-0.007410785543267462</v>
+        <v>-0.007612066535099937</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>0.005427020851185516</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4791,34 +4791,34 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1315912252320051</v>
+        <v>0.1126062457459736</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1140207712138837</v>
+        <v>0.1342731631333753</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1200919384962993</v>
+        <v>0.1200423658362917</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1208792439574706</v>
+        <v>0.1231397557034741</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.0736187231521257</v>
-      </c>
-      <c r="K78" s="5" t="n">
-        <v>-0.005420240137221199</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>-0.004805711931896162</v>
+        <v>0.07279843001126829</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0.01270558840554048</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>0.001724613686534315</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4828,40 +4828,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>IGF</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1725139399991877</v>
+        <v>0.2299657124531489</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.02223627883594648</v>
+        <v>0.06543696278709432</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.114039767925747</v>
+        <v>0.1057088960634056</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>-0.02098565862037782</v>
+        <v>-0.04923092824863606</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>-0.09418775261933843</v>
+        <v>-0.05245017233628069</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.08240593534711182</v>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v>-0.003739930955120707</v>
+        <v>-0.03642182261505655</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0.001742712294042992</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4880,40 +4880,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IGF</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Robotics &amp; AI</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.2541332399697496</v>
+        <v>0.1482264088501977</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.06480215695845093</v>
+        <v>0.0205889069985461</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.1120367266587625</v>
+        <v>0.1043969231097286</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.04820348949444919</v>
+        <v>-0.01165973051436586</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-0.05296324081020265</v>
+        <v>-0.07688815551373085</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.04247572815533984</v>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v>-0.004259346900142069</v>
+        <v>-0.07588577472236901</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.009240542881894243</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4932,49 +4932,53 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VNQ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+          <t>EDEN</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>U.S. Equity REITs</t>
+          <t>Denmark Equity</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.1280379352449863</v>
+        <v>0.1054209657380563</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05316603035906975</v>
+        <v>0.07817611883508402</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.1061041315662792</v>
+        <v>0.09912073717437253</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.03243508233017312</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>-0.02955022246286176</v>
+        <v>0.1222102605502378</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>0.06287202380952395</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.04785996155013661</v>
+        <v>-0.01905579399141633</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.002438248701367551</v>
+        <v>-0.005222841225626662</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4984,53 +4988,49 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EDEN</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>VNQ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
+          <t>U.S. Equity REITs</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.106413404983583</v>
+        <v>0.1144741550336943</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.09152572171726781</v>
+        <v>0.06305438706331401</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.1043526691782559</v>
+        <v>0.09836622212868829</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1405424971441942</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>0.05928999538958046</v>
+        <v>0.03587412992121819</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>-0.02441533079223701</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.01161490148842814</v>
+        <v>-0.03214941824862227</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0.002530761846583296</v>
+        <v>0.007757704569606894</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N82" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5040,49 +5040,49 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VFH</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.2473720974720039</v>
+        <v>0.09508563658794889</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.07210980589707816</v>
+        <v>0.08339266194079697</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.1028055792232818</v>
+        <v>0.09607754615467967</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1648814794486677</v>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>0.06223280129458653</v>
+        <v>0.0006511559330490968</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>-0.0152966345479506</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.02783425646778381</v>
+        <v>-0.01157298063297119</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.004522937755761292</v>
+        <v>-0.0003582945180938824</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5092,49 +5092,49 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>VFH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" s="13" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.09796380791803916</v>
+        <v>0.2136323698770677</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.0713672387573272</v>
+        <v>0.07044292144597097</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.1015646194269473</v>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>-0.002288399382873396</v>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>-0.01367613195598605</v>
+        <v>0.09376563728782683</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>0.1538760942531048</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0.04355188665514675</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.02741317226158668</v>
+        <v>-0.02132332105412293</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.008173418621179818</v>
+        <v>-0.003678061445261727</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5159,25 +5159,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.226075553632237</v>
+        <v>0.1936421212846433</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.0730899270095775</v>
+        <v>0.07132672527087336</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.09781724107083578</v>
+        <v>0.08929883173400799</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1631318471000425</v>
+        <v>0.152552237837057</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.06514461841392083</v>
+        <v>0.0456002104566593</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.02252407152682245</v>
+        <v>-0.0164987843001041</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.003156233561283583</v>
+        <v>-0.003869832893579561</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5211,25 +5211,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.3490403179240267</v>
+        <v>0.3280771083217551</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.05322720609303744</v>
+        <v>0.05218563372139151</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.09454853448805167</v>
+        <v>0.08219284503618107</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.09029001792904601</v>
+        <v>0.09797342983501145</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.02998786319735758</v>
+        <v>-0.01362254720773359</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.03775193798449616</v>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v>-0.005448281387709364</v>
+        <v>-0.02772815533980577</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>0.008458873761379326</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N86" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5263,25 +5263,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.3457390958425595</v>
+        <v>0.3246930134342738</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.05090696576167719</v>
+        <v>0.05062659339222453</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.09313519086990896</v>
+        <v>0.08096696645823531</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.08812480025202785</v>
+        <v>0.09687503059959623</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>-0.03144097780636856</v>
+        <v>-0.01443634114653647</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.038630377524144</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>-0.006679861454725433</v>
+        <v>-0.02806780781231488</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>0.008385222083852062</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5319,25 +5319,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.2317127876072786</v>
+        <v>0.2080142495312849</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.0005680418990761105</v>
+        <v>0.005301066277424438</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.08441491170410664</v>
+        <v>0.07729299364948794</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.08969639142972086</v>
+        <v>0.0902037611826052</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>-0.05027298208272601</v>
+        <v>-0.03927402190059881</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.07731991592892162</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>-0.01129500085309676</v>
+        <v>-0.06682669227076332</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>0.006316007454959527</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="N88" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5407,110 +5407,110 @@
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
-      <c r="A90" t="n">
+      <c r="A90" s="15" t="n">
         <v>89</v>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D90" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>US Dollar Index Bullish</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.02868848575421734</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.06976064067516541</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.06445729472280992</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0.02023121387283222</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0.0110991765127102</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>0.004982206405693912</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0.0007087172218285254</v>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="21" customHeight="1">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
         <is>
           <t>XLU</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" s="13" t="inlineStr">
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" s="12" t="inlineStr">
         <is>
           <t>Defensive Equity</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="F90" s="3" t="n">
-        <v>0.1135138050281166</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>-0.00649641398056866</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>0.06539554444629725</v>
-      </c>
-      <c r="I90" s="5" t="n">
-        <v>-0.1139530164053916</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>-0.07054428301464322</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>-0.06747912435116232</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>-0.01195600191296031</v>
-      </c>
-      <c r="M90" s="6" t="inlineStr">
+      <c r="F91" s="3" t="n">
+        <v>0.09628522316456323</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-0.004976909315993372</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0.05979074605639867</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>-0.1080686278673896</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>-0.07357147026055444</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>-0.06111362607514714</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0.003872216844143184</v>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
         <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N90" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="21" customHeight="1">
-      <c r="A91" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="16" t="inlineStr">
-        <is>
-          <t>UUP</t>
-        </is>
-      </c>
-      <c r="C91" s="15" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D91" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E91" s="15" t="inlineStr">
-        <is>
-          <t>US Dollar Index Bullish</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>0.02687481215326204</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>0.06549046790726076</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>0.06133724496361093</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>0.01767039307609086</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>0.008938148015731118</v>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>0.003913198150124586</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>0.001774937877174088</v>
-      </c>
-      <c r="M91" s="6" t="inlineStr">
-        <is>
-          <t>STEADY_POSITIVE</t>
-        </is>
-      </c>
       <c r="N91" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5539,25 +5539,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.01542072471457079</v>
+        <v>0.01732672312181882</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.04441063037917181</v>
+        <v>0.04839013451428054</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.0428293879410504</v>
+        <v>0.04640830061160695</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.009167303284950412</v>
+        <v>0.0126339969372129</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.003418154196733969</v>
+        <v>0.004939209726443794</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.0015163002274452</v>
+        <v>0.001893939393939448</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.0015163002274452</v>
+        <v>0.001135503406510141</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -5591,25 +5591,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.09035673360533791</v>
+        <v>0.08801158523529184</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02706039630362578</v>
+        <v>0.02663323249827942</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03879525088789815</v>
+        <v>0.03455273963676975</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.01668228115259041</v>
+        <v>0.01454969874522249</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.006006242221713087</v>
+        <v>-0.003472265135031738</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.01129660014737466</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>-0.00191009805170006</v>
+        <v>-0.007655005718964825</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>0.002424087777494144</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="N93" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5628,269 +5628,269 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Russell Midcap Growth</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.1578992607724272</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.05130117061576267</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0.02583001351527936</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0.03325969248581662</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>-0.03881098381064374</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>-0.07518904995451592</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>0.008425720620842458</v>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N94" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="21" customHeight="1">
+      <c r="A95" s="15" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="16" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr"/>
+      <c r="D95" s="22" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>1-3 Year Treasury</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0.04363954498738298</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0.01693575479864995</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0.02150463936141733</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0.002375301522071993</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>-9.834819146203877e-05</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>-0.004472700746247726</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0.0009838888205633278</v>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="21" customHeight="1">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>XRT</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D94" s="22" t="inlineStr">
+      <c r="D96" s="23" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="F94" s="3" t="n">
-        <v>0.2658907582584942</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>-0.02839193525125228</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>0.03850681758472851</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>0.04309552558696916</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>-0.04620810085147886</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>-0.06441821247892077</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>-0.02689429373246022</v>
-      </c>
-      <c r="M94" s="6" t="inlineStr">
+      <c r="F96" s="3" t="n">
+        <v>0.2543847599000142</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>-0.03766998186512971</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0.007804399898630798</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.04525609753383653</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>-0.03800690143156449</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>-0.04512222983778846</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>0.004446046623407973</v>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
         <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N94" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="21" customHeight="1">
-      <c r="A95" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>IWP</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Russell Midcap Growth</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>0.1838585885459676</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>-0.05859856925402995</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>0.0245481203055733</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0.03152591267229488</v>
-      </c>
-      <c r="J95" s="5" t="n">
-        <v>-0.05344899958024341</v>
-      </c>
-      <c r="K95" s="5" t="n">
-        <v>-0.08115449915110351</v>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v>-0.01219245090165721</v>
-      </c>
-      <c r="M95" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N95" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="21" customHeight="1">
-      <c r="A96" s="15" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="16" t="inlineStr">
-        <is>
-          <t>SHY</t>
-        </is>
-      </c>
-      <c r="C96" s="15" t="inlineStr"/>
-      <c r="D96" s="23" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="inlineStr">
-        <is>
-          <t>1-3 Year Treasury</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>0.0418554790154495</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>0.0163036689489624</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>0.02187413597769727</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0.001511318431892672</v>
-      </c>
-      <c r="J96" s="5" t="n">
-        <v>-0.000837920863984043</v>
-      </c>
-      <c r="K96" s="5" t="n">
-        <v>-0.005451226166327539</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v>-0.0003688222276863051</v>
-      </c>
-      <c r="M96" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
       <c r="N96" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
-      <c r="A97" t="n">
+      <c r="A97" s="15" t="n">
         <v>96</v>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="16" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0.03626268138515121</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>-0.009060559197648588</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>-0.00120264236319223</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>-0.01702502965241648</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>-0.01832150027623169</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>-0.007867378477100173</v>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>0.001323376500614426</v>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>BROAD_WEAKNESS</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>Long and 1m momentum negative; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="21" customHeight="1">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
         <is>
           <t>VCR</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D97" s="22" t="inlineStr">
+      <c r="D98" s="23" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="F97" s="3" t="n">
-        <v>0.182809870300594</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>-0.05193703990319309</v>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>0.01423590115630846</v>
-      </c>
-      <c r="I97" s="3" t="n">
-        <v>0.01454093707837867</v>
-      </c>
-      <c r="J97" s="5" t="n">
-        <v>-0.06146867894582086</v>
-      </c>
-      <c r="K97" s="5" t="n">
-        <v>-0.06524413204468438</v>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v>-0.01850387474300175</v>
-      </c>
-      <c r="M97" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N97" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="21" customHeight="1">
-      <c r="A98" s="15" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="16" t="inlineStr">
-        <is>
-          <t>TIP</t>
-        </is>
-      </c>
-      <c r="C98" s="15" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D98" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
       <c r="F98" s="3" t="n">
-        <v>0.0324400741943367</v>
+        <v>0.161724356719873</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.00939540774522829</v>
-      </c>
-      <c r="H98" s="3" t="n">
-        <v>0.001841245158691773</v>
-      </c>
-      <c r="I98" s="5" t="n">
-        <v>-0.0148769365689928</v>
+        <v>-0.05803184311770326</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>-0.007402505925005021</v>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v>0.00734188173506678</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.0196189135676631</v>
+        <v>-0.05695222870354899</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.01121600149546675</v>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v>-0.0002835002835002154</v>
+        <v>-0.05100691619202591</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>0.00230959286711796</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5900,40 +5900,40 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>FXE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="23" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>7-10 Year Treasury</t>
+          <t>Euro Currency</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.01538597710485456</v>
+        <v>0.07236610651352637</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.02644598068997051</v>
+        <v>-0.01219752729914003</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.00621891635294447</v>
-      </c>
-      <c r="I99" s="5" t="n">
-        <v>-0.03477829591004789</v>
+        <v>-0.009253443882858758</v>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>0.004313458031669937</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.02671881234823137</v>
+        <v>-0.003954474767205007</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.02035364193368949</v>
+        <v>-0.002971580772200277</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.001209721763994476</v>
+        <v>-0.000281716593107384</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5952,40 +5952,40 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FXE</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D100" s="22" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Euro Currency</t>
+          <t>7-10 Year Treasury</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.07631019183632248</v>
+        <v>0.02173734101011005</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.009364908924886173</v>
+        <v>-0.02537400790945676</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.007342979170091635</v>
-      </c>
-      <c r="I100" s="3" t="n">
-        <v>0.006961750797921828</v>
+        <v>-0.009988458693256375</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>-0.03383184688535446</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>-0.001530039581578824</v>
+        <v>-0.02651773446396233</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.0020368865704532</v>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v>-0.0005631159080243808</v>
+        <v>-0.01554077763163508</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>0.002752697643690905</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6019,25 +6019,25 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.03416340373991567</v>
+        <v>0.03910734404680705</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.0253269993765598</v>
+        <v>-0.02417005300869135</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01227545458995671</v>
+        <v>-0.01924910486495324</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>-0.01745238239234781</v>
+        <v>-0.01871951723950516</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>-0.03164744260810326</v>
+        <v>-0.02862729943516718</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>-0.01321374956940535</v>
-      </c>
-      <c r="L101" s="5" t="n">
-        <v>-0.0001917545541706422</v>
+        <v>-0.005017531126556229</v>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>0.004315304948216303</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="N101" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr"/>
-      <c r="D102" s="23" t="inlineStr">
+      <c r="D102" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -6071,25 +6071,25 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.04785345803437091</v>
+        <v>-0.03910794727109368</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.06161405462427538</v>
+        <v>-0.06020394699774678</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.04979175648478162</v>
+        <v>-0.0599781224510999</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.05287684827608152</v>
+        <v>-0.051848346366826</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-0.04752598183519485</v>
+        <v>-0.04908140829823937</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>-0.01244179706940673</v>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v>-0.002718398616088136</v>
+        <v>-0.000240233288224867</v>
+      </c>
+      <c r="L102" s="3" t="n">
+        <v>0.003840911906827005</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6127,25 +6127,25 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.01896516182230457</v>
+        <v>-0.02330811694949897</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.1046095954844778</v>
+        <v>-0.1059329964439453</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>-0.06340545625587957</v>
+        <v>-0.07205689687441519</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>-0.01997528830313011</v>
+        <v>-0.01545754328112114</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>-0.03390174583840833</v>
+        <v>-0.03319166160696208</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>-0.04399357171554841</v>
-      </c>
-      <c r="L103" s="5" t="n">
-        <v>-0.01734462110262225</v>
+        <v>-0.03650665590964086</v>
+      </c>
+      <c r="L103" s="3" t="n">
+        <v>0.003782307207396585</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="N103" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6183,25 +6183,25 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.04580275029989911</v>
+        <v>-0.07149227420351134</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.1551700754117606</v>
+        <v>-0.162151469625622</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>-0.1042912030459175</v>
+        <v>-0.1311770856391509</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.1249713893339437</v>
+        <v>0.1127272727272728</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.1087299796977217</v>
+        <v>0.08246738890117178</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>-0.05680291690654382</v>
+        <v>-0.03565097498522751</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>-0.01857028753993606</v>
+        <v>-0.00386571719226847</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -206,6 +206,9 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -687,25 +690,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.260982016074104</v>
+        <v>2.238944662041992</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.311801027654965</v>
+        <v>1.296178133248584</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.38991549968687</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.3319199583426318</v>
+        <v>0.3229189912965855</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1304453401971735</v>
+        <v>-0.1363216939439561</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.03268503511615339</v>
+        <v>-0.03922204213938407</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.0145050711088448</v>
+        <v>0.007649158592554883</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -743,25 +746,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.539019656450582</v>
+        <v>1.533425216106469</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9400283117280104</v>
+        <v>0.9357538229694546</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>1.320015622747218</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.3747884639736054</v>
+        <v>0.3717593752746817</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.210556452686355</v>
+        <v>-0.2122958435746771</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.1637865311308767</v>
+        <v>-0.1656289707750952</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.02364286825322748</v>
+        <v>0.02138746305801842</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -799,25 +802,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.821123410913834</v>
+        <v>1.805497353687918</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.157439387161808</v>
+        <v>1.145489596789781</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.312598998441777</v>
+        <v>1.31259916577323</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.4908218252349743</v>
+        <v>0.4825642399536483</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.1518094333230472</v>
+        <v>-0.1565075171722338</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.06709317585301844</v>
+        <v>-0.07226049868766404</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.01912996729537197</v>
+        <v>0.01348505891313101</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -855,25 +858,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.902459711620017</v>
+        <v>1.900763358778626</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.041766109785203</v>
+        <v>1.040572792362768</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>1.227028639618138</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.5161719096145325</v>
+        <v>0.5152857775808597</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1233508389906494</v>
+        <v>-0.1238631996925834</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.08318821165438728</v>
+        <v>-0.08372404554588075</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.03134418324291732</v>
+        <v>0.03074141048824597</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -907,25 +910,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.553483673620697</v>
+        <v>1.541445522100925</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9851815911428128</v>
+        <v>0.9758227286728212</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.178933257724606</v>
+        <v>1.178933517033134</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4978537038535247</v>
+        <v>0.490792103505344</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1384161719129451</v>
+        <v>-0.1424780910741782</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.08892042282383739</v>
+        <v>-0.09321568867180086</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.02048712037686684</v>
+        <v>0.01567605492633062</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -963,25 +966,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.494319805827963</v>
+        <v>1.483472518536784</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.88576272843951</v>
+        <v>0.8775619315607031</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.089520989351406</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.455481484051951</v>
+        <v>0.4491518924063194</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1422168333097801</v>
+        <v>-0.1459471570721483</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.09751434034416828</v>
+        <v>-0.1014390661165342</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.01909090909090927</v>
+        <v>0.0146590909090909</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1019,25 +1022,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.44063773353152</v>
+        <v>1.434749317565194</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8002255771820876</v>
+        <v>0.795882254579954</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.940028314473321</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3889840757911711</v>
+        <v>0.3856329369078815</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1050974025974026</v>
+        <v>-0.1072564935064936</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.07206221489050124</v>
+        <v>-0.07430100829868547</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.0168784932947188</v>
+        <v>0.01442511667373769</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1075,25 +1078,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.272901483915839</v>
+        <v>1.270820834443195</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.8130555683734633</v>
+        <v>0.8113958690248975</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.7891558977541133</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.4964383561643835</v>
+        <v>0.495068493150685</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.05250987571056931</v>
+        <v>0.05154639175257736</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.01335807050092752</v>
+        <v>0.01243042671614103</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.02409299709384083</v>
+        <v>0.02315552638980023</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -1127,25 +1130,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7911528677979494</v>
+        <v>0.7856180131315189</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.6701372362814395</v>
+        <v>0.6649761864300576</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.7152964224810276</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.25197258446974</v>
+        <v>0.2481037449632344</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.1488286806181713</v>
+        <v>0.1452785758947004</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>-0.02632733655111885</v>
+        <v>-0.02933617501410402</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.008439914302408758</v>
+        <v>0.005323638252288543</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -1183,25 +1186,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.2</v>
+        <v>1.19568345323741</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8623629719853834</v>
+        <v>0.8587088915956149</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.7052375152253347</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.4659635666347075</v>
+        <v>0.4630872483221478</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2605111294311622</v>
+        <v>0.2580379225061828</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.09214285714285708</v>
+        <v>0.09000000000000008</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.002609262883235597</v>
+        <v>-0.004566210045662156</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -1239,25 +1242,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.6437770037455095</v>
+        <v>0.6276030611382082</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.6379116185249694</v>
+        <v>0.6217953883711886</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.7017781642581455</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.06472525477789581</v>
+        <v>0.05424889142442235</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.01083236908835761</v>
+        <v>0.0008862847435928689</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.0375293014533522</v>
+        <v>-0.04699953117674638</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.00223566863502711</v>
+        <v>-0.01205317003231998</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1295,25 +1298,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.137146817955403</v>
+        <v>1.120403502145883</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6191494579722256</v>
+        <v>0.6064643534722092</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.6536075030319715</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1014070095546449</v>
+        <v>0.09277811927866719</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-0.04431879501948444</v>
+        <v>-0.05180600745326547</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.02083810396152974</v>
+        <v>-0.02850927410121373</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.01099420735311485</v>
+        <v>0.003073649367537401</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1351,34 +1354,34 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.211672993766111</v>
+        <v>1.203303836082411</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5692914278758947</v>
+        <v>0.5633529922132332</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.5577640784891604</v>
+        <v>0.5577639747011311</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1164073113671125</v>
+        <v>0.112182731669118</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.0197480422199523</v>
+        <v>0.01588922937237558</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.007399932727884195</v>
+        <v>0.003587846171095421</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.01502485314053326</v>
+        <v>0.01118391323994583</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1403,25 +1406,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.8928687723868447</v>
+        <v>0.8785411917942036</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.4997420020639836</v>
+        <v>0.4883900928792571</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.5368937048503613</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.1888082612336031</v>
+        <v>-0.1949483672899804</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.08297838775832145</v>
+        <v>-0.08991954566966398</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-0.02417324156454592</v>
+        <v>-0.03155950982037947</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.0104293412132801</v>
+        <v>0.002781157656874589</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1459,25 +1462,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.186084730537437</v>
+        <v>1.195219367588116</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6947419706746465</v>
+        <v>0.7018235135720523</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0.5337978139154207</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.3688929921359141</v>
+        <v>0.3746129628532913</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.285014969832883</v>
+        <v>0.2903844530876452</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.1049317943336832</v>
+        <v>0.1095487932843651</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.006115039174469761</v>
+        <v>0.01031912860691753</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1515,25 +1518,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.7187648592956184</v>
+        <v>0.7104157560617048</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.4706063027892593</v>
+        <v>0.4634628136241561</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.5013233061992033</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.100718809143264</v>
+        <v>0.095372053269835</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.0585365853658536</v>
+        <v>-0.06310975609756087</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.02045995241871534</v>
+        <v>-0.02521808088818389</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.005371968093765167</v>
+        <v>0.0004883607357968334</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1571,25 +1574,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.6980937108127421</v>
+        <v>0.6964302177574788</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.3926510162873016</v>
+        <v>0.3912867421726001</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.4828750110728948</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.3533885254020552</v>
+        <v>0.3520627137588321</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.05532886925240577</v>
+        <v>-0.0562542915983576</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.0608439646712462</v>
+        <v>-0.06176398429833163</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.008064781592547421</v>
+        <v>0.007077257315909025</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1627,25 +1630,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.7430601722848915</v>
+        <v>0.7361314833547414</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.3678152330546329</v>
+        <v>0.3623781480850803</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.4804405645667975</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.01252372494787246</v>
+        <v>-0.01644895715989114</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.1537942454667961</v>
+        <v>-0.1571579253542081</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.0760755508919202</v>
+        <v>-0.07974816369359916</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.005998286203941827</v>
+        <v>0.001999428734647202</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1683,25 +1686,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.5308840075618591</v>
+        <v>0.5289519217314198</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.5084619677587492</v>
+        <v>0.5065582752975406</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.4619433315712811</v>
+        <v>0.4619434238945752</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.117418737665286</v>
+        <v>0.1160084747720516</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.1764286782882509</v>
+        <v>0.1749439406016491</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.03181972596534943</v>
+        <v>0.03051749518740787</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>-0.0181563493346264</v>
+        <v>-0.01939550670761281</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1735,25 +1738,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.5105568248250847</v>
+        <v>0.5107901251279261</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.5113551912471683</v>
+        <v>0.511588749459384</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0.461607292045245</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1212188948342001</v>
+        <v>0.1213921630917854</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.1773243121276991</v>
+        <v>0.177506250670757</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.03403643336529227</v>
+        <v>0.03419622882710138</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-0.01850447444259085</v>
+        <v>-0.01835279842256954</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1791,25 +1794,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.584558309927852</v>
+        <v>0.5817859648170842</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.5373837987199606</v>
+        <v>0.5346938975597588</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.4505188056157297</v>
+        <v>0.4505187180657855</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.1527946771691253</v>
+        <v>0.1507776420602658</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.2424920621518849</v>
+        <v>0.2403181965566004</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.05988546495773117</v>
+        <v>0.05803108808290158</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-0.02689033550325481</v>
+        <v>-0.02859288933400095</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1847,25 +1850,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5182110626639249</v>
+        <v>0.5212023168510274</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.446472707561582</v>
+        <v>0.4493226193093143</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0.4386294013217875</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.2146884029528506</v>
+        <v>0.2170816418513883</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.1842680505112915</v>
+        <v>0.1866013537336562</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.005451929616194562</v>
+        <v>0.007432920512886687</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.005049504950495054</v>
+        <v>0.007029702970297036</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1903,25 +1906,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6407794700255223</v>
+        <v>0.6458365095800982</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3928794258100374</v>
+        <v>0.3971724136732793</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0.4170762664937646</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.1348416385427935</v>
+        <v>0.1383393292191653</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.03019510869103192</v>
+        <v>0.03337026873463</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.01707518589920143</v>
+        <v>-0.01404571743321403</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.009675229150164055</v>
+        <v>0.01278714495869626</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1955,25 +1958,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5756550103278046</v>
+        <v>0.5648338502091006</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.5351281678287416</v>
+        <v>0.5245853347860239</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.4008216425454265</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.1644645340751043</v>
+        <v>0.1564673157162724</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.2003584229390682</v>
+        <v>0.1921146953405017</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.09587696335078544</v>
+        <v>0.08835078534031404</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.005641330166270664</v>
+        <v>-0.01247030878859867</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -2007,25 +2010,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.749375181697769</v>
+        <v>0.747489266236689</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3646538749781536</v>
+        <v>0.3631827086618769</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.3999618665687914</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.3327515733093882</v>
+        <v>0.3313147992976273</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-0.003748049471527182</v>
+        <v>-0.004822059767482956</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>-0.02522068095838581</v>
+        <v>-0.02627154266498533</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.00968760204636987</v>
+        <v>0.008599107434418052</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2059,25 +2062,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.373369003827534</v>
+        <v>1.341382898654656</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.3932593333806689</v>
+        <v>0.3744822534159697</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.3627653555179977</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>-0.01413957181763137</v>
+        <v>-0.02742610049933447</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.04088210824324845</v>
+        <v>0.02685404748525322</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.02237654320987659</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>0.0004314529177005255</v>
+        <v>0.008597883597883715</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>-0.01305145076043568</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -2086,7 +2089,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2118,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6287193633382655</v>
+        <v>0.6150210293926057</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.21893385047591</v>
+        <v>0.2086820939538248</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.3624584417851</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-0.01108340053059376</v>
+        <v>-0.01940061330998333</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.2287984433273877</v>
+        <v>-0.2352845792119346</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.1053423626787057</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>0.007840644204280656</v>
+        <v>-0.1128668171557562</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>-0.0006357279084552303</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -2142,7 +2145,7 @@
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2171,25 +2174,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.7202570782424873</v>
+        <v>0.7178532991085502</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3303442283097238</v>
+        <v>0.3284851670627844</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.3587878653878944</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.3226558825215473</v>
+        <v>0.3208075651899072</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.01828987118867476</v>
+        <v>0.01686688366605216</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>-0.02093309618278838</v>
+        <v>-0.0223012724038858</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.009736136588119004</v>
+        <v>0.008325102299985732</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -2223,25 +2226,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.7147052306485704</v>
+        <v>0.7132749469368047</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3255325199691865</v>
+        <v>0.3244267115767872</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.3550576040462512</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3212080461896174</v>
+        <v>0.3201058454336403</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.01869694339731165</v>
+        <v>0.01784710862347549</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>-0.02178880365594904</v>
+        <v>-0.02260486371796977</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.009091674383365556</v>
+        <v>0.008249852681202041</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2279,25 +2282,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.4898766039181861</v>
+        <v>0.4925562380978952</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.250986983875344</v>
+        <v>0.253236960465048</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.3537359148051535</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.08493220931095569</v>
+        <v>0.08688352623417694</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>-0.1571669252823606</v>
+        <v>-0.155651038457329</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.07590027700831026</v>
+        <v>-0.07423822714681438</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.004516711833784992</v>
+        <v>0.006323396567299078</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2335,25 +2338,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.7334770963458626</v>
+        <v>0.7310057021251011</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.3263941113174655</v>
+        <v>0.324503089654663</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3381093666486981</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.3240059749912667</v>
+        <v>0.3221184638408294</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.01809687716022257</v>
+        <v>0.01664539058235359</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.008755080581024255</v>
+        <v>-0.01016828469567643</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.009716890595009575</v>
+        <v>0.008277351247600651</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2387,25 +2390,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.5380546213373463</v>
+        <v>0.5413949164019489</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.1349641404681428</v>
+        <v>0.137428891221685</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.3380381699447861</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>-0.04863502014936227</v>
+        <v>-0.04656898346382132</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.1869962385814079</v>
+        <v>-0.1852306747524373</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.151769982380266</v>
+        <v>-0.1499279192695819</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.008186577820085583</v>
+        <v>0.01037601142313194</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2443,25 +2446,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.9252945188951376</v>
+        <v>0.9043674045593209</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.2437261418055863</v>
+        <v>0.230207379394656</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.3304715339423887</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.002040398151487266</v>
+        <v>-0.01288778512810151</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.07420156148169199</v>
+        <v>-0.08426458798732583</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.0651989839119389</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>0.008771929824561431</v>
+        <v>-0.07535986452159182</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>-0.002192982456140302</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2470,7 +2473,7 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2499,25 +2502,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5027586588909818</v>
+        <v>0.5083506658082142</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.08566240452591778</v>
+        <v>0.08970232912722964</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.3236139635431958</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.1159501871598974</v>
+        <v>-0.1126604954723257</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1415749587817239</v>
+        <v>-0.1383806209950025</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.1797741377556211</v>
+        <v>-0.1767219452640147</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.001366289901875595</v>
+        <v>0.005092535088808692</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2555,25 +2558,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.4193252839732184</v>
+        <v>0.4202340592863016</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.2010678598309756</v>
+        <v>0.2018368877857912</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.3045790225491527</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.08805907760902887</v>
+        <v>0.08875574752682192</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.07179365268037552</v>
+        <v>-0.07119933436348502</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.07934449422306045</v>
+        <v>-0.07875501061070489</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.01087378640776704</v>
+        <v>0.01152103559870543</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2607,25 +2610,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.4294668953560006</v>
+        <v>0.4264665150658979</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2152545777396218</v>
+        <v>0.2127039027921473</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.3045311509168953</v>
+        <v>0.3045312415853025</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.1437668525698366</v>
+        <v>0.1413661425344577</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.03890885061845817</v>
+        <v>-0.04092613339077333</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.06843575418994408</v>
+        <v>-0.07039106145251384</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.006033182503770718</v>
+        <v>0.003921568627450966</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2663,25 +2666,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.5394440696424543</v>
+        <v>0.5408078577977011</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.3122125814789893</v>
+        <v>0.3133750660479824</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.3039135882829664</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.2617750273203197</v>
+        <v>0.2628928294352386</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.1346050310327658</v>
+        <v>0.1356101736895985</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.006364680351979013</v>
+        <v>0.007256215327485771</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.004409948844593448</v>
+        <v>-0.003527959075674603</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2719,25 +2722,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1271728912073526</v>
+        <v>0.1286187062208923</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.3322492337540661</v>
+        <v>0.3339578309041547</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.3004951102902829</v>
+        <v>0.3004949690059397</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.07300155969061506</v>
+        <v>0.074377790848833</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-0.03693986925322545</v>
+        <v>-0.03570464890596581</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.02441694952370521</v>
+        <v>0.0257308660900033</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.009947089947089927</v>
+        <v>-0.008677248677248617</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2771,25 +2774,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.3074446711932053</v>
+        <v>0.3047694922042878</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.297231979975989</v>
+        <v>0.2945776029342375</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.3002655537379906</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1235583914409391</v>
+        <v>0.1212593827475492</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.06002021278234126</v>
+        <v>0.0578512149777588</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.002333041703120431</v>
+        <v>-0.004374453193350836</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.003495484998543463</v>
+        <v>-0.005534517914360548</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2823,25 +2826,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.5617365938548884</v>
+        <v>0.5610895938888278</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2054600020967756</v>
+        <v>0.2049604255631936</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2917070022467936</v>
+        <v>0.2917069202044018</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.2393055161152127</v>
+        <v>0.2387919108394438</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.06207345576063872</v>
+        <v>-0.06246209935631797</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.06676978602732653</v>
+        <v>-0.06715648362980142</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.00772496346301077</v>
+        <v>0.007307397870415455</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2875,25 +2878,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4376624270100287</v>
+        <v>0.4332967505301029</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2125830033850131</v>
+        <v>0.2089007360876707</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2835516849073865</v>
+        <v>0.2835516020139315</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1514951987152906</v>
+        <v>0.1479985117244274</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.01654246191383713</v>
+        <v>-0.01952887747451759</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.0552908639027605</v>
+        <v>-0.05815961415897208</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.004769586869608045</v>
+        <v>0.001718454092726418</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -2931,25 +2934,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.5191474065868573</v>
+        <v>0.5182438692712823</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.1994540455343035</v>
+        <v>0.1987405784849845</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2738927634890074</v>
+        <v>0.2738926864500837</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2229995054449561</v>
+        <v>0.2222721068493305</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.0699275171868986</v>
+        <v>-0.07048069273179136</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.05843405354688347</v>
+        <v>-0.05899406501384608</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.01045040232379546</v>
+        <v>0.009849420720510205</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2987,25 +2990,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.758484687325548</v>
+        <v>0.7520401324161423</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1674905030998719</v>
+        <v>0.1632118439180965</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.2687196896505104</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.01469019286007378</v>
+        <v>-0.0183011899876897</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-0.09285984132980729</v>
+        <v>-0.09618435965243666</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.07978845711657845</v>
+        <v>-0.08316087989576149</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.009331651954602727</v>
+        <v>0.005632618747372753</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3039,25 +3042,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.4041075936714134</v>
+        <v>0.403316249921458</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.1485431820952259</v>
+        <v>0.1478959668757012</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2672166275493635</v>
+        <v>0.2672167318535699</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.04822773715454187</v>
+        <v>0.04763696443023924</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>-0.08848985134413856</v>
+        <v>-0.0890035711348518</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.09364890175378848</v>
+        <v>-0.09415971394517275</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.00738077214231625</v>
+        <v>0.00681302043906129</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -3091,25 +3094,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4141007352782209</v>
+        <v>0.4136633394429972</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2588148465515501</v>
+        <v>0.2584252953167663</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2658234043115031</v>
+        <v>0.2658232162978982</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1567113789850034</v>
+        <v>0.156353596312877</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.03586380506049958</v>
+        <v>0.03554340178024584</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.00553675792063979</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>0.0003094059405939209</v>
+        <v>-0.005844355582897531</v>
+      </c>
+      <c r="L46" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3118,7 +3121,7 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d flat.</t>
         </is>
       </c>
     </row>
@@ -3143,25 +3146,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3341763788665986</v>
+        <v>0.3367619920039371</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2301410062469862</v>
+        <v>0.2325250004451394</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.2627222602884116</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1013569727049872</v>
+        <v>0.1034913854427877</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.01612586237822233</v>
+        <v>0.01809509854562208</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.02580239144115803</v>
+        <v>-0.02391441157960983</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.001509596722018447</v>
+        <v>0.003450506793185371</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3199,25 +3202,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4055110808164142</v>
+        <v>0.4017274895322096</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.1649264702167323</v>
+        <v>0.1617902747292432</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2616565941168711</v>
+        <v>0.2616564709050067</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.136673745148175</v>
+        <v>0.1336137218801883</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.04449620667018206</v>
+        <v>-0.04706850488039327</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.07666913829895794</v>
+        <v>-0.07915482421623676</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.007807092826887407</v>
+        <v>0.005093989645912345</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3251,25 +3254,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4601376892904134</v>
+        <v>0.4626786188346796</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2525612082793383</v>
+        <v>0.2547409135245782</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2587156701482509</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1544520763239607</v>
+        <v>0.1564610521963639</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.03793030174245637</v>
+        <v>0.03973650658733519</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.004889477437098999</v>
+        <v>-0.003157787511459786</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.007944696657036676</v>
+        <v>0.009698720594304655</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3303,25 +3306,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4343010415750324</v>
+        <v>0.4323049666946326</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.2261670941311316</v>
+        <v>0.2244608461204027</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2573928912680641</v>
+        <v>0.2573929731133286</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1062708710943585</v>
+        <v>0.1047313903385914</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.001130402212035642</v>
+        <v>-0.00252042391783569</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.02483376306147367</v>
+        <v>-0.02619079929434109</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.004613448902558437</v>
+        <v>0.003215434083601254</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3359,25 +3362,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.2257336654041178</v>
+        <v>0.2277908016523813</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.2613764204219609</v>
+        <v>0.2634931488884122</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2554653410025938</v>
+        <v>0.2554652644905435</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.1477806693283723</v>
+        <v>0.1497068416884004</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.1111108515069255</v>
+        <v>0.112975485638072</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.004708277661131355</v>
+        <v>0.006394350066806886</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.004005595116988836</v>
+        <v>0.005690488301119068</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3411,25 +3414,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4367351555346763</v>
+        <v>0.4438728034890922</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.07386030785434783</v>
+        <v>0.07919520677441549</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0.2510045642986529</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>-0.07350345841991601</v>
+        <v>-0.06890065732654294</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.09974253908281527</v>
+        <v>-0.09527009278705245</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.141601606820369</v>
+        <v>-0.1373371148494238</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.006448598130841088</v>
+        <v>0.01144859813084098</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3463,25 +3466,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.3252481561665113</v>
+        <v>0.3237379971858705</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2583173827553611</v>
+        <v>0.2568834887745308</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.245823015229478</v>
+        <v>0.2458231004157341</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1225536354171952</v>
+        <v>0.1212743720150105</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.1095243804731652</v>
+        <v>0.1082599652247627</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.01002900682773267</v>
+        <v>0.008877976620521588</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.003831417624520994</v>
+        <v>-0.004966652476230959</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3519,25 +3522,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.3080876710443863</v>
+        <v>0.3064013047972807</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.1016394573264683</v>
+        <v>0.1002192409002773</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.2439600928773975</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.01732717285894769</v>
+        <v>0.01601565051640996</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.1329686488503464</v>
+        <v>-0.1340864121609614</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>-0.1144093258021872</v>
+        <v>-0.1155510155029443</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.007037922787837436</v>
+        <v>0.005739665186197396</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3571,25 +3574,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.1915537912133749</v>
+        <v>0.1939613997532961</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2503396767680126</v>
+        <v>0.2528660658456923</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>0.2412743983128098</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1341013214851243</v>
+        <v>0.1363927268694123</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.1050876801533993</v>
+        <v>0.1073205785384481</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0.007303202633941908</v>
+        <v>0.009338521400778177</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.003638315638792911</v>
+        <v>0.005666229273529888</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3623,25 +3626,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.4927317604670887</v>
+        <v>0.4921702184758729</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2064135525672925</v>
+        <v>0.2059597189405957</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0.2398734681355723</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1799139655004163</v>
+        <v>0.179470100597694</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.02599020894726445</v>
+        <v>-0.0263566159682822</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.02698655663516558</v>
+        <v>-0.02735258884600011</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.007997518011651827</v>
+        <v>0.00761832534730611</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3675,25 +3678,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4914661967790952</v>
+        <v>0.4908990117897356</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.205938966298628</v>
+        <v>0.2054805657805445</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2394962376707548</v>
+        <v>0.2394963661476472</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1798026550248886</v>
+        <v>0.1793540671767289</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.02599075919399596</v>
+        <v>-0.0263610996976047</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.0270733144258567</v>
+        <v>-0.02744324331730308</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.007905867658330346</v>
+        <v>0.007522638884946309</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3727,25 +3730,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3158891024316717</v>
+        <v>0.3189200305556283</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.1262289023865468</v>
+        <v>0.1288229802977847</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0.2393040933892123</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.02230340622991611</v>
+        <v>0.0246581093271856</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>-0.05623250008968705</v>
+        <v>-0.05405869117777451</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.09124087591240881</v>
+        <v>-0.0891477028767711</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.002783535682558513</v>
+        <v>0.005093278057447526</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3779,25 +3782,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3362066323407147</v>
+        <v>0.333201877360749</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1329051409563049</v>
+        <v>0.130357669800043</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2276686653366782</v>
+        <v>0.2276687909242543</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.09347207319802897</v>
+        <v>0.09101305262559234</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>-0.03961152471189977</v>
+        <v>-0.04177116977276019</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.07718982088248139</v>
+        <v>-0.07926496286588036</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.006162548377493415</v>
+        <v>0.003899970229234828</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -3835,25 +3838,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3919271046315291</v>
+        <v>0.3979249170476644</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.07051629975097984</v>
+        <v>0.07512915335010661</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.2246123511421001</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>-0.09004365764939393</v>
+        <v>-0.0861227359783141</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.0919920572078825</v>
+        <v>-0.08807945194636657</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.1258325144666449</v>
+        <v>-0.1220657276995306</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.004138709475136393</v>
+        <v>0.008465542108233581</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3880,7 +3883,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D61" s="20" t="inlineStr">
+      <c r="D61" s="21" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -3891,25 +3894,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3355208862526571</v>
+        <v>0.3272539443162166</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1490683760315614</v>
+        <v>0.14195549883284</v>
       </c>
       <c r="H61" s="3" t="n">
         <v>0.2034310803360759</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1785106707473885</v>
+        <v>0.1712154644525916</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.0262430347973841</v>
+        <v>0.01989046184801224</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.04517309316070939</v>
+        <v>-0.05108359133126927</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.001471670345842613</v>
+        <v>-0.007652685798381076</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -3943,25 +3946,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.4884989488888307</v>
+        <v>0.4872007636172402</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1798301752890308</v>
+        <v>0.1788014529893212</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.2006332262387114</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1693167603152623</v>
+        <v>0.1682971039403776</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>-0.006877582048748665</v>
+        <v>-0.007743509365311541</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.01732673267326734</v>
+        <v>-0.01818354912414333</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.007319215380111155</v>
+        <v>0.006440909534497941</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -3995,34 +3998,34 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.4485699058447328</v>
+        <v>0.4427074080653757</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1752666474488327</v>
+        <v>0.1705102334966848</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0.1978956471605651</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>-0.1331986818326777</v>
-      </c>
-      <c r="J63" s="3" t="n">
-        <v>0.0004907975460124447</v>
+        <v>-0.136706707770809</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>-0.003558282208589003</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.0188906268800384</v>
+        <v>-0.02286126819877277</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.009408269373607281</v>
+        <v>0.005323099777172491</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4047,25 +4050,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.4445938090393837</v>
+        <v>0.4392530155500654</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1732023251010593</v>
+        <v>0.1688648903838776</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.196453335693842</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>-0.1342565375487186</v>
+        <v>-0.137457269144512</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>-5.029801574318871e-05</v>
+        <v>-0.003747202172874275</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>-0.01943327825593721</v>
+        <v>-0.02305852178845358</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.008778383864011197</v>
+        <v>0.005048839274387928</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4099,7 +4102,7 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2715614477256438</v>
+        <v>0.2715613324707953</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>0.1536356643046668</v>
@@ -4151,25 +4154,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.2986810746393047</v>
+        <v>0.2985033149684471</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1574485295552537</v>
+        <v>0.1572899033620943</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1844909606897531</v>
+        <v>0.184490865179529</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.116888067890075</v>
+        <v>0.1167350904804203</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.00799782745037203</v>
+        <v>0.007859764468937769</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.02283042423451853</v>
+        <v>-0.02296426474619706</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.001600512163892454</v>
+        <v>0.001463325406987348</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4203,25 +4206,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.375204866734334</v>
+        <v>0.3749096401342507</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1635680059140636</v>
+        <v>0.1633180949081474</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1828020488329831</v>
+        <v>0.1828019286118927</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1395333867309287</v>
+        <v>0.1392886402697517</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.01595471088608957</v>
+        <v>0.01573660748754224</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.01626142171286971</v>
+        <v>-0.01647260900784198</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.003619649525998359</v>
+        <v>0.003404194197069721</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4255,25 +4258,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.375437158110167</v>
+        <v>0.3751482310734882</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1638786064019053</v>
+        <v>0.1636342282964791</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1827849705628419</v>
+        <v>0.182785080874406</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.139798144869955</v>
+        <v>0.1395587166282011</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.01578604325738286</v>
+        <v>0.01557266524178424</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.01598461650382643</v>
+        <v>-0.01619132071210205</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.003689647902171522</v>
+        <v>0.00347881087919033</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4307,25 +4310,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3735752912027084</v>
+        <v>0.373358576647707</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1627477542281526</v>
+        <v>0.1625640660024728</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1820542165113699</v>
+        <v>0.1820541061388952</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1390884803281527</v>
+        <v>0.1389086360841696</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.01556388160607192</v>
+        <v>0.01540353996303168</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.01633297526757871</v>
+        <v>-0.01648828089611354</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.003512061157395774</v>
+        <v>0.00335362230819003</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4363,25 +4366,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.1113287257679845</v>
+        <v>0.1138777480126261</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1419303734821009</v>
+        <v>0.1445494798432982</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0.1756045981260685</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1220588235294118</v>
+        <v>0.1246323529411766</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.1190417990711319</v>
+        <v>0.1216084087020288</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.02864417568427757</v>
+        <v>-0.02641629535327827</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.005159732133055206</v>
+        <v>0.007465144362718057</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4415,25 +4418,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.5421881810623568</v>
+        <v>0.5524859119722283</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.2822296981562014</v>
+        <v>0.290791595179146</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0.1633905674777287</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.02959479971926293</v>
+        <v>0.03646976499516619</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.08805579773321703</v>
+        <v>0.09532112757919209</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.102148954960259</v>
+        <v>0.1095083897556668</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.008999470619375449</v>
+        <v>-0.002382212811011253</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4471,25 +4474,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.4021147510100656</v>
+        <v>0.4011501347997128</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1566268027388706</v>
+        <v>0.1558310525382014</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1629421035477405</v>
+        <v>0.1629422121829309</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1557767834206549</v>
+        <v>0.1549815101350747</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.02694047523581511</v>
+        <v>0.0262338523501926</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.005430451601678321</v>
+        <v>-0.006114800520811259</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.004092261904761862</v>
+        <v>0.003401360544217802</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4523,25 +4526,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.3290879582406203</v>
+        <v>0.3284172662516007</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1330888397225398</v>
+        <v>0.1325169715917962</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1510047944633168</v>
+        <v>0.1510047107779968</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.07710197676224673</v>
+        <v>0.07655844338457007</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>-0.01062739373465327</v>
+        <v>-0.01112665661418166</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.015565490975327</v>
+        <v>-0.01606226196390126</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.003883823032759359</v>
+        <v>0.00337723741979068</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -4579,25 +4582,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.2531641889530138</v>
+        <v>0.2522446978637771</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.09810631382619772</v>
+        <v>0.09730059420900905</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0.1405408803314658</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.1219852907951933</v>
+        <v>0.1211620503242037</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.01483366655839791</v>
+        <v>0.01408904704111213</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.0372056514913659</v>
+        <v>-0.037912087912088</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>0.002042316804182764</v>
+        <v>0.001307082754676836</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -4631,25 +4634,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.4319875923469276</v>
+        <v>0.4318280056051793</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1307574328946068</v>
+        <v>0.130631593953507</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1361731791203218</v>
+        <v>0.1361732882983833</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1701418064640075</v>
+        <v>0.1700114721126524</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.01788992876329587</v>
+        <v>0.01777655274093415</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.004766655581421086</v>
+        <v>-0.00487750803680298</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.00819764177428417</v>
+        <v>0.008085345311622749</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4683,13 +4686,13 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.4002374710418513</v>
+        <v>0.4002373857556185</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1095867238939743</v>
+        <v>0.1095868310142489</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1245178715070989</v>
+        <v>0.124517980068837</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>0.1548532455994047</v>
@@ -4735,25 +4738,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.3862233527733521</v>
+        <v>0.3866171662258444</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1147004433733108</v>
+        <v>0.1150171869840146</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1232507024560034</v>
+        <v>0.1232507703017041</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1628062603113802</v>
+        <v>0.1631366029989687</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.03758196545812909</v>
+        <v>0.03787673306195249</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.007612066535099937</v>
+        <v>-0.007330138144911125</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>0.005427020851185516</v>
+        <v>0.00571265352756356</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -4780,7 +4783,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D78" s="20" t="inlineStr">
+      <c r="D78" s="21" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4791,25 +4794,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1126062457459736</v>
+        <v>0.1100014083758647</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1342731631333753</v>
+        <v>0.1316174693805794</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1200423658362917</v>
+        <v>0.1200424993345803</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1231397557034741</v>
+        <v>0.1205098629966306</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.07279843001126829</v>
+        <v>0.0702865405669888</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.01270558840554048</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>0.001724613686534315</v>
+        <v>0.01033440253640006</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>-0.0006208609271523002</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -4818,7 +4821,7 @@
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4843,25 +4846,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.2299657124531489</v>
+        <v>0.2326889358602715</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.06543696278709432</v>
+        <v>0.06779598816729671</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0.1057088960634056</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>-0.04923092824863606</v>
+        <v>-0.0471257935017565</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>-0.05245017233628069</v>
+        <v>-0.05035216544282939</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.03642182261505655</v>
+        <v>-0.03428832672965565</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.001742712294042992</v>
+        <v>0.003960709759188941</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -4895,25 +4898,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1482264088501977</v>
+        <v>0.1465837387373932</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.0205889069985461</v>
+        <v>0.01912883703145218</v>
       </c>
       <c r="H80" s="3" t="n">
         <v>0.1043969231097286</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.01165973051436586</v>
+        <v>-0.01307366509159869</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-0.07688815551373085</v>
+        <v>-0.07820877331700182</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.07588577472236901</v>
+        <v>-0.0772078265468007</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.009240542881894243</v>
+        <v>0.007796708056598156</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4951,25 +4954,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.1054209657380563</v>
+        <v>0.0929429026841353</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.07817611883508402</v>
+        <v>0.06600559736765965</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0.09912073717437253</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.1222102605502378</v>
+        <v>0.1095426788551923</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.06287202380952395</v>
+        <v>0.05087425595238093</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.01905579399141633</v>
+        <v>-0.03012875536480686</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.005222841225626662</v>
+        <v>-0.01645194986072429</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -5003,25 +5006,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1144741550336943</v>
+        <v>0.107540275971479</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.06305438706331401</v>
+        <v>0.05644024359814326</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.09836622212868829</v>
+        <v>0.09836603425027679</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.03587412992121819</v>
+        <v>0.02942935926870494</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.02441533079223701</v>
+        <v>-0.03048508672213879</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.03214941824862227</v>
+        <v>-0.03817105531741183</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0.007757704569606894</v>
+        <v>0.001487778958554786</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5055,25 +5058,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.09508563658794889</v>
+        <v>0.09927245364832826</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.08339266194079697</v>
+        <v>0.08753466494941176</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0.09607754615467967</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.0006511559330490968</v>
+        <v>0.004476823434824251</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>-0.0152966345479506</v>
+        <v>-0.01153193828815791</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.01157298063297119</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>-0.0003582945180938824</v>
+        <v>-0.007794048181388846</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>0.00346351367490727</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
@@ -5082,7 +5085,7 @@
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5099,7 @@
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" s="20" t="inlineStr">
+      <c r="D84" s="21" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -5107,25 +5110,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.2136323698770677</v>
+        <v>0.2102063444075619</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.07044292144597097</v>
+        <v>0.06742091511765747</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.09376563728782683</v>
+        <v>0.09376550797044514</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.1538760942531048</v>
+        <v>0.1506186074193216</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.04355188665514675</v>
+        <v>0.04060592041703215</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.02132332105412293</v>
+        <v>-0.02408614338339476</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.003678061445261727</v>
+        <v>-0.006490696668109086</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
@@ -5148,7 +5151,7 @@
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" s="20" t="inlineStr">
+      <c r="D85" s="21" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -5159,25 +5162,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1936421212846433</v>
+        <v>0.1906911179533191</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.07132672527087336</v>
+        <v>0.06867835856389704</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.08929883173400799</v>
+        <v>0.08929898895573007</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.152552237837057</v>
+        <v>0.149702912156372</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.0456002104566593</v>
+        <v>0.04301529028247719</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.0164987843001041</v>
+        <v>-0.01893018409169844</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.003869832893579561</v>
+        <v>-0.006332453825857565</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5211,25 +5214,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.3280771083217551</v>
+        <v>0.3275465338954842</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.05218563372139151</v>
+        <v>0.05176543210293838</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.08219284503618107</v>
+        <v>0.0821929144350142</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.09797342983501145</v>
+        <v>0.09753487198637956</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.01362254720773359</v>
+        <v>-0.01401653085240218</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.02772815533980577</v>
+        <v>-0.02811650485436901</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.008458873761379326</v>
+        <v>0.008056070248932512</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5266,10 +5269,10 @@
         <v>0.3246930134342738</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.05062659339222453</v>
+        <v>0.05062652405706003</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.08096696645823531</v>
+        <v>0.08096689512078492</v>
       </c>
       <c r="I87" s="3" t="n">
         <v>0.09687503059959623</v>
@@ -5300,7 +5303,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VOT</t>
+          <t>EUO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5308,45 +5311,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D88" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D88" s="22" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mid Growth</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>0.2080142495312849</v>
+          <t>2x Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-0.04088050314465408</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.005301066277424438</v>
+        <v>0.09672779575692192</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.07729299364948794</v>
+        <v>0.08090614886731395</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.0902037611826052</v>
-      </c>
-      <c r="J88" s="5" t="n">
-        <v>-0.03927402190059881</v>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>-0.06682669227076332</v>
+        <v>0.0300574130361364</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0.02866779089376048</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>0.01463739188290081</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.006316007454959527</v>
+        <v>0.005605011539729698</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N88" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5359,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EUO</t>
+          <t>VOT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5364,45 +5367,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D89" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2x Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>-0.05396132252027463</v>
+          <t>Mid Growth</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.2086772277501412</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.08398856325947102</v>
+        <v>0.00585272855613761</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0.07612580414581838</v>
+        <v>0.07729299364948794</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01744381080174429</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>0.02052489905787347</v>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>0.007306542676851491</v>
+        <v>0.09080201409541955</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.03874682034866983</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>-0.06631461033765396</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>0.000990099009900991</v>
+        <v>0.006868226685994294</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5423,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D90" s="21" t="inlineStr">
+      <c r="D90" s="22" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5431,25 +5434,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.02868848575421734</v>
+        <v>0.0312383509809453</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.06976064067516541</v>
+        <v>0.07241231365134326</v>
       </c>
       <c r="H90" s="3" t="n">
         <v>0.06445729472280992</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.02023121387283222</v>
+        <v>0.02276011560693636</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.0110991765127102</v>
+        <v>0.01360544217687076</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0.004982206405693912</v>
+        <v>0.007473309608540868</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0.0007087172218285254</v>
+        <v>0.003189227498228142</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -5483,25 +5486,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.09628522316456323</v>
+        <v>0.0973423931001125</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.004976909315993372</v>
+        <v>-0.004017479635073484</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.05979074605639867</v>
+        <v>0.05979064907809373</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.1080686278673896</v>
+        <v>-0.1072085204689973</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.07357147026055444</v>
+        <v>-0.07267809655781621</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.06111362607514714</v>
+        <v>-0.06020823902218186</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.003872216844143184</v>
+        <v>0.004840271055179146</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -5528,7 +5531,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D92" s="21" t="inlineStr">
+      <c r="D92" s="22" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5539,25 +5542,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.01732672312181882</v>
+        <v>0.01886521344033953</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.04839013451428054</v>
+        <v>0.04997560163641923</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0.04640830061160695</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.0126339969372129</v>
+        <v>0.01416539050535981</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.004939209726443794</v>
+        <v>0.006458966565349389</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.001893939393939448</v>
+        <v>0.003409090909090917</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.001135503406510141</v>
+        <v>0.00264950794852381</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -5580,7 +5583,7 @@
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr"/>
-      <c r="D93" s="20" t="inlineStr">
+      <c r="D93" s="21" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -5591,25 +5594,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.08801158523529184</v>
+        <v>0.08898092227190224</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02663323249827942</v>
+        <v>0.02754809087934285</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03455273963676975</v>
+        <v>0.03455294590452551</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.01454969874522249</v>
+        <v>0.01545358672934061</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.003472265135031738</v>
+        <v>-0.002584433374301698</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.007655005718964825</v>
+        <v>-0.006770900467600649</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>0.002424087777494144</v>
+        <v>0.003317172748150021</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5643,25 +5646,25 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.1578992607724272</v>
+        <v>0.1589175667921672</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.05130117061576267</v>
+        <v>-0.05046688364647434</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.02583001351527936</v>
+        <v>0.02582990467690127</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.03325969248581662</v>
+        <v>0.0341684521098149</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.03881098381064374</v>
+        <v>-0.03796561088523531</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.07518904995451592</v>
+        <v>-0.07437567181023663</v>
       </c>
       <c r="L94" s="3" t="n">
-        <v>0.008425720620842458</v>
+        <v>0.009312638580931232</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -5684,7 +5687,7 @@
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr"/>
-      <c r="D95" s="22" t="inlineStr">
+      <c r="D95" s="23" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -5695,25 +5698,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.04363954498738298</v>
+        <v>0.04325506811245194</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.01693575479864995</v>
+        <v>0.01656081979758128</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.02150463936141733</v>
+        <v>0.02150454198521112</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.002375301522071993</v>
+        <v>0.002005924495545264</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-9.834819146203877e-05</v>
+        <v>-0.0004669075913177334</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.004472700746247726</v>
+        <v>-0.004839647778777656</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>0.0009838888205633278</v>
+        <v>0.0006149305128519966</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -5740,7 +5743,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D96" s="23" t="inlineStr">
+      <c r="D96" s="24" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -5751,25 +5754,25 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.2543847599000142</v>
+        <v>0.2597870629693289</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.03766998186512971</v>
+        <v>-0.03352556613744062</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.007804399898630798</v>
+        <v>0.007804311379731477</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.04525609753383653</v>
+        <v>0.04975773882002121</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-0.03800690143156449</v>
+        <v>-0.03386385183849561</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.04512222983778846</v>
+        <v>-0.04100982408042042</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>0.004446046623407973</v>
+        <v>0.008771929824561431</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5807,25 +5810,25 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.03626268138515121</v>
+        <v>0.03567588458860604</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.009060559197648588</v>
+        <v>-0.009621838971538343</v>
       </c>
       <c r="H97" s="5" t="n">
         <v>-0.00120264236319223</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.01702502965241648</v>
+        <v>-0.01758186780845938</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.01832150027623169</v>
+        <v>-0.01887753454398799</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.007867378477100173</v>
+        <v>-0.008429334082607376</v>
       </c>
       <c r="L97" s="3" t="n">
-        <v>0.001323376500614426</v>
+        <v>0.0007562151432081166</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -5852,7 +5855,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D98" s="23" t="inlineStr">
+      <c r="D98" s="24" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -5863,25 +5866,25 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.161724356719873</v>
+        <v>0.1639343784048606</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.05803184311770326</v>
+        <v>-0.05623973216127642</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-0.007402505925005021</v>
+        <v>-0.007402353018979069</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>0.00734188173506678</v>
+        <v>0.009258211878231171</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.05695222870354899</v>
+        <v>-0.05515820931117865</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.05100691619202591</v>
+        <v>-0.04920158665581764</v>
       </c>
       <c r="L98" s="3" t="n">
-        <v>0.00230959286711796</v>
+        <v>0.004216349769040617</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5904,7 +5907,7 @@
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="21" t="inlineStr">
+      <c r="D99" s="22" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5915,25 +5918,25 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.07236610651352637</v>
+        <v>0.06914284513002489</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.01219752729914003</v>
+        <v>-0.01516668746506411</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>-0.009253443882858758</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>0.004313458031669937</v>
+        <v>0.001294596686626681</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.003954474767205007</v>
+        <v>-0.006948482981515514</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.002971580772200277</v>
+        <v>-0.005968472507621003</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.000281716593107384</v>
+        <v>-0.003286693586252221</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5956,7 +5959,7 @@
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" s="22" t="inlineStr">
+      <c r="D100" s="23" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -5967,25 +5970,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.02173734101011005</v>
+        <v>0.0221859361268022</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.02537400790945676</v>
+        <v>-0.02494600978305872</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.009988458693256375</v>
+        <v>-0.009988539527048035</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>-0.03383184688535446</v>
+        <v>-0.03340756225701158</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>-0.02651773446396233</v>
+        <v>-0.02609015907556389</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.01554077763163508</v>
+        <v>-0.01510838091597966</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0.002752697643690905</v>
+        <v>0.00319312926668136</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6008,7 +6011,7 @@
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" s="20" t="inlineStr">
+      <c r="D101" s="21" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -6019,25 +6022,25 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.03910734404680705</v>
+        <v>0.04119091649261852</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.02417005300869135</v>
+        <v>-0.02221336162257304</v>
       </c>
       <c r="H101" s="5" t="n">
         <v>-0.01924910486495324</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>-0.01871951723950516</v>
+        <v>-0.01675189667825527</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>-0.02862729943516718</v>
+        <v>-0.02667954552398022</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>-0.005017531126556229</v>
+        <v>-0.003022435944054491</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0.004315304948216303</v>
+        <v>0.006329113924050667</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6060,7 +6063,7 @@
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr"/>
-      <c r="D102" s="22" t="inlineStr">
+      <c r="D102" s="23" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -6071,34 +6074,34 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03910794727109368</v>
+        <v>-0.03460134611935095</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.06020394699774678</v>
+        <v>-0.05579611559635367</v>
       </c>
       <c r="H102" s="5" t="n">
         <v>-0.0599781224510999</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.051848346366826</v>
+        <v>-0.04740132552776632</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-0.04908140829823937</v>
-      </c>
-      <c r="K102" s="5" t="n">
-        <v>-0.000240233288224867</v>
+        <v>-0.04462140996638697</v>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>0.004448839920248249</v>
       </c>
       <c r="L102" s="3" t="n">
-        <v>0.003840911906827005</v>
+        <v>0.008549126502292337</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>REBOUND</t>
         </is>
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Weak long trend; 1m rebound not yet confirmed by 3m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6127,25 +6130,25 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.02330811694949897</v>
+        <v>-0.02473931711306465</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.1059329964439453</v>
+        <v>-0.107243121841662</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>-0.07205689687441519</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>-0.01545754328112114</v>
+        <v>-0.01690024732069251</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>-0.03319166160696208</v>
+        <v>-0.03460837887067381</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>-0.03650665590964086</v>
+        <v>-0.03791851553045578</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0.003782307207396585</v>
+        <v>0.002311409960075617</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6183,25 +6186,25 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.07149227420351134</v>
+        <v>-0.07452661317670262</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.162151469625622</v>
+        <v>-0.1648895367183487</v>
       </c>
       <c r="H104" s="5" t="n">
         <v>-0.1311770856391509</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.1127272727272728</v>
+        <v>0.1090909090909091</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.08246738890117178</v>
+        <v>0.07892991377404379</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>-0.03565097498522751</v>
+        <v>-0.03880244238723662</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>-0.00386571719226847</v>
+        <v>-0.007121057985757906</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -201,18 +201,21 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -690,25 +693,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.238944662041992</v>
+        <v>2.197055476691696</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.296178133248584</v>
+        <v>1.26648172239348</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.38991549968687</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.3229189912965855</v>
+        <v>0.305809715093357</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1363216939439561</v>
+        <v>-0.1474916225535429</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.03922204213938407</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.007649158592554883</v>
+        <v>-0.05164775796866561</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>-0.005382741231797938</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -717,7 +720,7 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -746,25 +749,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.533425216106469</v>
+        <v>1.504682511727272</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9357538229694546</v>
+        <v>0.9137920097345653</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>1.320015622747218</v>
+        <v>1.320015883643104</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.3717593752746817</v>
+        <v>0.3561961264422802</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.2122958435746771</v>
+        <v>-0.221232714000884</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.1656289707750952</v>
+        <v>-0.1750952986022871</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.02138746305801842</v>
+        <v>0.009799346710219314</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -783,7 +786,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FTXL</t>
+          <t>AIS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -798,29 +801,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>AI Infrastructure</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.805497353687918</v>
+        <v>1.881255301102629</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.145489596789781</v>
+        <v>1.026849642004773</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.31259916577323</v>
+        <v>1.227028639618138</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.4825642399536483</v>
+        <v>0.5050952591936197</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.1565075171722338</v>
+        <v>-0.1297553477648264</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.07226049868766404</v>
+        <v>-0.08988613529805767</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.01348505891313101</v>
+        <v>0.02380952380952372</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -839,14 +842,10 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AIS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>SOXX</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -854,29 +853,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Infrastructure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.900763358778626</v>
+        <v>1.51551310889466</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.040572792362768</v>
+        <v>0.9556616701786562</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>1.227028639618138</v>
+        <v>1.178933517033134</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.5152857775808597</v>
+        <v>0.4755802394219708</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1238631996925834</v>
+        <v>-0.1512281419340011</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.08372404554588075</v>
+        <v>-0.1024684071859556</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.03074141048824597</v>
+        <v>0.005312218101633626</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -895,10 +894,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SOXX</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>SOXQ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -910,25 +913,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.541445522100925</v>
+        <v>1.463446757383838</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9758227286728212</v>
+        <v>0.8624219988613668</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.178933517033134</v>
+        <v>1.089520989351406</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.490792103505344</v>
+        <v>0.4374664924451526</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1424780910741782</v>
+        <v>-0.1528339086334437</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.09321568867180086</v>
+        <v>-0.1086847136962867</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.01567605492633062</v>
+        <v>0.006477272727272609</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -947,7 +950,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOXQ</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -966,25 +969,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.483472518536784</v>
+        <v>1.415401665104408</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.8775619315607031</v>
+        <v>0.7816113374586577</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.089520989351406</v>
+        <v>0.940028314473321</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4491518924063194</v>
+        <v>0.3746220520056438</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1459471570721483</v>
+        <v>-0.1143506493506494</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.1014390661165342</v>
+        <v>-0.08165704378271943</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.0146590909090909</v>
+        <v>0.006364022061942975</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1003,7 +1006,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>EWT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1011,45 +1014,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Taiwan Equity</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.434749317565194</v>
+        <v>1.255424028345633</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.795882254579954</v>
+        <v>0.7991140938455092</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.940028314473321</v>
+        <v>0.7891558977541133</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3856329369078815</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>-0.1072564935064936</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>-0.07430100829868547</v>
+        <v>0.4849315068493152</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.04441661046343581</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.005565862708719838</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.01442511667373769</v>
+        <v>0.01621824317990073</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1059,53 +1062,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EWT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Taiwan Equity</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.270820834443195</v>
+        <v>0.7778919021250745</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.8113958690248975</v>
+        <v>0.6577722210125045</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.7891558977541133</v>
+        <v>0.7152964224810276</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.495068493150685</v>
+        <v>0.2427034898187375</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.05154639175257736</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.01243042671614103</v>
+        <v>0.1403232213848558</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>-0.03353601203535383</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.02315552638980023</v>
+        <v>0.0009738362656626087</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1115,49 +1114,53 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>BDRY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Dry Bulk Freight Futures</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7856180131315189</v>
+        <v>1.194244604316547</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.6649761864300576</v>
+        <v>0.8574908647990254</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7152964224810276</v>
+        <v>0.7052375152253347</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.2481037449632344</v>
+        <v>0.4621284755512944</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.1452785758947004</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>-0.02933617501410402</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>0.005323638252288543</v>
+        <v>0.2572135201978565</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.08928571428571419</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>-0.005218525766470972</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1170,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1175,45 +1178,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dry Bulk Freight Futures</t>
+          <t>Oil Services</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.19568345323741</v>
+        <v>0.6007799384973866</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8587088915956149</v>
+        <v>0.5950679769775422</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7052375152253347</v>
+        <v>0.7017781642581455</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.4630872483221478</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0.2580379225061828</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0.09000000000000008</v>
+        <v>0.03687472447683016</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>-0.01560845909549713</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>-0.06270511017346458</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.004566210045662156</v>
+        <v>-0.02833466987436506</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1226,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1238,38 +1241,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oil Services</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.6276030611382082</v>
+        <v>1.10391028713678</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.6217953883711886</v>
+        <v>0.5939685788901037</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.7017781642581455</v>
+        <v>0.6536075030319715</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.05424889142442235</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0.0008862847435928689</v>
+        <v>0.08427801840979376</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>-0.05918147044773614</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.04699953117674638</v>
+        <v>-0.03606594916418604</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.01205317003231998</v>
+        <v>-0.004728691334673241</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1282,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>EPU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1287,45 +1290,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Peru Equity</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.120403502145883</v>
+        <v>1.197396195364505</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6064643534722092</v>
+        <v>0.5591612290791566</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.6536075030319715</v>
+        <v>0.5577639747011311</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.09277811927866719</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>-0.05180600745326547</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>-0.02850927410121373</v>
+        <v>0.1092006754117099</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0.01316536147996827</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0.0008969615427738553</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.003073649367537401</v>
+        <v>0.008472661545413374</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1335,53 +1338,49 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EPU</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Peru Equity</t>
+          <t>Silver Bullion</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.203303836082411</v>
+        <v>0.8577010745685443</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5633529922132332</v>
+        <v>0.4718782249742002</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.5577639747011311</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0.112182731669118</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0.01588922937237558</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.003587846171095421</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0.01118391323994583</v>
+        <v>0.5368937048503613</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>-0.2038794306447111</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>-0.1000157753588895</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>-0.04230317273795536</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>-0.0083434729706241</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1391,49 +1390,53 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>BOAT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Silver Bullion</t>
+          <t>Global Shipping</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.8785411917942036</v>
+        <v>1.181517412012098</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.4883900928792571</v>
+        <v>0.6912011992259435</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5368937048503613</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>-0.1949483672899804</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>-0.08991954566966398</v>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>-0.03155950982037947</v>
+        <v>0.5337978139154207</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0.3660330067772257</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.2823302282055018</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.1026232948583421</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.002781157656874589</v>
+        <v>0.004012994458245656</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1446,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOAT</t>
+          <t>PICK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1451,45 +1454,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Global Shipping</t>
+          <t>Global Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.195219367588116</v>
+        <v>0.6962225891955893</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.7018235135720523</v>
+        <v>0.4513188820434806</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5337978139154207</v>
+        <v>0.5013233061992033</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.3746129628532913</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.2903844530876452</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>0.1095487932843651</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0.01031912860691753</v>
+        <v>0.08628256828500547</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>-0.07088414634146334</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>-0.03330689928628061</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>-0.007813771772749445</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1502,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PICK</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1507,36 +1510,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Global Metals &amp; Mining</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.7104157560617048</v>
+        <v>0.6845085175280921</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.4634628136241561</v>
+        <v>0.3815094443505727</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.5013233061992033</v>
+        <v>0.4828750110728948</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.095372053269835</v>
+        <v>0.3425610636490672</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.06310975609756087</v>
+        <v>-0.0628864850776788</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.02521808088818389</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>0.0004883607357968334</v>
+        <v>-0.06835745829244344</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1545,7 +1548,7 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1558,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>QTEC</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1563,36 +1566,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Lithium &amp; Battery</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.6964302177574788</v>
+        <v>0.7284602717368065</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.3912867421726001</v>
+        <v>0.3563584178259205</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4828750110728948</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>0.3520627137588321</v>
+        <v>0.4804404549040542</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>-0.02079474996605468</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.0562542915983576</v>
+        <v>-0.1608819995152714</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.06176398429833163</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0.007077257315909025</v>
+        <v>-0.08381427072402936</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>-0.002427877749214491</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1601,7 +1604,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1614,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>VDE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1626,137 +1629,137 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.7361314833547414</v>
+        <v>0.5134112313561485</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.3623781480850803</v>
+        <v>0.4912452001406786</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.4804405645667975</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>-0.01644895715989114</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>-0.1571579253542081</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>-0.07974816369359916</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>0.001999428734647202</v>
+        <v>0.4619434238945752</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0.1046650558482105</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0.1630014852963744</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.02004303023440146</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>-0.02936264209902495</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
-      <c r="A20" t="n">
+      <c r="A20" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>VDE</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr"/>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.4946833890648967</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.4954733660562816</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.4616074222677198</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.1094366533184026</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.1649524911997617</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.0231703419622884</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>-0.02881844380403464</v>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>XOP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.5289519217314198</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.5065582752975406</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>0.4619434238945752</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0.1160084747720516</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0.1749439406016491</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0.03051749518740787</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>-0.01939550670761281</v>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>STEADY_POSITIVE</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
-        <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr"/>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>Energy</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.5107901251279261</v>
+        <v>0.5639288007212577</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.511588749459384</v>
+        <v>0.5173683671939879</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.461607292045245</v>
+        <v>0.4505187180657855</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1213921630917854</v>
+        <v>0.1377862351005668</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.177506250670757</v>
+        <v>0.2263159446340324</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.03419622882710138</v>
+        <v>0.04608671938914655</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-0.01835279842256954</v>
+        <v>-0.03955933900851261</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1775,7 +1778,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1783,36 +1786,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.5817859648170842</v>
+        <v>0.5135747913838327</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.5346938975597588</v>
+        <v>0.4420555011263885</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.4505187180657855</v>
+        <v>0.4386295577231261</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.1507776420602658</v>
+        <v>0.2109788826601171</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.2403181965566004</v>
+        <v>0.1806514305166258</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.05803108808290158</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>-0.02859288933400095</v>
+        <v>0.002381393726321512</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0.001980198019801982</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1821,7 +1824,7 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1834,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>DXJ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1839,45 +1842,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Japan Hedged Equity</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5212023168510274</v>
+        <v>0.6393084462424521</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4493226193093143</v>
+        <v>0.3916305566134579</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.4386294013217875</v>
+        <v>0.4170762664937646</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.2170816418513883</v>
+        <v>0.133824128527849</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.1866013537336562</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>0.007432920512886687</v>
+        <v>0.0292714257692579</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>-0.0179564858165796</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.007029702970297036</v>
+        <v>0.008769944551318298</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1887,53 +1890,49 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DXJ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>DBC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Japan Hedged Equity</t>
+          <t>Broad Commodity Futures</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6458365095800982</v>
+        <v>0.5601289979835771</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3971724136732793</v>
+        <v>0.5200014943326683</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.4170762664937646</v>
+        <v>0.4008216425454265</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.1383393292191653</v>
+        <v>0.1529902642559109</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.03337026873463</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>-0.01404571743321403</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>0.01278714495869626</v>
+        <v>0.1885304659498208</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.08507853403141352</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>-0.01543942992874114</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1943,49 +1942,49 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DBC</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Broad Commodity Futures</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5648338502091006</v>
+        <v>0.7343822785570517</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.5245853347860239</v>
+        <v>0.3529581027637547</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.4008216425454265</v>
+        <v>0.3999618665687914</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.1564673157162724</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>0.1921146953405017</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0.08835078534031404</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>-0.01247030878859867</v>
+        <v>0.3213292199158893</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>-0.01228643132437479</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>-0.03357503152585117</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.001034069881354016</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1995,49 +1994,49 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.747489266236689</v>
+        <v>1.326797234695824</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3631827086618769</v>
+        <v>0.3659199049520672</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3999618665687914</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>0.3313147992976273</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>-0.004822059767482956</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>-0.02627154266498533</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>0.008599107434418052</v>
+        <v>0.3627653555179977</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-0.03348475757819103</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0.02045725177960733</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.002314814814814881</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>-0.01919965483766573</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2047,49 +2046,53 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SIL</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>QCLN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.341382898654656</v>
+        <v>0.6002955392934637</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.3744822534159697</v>
+        <v>0.1976615727860014</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3627653555179977</v>
+        <v>0.3624585749904523</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>-0.02742610049933447</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>0.02685404748525322</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0.008597883597883715</v>
+        <v>-0.02834161704782701</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>-0.2422571752878223</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>-0.1209556057185854</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>-0.01305145076043568</v>
+        <v>-0.009747827929646125</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2102,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>QCLN</t>
+          <t>FTEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2114,38 +2117,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6150210293926057</v>
+        <v>0.7055331225651258</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.2086820939538248</v>
+        <v>0.318957384634982</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3624584417851</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>-0.01940061330998333</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>-0.2352845792119346</v>
+        <v>0.3587877690259815</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0.3113349388652527</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0.009574072612611895</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.1128668171557562</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>-0.0006357279084552303</v>
+        <v>-0.02931317553700918</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.001093551573303264</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2155,14 +2158,10 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FTEC</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>VGT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -2174,25 +2173,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.7178532991085502</v>
+        <v>0.701115758978293</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3284851670627844</v>
+        <v>0.3150273402413921</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3587878653878944</v>
+        <v>0.3550576040462512</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.3208075651899072</v>
+        <v>0.3107371390078359</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.01686688366605216</v>
+        <v>0.01062351304586895</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>-0.0223012724038858</v>
+        <v>-0.02954137424514447</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.008325102299985732</v>
+        <v>0.001094368212812391</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -2211,10 +2210,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VGT</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>IYW</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -2226,25 +2229,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.7132749469368047</v>
+        <v>0.7172757342319811</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3244267115767872</v>
+        <v>0.3139973084307592</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3550576040462512</v>
+        <v>0.3381092593966335</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3201058454336403</v>
+        <v>0.3116317022795299</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.01784710862347549</v>
+        <v>0.008581576260859647</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>-0.02260486371796977</v>
+        <v>-0.01801941866596646</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.008249852681202041</v>
+        <v>0.0002799104286628218</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2263,44 +2266,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DRIV</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>AIRR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Autonomous &amp; Electric Vehicles</t>
+          <t>U.S. Industrial Renaissance</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.4925562380978952</v>
+        <v>0.5341336058736406</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.253236960465048</v>
+        <v>0.1320707374096364</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3537359148051535</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>0.08688352623417694</v>
+        <v>0.3380381699447861</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>-0.05106036756282339</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>-0.155651038457329</v>
+        <v>-0.18906885698933</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.07423822714681438</v>
+        <v>-0.153932404292808</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.006323396567299078</v>
+        <v>0.005616373155640231</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2319,7 +2318,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IYW</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2327,45 +2326,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.7310057021251011</v>
+        <v>0.8968685219223198</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.324503089654663</v>
+        <v>0.2253631561974059</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3381093666486981</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>0.3221184638408294</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0.01664539058235359</v>
+        <v>0.3304715339423887</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>-0.01677476546138834</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>-0.0878705058185113</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.01016828469567643</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>0.008277351247600651</v>
+        <v>-0.07900084674005081</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>-0.006122076023391876</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2375,40 +2374,44 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AIRR</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" s="18" t="inlineStr">
+          <t>XAR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>U.S. Industrial Renaissance</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.5413949164019489</v>
+        <v>0.5054302528022874</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.137428891221685</v>
+        <v>0.08759259072432224</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3380381699447861</v>
+        <v>0.3236139635431958</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>-0.04656898346382132</v>
+        <v>-0.1143785443653538</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.1852306747524373</v>
+        <v>-0.1400487751725126</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.1499279192695819</v>
+        <v>-0.1783158680096314</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.01037601142313194</v>
+        <v>0.003146607046743632</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2427,7 +2430,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>ROBO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2435,36 +2438,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.9043674045593209</v>
+        <v>0.4096922656545374</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.230207379394656</v>
+        <v>0.1929161635099303</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3304715339423887</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>-0.01288778512810151</v>
+        <v>0.3045790225491527</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.08067437648042364</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.08426458798732583</v>
+        <v>-0.07809342683941511</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.07535986452159182</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>-0.002192982456140302</v>
+        <v>-0.08559302051402962</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.004012944983818878</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2473,7 +2476,7 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2483,44 +2486,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XAR</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>SCHA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5083506658082142</v>
+        <v>0.4170367484398614</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.08970232912722964</v>
+        <v>0.2046872303578242</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.3236139635431958</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>-0.1126604954723257</v>
+        <v>0.3045312415853025</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.1338210538518381</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1383806209950025</v>
+        <v>-0.04726616496090641</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.1767219452640147</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>0.005092535088808692</v>
+        <v>-0.07653631284916185</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>-0.002714932126696712</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2529,7 +2528,7 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2538,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ROBO</t>
+          <t>CALF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2547,45 +2546,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Small Cap Cash Flow</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.4202340592863016</v>
+        <v>0.5277156504642782</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.2018368877857912</v>
+        <v>0.302215098678249</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.3045790225491527</v>
+        <v>0.3039134726249164</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.08875574752682192</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>-0.07119933436348502</v>
+        <v>0.2521619291320183</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.1259608041840046</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.07875501061070489</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>0.01152103559870543</v>
+        <v>-0.001302520437378774</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>-0.01199506085729407</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2595,49 +2594,53 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SCHA</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>ARGT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.4264665150658979</v>
+        <v>0.1250044276996893</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2127039027921473</v>
+        <v>0.3296859761937441</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.3045312415853025</v>
+        <v>0.3004949690059397</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.1413661425344577</v>
+        <v>0.07093721295328792</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.04092613339077333</v>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>-0.07039106145251384</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>0.003921568627450966</v>
+        <v>-0.03879269977411504</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0.02244607467425808</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>-0.01185185185185189</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2647,53 +2650,49 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CALF</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="inlineStr">
+          <t>SCHD</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Small Cap Cash Flow</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.5408078577977011</v>
+        <v>0.2933038423852066</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.3133750660479824</v>
+        <v>0.2832017013267309</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.3039135882829664</v>
+        <v>0.3002655537379906</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.2628928294352386</v>
+        <v>0.1114064883473072</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.1356101736895985</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0.007256215327485771</v>
+        <v>0.04855551010097714</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>-0.0131233595800524</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.003527959075674603</v>
+        <v>-0.01427323041071937</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2703,53 +2702,49 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ARGT</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>SPMO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1286187062208923</v>
+        <v>0.5494411538203954</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.3339578309041547</v>
+        <v>0.1959695020802679</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.3004949690059397</v>
+        <v>0.2917070022467936</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.074377790848833</v>
+        <v>0.2295485527977308</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-0.03570464890596581</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0.0257308660900033</v>
+        <v>-0.06945768407854536</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>-0.07411704047434908</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.008677248677248617</v>
+        <v>-0.0002087827962975464</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2759,49 +2754,49 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SCHD</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" s="19" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.3047694922042878</v>
+        <v>0.4247661183279492</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2945776029342375</v>
+        <v>0.2017057317665159</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.3002655537379906</v>
+        <v>0.2835516849073865</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1212593827475492</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>0.0578512149777588</v>
+        <v>0.1411659049606717</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>-0.02536440213331848</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.004374453193350836</v>
+        <v>-0.06376521810789104</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.005534517914360548</v>
+        <v>-0.004243529494283416</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2806,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SPMO</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" s="19" t="inlineStr">
+          <t>MTUM</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2826,25 +2825,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.5610895938888278</v>
+        <v>0.5050420698948952</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2049604255631936</v>
+        <v>0.1883171638664756</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2917069202044018</v>
+        <v>0.2738927634890074</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.2387919108394438</v>
+        <v>0.2116440051465807</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.06246209935631797</v>
+        <v>-0.0785632020821696</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.06715648362980142</v>
+        <v>-0.06717645478113299</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.007307397870415455</v>
+        <v>0.001068411739173936</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2863,40 +2862,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>ARKQ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4332967505301029</v>
+        <v>0.7486713878044076</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2089007360876707</v>
+        <v>0.1609752720730777</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2835516020139315</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>0.1479985117244274</v>
+        <v>0.2687196896505104</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>-0.02018875666803444</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.01952887747451759</v>
+        <v>-0.09792217604835662</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.05815961415897208</v>
+        <v>-0.08492373725760705</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.001718454092726418</v>
+        <v>0.003699033207229974</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -2915,44 +2918,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MTUM</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>PAVE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>U.S. Infrastructure Development</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.5182438692712823</v>
+        <v>0.3914460936721222</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.1987405784849845</v>
+        <v>0.1381863205393463</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2738926864500837</v>
+        <v>0.2672167318535699</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2222721068493305</v>
+        <v>0.03877537356569771</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.07048069273179136</v>
+        <v>-0.0967093679955533</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.05899406501384608</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>0.009849420720510205</v>
+        <v>-0.1018218968159373</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>-0.001703255109765434</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2961,7 +2960,7 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2971,53 +2970,49 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ARKQ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>FNDX</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>Fundamental Large Cap</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.7520401324161423</v>
+        <v>0.4009788602215101</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1632118439180965</v>
+        <v>0.2471339169516287</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2687196896505104</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>-0.0183011899876897</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>-0.09618435965243666</v>
+        <v>0.2658234043115031</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>0.1459778988212084</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0.02625170665288601</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.08316087989576149</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>0.005632618747372753</v>
+        <v>-0.0147646877883727</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>-0.008972772277227703</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3027,49 +3022,49 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>HEFA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>U.S. Infrastructure Development</t>
+          <t>Developed ex-US Currency-Hedged</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.403316249921458</v>
+        <v>0.3327399271236329</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.1478959668757012</v>
+        <v>0.2288165650257901</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2672167318535699</v>
+        <v>0.2627222602884116</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.04763696443023924</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>-0.0890035711348518</v>
+        <v>0.1001711878506537</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0.01503184228522247</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.09415971394517275</v>
+        <v>-0.02685126914201807</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.00681302043906129</v>
+        <v>0.0004313133491482546</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3079,49 +3074,53 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FNDX</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" s="19" t="inlineStr">
+          <t>IWO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fundamental Large Cap</t>
+          <t>Russell 2000 Growth</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4136633394429972</v>
+        <v>0.394237195276067</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2584252953167663</v>
+        <v>0.1555822258054673</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2658232162978982</v>
+        <v>0.2616565941168711</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.156353596312877</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>0.03554340178024584</v>
+        <v>0.1275561247986636</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>-0.05216060541897483</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.005844355582897531</v>
-      </c>
-      <c r="L46" s="20" t="n">
-        <v>0</v>
+        <v>-0.08407546776676833</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>-0.0002768472633647434</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d flat.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3130,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HEFA</t>
+          <t>EWJ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -3142,29 +3141,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Developed ex-US Currency-Hedged</t>
+          <t>Japan Equity</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3367619920039371</v>
+        <v>0.4499739711133486</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2325250004451394</v>
+        <v>0.2438422656225705</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2627222602884116</v>
+        <v>0.2587155470175007</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1034913854427877</v>
+        <v>0.1464161728343478</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.01809509854562208</v>
+        <v>0.03070548236294091</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.02391441157960983</v>
+        <v>-0.01181623713965563</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.003450506793185371</v>
+        <v>0.0009286009079654267</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3183,44 +3182,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IWO</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D48" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>VEA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Russell 2000 Growth</t>
+          <t>Developed Markets</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4017274895322096</v>
+        <v>0.4223252466272867</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.1617902747292432</v>
+        <v>0.2159291278567277</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2616564709050067</v>
+        <v>0.2573928912680641</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1336137218801883</v>
+        <v>0.09703398655975493</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.04706850488039327</v>
+        <v>-0.009470532446836266</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.07915482421623676</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>0.005093989645912345</v>
+        <v>-0.03297598045867811</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>-0.003774640011184105</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3229,7 +3224,7 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3239,49 +3234,53 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EWJ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>VHT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Japan Equity</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4626786188346796</v>
+        <v>0.2212317169209366</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2547409135245782</v>
+        <v>0.2567433356384632</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2587156701482509</v>
+        <v>0.2554652644905435</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1564610521963639</v>
+        <v>0.1435648958611413</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.03973650658733519</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>-0.003157787511459786</v>
+        <v>0.1070297654840391</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0.001018005980785386</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.009698720594304655</v>
+        <v>0.0003179043743641863</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3291,40 +3290,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Developed Markets</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4323049666946326</v>
+        <v>0.4360013786421664</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.2244608461204027</v>
+        <v>0.07331186030181769</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2573929731133286</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>0.1047313903385914</v>
+        <v>0.2510045642986529</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>-0.07397664357904776</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.00252042391783569</v>
+        <v>-0.100202323281445</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.02619079929434109</v>
+        <v>-0.1420400125370083</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.003215434083601254</v>
+        <v>0.005934579439252463</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3343,44 +3342,40 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>COWZ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Large Cap Cash Flow</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.2277908016523813</v>
+        <v>0.3133548089023255</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.2634931488884122</v>
+        <v>0.2470248761272689</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2554652644905435</v>
+        <v>0.2458231004157341</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.1497068416884004</v>
+        <v>0.1124794361249895</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.112975485638072</v>
+        <v>0.09956711039199551</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.006394350066806886</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>0.005690488301119068</v>
+        <v>0.0009646439459451983</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>-0.01277139208173694</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3389,7 +3384,7 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3399,40 +3394,44 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ITA</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>XMMO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4438728034890922</v>
+        <v>0.2980581417813073</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.07919520677441549</v>
+        <v>0.09319290700227989</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2510045642986529</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>-0.06890065732654294</v>
+        <v>0.2439600928773975</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0.009527066295434317</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.09527009278705245</v>
+        <v>-0.1396163990661091</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.1373371148494238</v>
-      </c>
-      <c r="L52" s="3" t="n">
-        <v>0.01144859813084098</v>
+        <v>-0.1211993750751111</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>-0.0006832934745473196</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3441,7 +3440,7 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3451,40 +3450,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COWZ</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Large Cap Cash Flow</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.3237379971858705</v>
+        <v>0.1880131904193729</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2568834887745308</v>
+        <v>0.2466243987126018</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2458231004157341</v>
+        <v>0.2412743983128098</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1212743720150105</v>
+        <v>0.1307314358207601</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.1082599652247627</v>
+        <v>0.1018040060577394</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.008877976620521588</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>-0.004966652476230959</v>
+        <v>0.004310086800359159</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>0.0006560897053562442</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3493,7 +3492,7 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3503,44 +3502,40 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>XMMO</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D54" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>QQQM</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.3064013047972807</v>
+        <v>0.4814497559733042</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.1002192409002773</v>
+        <v>0.1972956978056075</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2439600928773975</v>
+        <v>0.2398735461907</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.01601565051640996</v>
+        <v>0.170996316091176</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.1340864121609614</v>
+        <v>-0.03335165909680304</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>-0.1155510155029443</v>
+        <v>-0.03434047650738714</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.005739665186197396</v>
+        <v>0.0003791926643454957</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3554,54 +3549,54 @@
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
-      <c r="A55" t="n">
+      <c r="A55" s="16" t="n">
         <v>54</v>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>XLV</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Health Care</t>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr"/>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.1939613997532961</v>
+        <v>0.4801454115477375</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2528660658456923</v>
+        <v>0.1967855633901516</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2412743983128098</v>
+        <v>0.2394963661476472</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1363927268694123</v>
-      </c>
-      <c r="J55" s="3" t="n">
-        <v>0.1073205785384481</v>
-      </c>
-      <c r="K55" s="3" t="n">
-        <v>0.009338521400778177</v>
+        <v>0.1708475124264404</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>-0.03338385295122281</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>-0.03445819118473148</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.005666229273529888</v>
+        <v>0.0002554858489227652</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3611,40 +3606,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>QQQM</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.4921702184758729</v>
+        <v>0.3106821233469255</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2059597189405957</v>
+        <v>0.1217724095646773</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2398734681355723</v>
+        <v>0.2393040933892123</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.179470100597694</v>
+        <v>0.01825814706281226</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.0263566159682822</v>
+        <v>-0.05996699232297253</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.02735258884600011</v>
-      </c>
-      <c r="L56" s="3" t="n">
-        <v>0.00761832534730611</v>
+        <v>-0.09483683984542712</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>-0.001184483269173753</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3653,50 +3648,50 @@
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
-      <c r="A57" s="15" t="n">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E57" s="15" t="inlineStr">
-        <is>
-          <t>Nasdaq-100</t>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>VBK</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4908990117897356</v>
+        <v>0.3250573299776169</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2054805657805445</v>
+        <v>0.1234523680599164</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2394963661476472</v>
+        <v>0.2276687909242543</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1793540671767289</v>
+        <v>0.08434821236298884</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.0263610996976047</v>
+        <v>-0.04762494454298682</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.02744324331730308</v>
-      </c>
-      <c r="L57" s="3" t="n">
-        <v>0.007522638884946309</v>
+        <v>-0.08488968982088252</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>-0.002232807383149793</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3705,7 +3700,7 @@
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3715,40 +3710,44 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>XLI</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" s="18" t="inlineStr">
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D58" s="19" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3189200305556283</v>
+        <v>0.3922748039020296</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.1288229802977847</v>
+        <v>0.07078371155382768</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2393040933892123</v>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>0.0246581093271856</v>
+        <v>0.2246123511421001</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>-0.08981643217041779</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>-0.05405869117777451</v>
+        <v>-0.09176523951156279</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.0891477028767711</v>
+        <v>-0.1256141500163774</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.005093278057447526</v>
+        <v>0.004389540352417232</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3767,49 +3766,53 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VBK</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.333201877360749</v>
+        <v>0.3144597123155413</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.130357669800043</v>
+        <v>0.1309474745967232</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2276687909242543</v>
+        <v>0.2034310803360759</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.09101305262559234</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>-0.04177116977276019</v>
+        <v>0.1599254619382551</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0.01005909895017432</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.07926496286588036</v>
-      </c>
-      <c r="L59" s="3" t="n">
-        <v>0.003899970229234828</v>
+        <v>-0.06023079088094574</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>-0.01721854304635762</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3819,44 +3822,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PPA</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D60" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>ONEQ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3979249170476644</v>
+        <v>0.4776833027664722</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.07512915335010661</v>
+        <v>0.1712573873175991</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2246123511421001</v>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>-0.0861227359783141</v>
+        <v>0.2006331215364558</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0.1608203649837148</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.08807945194636657</v>
+        <v>-0.01409364302010541</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.1220657276995306</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>0.008465542108233581</v>
+        <v>-0.02446686976389956</v>
+      </c>
+      <c r="L60" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3865,7 +3864,7 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
         </is>
       </c>
     </row>
@@ -3875,96 +3874,92 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D61" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3272539443162166</v>
+        <v>0.4268964292058979</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.14195549883284</v>
+        <v>0.157682329201499</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2034310803360759</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>0.1712154644525916</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>0.01989046184801224</v>
+        <v>0.1978956471605651</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>-0.1461677474221325</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>-0.01447852760736201</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.05108359133126927</v>
+        <v>-0.03356996751293473</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.007652685798381076</v>
+        <v>-0.005694478831393956</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
-      <c r="A62" t="n">
+      <c r="A62" s="16" t="n">
         <v>61</v>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>ONEQ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Nasdaq Composite</t>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr"/>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.4872007636172402</v>
+        <v>0.4232669670106088</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1788014529893212</v>
+        <v>0.1558820925909532</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.2006332262387114</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>0.1682971039403776</v>
+        <v>0.196453335693842</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>-0.1470376902475667</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>-0.007743509365311541</v>
+        <v>-0.01481276563639566</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.01818354912414333</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>0.006440909534497941</v>
+        <v>-0.03390959086537271</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>-0.006114423442851624</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -3973,7 +3968,7 @@
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3983,101 +3978,101 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IAU</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gold Bullion</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.4427074080653757</v>
+        <v>0.2609876445417436</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1705102334966848</v>
+        <v>0.1440427868694505</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1978956471605651</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>-0.136706707770809</v>
-      </c>
-      <c r="J63" s="5" t="n">
-        <v>-0.003558282208589003</v>
+        <v>0.1899058173775483</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0.09163193819662041</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0.004393284875514603</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.02286126819877277</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>0.005323099777172491</v>
+        <v>-0.03854341229222336</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>-0.007851934941110472</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
-      <c r="A64" s="15" t="n">
+      <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr"/>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E64" s="15" t="inlineStr">
-        <is>
-          <t>Gold Bullion</t>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>QUAL</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Quality Factor</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.4392530155500654</v>
+        <v>0.2888386555921978</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1688648903838776</v>
+        <v>0.1486762844466596</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.196453335693842</v>
-      </c>
-      <c r="I64" s="5" t="n">
-        <v>-0.137457269144512</v>
-      </c>
-      <c r="J64" s="5" t="n">
-        <v>-0.003747202172874275</v>
+        <v>0.184490865179529</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>0.1084232316446101</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0.0003583424776849586</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>-0.02305852178845358</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>0.005048839274387928</v>
+        <v>-0.03023626588073447</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>-0.005990488384854609</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4087,40 +4082,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RSP</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" s="19" t="inlineStr">
+      <c r="D65" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Equal Weight</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2715613324707953</v>
+        <v>0.364419336897114</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1536356643046668</v>
+        <v>0.1544421262208857</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1899057195264289</v>
+        <v>0.1828019286118927</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1007854375841746</v>
+        <v>0.1305960132565136</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.01281527492204937</v>
+        <v>0.007986666725831038</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.03048145296435523</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0.0004673770798280241</v>
+        <v>-0.02397679755585902</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>-0.004251651824188518</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4129,7 +4124,7 @@
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4139,40 +4134,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>QUAL</t>
+          <t>IVV</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="19" t="inlineStr">
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Quality Factor</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.2985033149684471</v>
+        <v>0.364458081092095</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1572899033620943</v>
+        <v>0.1545883297913164</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.184490865179529</v>
+        <v>0.182785191185991</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1167350904804203</v>
+        <v>0.1306998716833028</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.007859764468937769</v>
+        <v>0.007677678664634202</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.02296426474619706</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>0.001463325406987348</v>
+        <v>-0.02383937641830058</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>-0.00432215897111532</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4181,50 +4176,50 @@
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
-      <c r="A67" t="n">
+      <c r="A67" s="16" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>VOO</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" s="19" t="inlineStr">
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr"/>
+      <c r="D67" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="16" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3749096401342507</v>
+        <v>0.362732139435479</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1633180949081474</v>
+        <v>0.153568770575276</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1828019286118927</v>
+        <v>0.1820542165113699</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1392886402697517</v>
+        <v>0.1300962681289961</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.01573660748754224</v>
+        <v>0.007546799454060338</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.01647260900784198</v>
-      </c>
-      <c r="L67" s="3" t="n">
-        <v>0.003404194197069721</v>
+        <v>-0.02409825669431975</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>-0.004409881302895546</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4233,7 +4228,7 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4243,40 +4238,44 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IVV</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XHE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3751482310734882</v>
+        <v>0.1084157780158332</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1636342282964791</v>
+        <v>0.1389371090693037</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.182785080874406</v>
+        <v>0.1756045981260685</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1395587166282011</v>
+        <v>0.1191176470588236</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.01557266524178424</v>
+        <v>0.1161085309215351</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.01619132071210205</v>
+        <v>-0.03119032463399118</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.00347881087919033</v>
+        <v>0.002524975299154519</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4290,54 +4289,54 @@
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
-      <c r="A69" s="15" t="n">
+      <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="16" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="inlineStr"/>
-      <c r="D69" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E69" s="15" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EWZ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Brazil Equity</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.373358576647707</v>
+        <v>0.5438358180079361</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1625640660024728</v>
+        <v>0.2835996016798725</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1820541061388952</v>
+        <v>0.1633905674777287</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1389086360841696</v>
+        <v>0.03069479416340748</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.01540353996303168</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>-0.01648828089611354</v>
-      </c>
-      <c r="L69" s="3" t="n">
-        <v>0.00335362230819003</v>
+        <v>0.08921825050857302</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>0.1033264645275243</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>-0.007940709370037213</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4346,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>XHE</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4355,36 +4354,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.1138777480126261</v>
+        <v>0.3908715705163566</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1445494798432982</v>
+        <v>0.1473519940470303</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1756045981260685</v>
+        <v>0.1629421035477405</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1246323529411766</v>
+        <v>0.1465087909002383</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.1216084087020288</v>
+        <v>0.01870560083798378</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.02641629535327827</v>
-      </c>
-      <c r="L70" s="3" t="n">
-        <v>0.007465144362718057</v>
+        <v>-0.01340574862080435</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>-0.003959396258503389</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4393,7 +4392,7 @@
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4402,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EWZ</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -4414,38 +4413,38 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Brazil Equity</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.5524859119722283</v>
+        <v>0.3230517303394433</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.290791595179146</v>
+        <v>0.1279426856075816</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1633905674777287</v>
+        <v>0.1510047107779968</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.03646976499516619</v>
-      </c>
-      <c r="J71" s="3" t="n">
-        <v>0.09532112757919209</v>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>0.1095083897556668</v>
+        <v>0.07221017636315818</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>-0.01512075965040849</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>-0.02003642987249543</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.002382212811011253</v>
+        <v>-0.0006754474839580915</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4454,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>SPGP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4463,36 +4462,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D72" s="19" t="inlineStr">
+      <c r="D72" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.4011501347997128</v>
+        <v>0.2424367929119193</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1558310525382014</v>
+        <v>0.08870617726518093</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1629422121829309</v>
+        <v>0.1405408024305901</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1549815101350747</v>
+        <v>0.1123808186336495</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.0262338523501926</v>
+        <v>0.00614643885673205</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.006114800520811259</v>
-      </c>
-      <c r="L72" s="3" t="n">
-        <v>0.003401360544217802</v>
+        <v>-0.04544740973312411</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>-0.006535413773384513</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4501,7 +4500,7 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4511,49 +4510,49 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>MGK</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.3284172662516007</v>
+        <v>0.4214606173976185</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1325169715917962</v>
+        <v>0.1224448921760679</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1510047107779968</v>
+        <v>0.1361731791203218</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.07655844338457007</v>
-      </c>
-      <c r="J73" s="5" t="n">
-        <v>-0.01112665661418166</v>
+        <v>0.1615397392745861</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0.010407111287424</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.01606226196390126</v>
+        <v>-0.0120829176366255</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.00337723741979068</v>
+        <v>0.0007860752386301684</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4563,44 +4562,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SPGP</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D74" s="19" t="inlineStr">
+          <t>VUG</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.2522446978637771</v>
+        <v>0.3901776055297477</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.09730059420900905</v>
+        <v>0.101615009490357</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1405408803314658</v>
+        <v>0.1245178715070989</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.1211620503242037</v>
+        <v>0.1465563184158305</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.01408904704111213</v>
+        <v>0.004223432347362666</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.037912087912088</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>0.001307082754676836</v>
+        <v>-0.02036682795093958</v>
+      </c>
+      <c r="L74" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -4609,7 +4604,7 @@
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d flat.</t>
         </is>
       </c>
     </row>
@@ -4619,40 +4614,40 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MGK</t>
+          <t>SCHG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" s="19" t="inlineStr">
+      <c r="D75" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.4318280056051793</v>
+        <v>0.3763779130758496</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.130631593953507</v>
+        <v>0.1067836036663254</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1361732882983833</v>
+        <v>0.1232507703017041</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1700114721126524</v>
+        <v>0.1545476931216689</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.01777655274093415</v>
+        <v>0.03021277536254585</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.00487750803680298</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>0.008085345311622749</v>
+        <v>-0.01466027628982225</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>-0.001713796058268935</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4661,7 +4656,7 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4671,49 +4666,53 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VUG</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>IAK</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D76" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.4002373857556185</v>
+        <v>0.1022626074385649</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1095868310142489</v>
+        <v>0.1237280951548987</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.124517980068837</v>
+        <v>0.1200424993345803</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1548532455994047</v>
+        <v>0.1126979284233816</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.01149038344291564</v>
-      </c>
-      <c r="K76" s="5" t="n">
-        <v>-0.01327782153707668</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>0.007236388697450025</v>
+        <v>0.06282475133545251</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0.003290585689835757</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>-0.007588300220750521</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4723,49 +4722,49 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SCHG</t>
+          <t>IGF</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.3866171662258444</v>
+        <v>0.2252971726620885</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1150171869840146</v>
+        <v>0.06139291927817614</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1232507703017041</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0.1631366029989687</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>0.03787673306195249</v>
+        <v>0.1057088960634056</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>-0.05283973067185799</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>-0.05604675558219696</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.007330138144911125</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>0.00571265352756356</v>
+        <v>-0.04007924413288633</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>-0.002059569074778111</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4775,53 +4774,49 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IAK</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>BOTZ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Robotics &amp; AI</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1100014083758647</v>
+        <v>0.1406701263312977</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1316174693805794</v>
+        <v>0.01387258514991463</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1200424993345803</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>0.1205098629966306</v>
-      </c>
-      <c r="J78" s="3" t="n">
-        <v>0.0702865405669888</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>0.01033440253640006</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>-0.0006208609271523002</v>
+        <v>0.1043969231097286</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>-0.01816382956963625</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>-0.08296299740877655</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>-0.08196721311475419</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>0.002598902685532645</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4831,49 +4826,53 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IGF</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>EDEN</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Denmark Equity</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.2326889358602715</v>
+        <v>0.08423727729767871</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.06779598816729671</v>
+        <v>0.05751453587875899</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1057088960634056</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>-0.0471257935017565</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>-0.05035216544282939</v>
+        <v>0.09912073717437253</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0.1007048311609744</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.04250372023809534</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.03428832672965565</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>0.003960709759188941</v>
+        <v>-0.03785407725321888</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>-0.02428621169916423</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4883,40 +4882,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>U.S. Equity REITs</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1465837387373932</v>
+        <v>0.09860849955235418</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.01912883703145218</v>
+        <v>0.04792056421428725</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.1043969231097286</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>-0.01307366509159869</v>
+        <v>0.09836603425027679</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.02112742449684157</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-0.07820877331700182</v>
+        <v>-0.03830375537760533</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.0772078265468007</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>0.007796708056598156</v>
+        <v>-0.04592774035517455</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>-0.006588735387885181</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4925,7 +4924,7 @@
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4935,53 +4934,49 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EDEN</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XLP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.0929429026841353</v>
+        <v>0.09050642544331566</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.06600559736765965</v>
+        <v>0.07886234615012455</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.09912073717437253</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>0.1095426788551923</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>0.05087425595238093</v>
+        <v>0.09607754615467967</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>-0.003533167897017409</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>-0.01941427108209914</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.03012875536480686</v>
+        <v>-0.01570618800188961</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.01645194986072429</v>
+        <v>-0.004538397229189139</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4991,49 +4986,49 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>VFH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+      <c r="D82" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>U.S. Equity REITs</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.107540275971479</v>
+        <v>0.1986101299150191</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.05644024359814326</v>
+        <v>0.05719313935641179</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.09836603425027679</v>
+        <v>0.09376563728782683</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.02942935926870494</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>-0.03048508672213879</v>
+        <v>0.1395935888519262</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0.03063495776495273</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.03817105531741183</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>0.001487778958554786</v>
+        <v>-0.03343723434400681</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>-0.01601038511466901</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N82" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5043,49 +5038,49 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.09927245364832826</v>
+        <v>0.178887488531229</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.08753466494941176</v>
+        <v>0.05808419686676292</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.09607754615467967</v>
+        <v>0.08929891034486337</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.004476823434824251</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>-0.01153193828815791</v>
+        <v>0.1383056094336323</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0.03267560958574856</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.007794048181388846</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>0.00346351367490727</v>
+        <v>-0.02865578325807572</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>-0.01618293755496925</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5095,49 +5090,49 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VFH</t>
+          <t>VONG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.2102063444075619</v>
+        <v>0.3179981291923279</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.06742091511765747</v>
+        <v>0.04420052146675557</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.09376550797044514</v>
+        <v>0.08219284503618107</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.1506186074193216</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>0.04060592041703215</v>
+        <v>0.08964083071100393</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>-0.02110823645643667</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.02408614338339476</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v>-0.006490696668109086</v>
+        <v>-0.0351067961165048</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>0.0008056070248934066</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5147,49 +5142,49 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>IWF</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Russell 1000 Growth</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1906911179533191</v>
+        <v>0.3146590033972314</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.06867835856389704</v>
+        <v>0.0426685428111151</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.08929898895573007</v>
+        <v>0.08096689512078492</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.149702912156372</v>
-      </c>
-      <c r="J85" s="3" t="n">
-        <v>0.04301529028247719</v>
+        <v>0.08856666456947182</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>-0.02190150306111882</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.01893018409169844</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>-0.006332453825857565</v>
+        <v>-0.03542971804459427</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>0.0007471980074720275</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5199,49 +5194,53 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VONG</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>EUO</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Large Growth</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>0.3275465338954842</v>
+          <t>2x Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>-0.03333333333333344</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.05176543210293838</v>
+        <v>0.1053577849694354</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.0821929144350142</v>
+        <v>0.08090614886731395</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.09753487198637956</v>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>-0.01401653085240218</v>
-      </c>
-      <c r="K86" s="5" t="n">
-        <v>-0.02811650485436901</v>
+        <v>0.03816278284363395</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0.03676222596964585</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>0.02262142381902854</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.008056070248932512</v>
+        <v>0.01351796900758329</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N86" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5251,40 +5250,44 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IWF</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" s="19" t="inlineStr">
+          <t>VOT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Russell 1000 Growth</t>
+          <t>Mid Growth</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.3246930134342738</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>0.05062652405706003</v>
+        <v>0.1995209717921596</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>-0.001767106668587703</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.08096689512078492</v>
+        <v>0.07729299364948794</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.09687503059959623</v>
+        <v>0.08253864573717418</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>-0.01443634114653647</v>
+        <v>-0.04602879178468755</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.02806780781231488</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>0.008385222083852062</v>
+        <v>-0.07338774203872622</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>-0.0007593014426728883</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
@@ -5293,20 +5296,20 @@
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
-      <c r="A88" t="n">
+      <c r="A88" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>EUO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
@@ -5316,31 +5319,31 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2x Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>-0.04088050314465408</v>
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>US Dollar Index Bullish</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.03451674912959546</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.09672779575692192</v>
+        <v>0.07582160747785771</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.08090614886731395</v>
+        <v>0.06445729472280992</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.0300574130361364</v>
+        <v>0.02601156069364152</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.02866779089376048</v>
+        <v>0.01682778374507699</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0.01463739188290081</v>
+        <v>0.01067615658362975</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.005605011539729698</v>
+        <v>0.006378454996456506</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5359,100 +5362,96 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VOT</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.09205654342236635</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-0.00881508329771763</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.05979064907809373</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>-0.1115090574609578</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.07714496507150692</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>-0.0647351742870077</v>
+      </c>
+      <c r="L89" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>USDU</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D89" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Mid Growth</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>0.2086772277501412</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>0.00585272855613761</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>0.07729299364948794</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>0.09080201409541955</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>-0.03874682034866983</v>
-      </c>
-      <c r="K89" s="5" t="n">
-        <v>-0.06631461033765396</v>
-      </c>
-      <c r="L89" s="3" t="n">
-        <v>0.006868226685994294</v>
-      </c>
-      <c r="M89" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N89" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="21" customHeight="1">
-      <c r="A90" s="15" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="16" t="inlineStr">
-        <is>
-          <t>UUP</t>
-        </is>
-      </c>
-      <c r="C90" s="15" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
       <c r="D90" s="22" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E90" s="15" t="inlineStr">
-        <is>
-          <t>US Dollar Index Bullish</t>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Bloomberg Dollar Bullish</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.0312383509809453</v>
+        <v>0.02155757149775073</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.07241231365134326</v>
+        <v>0.05275016910016217</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.06445729472280992</v>
+        <v>0.04640830061160695</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.02276011560693636</v>
+        <v>0.01684532924961712</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.01360544217687076</v>
+        <v>0.009118541033434679</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0.007473309608540868</v>
+        <v>0.0060606060606061</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0.003189227498228142</v>
+        <v>0.005299015897047621</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -5466,45 +5465,45 @@
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
-      <c r="A91" t="n">
+      <c r="A91" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>XLU</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Utilities</t>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>HYG</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr"/>
+      <c r="D91" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E91" s="16" t="inlineStr">
+        <is>
+          <t>High Yield Corporate Bonds</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.0973423931001125</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>-0.004017479635073484</v>
+        <v>0.08662658843733517</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0.02532668684107531</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.05979064907809373</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>-0.1072085204689973</v>
+        <v>0.03455284277063719</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0.01325843019648221</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.07267809655781621</v>
+        <v>-0.004740596221788573</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.06020823902218186</v>
+        <v>-0.008918013220913346</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.004840271055179146</v>
+        <v>0.001148252105128922</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -5523,96 +5522,92 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>USDU</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D92" s="22" t="inlineStr">
-        <is>
-          <t>Currency</t>
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bloomberg Dollar Bullish</t>
+          <t>Russell Midcap Growth</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.01886521344033953</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>0.04997560163641923</v>
+        <v>0.1504312820015545</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-0.05742011384824297</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.04640830061160695</v>
+        <v>0.02582990467690127</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.01416539050535981</v>
-      </c>
-      <c r="J92" s="3" t="n">
-        <v>0.006458966565349389</v>
-      </c>
-      <c r="K92" s="3" t="n">
-        <v>0.003409090909090917</v>
+        <v>0.0265954552431642</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>-0.04501038526363865</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>-0.08115382301256358</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.00264950794852381</v>
+        <v>0.001921655580192194</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
-      <c r="A93" s="15" t="n">
+      <c r="A93" s="16" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="16" t="inlineStr">
-        <is>
-          <t>HYG</t>
-        </is>
-      </c>
-      <c r="C93" s="15" t="inlineStr"/>
-      <c r="D93" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
-        </is>
-      </c>
-      <c r="E93" s="15" t="inlineStr">
-        <is>
-          <t>High Yield Corporate Bonds</t>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr"/>
+      <c r="D93" s="23" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E93" s="16" t="inlineStr">
+        <is>
+          <t>1-3 Year Treasury</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.08898092227190224</v>
+        <v>0.04171634382320044</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02754809087934285</v>
+        <v>0.01506146755599169</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03455294590452551</v>
+        <v>0.02150454198521112</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.01545358672934061</v>
+        <v>0.0005280396511564422</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.002584433374301698</v>
+        <v>-0.001941145190740623</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.006770900467600649</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>0.003317172748150021</v>
+        <v>-0.006307435908897485</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>-0.0008609027179929951</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5621,7 +5616,7 @@
       </c>
       <c r="N93" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5631,40 +5626,44 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IWP</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XRT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D94" s="24" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Russell Midcap Growth</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.1589175667921672</v>
+        <v>0.2414791159867113</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.05046688364647434</v>
+        <v>-0.04757073333774586</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.02582990467690127</v>
+        <v>0.007804399898630798</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.0341684521098149</v>
+        <v>0.0345021766835063</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.03796561088523531</v>
+        <v>-0.04790418657056272</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.07437567181023663</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>0.009312638580931232</v>
+        <v>-0.05494631025816776</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>-0.005888007690458941</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -5673,59 +5672,63 @@
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
-      <c r="A95" s="15" t="n">
+      <c r="A95" s="16" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="16" t="inlineStr">
-        <is>
-          <t>SHY</t>
-        </is>
-      </c>
-      <c r="C95" s="15" t="inlineStr"/>
-      <c r="D95" s="23" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E95" s="15" t="inlineStr">
-        <is>
-          <t>1-3 Year Treasury</t>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D95" s="18" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
+        </is>
+      </c>
+      <c r="E95" s="16" t="inlineStr">
+        <is>
+          <t>TIPS</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.04325506811245194</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>0.01656081979758128</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>0.02150454198521112</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0.002005924495545264</v>
+        <v>0.03098034970404218</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.0141121475258813</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>-0.001202713647768805</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>-0.02203594708834311</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-0.0004669075913177334</v>
+        <v>-0.02332580868603851</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.004839647778777656</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>0.0006149305128519966</v>
+        <v>-0.01292497892666478</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>-0.003781075716041249</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N95" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5738,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>VCR</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5750,85 +5753,81 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.2597870629693289</v>
+        <v>0.1525107451880932</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.03352556613744062</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>0.007804311379731477</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0.04975773882002121</v>
+        <v>-0.06550250085512099</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>-0.007402429471997984</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>-0.0006473256223520352</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-0.03386385183849561</v>
+        <v>-0.06443152081822012</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.04100982408042042</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>0.008771929824561431</v>
+        <v>-0.05853336045565494</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>-0.005639703512729688</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N96" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
-      <c r="A97" s="15" t="n">
+      <c r="A97" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="16" t="inlineStr">
-        <is>
-          <t>TIP</t>
-        </is>
-      </c>
-      <c r="C97" s="15" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D97" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
-        </is>
-      </c>
-      <c r="E97" s="15" t="inlineStr">
-        <is>
-          <t>TIPS</t>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>FXE</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" s="22" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Euro Currency</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.03567588458860604</v>
+        <v>0.06622160787579157</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.009621838971538343</v>
+        <v>-0.01785748886543281</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>-0.00120264236319223</v>
+        <v>-0.009253443882858758</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.01758186780845938</v>
+        <v>-0.001441180899948824</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.01887753454398799</v>
+        <v>-0.009661738492495076</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.008429334082607376</v>
-      </c>
-      <c r="L97" s="3" t="n">
-        <v>0.0007562151432081166</v>
+        <v>-0.008684405642846116</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>-0.006009953986289784</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -5837,7 +5836,7 @@
       </c>
       <c r="N97" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5847,44 +5846,40 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VCR</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D98" s="24" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" s="23" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>7-10 Year Treasury</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.1639343784048606</v>
+        <v>0.01792270797077555</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.05623973216127642</v>
+        <v>-0.02901274797077058</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-0.007402353018979069</v>
-      </c>
-      <c r="I98" s="3" t="n">
-        <v>0.009258211878231171</v>
+        <v>-0.009988539527048035</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>-0.03743900914914555</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.05515820931117865</v>
+        <v>-0.0301521252653485</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.04920158665581764</v>
-      </c>
-      <c r="L98" s="3" t="n">
-        <v>0.004216349769040617</v>
+        <v>-0.01921614971470553</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>-0.0009909711517285258</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5893,7 +5888,7 @@
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5903,40 +5898,40 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FXE</t>
+          <t>LQD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="22" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Euro Currency</t>
+          <t>Investment Grade Corporate Bonds</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.06914284513002489</v>
+        <v>0.03632924745239174</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.01516668746506411</v>
+        <v>-0.02677911322448678</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.009253443882858758</v>
-      </c>
-      <c r="I99" s="3" t="n">
-        <v>0.001294596686626681</v>
+        <v>-0.01924924430314967</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>-0.02134308128001017</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.006948482981515514</v>
+        <v>-0.03122430465008319</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.005968472507621003</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>-0.003286693586252221</v>
+        <v>-0.007677658036558843</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>0.001630226313770633</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5945,50 +5940,50 @@
       </c>
       <c r="N99" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
-      <c r="A100" t="n">
+      <c r="A100" s="16" t="n">
         <v>99</v>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>IEF</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C100" s="16" t="inlineStr"/>
       <c r="D100" s="23" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>7-10 Year Treasury</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>0.0221859361268022</v>
+      <c r="E100" s="16" t="inlineStr">
+        <is>
+          <t>20+ Year Treasury</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>-0.0407685119672373</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.02494600978305872</v>
+        <v>-0.06182780185649384</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.009988539527048035</v>
+        <v>-0.05997803926142375</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>-0.03340756225701158</v>
+        <v>-0.05348680697430352</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>-0.02609015907556389</v>
+        <v>-0.05072456557839544</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.01510838091597966</v>
+        <v>-0.001967786575556962</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0.00319312926668136</v>
+        <v>0.00210630652955035</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6007,40 +6002,44 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LQD</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>INDA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Investment Grade Corporate Bonds</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>0.04119091649261852</v>
+          <t>India Equity</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>-0.02964628910243294</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.02221336162257304</v>
+        <v>-0.111734980348119</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01924910486495324</v>
+        <v>-0.07205689687441519</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>-0.01675189667825527</v>
+        <v>-0.02184666117065137</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>-0.02667954552398022</v>
+        <v>-0.03946569520340004</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>-0.003022435944054491</v>
-      </c>
-      <c r="L101" s="3" t="n">
-        <v>0.006329113924050667</v>
+        <v>-0.04275917708753529</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>-0.002731666316453052</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6049,59 +6048,63 @@
       </c>
       <c r="N101" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
-      <c r="A102" s="15" t="n">
+      <c r="A102" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="16" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="C102" s="15" t="inlineStr"/>
-      <c r="D102" s="23" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="inlineStr">
-        <is>
-          <t>20+ Year Treasury</t>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>IPAY</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Digital Payments</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03460134611935095</v>
+        <v>-0.08495715339704712</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.05579611559635367</v>
+        <v>-0.1743016423495968</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.0599781224510999</v>
-      </c>
-      <c r="I102" s="5" t="n">
-        <v>-0.04740132552776632</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>-0.04462140996638697</v>
-      </c>
-      <c r="K102" s="3" t="n">
-        <v>0.004448839920248249</v>
-      </c>
-      <c r="L102" s="3" t="n">
-        <v>0.008549126502292337</v>
+        <v>-0.1311770856391509</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>0.09659090909090917</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>0.06676984302454136</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>-0.04963561158164276</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>-0.01831129196337744</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
-          <t>REBOUND</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>Weak long trend; 1m rebound not yet confirmed by 3m; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6114,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>INDA</t>
+          <t>DRIV</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6119,45 +6122,31 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>India Equity</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>-0.02473931711306465</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>-0.107243121841662</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>-0.07205689687441519</v>
-      </c>
-      <c r="I103" s="5" t="n">
-        <v>-0.01690024732069251</v>
-      </c>
-      <c r="J103" s="5" t="n">
-        <v>-0.03460837887067381</v>
-      </c>
-      <c r="K103" s="5" t="n">
-        <v>-0.03791851553045578</v>
-      </c>
-      <c r="L103" s="3" t="n">
-        <v>0.002311409960075617</v>
-      </c>
+          <t>Autonomous &amp; Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="F103" s="25" t="n"/>
+      <c r="G103" s="25" t="n"/>
+      <c r="H103" s="25" t="n"/>
+      <c r="I103" s="25" t="n"/>
+      <c r="J103" s="25" t="n"/>
+      <c r="K103" s="25" t="n"/>
+      <c r="L103" s="25" t="n"/>
       <c r="M103" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>INSUFFICIENT_DATA</t>
         </is>
       </c>
       <c r="N103" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Insufficient history for transition assessment.</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6156,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IPAY</t>
+          <t>FTXL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6182,38 +6171,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Digital Payments</t>
-        </is>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>-0.07452661317670262</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>-0.1648895367183487</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>-0.1311770856391509</v>
-      </c>
-      <c r="I104" s="3" t="n">
-        <v>0.1090909090909091</v>
-      </c>
-      <c r="J104" s="3" t="n">
-        <v>0.07892991377404379</v>
-      </c>
-      <c r="K104" s="5" t="n">
-        <v>-0.03880244238723662</v>
-      </c>
-      <c r="L104" s="5" t="n">
-        <v>-0.007121057985757906</v>
-      </c>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="F104" s="25" t="n"/>
+      <c r="G104" s="25" t="n"/>
+      <c r="H104" s="25" t="n"/>
+      <c r="I104" s="25" t="n"/>
+      <c r="J104" s="25" t="n"/>
+      <c r="K104" s="25" t="n"/>
+      <c r="L104" s="25" t="n"/>
       <c r="M104" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>INSUFFICIENT_DATA</t>
         </is>
       </c>
       <c r="N104" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Insufficient history for transition assessment.</t>
         </is>
       </c>
     </row>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -213,9 +213,6 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -749,7 +746,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.504682511727272</v>
+        <v>1.504682696040697</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0.9137920097345653</v>
@@ -786,7 +783,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AIS</t>
+          <t>FTXL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -801,29 +798,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Infrastructure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.881255301102629</v>
+        <v>1.776849582107071</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.026849642004773</v>
+        <v>1.123581207927733</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.227028639618138</v>
+        <v>1.312598998441777</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.5050952591936197</v>
+        <v>0.4674253336045502</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.1297553477648264</v>
+        <v>-0.1651206708957424</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.08988613529805767</v>
+        <v>-0.0817339238845145</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.02380952380952372</v>
+        <v>0.003136060212356018</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -842,10 +839,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SOXX</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>AIS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -853,29 +854,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>AI Infrastructure</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.51551310889466</v>
+        <v>1.881255301102629</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.9556616701786562</v>
+        <v>1.026849642004773</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>1.178933517033134</v>
+        <v>1.227028639618138</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.4755802394219708</v>
+        <v>0.5050952591936197</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1512281419340011</v>
+        <v>-0.1297553477648264</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.1024684071859556</v>
+        <v>-0.08988613529805767</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.005312218101633626</v>
+        <v>0.02380952380952372</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -894,14 +895,10 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SOXQ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>SOXX</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -913,25 +910,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.463446757383838</v>
+        <v>1.518322249479843</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.8624219988613668</v>
+        <v>0.9578452268826696</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.089520989351406</v>
+        <v>1.178933257724606</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4374664924451526</v>
+        <v>0.4772279461698796</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1528339086334437</v>
+        <v>-0.1502803607963801</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.1086847136962867</v>
+        <v>-0.1014661784880975</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.006477272727272609</v>
+        <v>0.006434800040092226</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -950,7 +947,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>SOXQ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -969,25 +966,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.415401665104408</v>
+        <v>1.463447018756307</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.7816113374586577</v>
+        <v>0.8624219988613668</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.940028314473321</v>
+        <v>1.089520989351406</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.3746220520056438</v>
+        <v>0.4374664924451526</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1143506493506494</v>
+        <v>-0.1528339086334437</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.08165704378271943</v>
+        <v>-0.1086847136962867</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.006364022061942975</v>
+        <v>0.006477272727272609</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1006,7 +1003,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EWT</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1014,45 +1011,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Taiwan Equity</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.255424028345633</v>
+        <v>1.415401665104408</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7991140938455092</v>
+        <v>0.7816113374586577</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.7891558977541133</v>
+        <v>0.940028314473321</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4849315068493152</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0.04441661046343581</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.005565862708719838</v>
+        <v>0.3746220520056438</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>-0.1143506493506494</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>-0.08165704378271943</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.01621824317990073</v>
+        <v>0.006364022061942975</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1062,49 +1059,53 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>EWT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Taiwan Equity</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.7778919021250745</v>
+        <v>1.255424028345633</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.6577722210125045</v>
+        <v>0.7991140938455092</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.7152964224810276</v>
+        <v>0.7891558977541133</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.2427034898187375</v>
+        <v>0.4849315068493152</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.1403232213848558</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>-0.03353601203535383</v>
+        <v>0.04441661046343581</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.005565862708719838</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.0009738362656626087</v>
+        <v>0.01621824317990073</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1114,53 +1115,49 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BDRY</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dry Bulk Freight Futures</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.194244604316547</v>
+        <v>0.7778919021250745</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8574908647990254</v>
+        <v>0.6577722210125045</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7052375152253347</v>
+        <v>0.7152964224810276</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.4621284755512944</v>
+        <v>0.2427034898187375</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.2572135201978565</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.08928571428571419</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>-0.005218525766470972</v>
+        <v>0.1403232213848558</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>-0.03353601203535383</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.0009738362656626087</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1167,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1178,45 +1175,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oil Services</t>
+          <t>Dry Bulk Freight Futures</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.6007799384973866</v>
+        <v>1.201438848920863</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.5950679769775422</v>
+        <v>0.8635809987819731</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7017781642581455</v>
+        <v>0.7052375152253347</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.03687472447683016</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>-0.01560845909549713</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>-0.06270511017346458</v>
+        <v>0.466922339405561</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.2613355317394888</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.09285714285714297</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.02833466987436506</v>
+        <v>-0.001956947162426559</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1223,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1241,29 +1238,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Oil Services</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.10391028713678</v>
+        <v>0.6007799384973866</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.5939685788901037</v>
+        <v>0.5950679769775422</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6536075030319715</v>
+        <v>0.7017781642581455</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.08427801840979376</v>
+        <v>0.03687472447683016</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-0.05918147044773614</v>
+        <v>-0.01560845909549713</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.03606594916418604</v>
+        <v>-0.06270511017346458</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.004728691334673241</v>
+        <v>-0.02833466987436506</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1282,7 +1279,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EPU</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1290,45 +1287,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Peru Equity</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.197396195364505</v>
+        <v>1.10391028713678</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.5591612290791566</v>
+        <v>0.5939685788901037</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.5577639747011311</v>
+        <v>0.6536075030319715</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1092006754117099</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0.01316536147996827</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0.0008969615427738553</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>0.008472661545413374</v>
+        <v>0.08427801840979376</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>-0.05918147044773614</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>-0.03606594916418604</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>-0.004728691334673241</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1338,49 +1335,53 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>EPU</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Silver Bullion</t>
+          <t>Peru Equity</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8577010745685443</v>
+        <v>1.197396195364505</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.4718782249742002</v>
+        <v>0.5591612290791566</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.5368937048503613</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>-0.2038794306447111</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>-0.1000157753588895</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>-0.04230317273795536</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>-0.0083434729706241</v>
+        <v>0.5577639747011311</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0.1092006754117099</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.01316536147996827</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.0008969615427738553</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.008472661545413374</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1390,53 +1391,49 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BOAT</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Global Shipping</t>
+          <t>Silver Bullion</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.181517412012098</v>
+        <v>0.8577010745685443</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.6912011992259435</v>
+        <v>0.4718782249742002</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5337978139154207</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0.3660330067772257</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0.2823302282055018</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0.1026232948583421</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>0.004012994458245656</v>
+        <v>0.5368937048503613</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>-0.2038794306447111</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>-0.1000157753588895</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>-0.04230317273795536</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>-0.0083434729706241</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1443,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PICK</t>
+          <t>BOAT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1454,45 +1451,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Global Metals &amp; Mining</t>
+          <t>Global Shipping</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.6962225891955893</v>
+        <v>1.181517412012098</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4513188820434806</v>
+        <v>0.6912011992259435</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5013233061992033</v>
+        <v>0.5337978139154207</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.08628256828500547</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>-0.07088414634146334</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>-0.03330689928628061</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>-0.007813771772749445</v>
+        <v>0.3660330067772257</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0.2823302282055018</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.1026232948583421</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0.004012994458245656</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1499,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>QTEC</t>
+          <t>PICK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1510,36 +1507,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Global Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.6845085175280921</v>
+        <v>0.6962227683624993</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.3815094443505727</v>
+        <v>0.4513188820434806</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.4828750110728948</v>
+        <v>0.5013233061992033</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.3425610636490672</v>
+        <v>0.08628256828500547</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.0628864850776788</v>
+        <v>-0.07088414634146334</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.06835745829244344</v>
-      </c>
-      <c r="L17" s="15" t="n">
-        <v>0</v>
+        <v>-0.03330689928628061</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>-0.007813771772749445</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1548,7 +1545,7 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1555,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1566,36 +1563,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.7284602717368065</v>
+        <v>0.6845085175280921</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.3563584178259205</v>
+        <v>0.3815094443505727</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4804404549040542</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>-0.02079474996605468</v>
+        <v>0.4828750110728948</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.3425610636490672</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.1608819995152714</v>
+        <v>-0.0628864850776788</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.08381427072402936</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>-0.002427877749214491</v>
+        <v>-0.06835745829244344</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1604,7 +1601,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
         </is>
       </c>
     </row>
@@ -1614,152 +1611,152 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>LIT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Lithium &amp; Battery</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.728460434896361</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0.356358518297361</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.4804405645667975</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>-0.02079474996605468</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>-0.1608819995152714</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>-0.08381427072402936</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>-0.002427877749214491</v>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>VDE</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>0.5134112313561485</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0.4912452001406786</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>0.4619434238945752</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>0.1046650558482105</v>
-      </c>
-      <c r="J19" s="3" t="n">
+      <c r="F20" s="3" t="n">
+        <v>0.5134113283503212</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.4912450117932252</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.4619432392479987</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.1046649524952612</v>
+      </c>
+      <c r="J20" s="3" t="n">
         <v>0.1630014852963744</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K20" s="3" t="n">
         <v>0.02004303023440146</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="L20" s="5" t="n">
         <v>-0.02936264209902495</v>
       </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>STEADY_POSITIVE</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>XLE</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr"/>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr"/>
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>0.4946833890648967</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.4954733660562816</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>0.4616074222677198</v>
-      </c>
-      <c r="I20" s="3" t="n">
+      <c r="F21" s="3" t="n">
+        <v>0.494683122866828</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.4954732328165075</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0.461607292045245</v>
+      </c>
+      <c r="I21" s="3" t="n">
         <v>0.1094366533184026</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="J21" s="3" t="n">
         <v>0.1649524911997617</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K21" s="3" t="n">
         <v>0.0231703419622884</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="L21" s="5" t="n">
         <v>-0.02881844380403464</v>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>STEADY_POSITIVE</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
-        <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>XOP</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Oil &amp; Gas E&amp;P</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0.5639288007212577</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0.5173683671939879</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>0.4505187180657855</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>0.1377862351005668</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0.2263159446340324</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0.04608671938914655</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>-0.03955933900851261</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1778,7 +1775,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1786,36 +1783,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.5135747913838327</v>
+        <v>0.5639287034296459</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.4420555011263885</v>
+        <v>0.5173683671939879</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.4386295577231261</v>
+        <v>0.4505187180657855</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.2109788826601171</v>
+        <v>0.1377862351005668</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.1806514305166258</v>
+        <v>0.2263159446340324</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.002381393726321512</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>0.001980198019801982</v>
+        <v>0.04608671938914655</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>-0.03955933900851261</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1824,7 +1821,7 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1831,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DXJ</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1842,45 +1839,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Japan Hedged Equity</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6393084462424521</v>
+        <v>0.5135746186739159</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.3916305566134579</v>
+        <v>0.4420553443525967</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.4170762664937646</v>
+        <v>0.4386294013217875</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.133824128527849</v>
+        <v>0.2109788826601171</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.0292714257692579</v>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>-0.0179564858165796</v>
+        <v>0.1806514305166258</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0.002381393726321512</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.008769944551318298</v>
+        <v>0.001980198019801982</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1890,49 +1887,53 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DBC</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+          <t>DXJ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Broad Commodity Futures</t>
+          <t>Japan Hedged Equity</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.5601289979835771</v>
+        <v>0.6393084462424521</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.5200014943326683</v>
+        <v>0.3916303908682723</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.4008216425454265</v>
+        <v>0.4170760977179588</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.1529902642559109</v>
+        <v>0.133824128527849</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.1885304659498208</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0.08507853403141352</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>-0.01543942992874114</v>
+        <v>0.0292714257692579</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>-0.0179564858165796</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.008769944551318298</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1942,49 +1943,49 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>DBC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Broad Commodity Futures</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.7343822785570517</v>
+        <v>0.5601289979835771</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.3529581027637547</v>
+        <v>0.5200014943326683</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.3999618665687914</v>
+        <v>0.4008216425454265</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.3213292199158893</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>-0.01228643132437479</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>-0.03357503152585117</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>0.001034069881354016</v>
+        <v>0.1529902642559109</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0.1885304659498208</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.08507853403141352</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>-0.01543942992874114</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1994,49 +1995,49 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1.326797234695824</v>
+        <v>0.7343822785570517</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3659199049520672</v>
+        <v>0.3529581027637547</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3627653555179977</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>-0.03348475757819103</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>0.02045725177960733</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>0.002314814814814881</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>-0.01919965483766573</v>
+        <v>0.3999618665687914</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>0.3213292199158893</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>-0.01228643132437479</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>-0.03357503152585117</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.001034069881354016</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2046,53 +2047,49 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>QCLN</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SIL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.6002955392934637</v>
+        <v>1.326797234695824</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.1976615727860014</v>
+        <v>0.3659199049520672</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3624585749904523</v>
+        <v>0.3627653555179977</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>-0.02834161704782701</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>-0.2422571752878223</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>-0.1209556057185854</v>
+        <v>-0.03348475757819103</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.02045725177960733</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.002314814814814881</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>-0.009747827929646125</v>
+        <v>-0.01919965483766573</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FTEC</t>
+          <t>QCLN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2117,38 +2114,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.7055331225651258</v>
+        <v>0.6002955392934637</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.318957384634982</v>
+        <v>0.1976614556925833</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3587877690259815</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>0.3113349388652527</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>0.009574072612611895</v>
+        <v>0.3624584417851</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>-0.02834161704782701</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>-0.2422571752878223</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.02931317553700918</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>0.001093551573303264</v>
+        <v>-0.1209556057185854</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>-0.009747827929646125</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2158,10 +2155,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VGT</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>FTEC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -2173,25 +2174,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.701115758978293</v>
+        <v>0.7055331225651258</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3150273402413921</v>
+        <v>0.3189574781722211</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3550576040462512</v>
+        <v>0.3587878653878944</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.3107371390078359</v>
+        <v>0.3113349388652527</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.01062351304586895</v>
+        <v>0.009574072612611895</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>-0.02954137424514447</v>
+        <v>-0.02931317553700918</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.001094368212812391</v>
+        <v>0.001093551573303264</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -2210,14 +2211,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IYW</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>VGT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -2229,25 +2226,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.7172757342319811</v>
+        <v>0.701115758978293</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3139973084307592</v>
+        <v>0.3150272292956409</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3381092593966335</v>
+        <v>0.3550574897232412</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3116317022795299</v>
+        <v>0.3107371390078359</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.008581576260859647</v>
+        <v>0.01062351304586895</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>-0.01801941866596646</v>
+        <v>-0.02954137424514447</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.0002799104286628218</v>
+        <v>0.001094368212812391</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2266,40 +2263,44 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AIRR</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>DRIV</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>U.S. Industrial Renaissance</t>
+          <t>Autonomous &amp; Electric Vehicles</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5341336058736406</v>
+        <v>0.4755852216264049</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.1320707374096364</v>
+        <v>0.2389871087302566</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3380381699447861</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>-0.05106036756282339</v>
+        <v>0.3537359148051535</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>0.07452518572044298</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>-0.18906885698933</v>
+        <v>-0.1652516550158633</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.153932404292808</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>0.005616373155640231</v>
+        <v>-0.0847645429362881</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>-0.005118940078289724</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2308,7 +2309,7 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2319,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>IYW</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2326,45 +2327,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.8968685219223198</v>
+        <v>0.7172757342319811</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.2253631561974059</v>
+        <v>0.313997413750204</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3304715339423887</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>-0.01677476546138834</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>-0.0878705058185113</v>
+        <v>0.3381093666486981</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0.3116315973389781</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.008581576260859647</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.07900084674005081</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>-0.006122076023391876</v>
+        <v>-0.01801941866596646</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.0002799104286628218</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2374,14 +2375,10 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>XAR</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>AIRR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -2389,29 +2386,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>U.S. Industrial Renaissance</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.5054302528022874</v>
+        <v>0.5341337758498388</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.08759259072432224</v>
+        <v>0.1320707374096364</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3236139635431958</v>
+        <v>0.3380381699447861</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>-0.1143785443653538</v>
+        <v>-0.05106036756282339</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.1400487751725126</v>
+        <v>-0.18906885698933</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.1783158680096314</v>
+        <v>-0.153932404292808</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.003146607046743632</v>
+        <v>0.005616373155640231</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2430,7 +2427,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ROBO</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2438,36 +2435,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.4096922656545374</v>
+        <v>0.8968686481124624</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1929161635099303</v>
+        <v>0.2253631561974059</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3045790225491527</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>0.08067437648042364</v>
+        <v>0.3304715339423887</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>-0.01677476546138834</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.07809342683941511</v>
+        <v>-0.0878705058185113</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.08559302051402962</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>0.004012944983818878</v>
+        <v>-0.07900084674005081</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>-0.006122076023391876</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2476,7 +2473,7 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2486,40 +2483,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SCHA</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XAR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.4170367484398614</v>
+        <v>0.505430395529215</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.2046872303578242</v>
+        <v>0.08759251623105135</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.3045312415853025</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>0.1338210538518381</v>
+        <v>0.3236138728839413</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>-0.1143784455758354</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.04726616496090641</v>
+        <v>-0.1400487751725126</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.07653631284916185</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>-0.002714932126696712</v>
+        <v>-0.1783158680096314</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0.003146607046743632</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2528,7 +2529,7 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2539,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CALF</t>
+          <t>ROBO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2546,45 +2547,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Small Cap Cash Flow</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5277156504642782</v>
+        <v>0.4096922656545374</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.302215098678249</v>
+        <v>0.1929161635099303</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.3039134726249164</v>
+        <v>0.3045790225491527</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.2521619291320183</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>0.1259608041840046</v>
+        <v>0.08067437648042364</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-0.07809342683941511</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.001302520437378774</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>-0.01199506085729407</v>
+        <v>-0.08559302051402962</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0.004012944983818878</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2594,53 +2595,49 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ARGT</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>SCHA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.1250044276996893</v>
+        <v>0.4170367484398614</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.3296859761937441</v>
+        <v>0.2046870628998725</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.3004949690059397</v>
+        <v>0.3045310602485005</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.07093721295328792</v>
+        <v>0.1338210538518381</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.03879269977411504</v>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>0.02244607467425808</v>
+        <v>-0.04726616496090641</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>-0.07653631284916185</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-0.01185185185185189</v>
+        <v>-0.002714932126696712</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2650,10 +2647,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SCHD</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>CALF</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -2661,29 +2662,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Small Cap Cash Flow</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.2933038423852066</v>
+        <v>0.5277156504642782</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2832017013267309</v>
+        <v>0.302215098678249</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.3002655537379906</v>
+        <v>0.3039134726249164</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1114064883473072</v>
+        <v>0.2521619291320183</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.04855551010097714</v>
+        <v>0.1259608041840046</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.0131233595800524</v>
+        <v>-0.001302520437378774</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.01427323041071937</v>
+        <v>-0.01199506085729407</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2702,49 +2703,53 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SPMO</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>ARGT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.5494411538203954</v>
+        <v>0.1250044276996893</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1959695020802679</v>
+        <v>0.3296859761937441</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2917070022467936</v>
+        <v>0.3004949690059397</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2295485527977308</v>
+        <v>0.07093721295328792</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-0.06945768407854536</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>-0.07411704047434908</v>
+        <v>-0.03879269977411504</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0.02244607467425808</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.0002087827962975464</v>
+        <v>-0.01185185185185189</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2759,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>SCHD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2765,38 +2770,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.4247661183279492</v>
+        <v>0.2933040309371149</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2017057317665159</v>
+        <v>0.2832017013267309</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2835516849073865</v>
+        <v>0.3002655537379906</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1411659049606717</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>-0.02536440213331848</v>
+        <v>0.1114065579691639</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0.04855551010097714</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.06376521810789104</v>
+        <v>-0.0131233595800524</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.004243529494283416</v>
+        <v>-0.01427323041071937</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2806,14 +2811,10 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MTUM</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>SPMO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -2825,25 +2826,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.5050420698948952</v>
+        <v>0.5494411538203954</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1883171638664756</v>
+        <v>0.1959695020802679</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2738927634890074</v>
+        <v>0.2917070022467936</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.2116440051465807</v>
+        <v>0.2295485527977308</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.0785632020821696</v>
+        <v>-0.06945768407854536</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.06717645478113299</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>0.001068411739173936</v>
+        <v>-0.07411704047434908</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>-0.0002087827962975464</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2852,7 +2853,7 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2862,44 +2863,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ARKQ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.7486713878044076</v>
+        <v>0.4247159381385248</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.1609752720730777</v>
+        <v>0.201663407752436</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2687196896505104</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>-0.02018875666803444</v>
+        <v>0.2835516849073865</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>0.1411257131561792</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.09792217604835662</v>
+        <v>-0.02539872874895854</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.08492373725760705</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>0.003699033207229974</v>
+        <v>-0.06379819224876704</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>-0.004278599985971687</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -2908,7 +2905,7 @@
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2918,40 +2915,44 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PAVE</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>MTUM</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>U.S. Infrastructure Development</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.3914460936721222</v>
+        <v>0.5050423004258826</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.1381863205393463</v>
+        <v>0.1883171638664756</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2672167318535699</v>
+        <v>0.2738927634890074</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.03877537356569771</v>
+        <v>0.2116440051465807</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.0967093679955533</v>
+        <v>-0.0785632020821696</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.1018218968159373</v>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>-0.001703255109765434</v>
+        <v>-0.06717645478113299</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0.001068411739173936</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2960,7 +2961,7 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2970,49 +2971,53 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FNDX</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>ARKQ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fundamental Large Cap</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4009788602215101</v>
+        <v>0.7486713878044076</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2471339169516287</v>
+        <v>0.1609752720730777</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2658234043115031</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0.1459778988212084</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>0.02625170665288601</v>
+        <v>0.2687196896505104</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>-0.02018875666803444</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>-0.09792217604835662</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.0147646877883727</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>-0.008972772277227703</v>
+        <v>-0.08492373725760705</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0.003699033207229974</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3022,49 +3027,49 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HEFA</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Developed ex-US Currency-Hedged</t>
+          <t>U.S. Infrastructure Development</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3327399271236329</v>
+        <v>0.3914460936721222</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2288165650257901</v>
+        <v>0.1381863205393463</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2627222602884116</v>
+        <v>0.2672167318535699</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1001711878506537</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>0.01503184228522247</v>
+        <v>0.03877537356569771</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>-0.0967093679955533</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.02685126914201807</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>0.0004313133491482546</v>
+        <v>-0.1018218968159373</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>-0.001703255109765434</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3074,14 +3079,10 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IWO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>FNDX</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3089,38 +3090,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Russell 2000 Growth</t>
+          <t>Fundamental Large Cap</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.394237195276067</v>
+        <v>0.4009789771004677</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.1555822258054673</v>
+        <v>0.2471338243328005</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2616565941168711</v>
+        <v>0.2658233103046936</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1275561247986636</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>-0.05216060541897483</v>
+        <v>0.1459778988212084</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>0.02625170665288601</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.08407546776676833</v>
+        <v>-0.0147646877883727</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.0002768472633647434</v>
+        <v>-0.008972772277227703</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3131,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EWJ</t>
+          <t>HEFA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -3141,29 +3142,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Japan Equity</t>
+          <t>Developed ex-US Currency-Hedged</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.4499739711133486</v>
+        <v>0.3327399271236329</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2438422656225705</v>
+        <v>0.2288165650257901</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2587155470175007</v>
+        <v>0.2627222602884116</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1464161728343478</v>
+        <v>0.1001711878506537</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.03070548236294091</v>
+        <v>0.01503184228522247</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.01181623713965563</v>
+        <v>-0.02685126914201807</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.0009286009079654267</v>
+        <v>0.0004313133491482546</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3182,40 +3183,44 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VEA</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>IWO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Developed Markets</t>
+          <t>Russell 2000 Growth</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4223252466272867</v>
+        <v>0.3942370309963887</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2159291278567277</v>
+        <v>0.1555821129526982</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2573928912680641</v>
+        <v>0.2616564709050067</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.09703398655975493</v>
+        <v>0.1275561247986636</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.009470532446836266</v>
+        <v>-0.05216060541897483</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.03297598045867811</v>
+        <v>-0.08407546776676833</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.003774640011184105</v>
+        <v>-0.0002768472633647434</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3234,53 +3239,49 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>EWJ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Japan Equity</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.2212317169209366</v>
+        <v>0.4499739711133486</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2567433356384632</v>
+        <v>0.2438423872983786</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2554652644905435</v>
+        <v>0.2587156701482509</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1435648958611413</v>
+        <v>0.1464161728343478</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.1070297654840391</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>0.001018005980785386</v>
+        <v>0.03070548236294091</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>-0.01181623713965563</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.0003179043743641863</v>
+        <v>0.0009286009079654267</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3290,40 +3291,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Developed Markets</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4360013786421664</v>
+        <v>0.422325354923214</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.07331186030181769</v>
+        <v>0.2159291278567277</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2510045642986529</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>-0.07397664357904776</v>
+        <v>0.2573928912680641</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>0.09703398655975493</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.100202323281445</v>
+        <v>-0.009470532446836266</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.1420400125370083</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>0.005934579439252463</v>
+        <v>-0.03297598045867811</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-0.003774640011184105</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3332,7 +3333,7 @@
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3342,40 +3343,44 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COWZ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>VHT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Large Cap Cash Flow</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.3133548089023255</v>
+        <v>0.2212317169209366</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.2470248761272689</v>
+        <v>0.2567434122284029</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2458231004157341</v>
+        <v>0.2554653410025938</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.1124794361249895</v>
+        <v>0.1435648958611413</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.09956711039199551</v>
+        <v>0.1070297654840391</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.0009646439459451983</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>-0.01277139208173694</v>
+        <v>0.001018005980785386</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0.0003179043743641863</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3384,7 +3389,7 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3394,44 +3399,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>XMMO</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.2980581417813073</v>
+        <v>0.4360012324762166</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.09319290700227989</v>
+        <v>0.07331186030181769</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2439600928773975</v>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>0.009527066295434317</v>
+        <v>0.2510045642986529</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>-0.07397664357904776</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.1396163990661091</v>
+        <v>-0.100202323281445</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.1211993750751111</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>-0.0006832934745473196</v>
+        <v>-0.1420400125370083</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>0.005934579439252463</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3440,7 +3441,7 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3450,40 +3451,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>COWZ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Large Cap Cash Flow</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.1880131904193729</v>
+        <v>0.3133549034829655</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2466243987126018</v>
+        <v>0.2470248761272689</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2412743983128098</v>
+        <v>0.2458231004157341</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1307314358207601</v>
+        <v>0.1124794361249895</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.1018040060577394</v>
+        <v>0.09956711039199551</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.004310086800359159</v>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>0.0006560897053562442</v>
+        <v>0.0009646439459451983</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>-0.01277139208173694</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3492,7 +3493,7 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3502,40 +3503,44 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>QQQM</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>XMMO</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4814497559733042</v>
+        <v>0.2980581417813073</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.1972956978056075</v>
+        <v>0.09319290700227989</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2398735461907</v>
+        <v>0.2439600928773975</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.170996316091176</v>
+        <v>0.009527066295434317</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.03335165909680304</v>
+        <v>-0.1396163990661091</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>-0.03434047650738714</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>0.0003791926643454957</v>
+        <v>-0.1211993750751111</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>-0.0006832934745473196</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3544,59 +3549,59 @@
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
-      <c r="A55" s="16" t="n">
+      <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>Nasdaq-100</t>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>XLV</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.4801454115477375</v>
+        <v>0.1880133187848854</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1967855633901516</v>
+        <v>0.2466242573687296</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2394963661476472</v>
+        <v>0.2412742575755278</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1708475124264404</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>-0.03338385295122281</v>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>-0.03445819118473148</v>
+        <v>0.1307313195355038</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0.1018040060577394</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0.004310086800359159</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.0002554858489227652</v>
+        <v>0.0006560897053562442</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3606,40 +3611,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>QQQM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" s="19" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3106821233469255</v>
+        <v>0.4814498713708459</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1217724095646773</v>
+        <v>0.1972956224309301</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2393040933892123</v>
+        <v>0.2398734681355723</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.01825814706281226</v>
+        <v>0.170996316091176</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.05996699232297253</v>
+        <v>-0.03335165909680304</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.09483683984542712</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>-0.001184483269173753</v>
+        <v>-0.03434047650738714</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>0.0003791926643454957</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3648,50 +3653,50 @@
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
-      <c r="A57" t="n">
+      <c r="A57" s="16" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>VBK</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Small Growth</t>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.3250573299776169</v>
+        <v>0.4801454115477375</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1234523680599164</v>
+        <v>0.1967855633901516</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2276687909242543</v>
+        <v>0.2394963661476472</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.08434821236298884</v>
+        <v>0.1708475124264404</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.04762494454298682</v>
+        <v>-0.03338385295122281</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.08488968982088252</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>-0.002232807383149793</v>
+        <v>-0.03445819118473148</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0.0002554858489227652</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3700,7 +3705,7 @@
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3710,14 +3715,10 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PPA</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>XLI</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" s="19" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -3725,29 +3726,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3922748039020296</v>
+        <v>0.3111484199813805</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.07078371155382768</v>
+        <v>0.1221714984740985</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2246123511421001</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>-0.08981643217041779</v>
+        <v>0.2393040933892123</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0.01862040907777662</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>-0.09176523951156279</v>
+        <v>-0.05963256018267826</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.1256141500163774</v>
-      </c>
-      <c r="L58" s="3" t="n">
-        <v>0.004389540352417232</v>
+        <v>-0.09451481322455979</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>-0.0008291382884215714</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3756,7 +3757,7 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3766,53 +3767,49 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D59" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>VBK</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3144597123155413</v>
+        <v>0.3250574099150532</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1309474745967232</v>
+        <v>0.1234522531334306</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2034310803360759</v>
+        <v>0.2276686653366782</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1599254619382551</v>
-      </c>
-      <c r="J59" s="3" t="n">
-        <v>0.01005909895017432</v>
+        <v>0.08434810529778858</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>-0.04762494454298682</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.06023079088094574</v>
+        <v>-0.08488968982088252</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.01721854304635762</v>
+        <v>-0.002232807383149793</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3822,40 +3819,44 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ONEQ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.4776833027664722</v>
+        <v>0.3922748962354334</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1712573873175991</v>
+        <v>0.07078371155382768</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2006331215364558</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>0.1608203649837148</v>
+        <v>0.2246123511421001</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>-0.08981635324863191</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.01409364302010541</v>
+        <v>-0.09176523951156279</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.02446686976389956</v>
-      </c>
-      <c r="L60" s="15" t="n">
-        <v>0</v>
+        <v>-0.1256141500163774</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0.004389540352417232</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3864,7 +3865,7 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3874,101 +3875,105 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IAU</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gold Bullion</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.4268964292058979</v>
+        <v>0.3144595149196234</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.157682329201499</v>
+        <v>0.1309474745967232</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.1978956471605651</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>-0.1461677474221325</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>-0.01447852760736201</v>
+        <v>0.2034310803360759</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>0.1599254619382551</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0.01005909895017432</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.03356996751293473</v>
+        <v>-0.06023079088094574</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.005694478831393956</v>
+        <v>-0.01721854304635762</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="21" customHeight="1">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ONEQ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Nasdaq Composite</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0.4776834653423609</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0.1712574894581185</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0.2006332262387114</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>0.1608204653120029</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>-0.01409364302010541</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>-0.02446686976389956</v>
+      </c>
+      <c r="L62" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N61" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="21" customHeight="1">
-      <c r="A62" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr"/>
-      <c r="D62" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E62" s="16" t="inlineStr">
-        <is>
-          <t>Gold Bullion</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>0.4232669670106088</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>0.1558820925909532</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>0.196453335693842</v>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>-0.1470376902475667</v>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v>-0.01481276563639566</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>-0.03390959086537271</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>-0.006114423442851624</v>
-      </c>
-      <c r="M62" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
         </is>
       </c>
     </row>
@@ -3978,101 +3983,101 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RSP</t>
+          <t>IAU</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Equal Weight</t>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.2609876445417436</v>
+        <v>0.4268964292058979</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1440427868694505</v>
+        <v>0.157682329201499</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1899058173775483</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>0.09163193819662041</v>
-      </c>
-      <c r="J63" s="3" t="n">
-        <v>0.004393284875514603</v>
+        <v>0.1978956471605651</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>-0.1461677474221325</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>-0.01447852760736201</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.03854341229222336</v>
+        <v>-0.03356996751293473</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.007851934941110472</v>
+        <v>-0.005694478831393956</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
-      <c r="A64" t="n">
+      <c r="A64" s="16" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>QUAL</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Quality Factor</t>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr"/>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.2888386555921978</v>
+        <v>0.4232669670106088</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1486762844466596</v>
+        <v>0.1558820925909532</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.184490865179529</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>0.1084232316446101</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>0.0003583424776849586</v>
+        <v>0.196453335693842</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>-0.1470376902475667</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>-0.01481276563639566</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>-0.03023626588073447</v>
+        <v>-0.03390959086537271</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>-0.005990488384854609</v>
+        <v>-0.006114423442851624</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4087,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VOO</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -4093,29 +4098,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.364419336897114</v>
+        <v>0.2609877588381782</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1544421262208857</v>
+        <v>0.144042692789847</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1828019286118927</v>
+        <v>0.1899057195264289</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1305960132565136</v>
+        <v>0.09163193819662041</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.007986666725831038</v>
+        <v>0.004393284875514603</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.02397679755585902</v>
+        <v>-0.03854341229222336</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.004251651824188518</v>
+        <v>-0.007851934941110472</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4134,7 +4139,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IVV</t>
+          <t>QUAL</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -4145,81 +4150,81 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>Quality Factor</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0.2888386555921978</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0.1486762844466596</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0.184490865179529</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>0.1084233178891734</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0.0003583424776849586</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>-0.03023626588073447</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>-0.005990488384854609</v>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
-      <c r="F66" s="3" t="n">
-        <v>0.364458081092095</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>0.1545883297913164</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>0.182785191185991</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>0.1306998716833028</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>0.007677678664634202</v>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>-0.02383937641830058</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>-0.00432215897111532</v>
-      </c>
-      <c r="M66" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="N66" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="21" customHeight="1">
-      <c r="A67" s="16" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="C67" s="16" t="inlineStr"/>
-      <c r="D67" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E67" s="16" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
       <c r="F67" s="3" t="n">
-        <v>0.362732139435479</v>
+        <v>0.3644191729921495</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.153568770575276</v>
+        <v>0.1544421262208857</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1820542165113699</v>
+        <v>0.1828019286118927</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1300962681289961</v>
+        <v>0.1305961257976715</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.007546799454060338</v>
+        <v>0.007986666725831038</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.02409825669431975</v>
+        <v>-0.02397679755585902</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.004409881302895546</v>
+        <v>-0.004251651824188518</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4238,44 +4243,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>XHE</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>IVV</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.1084157780158332</v>
+        <v>0.364512104535744</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1389371090693037</v>
+        <v>0.1546340633570602</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1756045981260685</v>
+        <v>0.182785080874406</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1191176470588236</v>
+        <v>0.1307447644786317</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.1161085309215351</v>
+        <v>0.007717687042558818</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.03119032463399118</v>
-      </c>
-      <c r="L68" s="3" t="n">
-        <v>0.002524975299154519</v>
+        <v>-0.02380061937924893</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>-0.004282627029306374</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4284,59 +4285,59 @@
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
-      <c r="A69" t="n">
+      <c r="A69" s="16" t="n">
         <v>68</v>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>EWZ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Brazil Equity</t>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr"/>
+      <c r="D69" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.5438358180079361</v>
+        <v>0.3627319891209817</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.2835996016798725</v>
+        <v>0.1535686628625854</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1633905674777287</v>
+        <v>0.1820541061388952</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.03069479416340748</v>
+        <v>0.1300962681289961</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.08921825050857302</v>
-      </c>
-      <c r="K69" s="3" t="n">
-        <v>0.1033264645275243</v>
+        <v>0.007546799454060338</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>-0.02409825669431975</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.007940709370037213</v>
+        <v>-0.004409881302895546</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4347,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>XHE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4354,36 +4355,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D70" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.3908715705163566</v>
+        <v>0.1084156753727865</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1473519940470303</v>
+        <v>0.1389371090693037</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1629421035477405</v>
+        <v>0.1756045981260685</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1465087909002383</v>
+        <v>0.1191176470588236</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.01870560083798378</v>
+        <v>0.1161085309215351</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.01340574862080435</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>-0.003959396258503389</v>
+        <v>-0.03119032463399118</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>0.002524975299154519</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4392,7 +4393,7 @@
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4403,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>EWZ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -4413,38 +4414,38 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Brazil Equity</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.3230517303394433</v>
+        <v>0.5438358180079361</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1279426856075816</v>
+        <v>0.2835996016798725</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1510047107779968</v>
+        <v>0.1633905674777287</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.07221017636315818</v>
-      </c>
-      <c r="J71" s="5" t="n">
-        <v>-0.01512075965040849</v>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>-0.02003642987249543</v>
+        <v>0.03069479416340748</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>0.08921825050857302</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0.1033264645275243</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.0006754474839580915</v>
+        <v>-0.007940709370037213</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4455,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPGP</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4469,29 +4470,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2424367929119193</v>
+        <v>0.3908715705163566</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.08870617726518093</v>
+        <v>0.1473519940470303</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1405408024305901</v>
+        <v>0.1629421035477405</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1123808186336495</v>
+        <v>0.1465087909002383</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.00614643885673205</v>
+        <v>0.01870560083798378</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.04544740973312411</v>
+        <v>-0.01340574862080435</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.006535413773384513</v>
+        <v>-0.003959396258503389</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4510,49 +4511,49 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MGK</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.4214606173976185</v>
+        <v>0.3230517303394433</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1224448921760679</v>
+        <v>0.1279427676161464</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1361731791203218</v>
+        <v>0.1510047944633168</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1615397392745861</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>0.010407111287424</v>
+        <v>0.07221017636315818</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>-0.01512075965040849</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.0120829176366255</v>
-      </c>
-      <c r="L73" s="3" t="n">
-        <v>0.0007860752386301684</v>
+        <v>-0.02003642987249543</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>-0.0006754474839580915</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4562,10 +4563,14 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VUG</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>SPGP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -4573,29 +4578,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3901776055297477</v>
+        <v>0.2424365992254389</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.101615009490357</v>
+        <v>0.08870617726518093</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1245178715070989</v>
+        <v>0.1405408024305901</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.1465563184158305</v>
+        <v>0.1123808186336495</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.004223432347362666</v>
+        <v>0.00614643885673205</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.02036682795093958</v>
-      </c>
-      <c r="L74" s="15" t="n">
-        <v>0</v>
+        <v>-0.04544740973312411</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>-0.006535413773384513</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -4604,7 +4609,7 @@
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d flat.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4619,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SCHG</t>
+          <t>MGK</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -4625,29 +4630,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3763779130758496</v>
+        <v>0.4214606173976185</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1067836036663254</v>
+        <v>0.1224448921760679</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1232507703017041</v>
+        <v>0.1361731791203218</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1545476931216689</v>
+        <v>0.1615397392745861</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.03021277536254585</v>
+        <v>0.010407111287424</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.01466027628982225</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>-0.001713796058268935</v>
+        <v>-0.0120829176366255</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0.0007860752386301684</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4656,7 +4661,7 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4666,53 +4671,49 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IAK</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D76" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>VUG</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1022626074385649</v>
+        <v>0.3901776055297477</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1237280951548987</v>
+        <v>0.101615009490357</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1200424993345803</v>
+        <v>0.1245178715070989</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1126979284233816</v>
+        <v>0.1465563184158305</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.06282475133545251</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>0.003290585689835757</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>-0.007588300220750521</v>
+        <v>0.004223432347362666</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>-0.02036682795093958</v>
+      </c>
+      <c r="L76" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d flat.</t>
         </is>
       </c>
     </row>
@@ -4722,49 +4723,49 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IGF</t>
+          <t>SCHG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" s="19" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2252971726620885</v>
+        <v>0.3763779130758496</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.06139291927817614</v>
+        <v>0.1067835368152616</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1057088960634056</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>-0.05283973067185799</v>
-      </c>
-      <c r="J77" s="5" t="n">
-        <v>-0.05604675558219696</v>
+        <v>0.1232507024560034</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0.1545476931216689</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0.03021277536254585</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.04007924413288633</v>
+        <v>-0.01466027628982225</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.002059569074778111</v>
+        <v>-0.001713796058268935</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4774,49 +4775,53 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BOTZ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>IAK</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D78" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1406701263312977</v>
+        <v>0.1022626074385649</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.01387258514991463</v>
+        <v>0.1237278272797779</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1043969231097286</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>-0.01816382956963625</v>
-      </c>
-      <c r="J78" s="5" t="n">
-        <v>-0.08296299740877655</v>
-      </c>
-      <c r="K78" s="5" t="n">
-        <v>-0.08196721311475419</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>0.002598902685532645</v>
+        <v>0.1200422323380346</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0.1126980597445204</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>0.06282475133545251</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0.003290585689835757</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>-0.007588300220750521</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4826,53 +4831,49 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EDEN</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>IGF</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.08423727729767871</v>
+        <v>0.2252970817396007</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.05751453587875899</v>
+        <v>0.06139291927817614</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.09912073717437253</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>0.1007048311609744</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>0.04250372023809534</v>
+        <v>0.1057088960634056</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>-0.05283973067185799</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>-0.05604675558219696</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.03785407725321888</v>
+        <v>-0.04007924413288633</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>-0.02428621169916423</v>
+        <v>-0.002059569074778111</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4882,40 +4883,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="18" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>U.S. Equity REITs</t>
+          <t>Robotics &amp; AI</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.09860849955235418</v>
+        <v>0.1406701263312977</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.04792056421428725</v>
+        <v>0.01387258514991463</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.09836603425027679</v>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>0.02112742449684157</v>
+        <v>0.1043969231097286</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>-0.01816382956963625</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-0.03830375537760533</v>
+        <v>-0.08296299740877655</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.04592774035517455</v>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v>-0.006588735387885181</v>
+        <v>-0.08196721311475419</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.002598902685532645</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4924,7 +4925,7 @@
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4934,49 +4935,53 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>XLP</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>EDEN</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Denmark Equity</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.09050642544331566</v>
+        <v>0.08423727729767871</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.07886234615012455</v>
+        <v>0.05751453587875899</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.09607754615467967</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>-0.003533167897017409</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>-0.01941427108209914</v>
+        <v>0.09912073717437253</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>0.1007048311609744</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>0.04250372023809534</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.01570618800188961</v>
+        <v>-0.03785407725321888</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.004538397229189139</v>
+        <v>-0.02428621169916423</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4986,49 +4991,49 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VFH</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>U.S. Equity REITs</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1986101299150191</v>
+        <v>0.09860859805713895</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.05719313935641179</v>
+        <v>0.04792065383906996</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.09376563728782683</v>
+        <v>0.09836612818947432</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1395935888519262</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>0.03063495776495273</v>
+        <v>0.02112750959718324</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>-0.03830375537760533</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.03343723434400681</v>
+        <v>-0.04592774035517455</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-0.01601038511466901</v>
+        <v>-0.006588735387885181</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N82" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5038,49 +5043,49 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.178887488531229</v>
+        <v>0.09024486506207108</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.05808419686676292</v>
+        <v>0.0786034709620862</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.08929891034486337</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>0.1383056094336323</v>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>0.03267560958574856</v>
+        <v>0.09607754615467967</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>-0.003772272115878383</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>-0.01964956459833611</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.02865578325807572</v>
+        <v>-0.01594237128011344</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.01618293755496925</v>
+        <v>-0.004777260241251691</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5090,49 +5095,49 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VONG</t>
+          <t>VFH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D84" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.3179981291923279</v>
+        <v>0.1986102102499248</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.04420052146675557</v>
+        <v>0.05719313935641179</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.08219284503618107</v>
+        <v>0.09376563728782683</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.08964083071100393</v>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>-0.02110823645643667</v>
+        <v>0.139593516233248</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0.03063495776495273</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.0351067961165048</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>0.0008056070248934066</v>
+        <v>-0.03343723434400681</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>-0.01601038511466901</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5142,49 +5147,49 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IWF</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Russell 1000 Growth</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.3146590033972314</v>
+        <v>0.1788875833206798</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.0426685428111151</v>
+        <v>0.05808419686676292</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.08096689512078492</v>
+        <v>0.08929891034486337</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.08856666456947182</v>
-      </c>
-      <c r="J85" s="5" t="n">
-        <v>-0.02190150306111882</v>
+        <v>0.1383056094336323</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0.03267560958574856</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.03542971804459427</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>0.0007471980074720275</v>
+        <v>-0.02865578325807572</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>-0.01618293755496925</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5194,53 +5199,49 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EUO</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D86" s="22" t="inlineStr">
-        <is>
-          <t>Currency</t>
+          <t>VONG</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2x Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>-0.03333333333333344</v>
+          <t>Large Growth</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.3179982358748332</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.1053577849694354</v>
+        <v>0.04420052146675557</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.08090614886731395</v>
+        <v>0.08219284503618107</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.03816278284363395</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>0.03676222596964585</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>0.02262142381902854</v>
+        <v>0.08964083071100393</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>-0.02110823645643667</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>-0.0351067961165048</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.01351796900758329</v>
+        <v>0.0008056070248934066</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N86" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5250,100 +5251,96 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VOT</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
+          <t>IWF</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Russell 1000 Growth</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.3146588940053539</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.04266861162109947</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0.08096696645823531</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0.08856673957249583</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>-0.02190150306111882</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>-0.03542971804459427</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>0.0007471980074720275</v>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N87" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="21" customHeight="1">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EUO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D87" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Mid Growth</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>0.1995209717921596</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>-0.001767106668587703</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>0.07729299364948794</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>0.08253864573717418</v>
-      </c>
-      <c r="J87" s="5" t="n">
-        <v>-0.04602879178468755</v>
-      </c>
-      <c r="K87" s="5" t="n">
-        <v>-0.07338774203872622</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>-0.0007593014426728883</v>
-      </c>
-      <c r="M87" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N87" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="21" customHeight="1">
-      <c r="A88" s="16" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="17" t="inlineStr">
-        <is>
-          <t>UUP</t>
-        </is>
-      </c>
-      <c r="C88" s="16" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E88" s="16" t="inlineStr">
-        <is>
-          <t>US Dollar Index Bullish</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>0.03451674912959546</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2x Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-0.03333333333333344</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.07582160747785771</v>
+        <v>0.1053577849694354</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.06445729472280992</v>
+        <v>0.08090614886731395</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.02601156069364152</v>
+        <v>0.03816278284363395</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.01682778374507699</v>
+        <v>0.03676222596964585</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0.01067615658362975</v>
+        <v>0.02262142381902854</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.006378454996456506</v>
+        <v>0.01351796900758329</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5362,157 +5359,161 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>VOT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D89" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Mid Growth</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.1995208959593489</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-0.001767211703863958</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.07729288029541204</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0.08253864573717418</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.04602879178468755</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>-0.07338774203872622</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>-0.0007593014426728883</v>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="inlineStr">
+        <is>
+          <t>US Dollar Index Bullish</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.03451674912959546</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.07582160747785771</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.06445729472280992</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0.02601156069364152</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0.01682778374507699</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>0.01067615658362975</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0.006378454996456506</v>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="21" customHeight="1">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>XLU</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" s="12" t="inlineStr">
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" s="12" t="inlineStr">
         <is>
           <t>Defensive Equity</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="F89" s="3" t="n">
-        <v>0.09205654342236635</v>
-      </c>
-      <c r="G89" s="5" t="n">
+      <c r="F91" s="3" t="n">
+        <v>0.09205643330773783</v>
+      </c>
+      <c r="G91" s="5" t="n">
         <v>-0.00881508329771763</v>
       </c>
-      <c r="H89" s="3" t="n">
+      <c r="H91" s="3" t="n">
         <v>0.05979064907809373</v>
       </c>
-      <c r="I89" s="5" t="n">
+      <c r="I91" s="5" t="n">
         <v>-0.1115090574609578</v>
       </c>
-      <c r="J89" s="5" t="n">
+      <c r="J91" s="5" t="n">
         <v>-0.07714496507150692</v>
       </c>
-      <c r="K89" s="5" t="n">
+      <c r="K91" s="5" t="n">
         <v>-0.0647351742870077</v>
       </c>
-      <c r="L89" s="15" t="n">
+      <c r="L91" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="M89" s="6" t="inlineStr">
+      <c r="M91" s="6" t="inlineStr">
         <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N89" s="7" t="inlineStr">
+      <c r="N91" s="7" t="inlineStr">
         <is>
           <t>Established trend; 3m and 1m now negative; 1d flat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="21" customHeight="1">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>USDU</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D90" s="22" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Bloomberg Dollar Bullish</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>0.02155757149775073</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0.05275016910016217</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>0.04640830061160695</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>0.01684532924961712</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>0.009118541033434679</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>0.0060606060606061</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>0.005299015897047621</v>
-      </c>
-      <c r="M90" s="6" t="inlineStr">
-        <is>
-          <t>STEADY_POSITIVE</t>
-        </is>
-      </c>
-      <c r="N90" s="7" t="inlineStr">
-        <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="21" customHeight="1">
-      <c r="A91" s="16" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>HYG</t>
-        </is>
-      </c>
-      <c r="C91" s="16" t="inlineStr"/>
-      <c r="D91" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
-        </is>
-      </c>
-      <c r="E91" s="16" t="inlineStr">
-        <is>
-          <t>High Yield Corporate Bonds</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>0.08662658843733517</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>0.02532668684107531</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>0.03455284277063719</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>0.01325843019648221</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>-0.004740596221788573</v>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>-0.008918013220913346</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>0.001148252105128922</v>
-      </c>
-      <c r="M91" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N91" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5522,49 +5523,53 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IWP</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>USDU</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Russell Midcap Growth</t>
+          <t>Bloomberg Dollar Bullish</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.1504312820015545</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>-0.05742011384824297</v>
+        <v>0.02155757149775073</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.05275016910016217</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.02582990467690127</v>
+        <v>0.04640830061160695</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.0265954552431642</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>-0.04501038526363865</v>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>-0.08115382301256358</v>
+        <v>0.01684532924961712</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0.009118541033434679</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>0.0060606060606061</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.001921655580192194</v>
+        <v>0.005299015897047621</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5574,40 +5579,40 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>HYG</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr"/>
-      <c r="D93" s="23" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
+      <c r="D93" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E93" s="16" t="inlineStr">
         <is>
-          <t>1-3 Year Treasury</t>
+          <t>High Yield Corporate Bonds</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.04171634382320044</v>
+        <v>0.08593431971429366</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.01506146755599169</v>
+        <v>0.02467336284028443</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.02150454198521112</v>
+        <v>0.03455284277063719</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.0005280396511564422</v>
+        <v>0.01261279592211206</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.001941145190740623</v>
+        <v>-0.005374665519267685</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.006307435908897485</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>-0.0008609027179929951</v>
+        <v>-0.009549516971887662</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>0.0005103342689463108</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5616,7 +5621,7 @@
       </c>
       <c r="N93" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5626,44 +5631,40 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>XRT</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D94" s="24" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Russell Midcap Growth</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.2414791159867113</v>
+        <v>0.1504312075146621</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.04757073333774586</v>
+        <v>-0.05742001384251527</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.007804399898630798</v>
+        <v>0.02583001351527936</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.0345021766835063</v>
+        <v>0.0265954552431642</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.04790418657056272</v>
+        <v>-0.04501038526363865</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.05494631025816776</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>-0.005888007690458941</v>
+        <v>-0.08115382301256358</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>0.001921655580192194</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -5672,7 +5673,7 @@
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5682,53 +5683,49 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>TIP</t>
-        </is>
-      </c>
-      <c r="C95" s="16" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D95" s="18" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="inlineStr"/>
+      <c r="D95" s="23" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
         </is>
       </c>
       <c r="E95" s="16" t="inlineStr">
         <is>
-          <t>TIPS</t>
+          <t>1-3 Year Treasury</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.03098034970404218</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>-0.0141121475258813</v>
-      </c>
-      <c r="H95" s="5" t="n">
-        <v>-0.001202713647768805</v>
-      </c>
-      <c r="I95" s="5" t="n">
-        <v>-0.02203594708834311</v>
+        <v>0.04171634382320044</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0.01506166108003404</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0.02150473673764175</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0.0005281336621643096</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-0.02332580868603851</v>
+        <v>-0.001941145190740623</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.01292497892666478</v>
+        <v>-0.006307435908897485</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.003781075716041249</v>
+        <v>-0.0008609027179929951</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N95" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5735,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VCR</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5753,81 +5750,85 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.1525107451880932</v>
+        <v>0.2414791159867113</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.06550250085512099</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>-0.007402429471997984</v>
-      </c>
-      <c r="I96" s="5" t="n">
-        <v>-0.0006473256223520352</v>
+        <v>-0.04757073333774586</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0.007804399898630798</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.03450207798971738</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-0.06443152081822012</v>
+        <v>-0.04790418657056272</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.05853336045565494</v>
+        <v>-0.05494631025816776</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.005639703512729688</v>
+        <v>-0.005888007690458941</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N96" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
-      <c r="A97" t="n">
+      <c r="A97" s="16" t="n">
         <v>96</v>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>FXE</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" s="22" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Euro Currency</t>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D97" s="18" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
+        </is>
+      </c>
+      <c r="E97" s="16" t="inlineStr">
+        <is>
+          <t>TIPS</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.06622160787579157</v>
+        <v>0.03098019581015032</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.01785748886543281</v>
+        <v>-0.01411200679942159</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>-0.009253443882858758</v>
+        <v>-0.001202571078605663</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.001441180899948824</v>
+        <v>-0.02203594708834311</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.009661738492495076</v>
+        <v>-0.02332587774023143</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.008684405642846116</v>
+        <v>-0.01292497892666478</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>-0.006009953986289784</v>
+        <v>-0.003781075716041249</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -5846,40 +5847,44 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IEF</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" s="23" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
+          <t>VCR</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D98" s="24" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>7-10 Year Treasury</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.01792270797077555</v>
+        <v>0.1525105262289241</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.02901274797077058</v>
+        <v>-0.06550250085512099</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-0.009988539527048035</v>
+        <v>-0.007402429471997984</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.03743900914914555</v>
+        <v>-0.0006472433069987238</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.0301521252653485</v>
+        <v>-0.06443152081822012</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.01921614971470553</v>
+        <v>-0.05853336045565494</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>-0.0009909711517285258</v>
+        <v>-0.005639703512729688</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5898,40 +5903,40 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LQD</t>
+          <t>FXE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D99" s="22" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Investment Grade Corporate Bonds</t>
+          <t>Euro Currency</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.03632924745239174</v>
+        <v>0.06622177175514521</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.02677911322448678</v>
+        <v>-0.01785748886543281</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.01924924430314967</v>
+        <v>-0.009253443882858758</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.02134308128001017</v>
+        <v>-0.001441037160302638</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.03122430465008319</v>
+        <v>-0.009661667801133311</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.007677658036558843</v>
-      </c>
-      <c r="L99" s="3" t="n">
-        <v>0.001630226313770633</v>
+        <v>-0.008684405642846116</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>-0.006009953986289784</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5940,50 +5945,50 @@
       </c>
       <c r="N99" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
-      <c r="A100" s="16" t="n">
+      <c r="A100" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="C100" s="16" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" s="23" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
       </c>
-      <c r="E100" s="16" t="inlineStr">
-        <is>
-          <t>20+ Year Treasury</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>-0.0407685119672373</v>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>7-10 Year Treasury</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0.01792262084057472</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.06182780185649384</v>
+        <v>-0.02901274797077058</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.05997803926142375</v>
+        <v>-0.009988539527048035</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>-0.05348680697430352</v>
+        <v>-0.03743900914914555</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>-0.05072456557839544</v>
+        <v>-0.0301521252653485</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.001967786575556962</v>
-      </c>
-      <c r="L100" s="3" t="n">
-        <v>0.00210630652955035</v>
+        <v>-0.01921614971470553</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>-0.0009909711517285258</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -5992,7 +5997,7 @@
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6002,44 +6007,40 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INDA</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>LQD</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" s="21" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>India Equity</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>-0.02964628910243294</v>
+          <t>Investment Grade Corporate Bonds</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0.03632916900525096</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.111734980348119</v>
+        <v>-0.02677904404067288</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.07205689687441519</v>
+        <v>-0.01924917458405639</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>-0.02184666117065137</v>
+        <v>-0.02134315123883856</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>-0.03946569520340004</v>
+        <v>-0.03122430465008319</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>-0.04275917708753529</v>
-      </c>
-      <c r="L101" s="5" t="n">
-        <v>-0.002731666316453052</v>
+        <v>-0.007677658036558843</v>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>0.001630226313770633</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6048,54 +6049,50 @@
       </c>
       <c r="N101" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
-      <c r="A102" t="n">
+      <c r="A102" s="16" t="n">
         <v>101</v>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>IPAY</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Digital Payments</t>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C102" s="16" t="inlineStr"/>
+      <c r="D102" s="23" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E102" s="16" t="inlineStr">
+        <is>
+          <t>20+ Year Treasury</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.08495715339704712</v>
+        <v>-0.0407684251720124</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.1743016423495968</v>
+        <v>-0.06182780185649384</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.1311770856391509</v>
-      </c>
-      <c r="I102" s="3" t="n">
-        <v>0.09659090909090917</v>
-      </c>
-      <c r="J102" s="3" t="n">
-        <v>0.06676984302454136</v>
+        <v>-0.05997803926142375</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>-0.05348672246542685</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>-0.05072456557839544</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>-0.04963561158164276</v>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v>-0.01831129196337744</v>
+        <v>-0.001967786575556962</v>
+      </c>
+      <c r="L102" s="3" t="n">
+        <v>0.00210630652955035</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6104,7 +6101,7 @@
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6111,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DRIV</t>
+          <t>INDA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6122,31 +6119,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Autonomous &amp; Electric Vehicles</t>
-        </is>
-      </c>
-      <c r="F103" s="25" t="n"/>
-      <c r="G103" s="25" t="n"/>
-      <c r="H103" s="25" t="n"/>
-      <c r="I103" s="25" t="n"/>
-      <c r="J103" s="25" t="n"/>
-      <c r="K103" s="25" t="n"/>
-      <c r="L103" s="25" t="n"/>
+          <t>India Equity</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>-0.02964628910243294</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>-0.111734980348119</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>-0.07205689687441519</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>-0.02184666117065137</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>-0.03946569520340004</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>-0.04275917708753529</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>-0.002731666316453052</v>
+      </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_DATA</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N103" s="7" t="inlineStr">
         <is>
-          <t>Insufficient history for transition assessment.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6167,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FTXL</t>
+          <t>IPAY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6171,24 +6182,38 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="F104" s="25" t="n"/>
-      <c r="G104" s="25" t="n"/>
-      <c r="H104" s="25" t="n"/>
-      <c r="I104" s="25" t="n"/>
-      <c r="J104" s="25" t="n"/>
-      <c r="K104" s="25" t="n"/>
-      <c r="L104" s="25" t="n"/>
+          <t>Digital Payments</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>-0.08495715339704712</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>-0.1743016423495968</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>-0.1311770856391509</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>0.09659090909090917</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>0.06676984302454136</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>-0.04963561158164276</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>-0.01831129196337744</v>
+      </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_DATA</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N104" s="7" t="inlineStr">
         <is>
-          <t>Insufficient history for transition assessment.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -56,7 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECFCCB"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00ECFCCB"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,12 +96,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
+        <fgColor rgb="00FCE7F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE7F3"/>
+        <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,12 +121,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0F2FE"/>
+        <fgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E7EB"/>
+        <fgColor rgb="00E0F2FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -201,9 +201,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -675,49 +672,53 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EWY</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>FTXL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>South Korea Equity</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.197055476691696</v>
+        <v>1.832371179500452</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.26648172239348</v>
+        <v>1.191457600656538</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.38991549968687</v>
+        <v>1.176101758987421</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.305809715093357</v>
+        <v>0.5237088156241601</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1474916225535429</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>-0.05164775796866561</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>-0.005382741231797938</v>
+        <v>-0.1409075304160513</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.007056582536040468</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.03889955785806798</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -727,53 +728,49 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PSI</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>EWY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Growth &amp; Technology</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>South Korea Equity</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.504682696040697</v>
+        <v>2.232784404335955</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.9137920097345653</v>
+        <v>1.31811744068228</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>1.320015883643104</v>
+        <v>1.154782282650168</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.3561961264422802</v>
+        <v>0.3871701546860782</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.221232714000884</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>-0.1750952986022871</v>
+        <v>-0.1079578700994734</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.07580123493090252</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.009799346710219314</v>
+        <v>0.04215563404352296</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -783,7 +780,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FTXL</t>
+          <t>PSI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -791,7 +788,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -802,25 +799,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.776849582107071</v>
+        <v>1.574026004770899</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.123581207927733</v>
+        <v>0.9711624285482421</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.312598998441777</v>
+        <v>1.143606176013775</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.4674253336045502</v>
+        <v>0.4098527830124987</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.1651206708957424</v>
+        <v>-0.1966081030213387</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.0817339238845145</v>
+        <v>-0.08044562914359932</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.003136060212356018</v>
+        <v>0.03619839802834246</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -847,7 +844,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -858,34 +855,34 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.881255301102629</v>
+        <v>1.956213511259383</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.026849642004773</v>
+        <v>1.105435105435105</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>1.227028639618138</v>
+        <v>1.068310068310068</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.5050952591936197</v>
+        <v>0.583780160857909</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1297553477648264</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>-0.08988613529805767</v>
+        <v>-0.1128769866099362</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.01794945433658812</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.02380952380952372</v>
+        <v>0.04342066529290545</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -899,7 +896,7 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -910,25 +907,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.518322249479843</v>
+        <v>1.563187422523682</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.9578452268826696</v>
+        <v>1.015272663265338</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.178933257724606</v>
+        <v>1.06028796286846</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4772279461698796</v>
+        <v>0.5372207371173916</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1502803607963801</v>
+        <v>-0.133310642269303</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.1014661784880975</v>
+        <v>-0.02184903295772711</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.006434800040092226</v>
+        <v>0.03461737640919416</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -955,7 +952,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -966,25 +963,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.463447018756307</v>
+        <v>1.509498100642836</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.8624219988613668</v>
+        <v>0.9196313768946232</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.089520989351406</v>
+        <v>0.9794101074906643</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4374664924451526</v>
+        <v>0.4928409264354912</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1528339086334437</v>
+        <v>-0.1370721643736043</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.1086847136962867</v>
+        <v>-0.03020027551128546</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.006477272727272609</v>
+        <v>0.03330698882240046</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1011,7 +1008,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -1022,25 +1019,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.415401665104408</v>
+        <v>1.456957464653919</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7816113374586577</v>
+        <v>0.8311414715392698</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.940028314473321</v>
+        <v>0.8604305924374638</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3746220520056438</v>
+        <v>0.4245433992938246</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1143506493506494</v>
+        <v>-0.101238841610975</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.08165704378271943</v>
+        <v>-0.01574319462239149</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.006364022061942975</v>
+        <v>0.0279345993108</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1067,7 +1064,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -1078,34 +1075,34 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.255424028345633</v>
+        <v>1.280200115897476</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.7991140938455092</v>
+        <v>0.8261046120534352</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.7891558977541133</v>
+        <v>0.7243515192424976</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.4849315068493152</v>
+        <v>0.5496215306980654</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.04441661046343581</v>
+        <v>0.05175530396727246</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.005565862708719838</v>
+        <v>0.05900948366701786</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.01621824317990073</v>
+        <v>0.01983394833948338</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1115,49 +1112,53 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>BDRY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Defensive Equity</t>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Dry Bulk Freight Futures</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7778919021250745</v>
+        <v>1.268221574344023</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.6577722210125045</v>
+        <v>0.9353233830845773</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7152964224810276</v>
+        <v>0.718905472636816</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.2427034898187375</v>
+        <v>0.4542056074766356</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.1403232213848558</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>-0.03353601203535383</v>
+        <v>0.3097643097643097</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1259044862518091</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.0009738362656626087</v>
+        <v>0.01699346405228752</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1167,53 +1168,49 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BDRY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Transportation &amp; Trade</t>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dry Bulk Freight Futures</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.201438848920863</v>
+        <v>0.8011900499529667</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8635809987819731</v>
+        <v>0.6962282391798982</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7052375152253347</v>
+        <v>0.7158396725745104</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.466922339405561</v>
+        <v>0.3081939558176163</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2613355317394888</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0.09285714285714297</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>-0.001956947162426559</v>
+        <v>0.1366337743443686</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>-0.01142964212104192</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.02659229472045666</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1242,34 +1239,34 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.6007799384973866</v>
+        <v>0.5938264411098892</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.5950679769775422</v>
+        <v>0.578758511853489</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.7017781642581455</v>
+        <v>0.6440122997753184</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.03687472447683016</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>-0.01560845909549713</v>
+        <v>0.05326308101622423</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0.01682111200644654</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.06270511017346458</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>-0.02833466987436506</v>
+        <v>-0.03969178815191798</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0.009878704514192815</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1298,34 +1295,34 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.10391028713678</v>
+        <v>1.126146643052305</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.5939685788901037</v>
+        <v>0.6595558348679367</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.6536075030319715</v>
+        <v>0.6354738315058084</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.08427801840979376</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>-0.05918147044773614</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>-0.03606594916418604</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>-0.004728691334673241</v>
+        <v>0.1627528430943797</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0.004207782858709042</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0.01472478672431943</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0.03135764342558489</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1340,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -1354,34 +1351,34 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.197396195364505</v>
+        <v>1.166308059963949</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5591612290791566</v>
+        <v>0.5920153628927736</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.5577639747011311</v>
+        <v>0.5417912784977723</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1092006754117099</v>
+        <v>0.1735638495722966</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.01316536147996827</v>
+        <v>0.01642664266426652</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.0008969615427738553</v>
+        <v>0.03257515144587964</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.008472661545413374</v>
+        <v>0.01198610955528179</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1391,49 +1388,53 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>BOAT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Silver Bullion</t>
+          <t>Global Shipping</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.8577010745685443</v>
+        <v>1.187735811136712</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.4718782249742002</v>
+        <v>0.7255824584536505</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5368937048503613</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>-0.2038794306447111</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>-0.1000157753588895</v>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>-0.04230317273795536</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>-0.0083434729706241</v>
+        <v>0.5377114376227534</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0.3722718186800078</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.3352215027451173</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.1221757322175734</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0.02093642938713369</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1443,53 +1444,49 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOAT</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Global Shipping</t>
+          <t>Silver Bullion</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.181517412012098</v>
+        <v>0.9243752028562155</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6912011992259435</v>
+        <v>0.5360103626943005</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5337978139154207</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.3660330067772257</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.2823302282055018</v>
+        <v>0.4880829015544039</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>-0.1369723435225619</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>-0.02177858439201452</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.1026232948583421</v>
+        <v>0.03220752089136503</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.004012994458245656</v>
+        <v>0.03926380368098159</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1518,90 +1515,86 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.6962227683624993</v>
+        <v>0.7196789716677079</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.4513188820434806</v>
+        <v>0.4880917751479625</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.5013233061992033</v>
+        <v>0.4773465681708029</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.08628256828500547</v>
+        <v>0.1465676755149798</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.07088414634146334</v>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>-0.03330689928628061</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>-0.007813771772749445</v>
+        <v>-0.02746566791510607</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0.007273315015354775</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0.02247744052502054</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="A18" t="n">
+      <c r="A18" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>QTEC</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Technology</t>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr"/>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.6845085175280921</v>
+        <v>0.4706236358940235</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.3815094443505727</v>
+        <v>0.470361347159467</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4828750110728948</v>
+        <v>0.4627809808954044</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.3425610636490672</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>-0.0628864850776788</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>-0.06835745829244344</v>
-      </c>
-      <c r="L18" s="15" t="n">
-        <v>0</v>
+        <v>0.1106086609808365</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.1792871089520247</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.005182160804020119</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>-0.0003123535842572966</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1604,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>VDE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1626,38 +1619,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.728460434896361</v>
+        <v>0.4882960436920567</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.356358518297361</v>
+        <v>0.4660239794897567</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.4804405645667975</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>-0.02079474996605468</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>-0.1608819995152714</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>-0.08381427072402936</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>-0.002427877749214491</v>
+        <v>0.4580507096085207</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0.1041802318566281</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0.1757860304545862</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.005468444841247644</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0.000166518650088765</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1660,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VDE</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1675,97 +1668,101 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.5199829672628018</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.4656157349395724</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.4471244451093954</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.2589453658706176</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.1886593750805832</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.01277795416466709</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0.0185276679841897</v>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LIT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.5134113283503212</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.4912450117932252</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>0.4619432392479987</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0.1046649524952612</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0.1630014852963744</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0.02004303023440146</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>-0.02936264209902495</v>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>STEADY_POSITIVE</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
-        <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr"/>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>Energy</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Lithium &amp; Battery</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.494683122866828</v>
+        <v>0.7223906242415876</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.4954732328165075</v>
+        <v>0.3770130399083618</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.461607292045245</v>
+        <v>0.4376093824261909</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1094366533184026</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0.1649524911997617</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0.0231703419622884</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>-0.02881844380403464</v>
+        <v>0.02526673875951824</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>-0.142834065483448</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>-0.04215077006214529</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0.01503221188260584</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1772,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1783,45 +1780,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.5639287034296459</v>
+        <v>0.6800627260220062</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.5173683671939879</v>
+        <v>0.3999913220126388</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.4505187180657855</v>
+        <v>0.4359489938622265</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.1377862351005668</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>0.2263159446340324</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0.04608671938914655</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>-0.03955933900851261</v>
+        <v>0.3801549797055879</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>-0.047997304427427</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>-0.02504105090311992</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0.01632706804042261</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1828,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1839,36 +1836,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5135746186739159</v>
+        <v>0.5344515468439641</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4420553443525967</v>
+        <v>0.4725775870877809</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.4386294013217875</v>
+        <v>0.4215002123156095</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.2109788826601171</v>
+        <v>0.1174814423948158</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.1806514305166258</v>
+        <v>0.2388513924808073</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.002381393726321512</v>
+        <v>0.03593202050175348</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.001980198019801982</v>
+        <v>0.001094890510948909</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1895,7 +1892,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -1906,34 +1903,34 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6393084462424521</v>
+        <v>0.6270969135633817</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3916303908682723</v>
+        <v>0.41178829099208</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.4170760977179588</v>
+        <v>0.3924326233702415</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.133824128527849</v>
+        <v>0.1493465622630548</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.0292714257692579</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>-0.0179564858165796</v>
+        <v>0.0311967915326794</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.01390061342788007</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.008769944551318298</v>
+        <v>0.01048852992315896</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1944,7 @@
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Inflation &amp; Real Assets</t>
         </is>
@@ -1958,25 +1955,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5601289979835771</v>
+        <v>0.5425399486078517</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.5200014943326683</v>
+        <v>0.4978483014763482</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.4008216425454265</v>
+        <v>0.3830480529839169</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.1529902642559109</v>
+        <v>0.1277758797403483</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1885304659498208</v>
+        <v>0.1912666907253697</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.08507853403141352</v>
+        <v>0.08300524934383202</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.01543942992874114</v>
+        <v>-0.00452352231604336</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -1999,7 +1996,7 @@
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -2010,34 +2007,34 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.7343822785570517</v>
+        <v>0.7561103577024879</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3529581027637547</v>
+        <v>0.3842733615972713</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3999618665687914</v>
+        <v>0.3701014257208357</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.3213292199158893</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>-0.01228643132437479</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>-0.03357503152585117</v>
+        <v>0.3626926106357811</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0.0105684692004735</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.01034371296196523</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.001034069881354016</v>
+        <v>0.01962703202305227</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2062,34 +2059,34 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.326797234695824</v>
+        <v>1.355887644165805</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.3659199049520672</v>
+        <v>0.4643321313468831</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3627653555179977</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>-0.03348475757819103</v>
+        <v>0.3558975082703129</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>0.07727744818674909</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.02045725177960733</v>
+        <v>0.10134224488655</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.002314814814814881</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>-0.01919965483766573</v>
+        <v>0.07997258082942982</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.03959089409435834</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2096,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>QCLN</t>
+          <t>FTEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2107,45 +2104,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6002955392934637</v>
+        <v>0.7261555191888269</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1976614556925833</v>
+        <v>0.3471468587106861</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3624584417851</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>-0.02834161704782701</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>-0.2422571752878223</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>-0.1209556057185854</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>-0.009747827929646125</v>
+        <v>0.3324618997013125</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0.3488298000135635</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0.03602812813227607</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.01102092225876428</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.01825293350717083</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2155,15 +2152,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FTEC</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
+          <t>VGT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -2174,34 +2167,34 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.7055331225651258</v>
+        <v>0.7212714441923189</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3189574781722211</v>
+        <v>0.3429432983613236</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3587878653878944</v>
+        <v>0.3291843155474095</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.3113349388652527</v>
+        <v>0.3480776768721869</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.009574072612611895</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>-0.02931317553700918</v>
+        <v>0.0362958075134403</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0.01035144836797719</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.001093551573303264</v>
+        <v>0.01774302051799537</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2211,11 +2204,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VGT</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" s="8" t="inlineStr">
+          <t>IYW</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -2226,34 +2223,34 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.701115758978293</v>
+        <v>0.7370497699931946</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3150272292956409</v>
+        <v>0.3399616781427572</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3550574897232412</v>
+        <v>0.3146792410827406</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3107371390078359</v>
+        <v>0.3488177888387118</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.01062351304586895</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>-0.02954137424514447</v>
+        <v>0.03242680116671703</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0.01923087873449236</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.001094368212812391</v>
+        <v>0.01670997401559071</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DRIV</t>
+          <t>CALF</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2271,45 +2268,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Autonomous &amp; Electric Vehicles</t>
+          <t>Small Cap Cash Flow</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.4755852216264049</v>
+        <v>0.5110201526469906</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2389871087302566</v>
+        <v>0.3008576846656956</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3537359148051535</v>
+        <v>0.3071706687350122</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.07452518572044298</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>-0.1652516550158633</v>
+        <v>0.2647072751181541</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0.1534837902597246</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.0847645429362881</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>-0.005118940078289724</v>
+        <v>-0.004829502543402087</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.001249776825566817</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2319,44 +2316,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IYW</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SCHD</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.7172757342319811</v>
+        <v>0.2822802727355507</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.313997413750204</v>
+        <v>0.283238694602242</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3381093666486981</v>
+        <v>0.3047898453365754</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.3116315973389781</v>
+        <v>0.1281778891186309</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.008581576260859647</v>
+        <v>0.07141579146308508</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.01801941866596646</v>
+        <v>-0.01651695160822952</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.0002799104286628218</v>
+        <v>0.002955082742316595</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2375,10 +2368,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AIRR</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>XAR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -2386,29 +2383,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>U.S. Industrial Renaissance</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.5341337758498388</v>
+        <v>0.4892006554139743</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.1320707374096364</v>
+        <v>0.08651383744951957</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3380381699447861</v>
+        <v>0.2980510646255203</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>-0.05106036756282339</v>
+        <v>-0.1025005291283249</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.18906885698933</v>
+        <v>-0.148594029924464</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.153932404292808</v>
+        <v>-0.1629652584099439</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.005616373155640231</v>
+        <v>0.003343101242312851</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2446,25 +2443,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.8968686481124624</v>
+        <v>0.9280021805015242</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.2253631561974059</v>
+        <v>0.2666260054208822</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3304715339423887</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>-0.01677476546138834</v>
+        <v>0.2924453394035098</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.03331701647914653</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.0878705058185113</v>
+        <v>-0.05873649716689966</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.07900084674005081</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>-0.006122076023391876</v>
+        <v>-0.01997711871864816</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.02381171278845273</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2473,7 +2470,7 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2480,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>DRIV</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2491,36 +2488,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Autonomous &amp; Electric Vehicles</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.505430395529215</v>
+        <v>0.4896398237672306</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.08759251623105135</v>
+        <v>0.2538522444654399</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.3236138728839413</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>-0.1143784455758354</v>
+        <v>0.2898249353004436</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.1199227194915655</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1400487751725126</v>
+        <v>-0.1351119985397546</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.1783158680096314</v>
+        <v>-0.02788959171937888</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.003146607046743632</v>
+        <v>0.02330508474576276</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2539,44 +2536,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ROBO</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>AIRR</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>U.S. Industrial Renaissance</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.4096922656545374</v>
+        <v>0.5352920644848953</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.1929161635099303</v>
+        <v>0.1483878368827733</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.3045790225491527</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>0.08067437648042364</v>
+        <v>0.2882679446023129</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>-0.0274379222943647</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.07809342683941511</v>
+        <v>-0.1704448742746615</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.08559302051402962</v>
+        <v>-0.108579980046558</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.004012944983818878</v>
+        <v>0.01495645588792116</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2595,40 +2588,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SCHA</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>QCLN</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.4170367484398614</v>
+        <v>0.6136795754387154</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2046870628998725</v>
+        <v>0.2142982238926159</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.3045310602485005</v>
+        <v>0.285281748110179</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.1338210538518381</v>
+        <v>0.01492423872899429</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.04726616496090641</v>
+        <v>-0.2123545797148944</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.07653631284916185</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>-0.002714932126696712</v>
+        <v>-0.05522798742138368</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0.02867536914187885</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2637,7 +2634,7 @@
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2647,53 +2644,49 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CALF</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="inlineStr">
+          <t>SCHA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Small Cap Cash Flow</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.5277156504642782</v>
+        <v>0.4161186164878679</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.302215098678249</v>
+        <v>0.2218271166052124</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.3039134726249164</v>
+        <v>0.2784100873473123</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.2521619291320183</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>0.1259608041840046</v>
+        <v>0.1617695778972048</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>-0.02508525178901266</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.001302520437378774</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>-0.01199506085729407</v>
+        <v>-0.04426042261564833</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0.01240169388989698</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2696,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ARGT</t>
+          <t>VHT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2711,45 +2704,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1250044276996893</v>
+        <v>0.2148908287266553</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.3296859761937441</v>
+        <v>0.2653927758144858</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.3004949690059397</v>
+        <v>0.2729384213304642</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.07093721295328792</v>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>-0.03879269977411504</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0.02244607467425808</v>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>-0.01185185185185189</v>
+        <v>0.1711580503673249</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>0.1278589806485781</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>-0.005927738050432785</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>0.007277696561367675</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2759,49 +2752,49 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SCHD</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" s="20" t="inlineStr">
+      <c r="D40" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.2933040309371149</v>
+        <v>0.4203430931872503</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2832017013267309</v>
+        <v>0.2150917392445053</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.3002655537379906</v>
+        <v>0.2694742212062169</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1114065579691639</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>0.04855551010097714</v>
+        <v>0.1708477892844722</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>-0.00866363738645981</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.0131233595800524</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>-0.01427323041071937</v>
+        <v>-0.04283858707271659</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0.009509721048182485</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2811,49 +2804,49 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SPMO</t>
+          <t>FNDX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Fundamental Large Cap</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.5494411538203954</v>
+        <v>0.3926606798859531</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1959695020802679</v>
+        <v>0.2545317458633416</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2917070022467936</v>
+        <v>0.2634871245582071</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.2295485527977308</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>-0.06945768407854536</v>
+        <v>0.1664401086182863</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0.04602819994686791</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.07411704047434908</v>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>-0.0002087827962975464</v>
+        <v>-0.007087827426810578</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>0.005931938807367976</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2863,49 +2856,49 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>HEFA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Developed ex-US Currency-Hedged</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4247159381385248</v>
+        <v>0.3343353058387137</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.201663407752436</v>
+        <v>0.2517424702370217</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2835516849073865</v>
+        <v>0.2613589296754624</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1411257131561792</v>
-      </c>
-      <c r="J42" s="5" t="n">
-        <v>-0.02539872874895854</v>
+        <v>0.1225960164627071</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>0.02333034702727965</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.06379819224876704</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>-0.004278599985971687</v>
+        <v>-0.007623888182973326</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>0.01013149385643453</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2915,53 +2908,49 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MTUM</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XLV</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.5050423004258826</v>
+        <v>0.1789930677142921</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.1883171638664756</v>
+        <v>0.2528660658456923</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2738927634890074</v>
+        <v>0.2611882886898127</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2116440051465807</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>-0.0785632020821696</v>
+        <v>0.1557007729229209</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0.123705271015661</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.06717645478113299</v>
+        <v>-0.006598715607140648</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.001068411739173936</v>
+        <v>0.005006854622399803</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2971,44 +2960,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ARKQ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SPMO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.7486713878044076</v>
+        <v>0.5709445678842062</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1609752720730777</v>
+        <v>0.2222158752552148</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2687196896505104</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>-0.02018875666803444</v>
+        <v>0.2568650373177859</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>0.2698687767654164</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-0.09792217604835662</v>
+        <v>-0.05482555744399653</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.08492373725760705</v>
+        <v>-0.0275679257786613</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.003699033207229974</v>
+        <v>0.0214395099540583</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3027,40 +3012,44 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PAVE</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" s="19" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>ROBO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>U.S. Infrastructure Development</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3914460936721222</v>
+        <v>0.4130815749620533</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.1381863205393463</v>
+        <v>0.2085622265211911</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2672167318535699</v>
+        <v>0.2544026560188233</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.03877537356569771</v>
+        <v>0.1142049469964663</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>-0.0967093679955533</v>
+        <v>-0.06065300285986663</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.1018218968159373</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>-0.001703255109765434</v>
+        <v>-0.03654363236372515</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0.01637441980402254</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -3069,7 +3058,7 @@
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3079,40 +3068,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FNDX</t>
+          <t>COWZ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="D46" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fundamental Large Cap</t>
+          <t>Large Cap Cash Flow</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4009789771004677</v>
+        <v>0.2965567595247445</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2471338243328005</v>
+        <v>0.2462925028729852</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2658233103046936</v>
+        <v>0.2516562329368497</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1459778988212084</v>
+        <v>0.1299784099657375</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.02625170665288601</v>
+        <v>0.1269403132801812</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.0147646877883727</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>-0.008972772277227703</v>
+        <v>-0.004285306079033435</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.001868621532269854</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3121,7 +3110,7 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3131,49 +3120,49 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HEFA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Developed ex-US Currency-Hedged</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3327399271236329</v>
+        <v>0.413006086229877</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2288165650257901</v>
+        <v>0.06706548223323128</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2627222602884116</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>0.1001711878506537</v>
-      </c>
-      <c r="J47" s="3" t="n">
-        <v>0.01503184228522247</v>
+        <v>0.2506848783201658</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>-0.06973979759139748</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>-0.1138880892383025</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.02685126914201807</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>0.0004313133491482546</v>
+        <v>-0.1468150764991734</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>-0.00176522506619603</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3172,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IWO</t>
+          <t>ARGT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3191,45 +3180,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Russell 2000 Growth</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.3942370309963887</v>
+        <v>0.1231944894852104</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.1555821129526982</v>
+        <v>0.3108958501354966</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2616564709050067</v>
+        <v>0.2434950948006611</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1275561247986636</v>
+        <v>0.08780130069548653</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.05216060541897483</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>-0.08407546776676833</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>-0.0002768472633647434</v>
+        <v>-0.02704086753495305</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0.05420267085624508</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.00599700149925031</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3239,49 +3228,49 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EWJ</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Japan Equity</t>
+          <t>U.S. Infrastructure Development</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4499739711133486</v>
+        <v>0.3855548087792697</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2438423872983786</v>
+        <v>0.1504113958479962</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2587156701482509</v>
+        <v>0.2434944755950332</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1464161728343478</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>0.03070548236294091</v>
+        <v>0.05571410554195788</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>-0.08394318523017519</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.01181623713965563</v>
+        <v>-0.07485604606525909</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.0009286009079654267</v>
+        <v>0.00511848341232235</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3291,40 +3280,44 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VEA</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>IWO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Developed Markets</t>
+          <t>Russell 2000 Growth</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.422325354923214</v>
+        <v>0.3927968606804535</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.2159291278567277</v>
+        <v>0.1694187964749572</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2573928912680641</v>
+        <v>0.2405129006938687</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.09703398655975493</v>
+        <v>0.1611238756270694</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.009470532446836266</v>
+        <v>-0.03694428411647088</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.03297598045867811</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>-0.003774640011184105</v>
+        <v>-0.05731024980001886</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.01235080723325299</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3333,7 +3326,7 @@
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3343,53 +3336,49 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>VEA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Developed Markets</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.2212317169209366</v>
+        <v>0.4255527328557043</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.2567434122284029</v>
+        <v>0.2345962090996794</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2554653410025938</v>
+        <v>0.2366461820496166</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.1435648958611413</v>
+        <v>0.132141190224305</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.1070297654840391</v>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>0.001018005980785386</v>
+        <v>0.00903339557743732</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>-0.001657687525901452</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.0003179043743641863</v>
+        <v>0.01417344934044329</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3399,40 +3388,44 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ITA</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" s="19" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>MTUM</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4360012324762166</v>
+        <v>0.51884323878377</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.07331186030181769</v>
+        <v>0.2162354060654474</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2510045642986529</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>-0.07397664357904776</v>
+        <v>0.2363091488547286</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0.2471006633947246</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.100202323281445</v>
+        <v>-0.06556436094727558</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.1420400125370083</v>
+        <v>-0.01623683106112794</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.005934579439252463</v>
+        <v>0.02101190674715681</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3451,49 +3444,49 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COWZ</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Large Cap Cash Flow</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.3133549034829655</v>
+        <v>0.2973597635515801</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2470248761272689</v>
+        <v>0.1290331971555523</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2458231004157341</v>
+        <v>0.2246314346599192</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1124794361249895</v>
-      </c>
-      <c r="J53" s="3" t="n">
-        <v>0.09956711039199551</v>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>0.0009646439459451983</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>-0.01277139208173694</v>
+        <v>0.0299860562703278</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>-0.05536530576508958</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>-0.0780628643024458</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>0.003141485389129173</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3496,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>XMMO</t>
+          <t>ARKQ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3511,36 +3504,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.2980581417813073</v>
+        <v>0.7718151338943267</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.09319290700227989</v>
+        <v>0.1814942318102704</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2439600928773975</v>
+        <v>0.2230669327581214</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.009527066295434317</v>
+        <v>0.02976040353089537</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.1396163990661091</v>
+        <v>-0.06809190505173468</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>-0.1211993750751111</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>-0.0006832934745473196</v>
+        <v>-0.03399053627760251</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>0.02596532372895544</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3549,7 +3542,7 @@
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3559,49 +3552,49 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>EWJ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Japan Equity</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.1880133187848854</v>
+        <v>0.4526297774418795</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2466242573687296</v>
+        <v>0.2592285419706604</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2412742575755278</v>
+        <v>0.2228146425795936</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1307313195355038</v>
+        <v>0.1734237141227468</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.1018040060577394</v>
+        <v>0.03980942297511891</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0.004310086800359159</v>
+        <v>0.02977875642235484</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.0006560897053562442</v>
+        <v>0.01236985877744545</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3608,7 @@
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -3626,25 +3619,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.4814498713708459</v>
+        <v>0.4928063236978504</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1972956224309301</v>
+        <v>0.2153914166511604</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2398734681355723</v>
+        <v>0.2200577400434403</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.170996316091176</v>
+        <v>0.2045413828196687</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.03335165909680304</v>
+        <v>-0.009777193212141544</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.03434047650738714</v>
+        <v>-0.003824674225757274</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.0003791926643454957</v>
+        <v>0.01419710544452113</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3658,45 +3651,45 @@
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
-      <c r="A57" s="16" t="n">
+      <c r="A57" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr"/>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="C57" s="15" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
       </c>
-      <c r="E57" s="16" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
         <is>
           <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4801454115477375</v>
+        <v>0.4917495181143843</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1967855633901516</v>
+        <v>0.2150156715005775</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2394963661476472</v>
+        <v>0.2195368181553883</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1708475124264404</v>
+        <v>0.2044678124078645</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.03338385295122281</v>
+        <v>-0.009514601429637781</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.03445819118473148</v>
+        <v>-0.003707265403966487</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.0002554858489227652</v>
+        <v>0.01437450334884782</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3715,10 +3708,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>XLI</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D58" s="19" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -3726,29 +3723,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3111484199813805</v>
+        <v>0.3744340209162895</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.1221714984740985</v>
+        <v>0.07075283884035199</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2393040933892123</v>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>0.01862040907777662</v>
+        <v>0.2186822834083209</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>-0.08036552343411341</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>-0.05963256018267826</v>
+        <v>-0.09680678076192939</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.09451481322455979</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>-0.0008291382884215714</v>
+        <v>-0.121384750219106</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>0.001435974277330443</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3757,7 +3754,7 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3767,40 +3764,44 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VBK</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" s="20" t="inlineStr">
+          <t>XMMO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3250574099150532</v>
+        <v>0.2946112872800928</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1234522531334306</v>
+        <v>0.1134989353036362</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2276686653366782</v>
+        <v>0.212536823845106</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.08434810529778858</v>
+        <v>0.02457359161809358</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>-0.04762494454298682</v>
+        <v>-0.1268894793792031</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.08488968982088252</v>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v>-0.002232807383149793</v>
+        <v>-0.08167825223435943</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>0.01169230769230767</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -3809,7 +3810,7 @@
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3820,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PPA</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3827,45 +3828,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D60" s="19" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3922748962354334</v>
+        <v>0.3030062772179487</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.07078371155382768</v>
+        <v>0.140913181067897</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2246123511421001</v>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>-0.08981635324863191</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>-0.09176523951156279</v>
+        <v>0.2076232471273391</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0.1720235581836023</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>0.02598225014715205</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.1256141500163774</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>0.004389540352417232</v>
+        <v>-0.05524079320113306</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>-0.001197963462114426</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3875,53 +3876,49 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D61" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>VBK</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3144595149196234</v>
+        <v>0.3239772570620578</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1309474745967232</v>
+        <v>0.1385883590590253</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2034310803360759</v>
+        <v>0.2003807911823312</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1599254619382551</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>0.01005909895017432</v>
+        <v>0.1107038718309439</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>-0.02796892953314156</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.06023079088094574</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>-0.01721854304635762</v>
+        <v>-0.05147735833263589</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>0.0143517827838282</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3931,49 +3928,49 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ONEQ</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" s="20" t="inlineStr">
+      <c r="D62" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.4776834653423609</v>
+        <v>0.250117504825214</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1712574894581185</v>
+        <v>0.1525409842696304</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.2006332262387114</v>
+        <v>0.1876646018689205</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1608204653120029</v>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v>-0.01409364302010541</v>
+        <v>0.1114524158837908</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>0.02452765577581828</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.02446686976389956</v>
-      </c>
-      <c r="L62" s="15" t="n">
-        <v>0</v>
+        <v>-0.0295736839710633</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>0.004757866968155167</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3983,101 +3980,105 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IAU</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>XHE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gold Bullion</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.4268964292058979</v>
+        <v>0.09062905038199776</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.157682329201499</v>
+        <v>0.1416089823725264</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1978956471605651</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>-0.1461677474221325</v>
-      </c>
-      <c r="J63" s="5" t="n">
-        <v>-0.01447852760736201</v>
+        <v>0.1842789574513684</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0.1481992721796963</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0.1417519341152982</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.03356996751293473</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>-0.005694478831393956</v>
+        <v>-0.03603034134007588</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>0.001971090670170872</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
-      <c r="A64" s="16" t="n">
+      <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr"/>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E64" s="16" t="inlineStr">
-        <is>
-          <t>Gold Bullion</t>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ONEQ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.4232669670106088</v>
+        <v>0.4907513806261772</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1558820925909532</v>
+        <v>0.1863454165205243</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.196453335693842</v>
-      </c>
-      <c r="I64" s="5" t="n">
-        <v>-0.1470376902475667</v>
-      </c>
-      <c r="J64" s="5" t="n">
-        <v>-0.01481276563639566</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>-0.03390959086537271</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>-0.006114423442851624</v>
+        <v>0.1839450644878686</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>0.1907064703226042</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0.01380198140180622</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>0.002027418420544658</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0.01288181906899588</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4087,40 +4088,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RSP</t>
+          <t>QUAL</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" s="20" t="inlineStr">
+      <c r="D65" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Equal Weight</t>
+          <t>Quality Factor</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2609877588381782</v>
+        <v>0.2806109256024816</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.144042692789847</v>
+        <v>0.1538918028254443</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1899057195264289</v>
+        <v>0.1828172450824099</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.09163193819662041</v>
+        <v>0.1284493015866939</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.004393284875514603</v>
+        <v>0.01944375470572357</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.03854341229222336</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>-0.007851934941110472</v>
+        <v>-0.0244547011613363</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.003588351658462496</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4129,7 +4130,7 @@
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4139,40 +4140,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>QUAL</t>
+          <t>IVV</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="20" t="inlineStr">
+      <c r="D66" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Quality Factor</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.2888386555921978</v>
+        <v>0.3670377619646923</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1486762844466596</v>
+        <v>0.1665969281255586</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.184490865179529</v>
+        <v>0.1762489654120805</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1084233178891734</v>
+        <v>0.1566829462327608</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.0003583424776849586</v>
+        <v>0.02968378500116531</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.03023626588073447</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>-0.005990488384854609</v>
+        <v>-0.008205777492982125</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0.00902558130301867</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4181,7 +4182,7 @@
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4196,7 @@
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" s="20" t="inlineStr">
+      <c r="D67" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -4206,25 +4207,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3644191729921495</v>
+        <v>0.3655094639765866</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1544421262208857</v>
+        <v>0.1657189193333604</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1828019286118927</v>
+        <v>0.1762407210770465</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1305961257976715</v>
+        <v>0.1560850484525858</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.007986666725831038</v>
+        <v>0.02893386450063917</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.02397679755585902</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>-0.004251651824188518</v>
+        <v>-0.008945279274170659</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0.008438635970226871</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4233,50 +4234,50 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
-      <c r="A68" t="n">
+      <c r="A68" s="15" t="n">
         <v>67</v>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>IVV</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" s="20" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr"/>
+      <c r="D68" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="15" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.364512104535744</v>
+        <v>0.3641044731970677</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1546340633570602</v>
+        <v>0.1652393950520699</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.182785080874406</v>
+        <v>0.1756872247120298</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1307447644786317</v>
+        <v>0.156089412920948</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.007717687042558818</v>
+        <v>0.02919128103797086</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.02380061937924893</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>-0.004282627029306374</v>
+        <v>-0.008886572415141125</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>0.008726211789669147</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4285,115 +4286,111 @@
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
-      <c r="A69" s="16" t="n">
+      <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="C69" s="16" t="inlineStr"/>
-      <c r="D69" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E69" s="16" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3627319891209817</v>
+        <v>0.449134581419993</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1535686628625854</v>
+        <v>0.1798964624676445</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1820541061388952</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>0.1300962681289961</v>
+        <v>0.1750071901064134</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>-0.09953906935908696</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.007546799454060338</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>-0.02409825669431975</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>-0.004409881302895546</v>
+        <v>0.03026117528879957</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>0.004161057398115231</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>0.0215388446215139</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
-      <c r="A70" t="n">
+      <c r="A70" s="15" t="n">
         <v>69</v>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>XHE</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D70" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Health Equipment</t>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr"/>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.1084156753727865</v>
+        <v>0.4463556535250965</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1389371090693037</v>
+        <v>0.1786271680555966</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1756045981260685</v>
-      </c>
-      <c r="I70" s="3" t="n">
-        <v>0.1191176470588236</v>
+        <v>0.1736211313642924</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>-0.1000359760759095</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.1161085309215351</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>-0.03119032463399118</v>
+        <v>0.02997941327843545</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>0.004265462300840461</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.002524975299154519</v>
+        <v>0.02172359217848574</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4403,49 +4400,53 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EWZ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>OEF</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Brazil Equity</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.5438358180079361</v>
+        <v>0.3979038686575651</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.2835996016798725</v>
+        <v>0.158509640725768</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1633905674777287</v>
+        <v>0.1576124926328364</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.03069479416340748</v>
+        <v>0.174522780581764</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.08921825050857302</v>
+        <v>0.04092796785374198</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.1033264645275243</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>-0.007940709370037213</v>
+        <v>0.0007749986274692144</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>0.009204172558226364</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4455,53 +4456,49 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>OEF</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D72" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>EWZ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>Brazil Equity</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.3908715705163566</v>
+        <v>0.4965613479471813</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1473519940470303</v>
+        <v>0.2661976336565888</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1629421035477405</v>
+        <v>0.1473745698904827</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1465087909002383</v>
+        <v>0.03541221226950597</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.01870560083798378</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>-0.01340574862080435</v>
+        <v>0.09029610085019057</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>0.103560830860534</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.003959396258503389</v>
+        <v>-0.00773745997865527</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4511,49 +4508,53 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VWO</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>SPGP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.3230517303394433</v>
+        <v>0.2307355042161323</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1279427676161464</v>
+        <v>0.09408104349531055</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1510047944633168</v>
+        <v>0.1423995134838574</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.07221017636315818</v>
-      </c>
-      <c r="J73" s="5" t="n">
-        <v>-0.01512075965040849</v>
+        <v>0.1260808380793597</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0.02703972916287634</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.02003642987249543</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>-0.0006754474839580915</v>
+        <v>-0.0422955974842768</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0.001726831675026741</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4564,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SPGP</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4573,34 +4574,34 @@
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.2424365992254389</v>
+        <v>0.08187039631922799</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.08870617726518093</v>
+        <v>0.1334628410086762</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1405408024305901</v>
+        <v>0.1409992989182709</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.1123808186336495</v>
+        <v>0.1295030256577214</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.00614643885673205</v>
+        <v>0.0665900768667842</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.04544740973312411</v>
+        <v>-0.006605138072161343</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.006535413773384513</v>
+        <v>-0.002293896844154153</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -4619,49 +4620,49 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MGK</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.4214606173976185</v>
+        <v>0.3197633527379904</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1224448921760679</v>
+        <v>0.1333647174341788</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1361731791203218</v>
+        <v>0.1295767337529146</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1615397392745861</v>
+        <v>0.1051672690761787</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.010407111287424</v>
-      </c>
-      <c r="K75" s="5" t="n">
-        <v>-0.0120829176366255</v>
+        <v>0.001690673470098103</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>0.003353454057679395</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.0007860752386301684</v>
+        <v>0.01115241635687747</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4671,49 +4672,49 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VUG</t>
+          <t>MGK</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" s="20" t="inlineStr">
+      <c r="D76" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.3901776055297477</v>
+        <v>0.439187009211188</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.101615009490357</v>
+        <v>0.1383742588048023</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1245178715070989</v>
+        <v>0.125635969403153</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1465563184158305</v>
+        <v>0.1942645435012849</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.004223432347362666</v>
-      </c>
-      <c r="K76" s="5" t="n">
-        <v>-0.02036682795093958</v>
-      </c>
-      <c r="L76" s="15" t="n">
-        <v>0</v>
+        <v>0.038028190955818</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0.01131652661064431</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0.01279174147217232</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d flat.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4723,49 +4724,49 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SCHG</t>
+          <t>IGF</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.3763779130758496</v>
+        <v>0.2186048172921202</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1067835368152616</v>
+        <v>0.07723854163202937</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1232507024560034</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0.1545476931216689</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>0.03021277536254585</v>
+        <v>0.118318233890925</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>-0.03315653051764555</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>-0.03819339193695059</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.01466027628982225</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>-0.001713796058268935</v>
+        <v>-0.03673345476624157</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>0.007461501825686501</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4775,53 +4776,49 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IAK</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>SCHG</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1022626074385649</v>
+        <v>0.3839571242799802</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1237278272797779</v>
+        <v>0.1182918722614199</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1200422323380346</v>
+        <v>0.1173409437986126</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1126980597445204</v>
+        <v>0.1810194497500592</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.06282475133545251</v>
+        <v>0.05548015179401489</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.003290585689835757</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>-0.007588300220750521</v>
+        <v>0.0008510638297871687</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>0.009442060085836923</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4831,49 +4828,49 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IGF</t>
+          <t>VUG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="19" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.2252970817396007</v>
+        <v>0.4011594439649404</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.06139291927817614</v>
+        <v>0.1158430976014615</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1057088960634056</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>-0.05283973067185799</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>-0.05604675558219696</v>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>-0.04007924413288633</v>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v>-0.002059569074778111</v>
+        <v>0.1135617282515264</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0.1764680792530826</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.02952497753258676</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0.002048713862963902</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0.01125660464047784</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4883,49 +4880,49 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1406701263312977</v>
+        <v>0.07534120459688909</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.01387258514991463</v>
+        <v>0.07450833781220489</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.1043969231097286</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>-0.01816382956963625</v>
-      </c>
-      <c r="J80" s="5" t="n">
-        <v>-0.08296299740877655</v>
+        <v>0.1027272280845244</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.02179632673212706</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0.003448981426473097</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.08196721311475419</v>
+        <v>-0.02559009114279032</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.002598902685532645</v>
+        <v>0.0007200288011521838</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4935,44 +4932,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EDEN</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>VFH</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.08423727729767871</v>
+        <v>0.1806296278003494</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05751453587875899</v>
+        <v>0.05739061646384447</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.09912073717437253</v>
+        <v>0.1002147421287896</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.1007048311609744</v>
+        <v>0.1509997698813321</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.04250372023809534</v>
+        <v>0.0342091334319512</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.03785407725321888</v>
+        <v>-0.03892342469624177</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.02428621169916423</v>
+        <v>-0.002858399296393865</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -4995,7 +4988,7 @@
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" s="18" t="inlineStr">
+      <c r="D82" s="17" t="inlineStr">
         <is>
           <t>Inflation &amp; Real Assets</t>
         </is>
@@ -5006,25 +4999,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.09860859805713895</v>
+        <v>0.08501377966123558</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.04792065383906996</v>
+        <v>0.05822491678503661</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.09836612818947432</v>
+        <v>0.1001482042231658</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.02112750959718324</v>
+        <v>0.04110768837678536</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.03830375537760533</v>
+        <v>-0.009228813063245966</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.04592774035517455</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>-0.006588735387885181</v>
+        <v>-0.03810694529809466</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>0.00449293966623876</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5033,7 +5026,7 @@
       </c>
       <c r="N82" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5043,49 +5036,53 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLP</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>EDEN</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Denmark Equity</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.09024486506207108</v>
+        <v>0.08423727729767871</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.0786034709620862</v>
+        <v>0.05751453587875899</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.09607754615467967</v>
-      </c>
-      <c r="I83" s="5" t="n">
-        <v>-0.003772272115878383</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>-0.01964956459833611</v>
+        <v>0.09912073717437253</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0.1007048311609744</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0.04250372023809534</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.01594237128011344</v>
+        <v>-0.03785407725321888</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.004777260241251691</v>
+        <v>-0.02428621169916423</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5095,49 +5092,53 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VFH</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>EUO</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D84" s="21" t="inlineStr">
         <is>
-          <t>Financials &amp; Credit</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>0.1986102102499248</v>
+          <t>2x Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>-0.0306573957016435</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05719313935641179</v>
+        <v>0.1181188479766679</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.09376563728782683</v>
+        <v>0.09697411593146188</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.139593516233248</v>
+        <v>0.02131202131202126</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.03063495776495273</v>
-      </c>
-      <c r="K84" s="5" t="n">
-        <v>-0.03343723434400681</v>
+        <v>0.0158993044054323</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>0.01927550681289469</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.01601038511466901</v>
+        <v>-0.002277163305139829</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5152,7 @@
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" s="21" t="inlineStr">
+      <c r="D85" s="20" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -5162,25 +5163,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1788875833206798</v>
+        <v>0.1608241115404103</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05808419686676292</v>
+        <v>0.05647310647546022</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.08929891034486337</v>
+        <v>0.09666913995945126</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1383056094336323</v>
+        <v>0.1476946611059231</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.03267560958574856</v>
+        <v>0.03450852586685271</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.02865578325807572</v>
+        <v>-0.03665283540802222</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.01618293755496925</v>
+        <v>-0.003754693366708417</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5199,40 +5200,40 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VONG</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D86" s="13" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.3179982358748332</v>
+        <v>0.09238222406347818</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.04420052146675557</v>
+        <v>0.0139599376434143</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.08219284503618107</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>0.08964083071100393</v>
+        <v>0.07553051698947244</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>-0.1000001494545475</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.02110823645643667</v>
+        <v>-0.06061634757614409</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.0351067961165048</v>
+        <v>-0.05724670604270787</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.0008056070248934066</v>
+        <v>0.004356243949661165</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5246,54 +5247,58 @@
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
-      <c r="A87" t="n">
+      <c r="A87" s="15" t="n">
         <v>86</v>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>IWF</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Russell 1000 Growth</t>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>US Dollar Index Bullish</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.3146588940053539</v>
+        <v>0.03707791771946667</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.04266861162109947</v>
+        <v>0.08103814015490429</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.08096696645823531</v>
+        <v>0.07265208970236281</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.08856673957249583</v>
-      </c>
-      <c r="J87" s="5" t="n">
-        <v>-0.02190150306111882</v>
-      </c>
-      <c r="K87" s="5" t="n">
-        <v>-0.03542971804459427</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>0.0007471980074720275</v>
+        <v>0.01831238779174149</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0.00638750887154016</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>0.007818052594172009</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>-0.00140845070422535</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5303,53 +5308,49 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EUO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D88" s="22" t="inlineStr">
-        <is>
-          <t>Currency</t>
+          <t>VONG</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2x Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>-0.03333333333333344</v>
+          <t>Large Growth</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.3322569281500978</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1053577849694354</v>
+        <v>0.06145174149714094</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.08090614886731395</v>
+        <v>0.0669253125560314</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.03816278284363395</v>
+        <v>0.1222965046695117</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.03676222596964585</v>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>0.02262142381902854</v>
+        <v>0.006861488130357918</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>-0.005130228887134991</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.01351796900758329</v>
+        <v>0.01465024551235605</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N88" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5359,109 +5360,101 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VOT</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D89" s="20" t="inlineStr">
+          <t>BOTZ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Robotics &amp; AI</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.1475484716763342</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.02581466678696387</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.06576253755155004</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0.009973934965964659</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.06364480807366879</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>-0.03748290013679889</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>0.01324884792626735</v>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>IWF</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Mid Growth</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>0.1995208959593489</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>-0.001767211703863958</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>0.07729288029541204</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>0.08253864573717418</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>-0.04602879178468755</v>
-      </c>
-      <c r="K89" s="5" t="n">
-        <v>-0.07338774203872622</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>-0.0007593014426728883</v>
-      </c>
-      <c r="M89" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N89" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="21" customHeight="1">
-      <c r="A90" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>UUP</t>
-        </is>
-      </c>
-      <c r="C90" s="16" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D90" s="22" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E90" s="16" t="inlineStr">
-        <is>
-          <t>US Dollar Index Bullish</t>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Russell 1000 Growth</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.03451674912959546</v>
+        <v>0.32956799760155</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.07582160747785771</v>
+        <v>0.05956158173529325</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.06445729472280992</v>
+        <v>0.06536126069574189</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.02601156069364152</v>
+        <v>0.121250354108237</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.01682778374507699</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>0.01067615658362975</v>
+        <v>0.006579156910872852</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>-0.005443861321427268</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0.006378454996456506</v>
+        <v>0.01451800232288036</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N90" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5471,40 +5464,44 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>XLU</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>VOT</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D91" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Mid Growth</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.09205643330773783</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>-0.00881508329771763</v>
+        <v>0.1918603234909539</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0.01249590429098157</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.05979064907809373</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>-0.1115090574609578</v>
+        <v>0.06071329154876204</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0.107002673491694</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.07714496507150692</v>
+        <v>-0.0276011647635368</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.0647351742870077</v>
-      </c>
-      <c r="L91" s="15" t="n">
-        <v>0</v>
+        <v>-0.04545751207414173</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0.01032743851892781</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -5513,7 +5510,7 @@
       </c>
       <c r="N91" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d flat.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5528,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D92" s="22" t="inlineStr">
+      <c r="D92" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5542,190 +5539,190 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.02155757149775073</v>
+        <v>0.02420765328850982</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.05275016910016217</v>
+        <v>0.05841343381192776</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.04640830061160695</v>
+        <v>0.05362964428057437</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.01684532924961712</v>
+        <v>0.011043412033511</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.009118541033434679</v>
+        <v>0.001508864579403912</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.0060606060606061</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>0.005299015897047621</v>
+        <v>0.004540295119182858</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>-0.0003765060240963347</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
-      <c r="A93" s="16" t="n">
+      <c r="A93" s="15" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="17" t="inlineStr">
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>HYG</t>
         </is>
       </c>
-      <c r="C93" s="16" t="inlineStr"/>
-      <c r="D93" s="21" t="inlineStr">
+      <c r="C93" s="15" t="inlineStr"/>
+      <c r="D93" s="20" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
       </c>
-      <c r="E93" s="16" t="inlineStr">
+      <c r="E93" s="15" t="inlineStr">
         <is>
           <t>High Yield Corporate Bonds</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.08593431971429366</v>
+        <v>0.08705506527008855</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02467336284028443</v>
+        <v>0.02896185158138609</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03455284277063719</v>
+        <v>0.03427767476531041</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.01261279592211206</v>
-      </c>
-      <c r="J93" s="5" t="n">
-        <v>-0.005374665519267685</v>
+        <v>0.02134604422774622</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>0.001805173775986324</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.009549516971887662</v>
+        <v>-0.005139648001326491</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>0.0005103342689463108</v>
+        <v>0.003442999234888999</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N93" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="21" customHeight="1">
+      <c r="A94" s="15" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr"/>
+      <c r="D94" s="22" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>1-3 Year Treasury</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.04337854580101408</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0.01582124726319201</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0.02126136836532844</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0.003580766045005568</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0.002338463647773459</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>-0.005326864670152087</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>0.00123092072870512</v>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N94" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="21" customHeight="1">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Russell Midcap Growth</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0.1419888093772792</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.04207667126745407</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0.007945198259429853</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0.04865500872794892</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>-0.02421402639626069</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>-0.04962756865478812</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0.01099144290351139</v>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
           <t>FAST_REVERSAL</t>
         </is>
       </c>
-      <c r="N93" s="7" t="inlineStr">
+      <c r="N95" s="7" t="inlineStr">
         <is>
           <t>Established trend; 3m and 1m now negative; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="21" customHeight="1">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>IWP</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" s="20" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Russell Midcap Growth</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>0.1504312075146621</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>-0.05742001384251527</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>0.02583001351527936</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>0.0265954552431642</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>-0.04501038526363865</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>-0.08115382301256358</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>0.001921655580192194</v>
-      </c>
-      <c r="M94" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N94" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="21" customHeight="1">
-      <c r="A95" s="16" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>SHY</t>
-        </is>
-      </c>
-      <c r="C95" s="16" t="inlineStr"/>
-      <c r="D95" s="23" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E95" s="16" t="inlineStr">
-        <is>
-          <t>1-3 Year Treasury</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>0.04171634382320044</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>0.01506166108003404</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>0.02150473673764175</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0.0005281336621643096</v>
-      </c>
-      <c r="J95" s="5" t="n">
-        <v>-0.001941145190740623</v>
-      </c>
-      <c r="K95" s="5" t="n">
-        <v>-0.006307435908897485</v>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v>-0.0008609027179929951</v>
-      </c>
-      <c r="M95" s="6" t="inlineStr">
-        <is>
-          <t>FAST_REVERSAL</t>
-        </is>
-      </c>
-      <c r="N95" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5740,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D96" s="24" t="inlineStr">
+      <c r="D96" s="23" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -5754,25 +5751,25 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.2414791159867113</v>
+        <v>0.2196676177423709</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.04757073333774586</v>
+        <v>-0.04209039747821941</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.007804399898630798</v>
+        <v>0.004001728229553025</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.03450207798971738</v>
+        <v>0.05753298213549396</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-0.04790418657056272</v>
+        <v>-0.01467337380358114</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.05494631025816776</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v>-0.005888007690458941</v>
+        <v>-0.04590841271663038</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>0.00483500543938109</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5781,63 +5778,63 @@
       </c>
       <c r="N96" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
-      <c r="A97" s="16" t="n">
+      <c r="A97" s="15" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="17" t="inlineStr">
+      <c r="B97" s="16" t="inlineStr">
         <is>
           <t>TIP</t>
         </is>
       </c>
-      <c r="C97" s="16" t="inlineStr">
+      <c r="C97" s="15" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D97" s="18" t="inlineStr">
+      <c r="D97" s="17" t="inlineStr">
         <is>
           <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
-      <c r="E97" s="16" t="inlineStr">
+      <c r="E97" s="15" t="inlineStr">
         <is>
           <t>TIPS</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.03098019581015032</v>
+        <v>0.03245800739427462</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.01411200679942159</v>
-      </c>
-      <c r="H97" s="5" t="n">
-        <v>-0.001202571078605663</v>
+        <v>-0.01331083036473879</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>0.0002413084623060779</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.02203594708834311</v>
+        <v>-0.01851640530302545</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.02332587774023143</v>
+        <v>-0.01510735489239412</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.01292497892666478</v>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v>-0.003781075716041249</v>
+        <v>-0.01354886937021116</v>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>0.001707941929974366</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N97" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5847,44 +5844,40 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VCR</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D98" s="24" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" s="22" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>7-10 Year Treasury</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.1525105262289241</v>
+        <v>0.02188167931441476</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.06550250085512099</v>
+        <v>-0.02501292569517288</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-0.007402429471997984</v>
+        <v>-0.00964029879872752</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.0006472433069987238</v>
+        <v>-0.02843282705853778</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.06443152081822012</v>
+        <v>-0.02037349508233233</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.05853336045565494</v>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v>-0.005639703512729688</v>
+        <v>-0.01552226618045838</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>0.004739336492890933</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5893,7 +5886,7 @@
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5903,40 +5896,40 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FXE</t>
+          <t>LQD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="22" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D99" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Euro Currency</t>
+          <t>Investment Grade Corporate Bonds</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.06622177175514521</v>
+        <v>0.03966739906022587</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.01785748886543281</v>
+        <v>-0.0207829844104328</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.009253443882858758</v>
+        <v>-0.01707549618944681</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.001441037160302638</v>
+        <v>-0.01085038437088592</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.009661667801133311</v>
+        <v>-0.02298930292386137</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.008684405642846116</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>-0.006009953986289784</v>
+        <v>-0.003771895203154463</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>0.005265677357587428</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5945,7 +5938,7 @@
       </c>
       <c r="N99" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5955,40 +5948,40 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>FXE</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" s="23" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
+      <c r="D100" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>7-10 Year Treasury</t>
+          <t>Euro Currency</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.01792262084057472</v>
+        <v>0.06422220855376626</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.02901274797077058</v>
+        <v>-0.02418425838286309</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.009988539527048035</v>
-      </c>
-      <c r="I100" s="5" t="n">
-        <v>-0.03743900914914555</v>
-      </c>
-      <c r="J100" s="5" t="n">
-        <v>-0.0301521252653485</v>
+        <v>-0.01749065182879961</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>0.00592793720212681</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>0.002031420266108697</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.01921614971470553</v>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v>-0.0009909711517285258</v>
+        <v>-0.006812766277005555</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>0.001700519603212047</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -5997,7 +5990,7 @@
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6007,40 +6000,44 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LQD</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" s="21" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>VCR</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D101" s="23" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Investment Grade Corporate Bonds</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.03632916900525096</v>
+        <v>0.1648339122211882</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.02677904404067288</v>
+        <v>-0.05737481398411259</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01924917458405639</v>
-      </c>
-      <c r="I101" s="5" t="n">
-        <v>-0.02134315123883856</v>
+        <v>-0.01796488796033358</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>0.03642852084795156</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>-0.03122430465008319</v>
+        <v>-0.02845011732278158</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>-0.007677658036558843</v>
+        <v>-0.04013087265477233</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0.001630226313770633</v>
+        <v>0.01420623345757033</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6054,54 +6051,54 @@
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
-      <c r="A102" s="16" t="n">
+      <c r="A102" s="15" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="17" t="inlineStr">
+      <c r="B102" s="16" t="inlineStr">
         <is>
           <t>TLT</t>
         </is>
       </c>
-      <c r="C102" s="16" t="inlineStr"/>
-      <c r="D102" s="23" t="inlineStr">
+      <c r="C102" s="15" t="inlineStr"/>
+      <c r="D102" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
       </c>
-      <c r="E102" s="16" t="inlineStr">
+      <c r="E102" s="15" t="inlineStr">
         <is>
           <t>20+ Year Treasury</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.0407684251720124</v>
+        <v>-0.0376250111671772</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.06182780185649384</v>
+        <v>-0.05604535294486157</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.05997803926142375</v>
+        <v>-0.05838022746581295</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.05348672246542685</v>
+        <v>-0.04026839573470709</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-0.05072456557839544</v>
-      </c>
-      <c r="K102" s="5" t="n">
-        <v>-0.001967786575556962</v>
+        <v>-0.04441309453187736</v>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>0.002479636249212991</v>
       </c>
       <c r="L102" s="3" t="n">
-        <v>0.00210630652955035</v>
+        <v>0.008283877349159363</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>REBOUND</t>
         </is>
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d up.</t>
+          <t>Weak long trend; 1m rebound not yet confirmed by 3m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6116,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D103" s="8" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -6130,25 +6127,25 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.02964628910243294</v>
+        <v>-0.02669902912621358</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.111734980348119</v>
+        <v>-0.1067384444031929</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>-0.07205689687441519</v>
-      </c>
-      <c r="I103" s="5" t="n">
-        <v>-0.02184666117065137</v>
+        <v>-0.08334880267310185</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>0.0083822296730931</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>-0.03946569520340004</v>
+        <v>-0.01916021198532414</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>-0.04275917708753529</v>
-      </c>
-      <c r="L103" s="5" t="n">
-        <v>-0.002731666316453052</v>
+        <v>-0.02551640340218719</v>
+      </c>
+      <c r="L103" s="3" t="n">
+        <v>0.01390644753476611</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6157,7 +6154,7 @@
       </c>
       <c r="N103" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6172,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -6186,25 +6183,25 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.08495715339704712</v>
+        <v>-0.09720113063403135</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.1743016423495968</v>
+        <v>-0.1732134270037449</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>-0.1311770856391509</v>
+        <v>-0.1313010102058796</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.09659090909090917</v>
+        <v>0.1307908282639212</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.06676984302454136</v>
+        <v>0.09072444143534186</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>-0.04963561158164276</v>
-      </c>
-      <c r="L104" s="5" t="n">
-        <v>-0.01831129196337744</v>
+        <v>-0.0482473414730209</v>
+      </c>
+      <c r="L104" s="3" t="n">
+        <v>0.001658031088082934</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
@@ -6213,7 +6210,7 @@
       </c>
       <c r="N104" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -207,6 +207,9 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -691,25 +694,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.832371179500452</v>
+        <v>1.832492939073123</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.191457600656538</v>
+        <v>1.191551965788332</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.176101758987421</v>
+        <v>1.176101915391165</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.5237088156241601</v>
+        <v>0.5237743176796852</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1409075304160513</v>
+        <v>-0.1408705992635458</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.007056582536040468</v>
+        <v>0.007099874453439403</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.03889955785806798</v>
+        <v>0.03894421865928277</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -743,25 +746,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.232784404335955</v>
+        <v>2.221121357944451</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.31811744068228</v>
+        <v>1.30975427510422</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>1.154782282650168</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.3871701546860782</v>
+        <v>0.3821656050955415</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.1079578700994734</v>
+        <v>-0.1111761263897016</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.07580123493090252</v>
+        <v>0.07192002352249327</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.04215563404352296</v>
+        <v>0.03839580722342495</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -799,25 +802,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.574026004770899</v>
+        <v>1.568860538758466</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9711624285482421</v>
+        <v>0.9672064047628717</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.143606176013775</v>
+        <v>1.143605936403186</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.4098527830124987</v>
+        <v>0.407023436710928</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.1966081030213387</v>
+        <v>-0.1982203805015247</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.08044562914359932</v>
+        <v>-0.08229102590390258</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.03619839802834246</v>
+        <v>0.03411891558841651</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -855,25 +858,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.956213511259383</v>
+        <v>1.947873227689741</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.105435105435105</v>
+        <v>1.099495099495099</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>1.068310068310068</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.583780160857909</v>
+        <v>0.5793118856121537</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1128769866099362</v>
+        <v>-0.1153798022775623</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.01794945433658812</v>
+        <v>0.015077541642734</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.04342066529290545</v>
+        <v>0.04047689137474242</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -907,25 +910,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.563187422523682</v>
+        <v>1.555834986709035</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.015272663265338</v>
+        <v>1.009492144472026</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.06028796286846</v>
+        <v>1.060288206804791</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.5372207371173916</v>
+        <v>0.5328113982319203</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.133310642269303</v>
+        <v>-0.1357967179335159</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.02184903295772711</v>
+        <v>-0.02465483332137453</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.03461737640919416</v>
+        <v>0.03164960363303204</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -963,25 +966,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.509498100642836</v>
+        <v>1.500723631759469</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9196313768946232</v>
+        <v>0.9129195321322225</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.9794101074906643</v>
+        <v>0.9794102658697132</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4928409264354912</v>
+        <v>0.4876212029164859</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1370721643736043</v>
+        <v>-0.1400893945681021</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.03020027551128546</v>
+        <v>-0.03359118363886826</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.03330698882240046</v>
+        <v>0.02969402732302151</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1019,25 +1022,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.456957464653919</v>
+        <v>1.452444864460279</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8311414715392698</v>
+        <v>0.827778283743825</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.8604305924374638</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4245433992938246</v>
+        <v>0.4219269946909847</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.101238841610975</v>
+        <v>-0.102889561998173</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.01574319462239149</v>
+        <v>-0.01755094160801729</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.0279345993108</v>
+        <v>0.0260466309846763</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1075,25 +1078,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.280200115897476</v>
+        <v>1.277312481196204</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.8261046120534352</v>
+        <v>0.8237920417622775</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.7243515192424976</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5496215306980654</v>
+        <v>0.5476590972806279</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.05175530396727246</v>
+        <v>0.05042336599752639</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.05900948366701786</v>
+        <v>0.05766835903822209</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.01983394833948338</v>
+        <v>0.01854243542435419</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -1131,25 +1134,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.268221574344023</v>
+        <v>1.274052478134111</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9353233830845773</v>
+        <v>0.9402985074626868</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.718905472636816</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.4542056074766356</v>
+        <v>0.457943925233645</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.3097643097643097</v>
+        <v>0.3131313131313129</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1259044862518091</v>
+        <v>0.1287988422575976</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.01699346405228752</v>
+        <v>0.01960784313725483</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -1183,25 +1186,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8011900499529667</v>
+        <v>0.8168941330268553</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.6962282391798982</v>
+        <v>0.711017049057731</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7158396725745104</v>
+        <v>0.7158395322850641</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.3081939558176163</v>
+        <v>0.3195997408759199</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.1366337743443686</v>
+        <v>0.1465437731350889</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.01142964212104192</v>
+        <v>-0.002810567734682468</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.02659229472045666</v>
+        <v>0.03554287196782968</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -1239,25 +1242,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.5938264411098892</v>
+        <v>0.5841561221878504</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.578758511853489</v>
+        <v>0.5691796154838975</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.6440122997753184</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.05326308101622423</v>
+        <v>0.04687255464552154</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.01682111200644654</v>
+        <v>0.01065169218372275</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.03969178815191798</v>
+        <v>-0.04551832386025823</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.009878704514192815</v>
+        <v>0.003751406777541488</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1295,25 +1298,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.126146643052305</v>
+        <v>1.127615821891222</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6595558348679367</v>
+        <v>0.6607025969328</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.6354738315058084</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1627528430943797</v>
+        <v>0.1635563116027947</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.004207782858709042</v>
+        <v>0.004901695872316258</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.01472478672431943</v>
+        <v>0.01542596704452515</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.03135764342558489</v>
+        <v>0.03207031713980291</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1351,25 +1354,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.166308059963949</v>
+        <v>1.168706009997117</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5920153628927736</v>
+        <v>0.5937776114680366</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.5417912784977723</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1735638495722966</v>
+        <v>0.1748629018742363</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.01642664266426652</v>
+        <v>0.01755175517551755</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.03257515144587964</v>
+        <v>0.03371813921591049</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.01198610955528179</v>
+        <v>0.01310630670998103</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -1407,25 +1410,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.187735811136712</v>
+        <v>1.177539428720899</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.7255824584536505</v>
+        <v>0.7175399292304787</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5377114376227534</v>
+        <v>0.5377113432705916</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.3722718186800078</v>
+        <v>0.3658760700843702</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.3352215027451173</v>
+        <v>0.3289984345928749</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.1221757322175734</v>
+        <v>0.1169456066945607</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.02093642938713369</v>
+        <v>0.016178149980967</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1459,25 +1462,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.9243752028562155</v>
+        <v>0.9279454722492697</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.5360103626943005</v>
+        <v>0.5388601036269429</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0.4880829015544039</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.1369723435225619</v>
+        <v>-0.1353711790393014</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.02177858439201452</v>
+        <v>-0.01996370235934664</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.03220752089136503</v>
+        <v>0.03412256267409464</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.03926380368098159</v>
+        <v>0.04119193689745848</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1515,25 +1518,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.7196789716677079</v>
+        <v>0.7227141681096243</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.4880917751479625</v>
+        <v>0.4907183812979348</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.4773465681708029</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.1465676755149798</v>
+        <v>0.1485914631322238</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.02746566791510607</v>
+        <v>-0.02574906367041196</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.007273315015354775</v>
+        <v>0.009051236463552659</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.02247744052502054</v>
+        <v>0.02428219852337987</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1567,25 +1570,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.4706236358940235</v>
+        <v>0.4692451416251024</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.470361347159467</v>
+        <v>0.4689832274699355</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4627809808954044</v>
+        <v>0.4627811090740497</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.1106086609808365</v>
+        <v>0.1095676280225668</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.1792871089520247</v>
+        <v>0.1781817000075299</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.005182160804020119</v>
+        <v>0.004239949748743754</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-0.0003123535842572966</v>
+        <v>-0.00124941433702952</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1623,25 +1626,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.4882960436920567</v>
+        <v>0.485652880346314</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.4660239794897567</v>
+        <v>0.463420462793843</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.4580507096085207</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.1041802318566281</v>
+        <v>0.1022193146348391</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.1757860304545862</v>
+        <v>0.1736979482649781</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.005468444841247644</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>0.000166518650088765</v>
+        <v>0.003682830199207565</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>-0.001609680284191839</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1650,7 +1653,7 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1679,25 +1682,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.5199829672628018</v>
+        <v>0.5258076151208244</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4656157349395724</v>
+        <v>0.4712320508681362</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.4471244451093954</v>
+        <v>0.4471242881227626</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.2589453658706176</v>
+        <v>0.2637698472629908</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.1886593750805832</v>
+        <v>0.1932145092368462</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.01277795416466709</v>
+        <v>0.01665908239066782</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.0185276679841897</v>
+        <v>0.02243083003952573</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1735,25 +1738,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.7223906242415876</v>
+        <v>0.724334083338052</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.3770130399083618</v>
+        <v>0.3785668944168274</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.4376093824261909</v>
+        <v>0.4376094889367927</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.02526673875951824</v>
+        <v>0.02642359826728624</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.142834065483448</v>
+        <v>-0.1418668824825832</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.04215077006214529</v>
+        <v>-0.04106998108619286</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.01503221188260584</v>
+        <v>0.01617752326413768</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1791,25 +1794,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.6800627260220062</v>
+        <v>0.6816951756343352</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.3999913220126388</v>
+        <v>0.4013516374672259</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0.4359489938622265</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.3801549797055879</v>
+        <v>0.3814960209814151</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.047997304427427</v>
+        <v>-0.04707228156533216</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.02504105090311992</v>
+        <v>-0.0240937223695844</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.01632706804042261</v>
+        <v>0.01731459231706101</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1847,25 +1850,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5344515468439641</v>
+        <v>0.5310150070172128</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4725775870877809</v>
+        <v>0.4692797986265147</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0.4215002123156095</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.1174814423948158</v>
+        <v>0.1149788799229148</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.2388513924808073</v>
+        <v>0.2360770260479823</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.03593202050175348</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>0.001094890510948909</v>
+        <v>0.03361208524413284</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>-0.001147028154327434</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1874,7 +1877,7 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1906,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6270969135633817</v>
+        <v>0.6219491276717437</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.41178829099208</v>
+        <v>0.4073215984639635</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0.3924326233702415</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.1493465622630548</v>
+        <v>0.145710197140442</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.0311967915326794</v>
+        <v>0.02793423507634274</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.01390061342788007</v>
+        <v>0.01069277955990766</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.01048852992315896</v>
+        <v>0.007291491390431393</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1955,25 +1958,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5425399486078517</v>
+        <v>0.5434745380950423</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4978483014763482</v>
+        <v>0.4987558133221384</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.3830480529839169</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.1277758797403483</v>
+        <v>0.1284591732148959</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1912666907253697</v>
+        <v>0.1919884518224468</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.08300524934383202</v>
+        <v>0.08366141732283472</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.00452352231604336</v>
+        <v>-0.003920386007237542</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -2007,25 +2010,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.7561103577024879</v>
+        <v>0.7603241236242442</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3842733615972713</v>
+        <v>0.3875949090683111</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.3701014257208357</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.3626926106357811</v>
+        <v>0.3659625267992501</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.0105684692004735</v>
+        <v>0.01299331622585598</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.01034371296196523</v>
+        <v>0.01276802068742589</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.01962703202305227</v>
+        <v>0.02207361496221383</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2059,25 +2062,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.355887644165805</v>
+        <v>1.371588577370338</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.4643321313468831</v>
+        <v>0.4740912474237744</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.3558975082703129</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.07727744818674909</v>
+        <v>0.08445701861262078</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.10134224488655</v>
+        <v>0.1086821963757969</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.07997258082942982</v>
+        <v>0.08717011310407852</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.03959089409435834</v>
+        <v>0.04651930056087084</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -2115,34 +2118,34 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.7261555191888269</v>
+        <v>0.7312928668273277</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3471468587106861</v>
+        <v>0.3511560856148321</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.3324618997013125</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.3488298000135635</v>
+        <v>0.3528440354982558</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.03602812813227607</v>
+        <v>0.03911143847658072</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.01102092225876428</v>
+        <v>0.01402980897068073</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.01825293350717083</v>
+        <v>0.02128334331724147</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2167,34 +2170,34 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.7212714441923189</v>
+        <v>0.7262490944068716</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3429432983613236</v>
+        <v>0.3468268822200897</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.3291843155474095</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.3480776768721869</v>
+        <v>0.3519762234458486</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.0362958075134403</v>
+        <v>0.03929261435992215</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.01035144836797719</v>
+        <v>0.01327322814926113</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.01774302051799537</v>
+        <v>0.0206861755802219</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2223,25 +2226,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.7370497699931946</v>
+        <v>0.7420357822813033</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3399616781427572</v>
+        <v>0.3438077522395773</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.3146792410827406</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3488177888387118</v>
+        <v>0.3526892825117047</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.03242680116671703</v>
+        <v>0.03539016201621048</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.01923087873449236</v>
+        <v>0.02215636350418593</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.01670997401559071</v>
+        <v>0.01962822306616019</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2279,25 +2282,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5110201526469906</v>
+        <v>0.5131758290786077</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3008576846656956</v>
+        <v>0.3027134017622231</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.3071706687350122</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.2647072751181541</v>
+        <v>0.2665113134753372</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1534837902597246</v>
+        <v>0.1551292735553875</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.004829502543402087</v>
+        <v>-0.003409858467144589</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.001249776825566817</v>
+        <v>0.002678093197643339</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2331,25 +2334,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.2822802727355507</v>
+        <v>0.2800133326364371</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.283238694602242</v>
+        <v>0.2809701524196808</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3047898453365754</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.1281778891186309</v>
+        <v>0.1261835387947297</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.07141579146308508</v>
+        <v>0.06952171522596706</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.01651695160822952</v>
+        <v>-0.01825557809330614</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.002955082742316595</v>
+        <v>0.001182033096926771</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2387,25 +2390,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.4892006554139743</v>
+        <v>0.4875468077181953</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.08651383744951957</v>
+        <v>0.08530709645358647</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.2980510646255203</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>-0.1025005291283249</v>
+        <v>-0.1034973405521642</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.148594029924464</v>
+        <v>-0.1495396474148811</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.1629652584099439</v>
+        <v>-0.1638949144372137</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.003343101242312851</v>
+        <v>0.002228734161542123</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2443,25 +2446,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.9280021805015242</v>
+        <v>0.9323304899943885</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.2666260054208822</v>
+        <v>0.2694695444057531</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.2924453394035098</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.03331701647914653</v>
+        <v>0.03563678348812438</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.05873649716689966</v>
+        <v>-0.05662338765084107</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.01997711871864816</v>
+        <v>-0.01777699551174861</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.02381171278845273</v>
+        <v>0.02611014066378603</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2499,25 +2502,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.4896398237672306</v>
+        <v>0.4936051471667882</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.2538522444654399</v>
+        <v>0.2571899168109555</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.2898249353004436</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.1199227194915655</v>
+        <v>0.1229038802355535</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1351119985397546</v>
+        <v>-0.1328097234693193</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.02788959171937888</v>
+        <v>-0.02530189764232327</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.02330508474576276</v>
+        <v>0.02602905569007263</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2551,25 +2554,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5352920644848953</v>
+        <v>0.5251256822665098</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.1483878368827733</v>
+        <v>0.1407833287295672</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.2882679446023129</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>-0.0274379222943647</v>
+        <v>-0.03387813004637918</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.1704448742746615</v>
+        <v>-0.1759381044487427</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.108579980046558</v>
+        <v>-0.1144828732956434</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.01495645588792116</v>
+        <v>0.008235516849678159</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2659,25 +2662,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4161186164878679</v>
+        <v>0.4173879191019889</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2218271166052124</v>
+        <v>0.222922356027321</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.2784100873473123</v>
+        <v>0.2784101763605011</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1617695778972048</v>
+        <v>0.1628109010922127</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.02508525178901266</v>
+        <v>-0.02421141126178428</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.04426042261564833</v>
+        <v>-0.04340376927470024</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.01240169388989698</v>
+        <v>0.01330913490623109</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2715,25 +2718,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.2148908287266553</v>
+        <v>0.2137407664181021</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2653927758144858</v>
+        <v>0.2641951313178537</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2729384213304642</v>
+        <v>0.2729384988769445</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1711580503673249</v>
+        <v>0.1700495240536786</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.1278589806485781</v>
+        <v>0.1267914378367951</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>-0.005927738050432785</v>
+        <v>-0.006868648852088821</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.007277696561367675</v>
+        <v>0.006324286531494083</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2767,25 +2770,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.4203430931872503</v>
+        <v>0.4246049239569067</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2150917392445053</v>
+        <v>0.2187375291382552</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2694742212062169</v>
+        <v>0.2694741390866771</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1708477892844722</v>
+        <v>0.1743609045548116</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>-0.00866363738645981</v>
+        <v>-0.005689144078778408</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.04283858707271659</v>
+        <v>-0.03996663530690314</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.009509721048182485</v>
+        <v>0.012538743307974</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2819,25 +2822,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.3926606798859531</v>
+        <v>0.3939574993506101</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2545317458633416</v>
+        <v>0.2556997454816123</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2634871245582071</v>
+        <v>0.2634870307249093</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1664401086182863</v>
+        <v>0.1675261794829217</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.04602819994686791</v>
+        <v>0.04700215544030084</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.007087827426810578</v>
+        <v>-0.006163328197226536</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.005931938807367976</v>
+        <v>0.006868560724320849</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2871,25 +2874,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.3343353058387137</v>
+        <v>0.3346200551570746</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2517424702370217</v>
+        <v>0.252009466530954</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2613589296754624</v>
+        <v>0.2613588011434105</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1225960164627071</v>
+        <v>0.1228355802733052</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.02333034702727965</v>
+        <v>0.02354872738302594</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.007623888182973326</v>
+        <v>-0.007412113511224061</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.01013149385643453</v>
+        <v>0.01034705755550758</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -2923,25 +2926,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.1789930677142921</v>
+        <v>0.1775945823721246</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2528660658456923</v>
+        <v>0.2513798127404647</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2611882886898127</v>
+        <v>0.2611881456946681</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1557007729229209</v>
+        <v>0.1543300369141281</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.123705271015661</v>
+        <v>0.1223723663587417</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.006598715607140648</v>
+        <v>-0.007777057679844379</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.005006854622399803</v>
+        <v>0.003814746378971057</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2975,25 +2978,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.5709445678842062</v>
+        <v>0.5686962568535459</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2222158752552148</v>
+        <v>0.2204667589010945</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.2568650373177859</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.2698687767654164</v>
+        <v>0.2680514642185938</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-0.05482555744399653</v>
+        <v>-0.05617819907502253</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.0275679257786613</v>
+        <v>-0.02895957587806497</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.0214395099540583</v>
+        <v>0.01997772518446328</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3086,13 +3089,13 @@
         <v>0.2965567595247445</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2462925028729852</v>
+        <v>0.2462924178635306</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2516562329368497</v>
+        <v>0.2516561475615355</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1299784099657375</v>
+        <v>0.1299783400833772</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>0.1269403132801812</v>
@@ -3135,25 +3138,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.413006086229877</v>
+        <v>0.4128085381585544</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.06706548223323128</v>
+        <v>0.06691651315850944</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.2506848783201658</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>-0.06973979759139748</v>
+        <v>-0.06986966778578629</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>-0.1138880892383025</v>
+        <v>-0.1140117960525927</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.1468150764991734</v>
+        <v>-0.146934186498266</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.00176522506619603</v>
+        <v>-0.001904584939843024</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3191,25 +3194,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.1231944894852104</v>
+        <v>0.1193684064893059</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.3108958501354966</v>
+        <v>0.3064303756619671</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.2434950948006611</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.08780130069548653</v>
+        <v>0.08409578210678581</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.02704086753495305</v>
+        <v>-0.03035518435833828</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.05420267085624508</v>
+        <v>0.05061160363595563</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.00599700149925031</v>
+        <v>0.002570143499678768</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3243,25 +3246,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.3855548087792697</v>
+        <v>0.3837255210272035</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.1504113958479962</v>
+        <v>0.1488925577169258</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2434944755950332</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.05571410554195788</v>
+        <v>0.05432029212460709</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-0.08394318523017519</v>
+        <v>-0.08515261520063711</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.07485604606525909</v>
+        <v>-0.07607747339033322</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.00511848341232235</v>
+        <v>0.003791469194312835</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3299,25 +3302,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.3927968606804535</v>
+        <v>0.3973306798237357</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.1694187964749572</v>
+        <v>0.1732254774602819</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0.2405129006938687</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1611238756270694</v>
+        <v>0.1649035550646498</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.03694428411647088</v>
+        <v>-0.03380935427567044</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.05731024980001886</v>
+        <v>-0.05424161505773151</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.01235080723325299</v>
+        <v>0.01564620198831368</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3351,25 +3354,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4255527328557043</v>
+        <v>0.4261444940565575</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.2345962090996794</v>
+        <v>0.2351087828253562</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2366461820496166</v>
+        <v>0.2366462626380019</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.132141190224305</v>
+        <v>0.1326111533584786</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.00903339557743732</v>
+        <v>0.009452255434464263</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.001657687525901452</v>
+        <v>-0.001243265644426117</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.01417344934044329</v>
+        <v>0.01459444288520895</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3407,25 +3410,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.51884323878377</v>
+        <v>0.5187441251057601</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2162354060654474</v>
+        <v>0.2161558735861659</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2363091488547286</v>
+        <v>0.2363090739069289</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.2471006633947246</v>
+        <v>0.2470191881611052</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.06556436094727558</v>
+        <v>-0.06562540923650251</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.01623683106112794</v>
+        <v>-0.01630110200281532</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.02101190674715681</v>
+        <v>0.02094520228129282</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3459,25 +3462,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.2973597635515801</v>
+        <v>0.2990463912051122</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1290331971555523</v>
+        <v>0.1305009753361384</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2246314346599192</v>
+        <v>0.2246315593205175</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.0299860562703278</v>
+        <v>0.03132496511208793</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.05536530576508958</v>
+        <v>-0.05413734764211808</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>-0.0780628643024458</v>
+        <v>-0.0768644113961976</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.003141485389129173</v>
+        <v>0.004445498192163999</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3515,25 +3518,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.7718151338943267</v>
+        <v>0.7742741801247295</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.1814942318102704</v>
+        <v>0.183133990316334</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.2230669327581214</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.02976040353089537</v>
+        <v>0.03118957545187051</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.06809190505173468</v>
+        <v>-0.06679853925745594</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>-0.03399053627760251</v>
+        <v>-0.03264984227129342</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.02596532372895544</v>
+        <v>0.02738922857860793</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3567,25 +3570,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.4526297774418795</v>
+        <v>0.4507071036476042</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2592285419706604</v>
+        <v>0.2575617085478299</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>0.2228146425795936</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1734237141227468</v>
+        <v>0.1718704600464211</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.03980942297511891</v>
+        <v>0.03843303335097925</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0.02977875642235484</v>
+        <v>0.02841564433259935</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.01236985877744545</v>
+        <v>0.01102979074322219</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3619,25 +3622,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.4928063236978504</v>
+        <v>0.4957988343358695</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2153914166511604</v>
+        <v>0.2178278155904925</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0.2200577400434403</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.2045413828196687</v>
+        <v>0.206956031555275</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.009777193212141544</v>
+        <v>-0.00779217195634907</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.003824674225757274</v>
+        <v>-0.001827720426467949</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.01419710544452113</v>
+        <v>0.01623018607856652</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3671,25 +3674,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4917495181143843</v>
+        <v>0.494587662319625</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2150156715005775</v>
+        <v>0.217327108918048</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2195368181553883</v>
+        <v>0.2195366916404247</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.2044678124078645</v>
+        <v>0.2067593088405073</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.009514601429637781</v>
+        <v>-0.007630205903225717</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.003707265403966487</v>
+        <v>-0.001811821438028716</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.01437450334884782</v>
+        <v>0.01630434782608692</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3727,25 +3730,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3744340209162895</v>
+        <v>0.3747768624180563</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.07075283884035199</v>
+        <v>0.07101985949841705</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0.2186822834083209</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>-0.08036552343411341</v>
+        <v>-0.08013618815317425</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>-0.09680678076192939</v>
+        <v>-0.09658154554516185</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.121384750219106</v>
+        <v>-0.1211656441717792</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.001435974277330443</v>
+        <v>0.001685708934257457</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3783,25 +3786,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2946112872800928</v>
+        <v>0.2913738840880569</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1134989353036362</v>
+        <v>0.1107145629441855</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.212536823845106</v>
+        <v>0.2125369630839975</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.02457359161809358</v>
+        <v>0.02201146517244146</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>-0.1268894793792031</v>
+        <v>-0.1290728457797824</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.08167825223435943</v>
+        <v>-0.08397467725918573</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.01169230769230767</v>
+        <v>0.009162393162393201</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -3839,25 +3842,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3030062772179487</v>
+        <v>0.3055458696623015</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.140913181067897</v>
+        <v>0.1431368499365449</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.2076232471273391</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1720235581836023</v>
+        <v>0.174307861970167</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.02598225014715205</v>
+        <v>0.02798191570216146</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.05524079320113306</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>-0.001197963462114426</v>
+        <v>-0.05339943342776199</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0.00074872716382135</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3866,7 +3869,7 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3891,25 +3894,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3239772570620578</v>
+        <v>0.3235487037743068</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1385883590590253</v>
+        <v>0.1382198325583388</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2003807911823312</v>
+        <v>0.200380668492671</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1107038718309439</v>
+        <v>0.1103444841797456</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>-0.02796892953314156</v>
+        <v>-0.02828344717566222</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.05147735833263589</v>
+        <v>-0.05178426941212577</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.0143517827838282</v>
+        <v>0.01402357153513356</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -3943,25 +3946,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.250117504825214</v>
+        <v>0.2502933383155079</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1525409842696304</v>
+        <v>0.1527030932739348</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.1876646018689205</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1114524158837908</v>
+        <v>0.1116087456342552</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.02452765577581828</v>
+        <v>0.02467175924842979</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.0295736839710633</v>
+        <v>-0.02943719004504297</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.004757866968155167</v>
+        <v>0.004899189749387522</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -4051,25 +4054,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.4907513806261772</v>
+        <v>0.4954912202601172</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1863454165205243</v>
+        <v>0.1901173982861257</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.1839450644878686</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1907064703226042</v>
+        <v>0.1944923180459537</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.01380198140180622</v>
+        <v>0.01702536182248826</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.002027418420544658</v>
+        <v>0.005213361652828707</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.01288181906899588</v>
+        <v>0.01610227383624485</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4103,25 +4106,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2806109256024816</v>
+        <v>0.2816675837120779</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1538918028254443</v>
+        <v>0.1548438092026281</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1828172450824099</v>
+        <v>0.1828171496166644</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1284493015866939</v>
+        <v>0.1293804971898489</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.01944375470572357</v>
+        <v>0.02028491847307201</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.0244547011613363</v>
+        <v>-0.02364975890238163</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>0.003588351658462496</v>
+        <v>0.004416432810415483</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4155,25 +4158,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3670377619646923</v>
+        <v>0.3688843547730598</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1665969281255586</v>
+        <v>0.1681728935475131</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0.1762489654120805</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1566829462327608</v>
+        <v>0.158245518774724</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.02968378500116531</v>
+        <v>0.03107479332768004</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.008205777492982125</v>
+        <v>-0.006865954489267523</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.00902558130301867</v>
+        <v>0.01038868229159773</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4207,25 +4210,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3655094639765866</v>
+        <v>0.3680489557893116</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1657189193333604</v>
+        <v>0.1678867628014238</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1762407210770465</v>
+        <v>0.1762408407888809</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1560850484525858</v>
+        <v>0.1582348582953645</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.02893386450063917</v>
+        <v>0.03084722905148496</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.008945279274170659</v>
+        <v>-0.007102353274737738</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.008438635970226871</v>
+        <v>0.01031388840805492</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4259,25 +4262,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3641044731970677</v>
+        <v>0.3663820755542719</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1652393950520699</v>
+        <v>0.1671849586397751</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.1756872247120298</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.156089412920948</v>
+        <v>0.1580196990711256</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.02919128103797086</v>
+        <v>0.03090968936648553</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.008886572415141125</v>
+        <v>-0.00723174148152983</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.008726211789669147</v>
+        <v>0.01041045023539566</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4311,25 +4314,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.449134581419993</v>
+        <v>0.4471918050158954</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1798964624676445</v>
+        <v>0.1783146390566579</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0.1750071901064134</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>-0.09953906935908696</v>
+        <v>-0.1007462686567165</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.03026117528879957</v>
+        <v>0.02887995981918623</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.004161057398115231</v>
+        <v>0.002814832945783996</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.0215388446215139</v>
+        <v>0.0201693227091635</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4363,25 +4366,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.4463556535250965</v>
+        <v>0.4439706573194087</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1786271680555966</v>
+        <v>0.1766836479283842</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0.1736211313642924</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>-0.1000359760759095</v>
+        <v>-0.1015199892071773</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.02997941327843545</v>
+        <v>0.02828100874935657</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0.004265462300840461</v>
+        <v>0.002609459289925953</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.02172359217848574</v>
+        <v>0.02003880124572421</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
@@ -4419,25 +4422,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.3979038686575651</v>
+        <v>0.4014513148009016</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.158509640725768</v>
+        <v>0.1614498181553188</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1576124926328364</v>
+        <v>0.1576126008259451</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.174522780581764</v>
+        <v>0.1775034876489061</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.04092796785374198</v>
+        <v>0.0435696376463286</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.0007749986274692144</v>
+        <v>0.003314768106908783</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0.009204172558226364</v>
+        <v>0.01176533361790688</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4471,25 +4474,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.4965613479471813</v>
+        <v>0.5082311109402715</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2661976336565888</v>
+        <v>0.2760711005010701</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1473745698904827</v>
+        <v>0.1473744953811651</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.03541221226950597</v>
+        <v>0.04348614455125266</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.09029610085019057</v>
+        <v>0.09879800644972137</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>0.103560830860534</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>-0.00773745997865527</v>
+        <v>0.1121661721068248</v>
+      </c>
+      <c r="L72" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4498,7 +4501,7 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d flat.</t>
         </is>
       </c>
     </row>
@@ -4527,25 +4530,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2307355042161323</v>
+        <v>0.2300283010861444</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.09408104349531055</v>
+        <v>0.09345236451776429</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0.1423995134838574</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1260808380793597</v>
+        <v>0.1254337714345923</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.02703972916287634</v>
+        <v>0.0264495733506831</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.0422955974842768</v>
+        <v>-0.04284591194968557</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.001726831675026741</v>
+        <v>0.00115122111668442</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
@@ -4583,25 +4586,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.08187039631922799</v>
+        <v>0.08066438180371849</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1334628410086762</v>
+        <v>0.1321993138397124</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0.1409992989182709</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.1295030256577214</v>
+        <v>0.1282439126910577</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.0665900768667842</v>
+        <v>0.06540109608019828</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.006605138072161343</v>
+        <v>-0.007712524527316744</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.002293896844154153</v>
+        <v>-0.00340608925344088</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -4635,25 +4638,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3197633527379904</v>
+        <v>0.320865985053165</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1333647174341788</v>
+        <v>0.1343117953085837</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1295767337529146</v>
+        <v>0.1295768153649013</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1051672690761787</v>
+        <v>0.1060907042943238</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.001690673470098103</v>
+        <v>0.00252764762908031</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.003353454057679395</v>
+        <v>0.004191817572099188</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.01115241635687747</v>
+        <v>0.01199729638391345</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4687,34 +4690,34 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.439187009211188</v>
+        <v>0.4431733229178529</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1383742588048023</v>
+        <v>0.1415273007359035</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>0.125635969403153</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1942645435012849</v>
+        <v>0.197572389012866</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.038028190955818</v>
+        <v>0.04090329673621862</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.01131652661064431</v>
+        <v>0.01411764705882357</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.01279174147217232</v>
+        <v>0.01559694793536814</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4739,25 +4742,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2186048172921202</v>
+        <v>0.2197569806869759</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.07723854163202937</v>
+        <v>0.07825704639877906</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>0.118318233890925</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>-0.03315653051764555</v>
+        <v>-0.0322424018039843</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.03819339193695059</v>
+        <v>-0.03728402546226128</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.03673345476624157</v>
+        <v>-0.03582270795385534</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>0.007461501825686501</v>
+        <v>0.008414033973646706</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -4791,25 +4794,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3839571242799802</v>
+        <v>0.3882721833409437</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1182918722614199</v>
+        <v>0.1217785421374409</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1173409437986126</v>
+        <v>0.1173408762459676</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1810194497500592</v>
+        <v>0.1847017666285315</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.05548015179401489</v>
+        <v>0.05877104795890542</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.0008510638297871687</v>
+        <v>0.003971631205673676</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0.009442060085836923</v>
+        <v>0.01258941344778242</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -4843,25 +4846,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.4011594439649404</v>
+        <v>0.4056157383461902</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1158430976014615</v>
+        <v>0.119392002614475</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1135617282515264</v>
+        <v>0.1135618359341912</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.1764680792530826</v>
+        <v>0.1802096860476174</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.02952497753258676</v>
+        <v>0.03279925051883281</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.002048713862963902</v>
+        <v>0.005235602094240788</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.01125660464047784</v>
+        <v>0.01447277739490005</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -4895,25 +4898,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.07534120459688909</v>
+        <v>0.07263339727272355</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.07450833781220489</v>
+        <v>0.07180252219322658</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.1027272280845244</v>
+        <v>0.1027273364906989</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.02179632673212706</v>
+        <v>0.01922314974911066</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.003448981426473097</v>
+        <v>0.000922008334980795</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.02559009114279032</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>0.0007200288011521838</v>
+        <v>-0.02804393549894824</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>-0.001800072002880015</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4922,7 +4925,7 @@
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4947,25 +4950,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.1806296278003494</v>
+        <v>0.1814106396820252</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05739061646384447</v>
+        <v>0.05809010308995055</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0.1002147421287896</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.1509997698813321</v>
+        <v>0.1517611809749688</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.0342091334319512</v>
+        <v>0.03489328500864253</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.03892342469624177</v>
+        <v>-0.03828765187906202</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.002858399296393865</v>
+        <v>-0.002198768689533948</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -4999,25 +5002,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.08501377966123558</v>
+        <v>0.0829337855732375</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.05822491678503661</v>
+        <v>0.05619646143149937</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.1001482042231658</v>
+        <v>0.1001482988150126</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.04110768837678536</v>
+        <v>0.03911195478884255</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.009228813063245966</v>
+        <v>-0.01112805495513758</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.03810694529809466</v>
+        <v>-0.03995082974800257</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0.00449293966623876</v>
+        <v>0.002567394094993514</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5100,7 +5103,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D84" s="21" t="inlineStr">
+      <c r="D84" s="22" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5163,25 +5166,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1608241115404103</v>
+        <v>0.1620740092576565</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05647310647546022</v>
+        <v>0.05761080655967143</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.09666913995945126</v>
+        <v>0.09666921927951577</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1476946611059231</v>
+        <v>0.1489305132176668</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.03450852586685271</v>
+        <v>0.03562249771810944</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.03665283540802222</v>
+        <v>-0.03561549100968187</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.003754693366708417</v>
+        <v>-0.002681923833363076</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5215,25 +5218,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.09238222406347818</v>
+        <v>0.09159265977582076</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.0139599376434143</v>
+        <v>0.01322695455596112</v>
       </c>
       <c r="H86" s="3" t="n">
         <v>0.07553051698947244</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-0.1000001494545475</v>
+        <v>-0.1006507517561467</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.06061634757614409</v>
+        <v>-0.06129542009596856</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.05724670604270787</v>
+        <v>-0.05792821444797824</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.004356243949661165</v>
+        <v>0.003630203291384193</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5260,7 +5263,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D87" s="21" t="inlineStr">
+      <c r="D87" s="22" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5323,25 +5326,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.3322569281500978</v>
+        <v>0.3346879686868809</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.06145174149714094</v>
+        <v>0.06338847524546032</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.0669253125560314</v>
+        <v>0.06692524401013467</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.1222965046695117</v>
+        <v>0.1243443285177783</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.006861488130357918</v>
+        <v>0.008698680849675622</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.005130228887134991</v>
+        <v>-0.003314917127071881</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.01465024551235605</v>
+        <v>0.01650165016501637</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5375,25 +5378,25 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.1475484716763342</v>
+        <v>0.1462436979734618</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.02581466678696387</v>
+        <v>0.02464830559675701</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>0.06576253755155004</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.009973934965964659</v>
+        <v>0.008825584840932432</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>-0.06364480807366879</v>
+        <v>-0.06470945297637065</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.03748290013679889</v>
+        <v>-0.03857729138166888</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>0.01324884792626735</v>
+        <v>0.01209677419354849</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -5427,25 +5430,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.32956799760155</v>
+        <v>0.3326121183081854</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.05956158173529325</v>
+        <v>0.06198759566027379</v>
       </c>
       <c r="H90" s="3" t="n">
         <v>0.06536126069574189</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.121250354108237</v>
+        <v>0.1238176130758573</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.006579156910872852</v>
+        <v>0.008883860189432102</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>-0.005443861321427268</v>
+        <v>-0.003166686418900611</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0.01451800232288036</v>
+        <v>0.0168408826945412</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -5483,25 +5486,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1918603234909539</v>
+        <v>0.189741533130914</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.01249590429098157</v>
+        <v>0.01069607987194998</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.06071329154876204</v>
+        <v>0.06071340359587785</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.107002673491694</v>
+        <v>0.1050347360187334</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.0276011647635368</v>
+        <v>-0.02932981470481388</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.04545751207414173</v>
+        <v>-0.04715441848322666</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.01032743851892781</v>
+        <v>0.008531362254766695</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -5528,7 +5531,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D92" s="21" t="inlineStr">
+      <c r="D92" s="22" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5539,25 +5542,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.02420765328850982</v>
+        <v>0.0238218876940508</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.05841343381192776</v>
+        <v>0.05801478468431487</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0.05362964428057437</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.011043412033511</v>
+        <v>0.01066260472201064</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.001508864579403912</v>
+        <v>0.001131648434552934</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.004540295119182858</v>
+        <v>0.004161937192584064</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>-0.0003765060240963347</v>
+        <v>-0.0007530120481927804</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -5591,25 +5594,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.08705506527008855</v>
+        <v>0.08760741197627819</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02896185158138609</v>
+        <v>0.02948479467759824</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03427767476531041</v>
+        <v>0.03427757158260181</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.02134604422774622</v>
+        <v>0.02186521873237357</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0.001805173775986324</v>
+        <v>0.002314415191045915</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.005139648001326491</v>
+        <v>-0.004633936804478767</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>0.003442999234888999</v>
+        <v>0.003953073195613444</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5632,7 +5635,7 @@
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr"/>
-      <c r="D94" s="22" t="inlineStr">
+      <c r="D94" s="23" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -5643,19 +5646,19 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.04337854580101408</v>
+        <v>0.04337864791136203</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01582124726319201</v>
+        <v>0.01582144083877179</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.02126136836532844</v>
+        <v>0.02126156297758142</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>0.003580766045005568</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>0.002338463647773459</v>
+        <v>0.002338369412244745</v>
       </c>
       <c r="K94" s="5" t="n">
         <v>-0.005326864670152087</v>
@@ -5695,25 +5698,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1419888093772792</v>
+        <v>0.1424054415587372</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.04207667126745407</v>
+        <v>-0.04172729396279484</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.007945198259429853</v>
+        <v>0.007945090759379436</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.04865500872794892</v>
+        <v>0.04903758990588658</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-0.02421402639626069</v>
+        <v>-0.02385803005419451</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.04962756865478812</v>
+        <v>-0.04928084394433763</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>0.01099144290351139</v>
+        <v>0.01136028326940086</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -5740,7 +5743,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D96" s="23" t="inlineStr">
+      <c r="D96" s="24" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -5751,25 +5754,25 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.2196676177423709</v>
+        <v>0.2226019798685404</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.04209039747821941</v>
+        <v>-0.03978587560885494</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.004001728229553025</v>
+        <v>0.004001639964004156</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.05753298213549396</v>
+        <v>0.06007737224120935</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-0.01467337380358114</v>
+        <v>-0.01230280571457254</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.04590841271663038</v>
+        <v>-0.04361299208079883</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>0.00483500543938109</v>
+        <v>0.007252508159071525</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5807,25 +5810,25 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.03245800739427462</v>
+        <v>0.03255588286597377</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.01331083036473879</v>
+        <v>-0.01321743770248618</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.0002413084623060779</v>
+        <v>0.000241237138472572</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.01851640530302545</v>
+        <v>-0.01842336574523251</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.01510735489239412</v>
+        <v>-0.01501406203977429</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.01354886937021116</v>
+        <v>-0.01345542889179585</v>
       </c>
       <c r="L97" s="3" t="n">
-        <v>0.001707941929974366</v>
+        <v>0.001802827592750633</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -5848,7 +5851,7 @@
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" s="22" t="inlineStr">
+      <c r="D98" s="23" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -5859,25 +5862,25 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.02188167931441476</v>
+        <v>0.02199368950511493</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.02501292569517288</v>
+        <v>-0.02490605187500006</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-0.00964029879872752</v>
+        <v>-0.009640379611043581</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.02843282705853778</v>
+        <v>-0.02832632783488509</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.02037349508233233</v>
+        <v>-0.02026603276279326</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.01552226618045838</v>
+        <v>-0.01541427169451937</v>
       </c>
       <c r="L98" s="3" t="n">
-        <v>0.004739336492890933</v>
+        <v>0.004849553620632552</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5911,25 +5914,25 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.03966739906022587</v>
+        <v>0.03956830458517246</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.0207829844104328</v>
+        <v>-0.02087617350838999</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.01707549618944681</v>
+        <v>-0.01707542625358827</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.01085038437088592</v>
+        <v>-0.0109445890961839</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.02298930292386137</v>
+        <v>-0.02308235156167826</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.003771895203154463</v>
+        <v>-0.003866774070278023</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.005265677357587428</v>
+        <v>0.005169937769267552</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5952,7 +5955,7 @@
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" s="21" t="inlineStr">
+      <c r="D100" s="22" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5963,25 +5966,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.06422220855376626</v>
+        <v>0.06432290447583155</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.02418425838286309</v>
+        <v>-0.02409229486407527</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.01749065182879961</v>
+        <v>-0.01749072081556802</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0.00592793720212681</v>
+        <v>0.006022736396023021</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.002031420266108697</v>
+        <v>0.002125924785609357</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.006812766277005555</v>
+        <v>-0.006719095878653825</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0.001700519603212047</v>
+        <v>0.001794992914501803</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6008,7 +6011,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D101" s="23" t="inlineStr">
+      <c r="D101" s="24" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -6019,25 +6022,25 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.1648339122211882</v>
+        <v>0.167253522215207</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.05737481398411259</v>
+        <v>-0.05541679625516382</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01796488796033358</v>
+        <v>-0.01796481273171724</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.03642852084795156</v>
+        <v>0.03858130697455331</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>-0.02845011732278158</v>
+        <v>-0.02643209189540552</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>-0.04013087265477233</v>
+        <v>-0.03813710955472627</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0.01420623345757033</v>
+        <v>0.0163128612326473</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6060,7 +6063,7 @@
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr"/>
-      <c r="D102" s="22" t="inlineStr">
+      <c r="D102" s="23" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -6071,25 +6074,25 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.0376250111671772</v>
+        <v>-0.03691694863707329</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.05604535294486157</v>
+        <v>-0.05535084308804594</v>
       </c>
       <c r="H102" s="5" t="n">
         <v>-0.05838022746581295</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.04026839573470709</v>
+        <v>-0.03956227806142787</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-0.04441309453187736</v>
+        <v>-0.04371002629977327</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>0.002479636249212991</v>
+        <v>0.00321720557079419</v>
       </c>
       <c r="L102" s="3" t="n">
-        <v>0.008283877349159363</v>
+        <v>0.00902571711177047</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6127,25 +6130,25 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.02669902912621358</v>
+        <v>-0.02710355987055013</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.1067384444031929</v>
+        <v>-0.1071097085576387</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>-0.08334880267310185</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0.0083822296730931</v>
+        <v>0.007963118189438401</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>-0.01916021198532414</v>
+        <v>-0.01956787607011823</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>-0.02551640340218719</v>
+        <v>-0.02592142567841238</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0.01390644753476611</v>
+        <v>0.01348504003371254</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6183,25 +6186,25 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.09720113063403135</v>
+        <v>-0.09215756153142818</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.1732134270037449</v>
+        <v>-0.1685945076015311</v>
       </c>
       <c r="H104" s="5" t="n">
         <v>-0.1313010102058796</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.1307908282639212</v>
+        <v>0.1371080954609265</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.09072444143534186</v>
+        <v>0.09681787406905884</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>-0.0482473414730209</v>
+        <v>-0.04293028751476957</v>
       </c>
       <c r="L104" s="3" t="n">
-        <v>0.001658031088082934</v>
+        <v>0.007253886010362809</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -207,9 +207,6 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -694,25 +691,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.832492939073123</v>
+        <v>1.831883878141396</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.191551965788332</v>
+        <v>1.191080927666467</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.176101915391165</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.5237743176796852</v>
+        <v>0.5234466551362986</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1408705992635458</v>
+        <v>-0.1410552550260734</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.007099874453439403</v>
+        <v>0.006883414866444504</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.03894421865928277</v>
+        <v>0.03872091465320904</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -746,25 +743,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.221121357944451</v>
+        <v>2.223065199009701</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.30975427510422</v>
+        <v>1.311148136033897</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>1.154782282650168</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.3821656050955415</v>
+        <v>0.3829996966939642</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.1111761263897016</v>
+        <v>-0.1106397503413303</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.07192002352249327</v>
+        <v>0.07256689209056155</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.03839580722342495</v>
+        <v>0.03902244502677443</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -802,25 +799,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.568860538758466</v>
+        <v>1.568477522820564</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9672064047628717</v>
+        <v>0.9669133822850637</v>
       </c>
       <c r="H4" s="10" t="n">
         <v>1.143605936403186</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.407023436710928</v>
+        <v>0.406813855503404</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.1982203805015247</v>
+        <v>-0.19833980846302</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.08229102590390258</v>
+        <v>-0.08242772196022141</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.03411891558841651</v>
+        <v>0.03396487985212571</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -858,25 +855,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.947873227689741</v>
+        <v>1.949958298582152</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.099495099495099</v>
+        <v>1.100980100980101</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>1.068310068310068</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.5793118856121537</v>
+        <v>0.5804289544235925</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1153798022775623</v>
+        <v>-0.1147540983606558</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.015077541642734</v>
+        <v>0.01579551981619742</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.04047689137474242</v>
+        <v>0.04121283485428306</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -910,25 +907,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.555834986709035</v>
+        <v>1.561707452085938</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.009492144472026</v>
+        <v>1.014108990986017</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>1.060288206804791</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.5328113982319203</v>
+        <v>0.5363330616432453</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1357967179335159</v>
+        <v>-0.1338111944164601</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.02465483332137453</v>
+        <v>-0.02241395920544154</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.03164960363303204</v>
+        <v>0.03401983826634258</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -966,25 +963,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.500723631759469</v>
+        <v>1.504288521691463</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9129195321322225</v>
+        <v>0.9156461281882204</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.9794102658697132</v>
+        <v>0.9794101074906643</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4876212029164859</v>
+        <v>0.4897417155960819</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1400893945681021</v>
+        <v>-0.1388636448015874</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.03359118363886826</v>
+        <v>-0.0322136272120378</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.02969402732302151</v>
+        <v>0.03116179293214416</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1022,25 +1019,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.452444864460279</v>
+        <v>1.456125043258976</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.827778283743825</v>
+        <v>0.8305210776740908</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.8604305924374638</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4219269946909847</v>
+        <v>0.4240607615515533</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.102889561998173</v>
+        <v>-0.1015433434299726</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.01755094160801729</v>
+        <v>-0.01607666251294382</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.0260466309846763</v>
+        <v>0.02758633330889371</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1078,25 +1075,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.277312481196204</v>
+        <v>1.282056452491151</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.8237920417622775</v>
+        <v>0.8275912643834651</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.7243515192424976</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5476590972806279</v>
+        <v>0.5508830950378469</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.05042336599752639</v>
+        <v>0.05261154980496618</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.05766835903822209</v>
+        <v>0.05987163521410088</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.01854243542435419</v>
+        <v>0.02066420664206636</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -1134,25 +1131,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.274052478134111</v>
+        <v>1.301749271137026</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9402985074626868</v>
+        <v>0.9639303482587065</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.718905472636816</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.457943925233645</v>
+        <v>0.4757009345794392</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.3131313131313129</v>
+        <v>0.3291245791245789</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1287988422575976</v>
+        <v>0.142547033285094</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.01960784313725483</v>
+        <v>0.03202614379084956</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -1186,25 +1183,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8168941330268553</v>
+        <v>0.8008486568426647</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.711017049057731</v>
+        <v>0.6959067402717898</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7158395322850641</v>
+        <v>0.7158396725745104</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.3195997408759199</v>
+        <v>0.3079460039685227</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.1465437731350889</v>
+        <v>0.1364183395880485</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-0.002810567734682468</v>
+        <v>-0.01161701330335407</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.03554287196782968</v>
+        <v>0.02639771695420934</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -1242,25 +1239,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.5841561221878504</v>
+        <v>0.5811958204770222</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.5691796154838975</v>
+        <v>0.5662473002687165</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.6440122997753184</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.04687255464552154</v>
+        <v>0.04491627106265339</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.01065169218372275</v>
+        <v>0.008763094278807504</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.04551832386025823</v>
+        <v>-0.04730195724036235</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.003751406777541488</v>
+        <v>0.001875703388770855</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1298,25 +1295,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.127615821891222</v>
+        <v>1.120759653976278</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6607025969328</v>
+        <v>0.6553510406301049</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.6354738315058084</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1635563116027947</v>
+        <v>0.1598067918968586</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.004901695872316258</v>
+        <v>0.00166343514214895</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.01542596704452515</v>
+        <v>0.01215379221689861</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.03207031713980291</v>
+        <v>0.02874450647345284</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1354,25 +1351,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.168706009997117</v>
+        <v>1.172542730050186</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5937776114680366</v>
+        <v>0.5965972091884577</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.5417912784977723</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1748629018742363</v>
+        <v>0.1769413855573396</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.01755175517551755</v>
+        <v>0.01935193519351941</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.03371813921591049</v>
+        <v>0.03554691964795986</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.01310630670998103</v>
+        <v>0.0148986221574996</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -1410,25 +1407,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.177539428720899</v>
+        <v>1.179170680397156</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.7175399292304787</v>
+        <v>0.7188267169654332</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.5377113432705916</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.3658760700843702</v>
+        <v>0.366899389859672</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.3289984345928749</v>
+        <v>0.3299941254972338</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.1169456066945607</v>
+        <v>0.1177824267782428</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.016178149980967</v>
+        <v>0.01693947468595347</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1462,25 +1459,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.9279454722492697</v>
+        <v>0.913988964621876</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.5388601036269429</v>
+        <v>0.527720207253886</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0.4880829015544039</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.1353711790393014</v>
+        <v>-0.1416302765647744</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.01996370235934664</v>
+        <v>-0.0270582412143211</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.03412256267409464</v>
+        <v>0.02663649025069637</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.04119193689745848</v>
+        <v>0.03365468886941292</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1518,25 +1515,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.7227141681096243</v>
+        <v>0.7199549150200295</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.4907183812979348</v>
+        <v>0.4883305575252326</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.4773465681708029</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.1485914631322238</v>
+        <v>0.1467516562074564</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.02574906367041196</v>
+        <v>-0.02730961298377033</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.009051236463552659</v>
+        <v>0.00743494423791824</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.02428219852337987</v>
+        <v>0.02264150943396226</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1570,25 +1567,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.4692451416251024</v>
+        <v>0.4811919621264416</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.4689832274699355</v>
+        <v>0.4809279183154322</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4627811090740497</v>
+        <v>0.4627809808954044</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.1095676280225668</v>
+        <v>0.118589913660905</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.1781817000075299</v>
+        <v>0.1877619108598192</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.004239949748743754</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>-0.00124941433702952</v>
+        <v>0.01240577889447225</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0.006871778853662303</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1597,7 +1594,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1626,25 +1623,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.485652880346314</v>
+        <v>0.4950688156528953</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.463420462793843</v>
+        <v>0.4726954910230361</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.4580507096085207</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.1022193146348391</v>
+        <v>0.1092050822374617</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.1736979482649781</v>
+        <v>0.1811367410654567</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.003682830199207565</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>-0.001609680284191839</v>
+        <v>0.01004408236147536</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0.004718028419183007</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -1653,7 +1650,7 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1682,25 +1679,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.5258076151208244</v>
+        <v>0.5267664731581541</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4712320508681362</v>
+        <v>0.4721562809184545</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0.4471242881227626</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.2637698472629908</v>
+        <v>0.2645637492642674</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.1932145092368462</v>
+        <v>0.1939640882752187</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.01665908239066782</v>
+        <v>0.01729774906076931</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.02243083003952573</v>
+        <v>0.02307312252964411</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1738,25 +1735,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.724334083338052</v>
+        <v>0.7223906242415876</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.3785668944168274</v>
+        <v>0.3770130399083618</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.4376094889367927</v>
+        <v>0.4376093824261909</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.02642359826728624</v>
+        <v>0.02526673875951824</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.1418668824825832</v>
+        <v>-0.142834065483448</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.04106998108619286</v>
+        <v>-0.04215077006214529</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.01617752326413768</v>
+        <v>0.01503221188260584</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1794,25 +1791,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.6816951756343352</v>
+        <v>0.6816407606472576</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.4013516374672259</v>
+        <v>0.4013062936187397</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0.4359489938622265</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.3814960209814151</v>
+        <v>0.3814513196055542</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.04707228156533216</v>
+        <v>-0.04710311566073522</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.0240937223695844</v>
+        <v>-0.0241252999873689</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.01731459231706101</v>
+        <v>0.01728167484117327</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1850,25 +1847,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5310150070172128</v>
+        <v>0.5390865339757844</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4692797986265147</v>
+        <v>0.4770257668727447</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0.4215002123156095</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.1149788799229148</v>
+        <v>0.12085699177552</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.2360770260479823</v>
+        <v>0.2425935611576413</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.03361208524413284</v>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>-0.001147028154327434</v>
+        <v>0.03906123550040475</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0.004118873826902902</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1877,7 +1874,7 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1906,25 +1903,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6219491276717437</v>
+        <v>0.6241166636739779</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.4073215984639635</v>
+        <v>0.4092022268564697</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.3924326233702415</v>
+        <v>0.3924325401219269</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.145710197140442</v>
+        <v>0.1472412982447002</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.02793423507634274</v>
+        <v>0.02930794305795836</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.01069277955990766</v>
+        <v>0.01204344645168565</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.007291491390431393</v>
+        <v>0.008637612877895773</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1958,25 +1955,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5434745380950423</v>
+        <v>0.5444091275822327</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4987558133221384</v>
+        <v>0.4996633251679281</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.3830480529839169</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.1284591732148959</v>
+        <v>0.129142466689443</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1919884518224468</v>
+        <v>0.1927102129195235</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.08366141732283472</v>
+        <v>0.08431758530183719</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.003920386007237542</v>
+        <v>-0.003317249698431834</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -2010,25 +2007,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.7603241236242442</v>
+        <v>0.7609797241353082</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3875949090683111</v>
+        <v>0.3881115942304727</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.3701014257208357</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.3659625267992501</v>
+        <v>0.366471156922533</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.01299331622585598</v>
+        <v>0.01337051465202665</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.01276802068742589</v>
+        <v>0.01314513522249761</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.02207361496221383</v>
+        <v>0.02245419453052788</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2062,25 +2059,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.371588577370338</v>
+        <v>1.367850259940687</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.4740912474237744</v>
+        <v>0.4717676483578479</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.3558975082703129</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.08445701861262078</v>
+        <v>0.08274759708265123</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.1086821963757969</v>
+        <v>0.1069345888783573</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.08717011310407852</v>
+        <v>0.08545641494344802</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.04651930056087084</v>
+        <v>0.04486967997360614</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -2118,25 +2115,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.7312928668273277</v>
+        <v>0.7324276695682719</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3511560856148321</v>
+        <v>0.3520418450471436</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.3324618997013125</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.3528440354982558</v>
+        <v>0.3537309014774321</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.03911143847658072</v>
+        <v>0.0397926349479969</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.01402980897068073</v>
+        <v>0.0146945630116857</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.02128334331724147</v>
+        <v>0.02195285246132683</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -2170,25 +2167,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.7262490944068716</v>
+        <v>0.7276716550817506</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3468268822200897</v>
+        <v>0.3479364776083087</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.3291843155474095</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.3519762234458486</v>
+        <v>0.3530900611649506</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.03929261435992215</v>
+        <v>0.04014884488748849</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.01327322814926113</v>
+        <v>0.01410802237248521</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.0206861755802219</v>
+        <v>0.02152707702657253</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -2226,25 +2223,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.7420357822813033</v>
+        <v>0.7444947301863378</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3438077522395773</v>
+        <v>0.3457044463147212</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.3146792410827406</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3526892825117047</v>
+        <v>0.3545985122682489</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.03539016201621048</v>
+        <v>0.0368515454488374</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.02215636350418593</v>
+        <v>0.023599068322117</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.01962822306616019</v>
+        <v>0.02106735958424943</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2282,25 +2279,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5131758290786077</v>
+        <v>0.511559188235575</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3027134017622231</v>
+        <v>0.3013217290905161</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3071706687350122</v>
+        <v>0.3071707844032689</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.2665113134753372</v>
+        <v>0.2651582030976929</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1551292735553875</v>
+        <v>0.1538951610836405</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.003409858467144589</v>
+        <v>-0.004474591524337712</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.002678093197643339</v>
+        <v>0.001606855918586003</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2334,25 +2331,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.2800133326364371</v>
+        <v>0.2803913251187999</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.2809701524196808</v>
+        <v>0.2813482427834408</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3047898453365754</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.1261835387947297</v>
+        <v>0.1265158710144492</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.06952171522596706</v>
+        <v>0.06983739459881999</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.01825557809330614</v>
+        <v>-0.01796580701246009</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.001182033096926771</v>
+        <v>0.001477541371158297</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2390,25 +2387,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.4875468077181953</v>
+        <v>0.478296732852427</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.08530709645358647</v>
+        <v>0.07855828569855228</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.2980510646255203</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>-0.1034973405521642</v>
+        <v>-0.10907210073734</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.1495396474148811</v>
+        <v>-0.1548281007872138</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.1638949144372137</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>0.002228734161542123</v>
+        <v>-0.1690941018489825</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>-0.004003466919806797</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2417,7 +2414,7 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2446,25 +2443,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.9323304899943885</v>
+        <v>0.9273095236939657</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.2694695444057531</v>
+        <v>0.266171039183303</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.2924453394035098</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.03563678348812438</v>
+        <v>0.03294585375770986</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.05662338765084107</v>
+        <v>-0.05907459468946907</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.01777699551174861</v>
+        <v>-0.02032913843175221</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.02611014066378603</v>
+        <v>0.02344396432839946</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2502,25 +2499,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.4936051471667882</v>
+        <v>0.4914021897225895</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.2571899168109555</v>
+        <v>0.2553356543967802</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.2898249353004436</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.1229038802355535</v>
+        <v>0.1212476798222268</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1328097234693193</v>
+        <v>-0.1340887651751167</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.02530189764232327</v>
+        <v>-0.02673950546290971</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.02602905569007263</v>
+        <v>0.02451573849878952</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2554,25 +2551,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5251256822665098</v>
+        <v>0.5186819283647455</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.1407833287295672</v>
+        <v>0.1359635700409154</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.2882679446023129</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>-0.03387813004637918</v>
+        <v>-0.0379599518610364</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.1759381044487427</v>
+        <v>-0.1794197292069633</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.1144828732956434</v>
+        <v>-0.1182241436647822</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.008235516849678159</v>
+        <v>0.003975766755017096</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2610,25 +2607,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.6136795754387154</v>
+        <v>0.6146866565134639</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2142982238926159</v>
+        <v>0.2150560551120206</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.285281748110179</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.01492423872899429</v>
+        <v>0.01555764266412796</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.2123545797148944</v>
+        <v>-0.2118630181877765</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.05522798742138368</v>
+        <v>-0.05463836477987427</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.02867536914187885</v>
+        <v>0.02931735501818977</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2662,25 +2659,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4173879191019889</v>
+        <v>0.4097719896485363</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.222922356027321</v>
+        <v>0.216351429935234</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.2784101763605011</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1628109010922127</v>
+        <v>0.1565629619221651</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.02421141126178428</v>
+        <v>-0.02945445442515382</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.04340376927470024</v>
+        <v>-0.04854368932038844</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.01330913490623109</v>
+        <v>0.007864488808227321</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2718,25 +2715,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.2137407664181021</v>
+        <v>0.2151973319991503</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2641951313178537</v>
+        <v>0.2657122453235405</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0.2729384988769445</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1700495240536786</v>
+        <v>0.1714536573842973</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.1267914378367951</v>
+        <v>0.1281436587317202</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>-0.006868648852088821</v>
+        <v>-0.005676828503324516</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.006324286531494083</v>
+        <v>0.007531939236000706</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2770,25 +2767,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.4246049239569067</v>
+        <v>0.4141983901447821</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2187375291382552</v>
+        <v>0.2098348269983137</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.2694741390866771</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1743609045548116</v>
+        <v>0.1657823672667735</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>-0.005689144078778408</v>
+        <v>-0.01295244169055865</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.03996663530690314</v>
+        <v>-0.04697954078156408</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.012538743307974</v>
+        <v>0.005142293603831893</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2822,25 +2819,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.3939574993506101</v>
+        <v>0.3948218541253792</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2556997454816123</v>
+        <v>0.2564784740059423</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.2634870307249093</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1675261794829217</v>
+        <v>0.168250226726012</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.04700215544030084</v>
+        <v>0.04765145910258961</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.006163328197226536</v>
+        <v>-0.005546995377503805</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.006868560724320849</v>
+        <v>0.007492975335622987</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2874,25 +2871,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.3346200551570746</v>
+        <v>0.3329117040320986</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.252009466530954</v>
+        <v>0.2504068508705717</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2613588011434105</v>
+        <v>0.2613589296754624</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1228355802733052</v>
+        <v>0.1213981974097167</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.02354872738302594</v>
+        <v>0.02223844524854801</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.007412113511224061</v>
+        <v>-0.008682761541719541</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.01034705755550758</v>
+        <v>0.009053675361069269</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
@@ -2926,25 +2923,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.1775945823721246</v>
+        <v>0.1803918049425355</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2513798127404647</v>
+        <v>0.2543521770678565</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2611881456946681</v>
+        <v>0.2611882886898127</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1543300369141281</v>
+        <v>0.1570716296608641</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.1223723663587417</v>
+        <v>0.12503817567258</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.007777057679844379</v>
+        <v>-0.005420373534437029</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.003814746378971057</v>
+        <v>0.006198962865828106</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2978,25 +2975,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.5686962568535459</v>
+        <v>0.5688033131735384</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2204667589010945</v>
+        <v>0.2205500501560527</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.2568650373177859</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.2680514642185938</v>
+        <v>0.2681380029112996</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-0.05617819907502253</v>
+        <v>-0.05611378756878327</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.02895957587806497</v>
+        <v>-0.02889330682571245</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.01997772518446328</v>
+        <v>0.02004733398301539</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3034,25 +3031,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.4130815749620533</v>
+        <v>0.4094964384024642</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2085622265211911</v>
+        <v>0.2054959770564664</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>0.2544026560188233</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1142049469964663</v>
+        <v>0.1113780918727914</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>-0.06065300285986663</v>
+        <v>-0.0630362249761679</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.03654363236372515</v>
+        <v>-0.03898802248838917</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.01637441980402254</v>
+        <v>0.0137957710159875</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -3086,25 +3083,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.2965567595247445</v>
+        <v>0.2971148183882415</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2462924178635306</v>
+        <v>0.2468289271927298</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2516561475615355</v>
+        <v>0.2516562329368497</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1299783400833772</v>
+        <v>0.1304647708308591</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.1269403132801812</v>
+        <v>0.1274253664996705</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.004285306079033435</v>
+        <v>-0.003856734474763313</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.001868621532269854</v>
+        <v>0.002299841885870402</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3138,25 +3135,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.4128085381585544</v>
+        <v>0.4063645636291147</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.06691651315850944</v>
+        <v>0.0620502705220396</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2506848783201658</v>
+        <v>0.2506849730840535</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>-0.06986966778578629</v>
+        <v>-0.07411203297592894</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>-0.1140117960525927</v>
+        <v>-0.1180528853194105</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.146934186498266</v>
+        <v>-0.1508251131352935</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.001904584939843024</v>
+        <v>-0.006457007478979926</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3194,25 +3191,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.1193684064893059</v>
+        <v>0.1219988385489903</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.3064303756619671</v>
+        <v>0.3095003893625188</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.2434950948006611</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.08409578210678581</v>
+        <v>0.0866433261365176</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.03035518435833828</v>
+        <v>-0.02807659154226083</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.05061160363595563</v>
+        <v>0.0530804623499046</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.002570143499678768</v>
+        <v>0.004926108374384341</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3246,25 +3243,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.3837255210272035</v>
+        <v>0.3826803515773269</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.1488925577169258</v>
+        <v>0.1480246502134568</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2434944755950332</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.05432029212460709</v>
+        <v>0.0535238273146923</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-0.08515261520063711</v>
+        <v>-0.08584371804090107</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.07607747339033322</v>
+        <v>-0.07677543186180436</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.003791469194312835</v>
+        <v>0.003033175355450224</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3302,25 +3299,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.3973306798237357</v>
+        <v>0.3855578286807397</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.1732254774602819</v>
+        <v>0.1633407888966254</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2405129006938687</v>
+        <v>0.2405127795920026</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1649035550646498</v>
+        <v>0.1550890933317735</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.03380935427567044</v>
+        <v>-0.04194963428245457</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.05424161505773151</v>
+        <v>-0.06220975064904899</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.01564620198831368</v>
+        <v>0.00708925258231563</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3354,25 +3351,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4261444940565575</v>
+        <v>0.4231856880522911</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.2351087828253562</v>
+        <v>0.2325462361497423</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2366462626380019</v>
+        <v>0.2366461820496166</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.1326111533584786</v>
+        <v>0.1302612701444359</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.009452255434464263</v>
+        <v>0.007357956149330436</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.001243265644426117</v>
+        <v>-0.003315375051802683</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.01459444288520895</v>
+        <v>0.01248947516138088</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3410,25 +3407,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.5187441251057601</v>
+        <v>0.5187935094921006</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2161558735861659</v>
+        <v>0.2161956029603642</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0.2363090739069289</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.2470191881611052</v>
+        <v>0.2470599257779149</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.06562540923650251</v>
+        <v>-0.06559488509188904</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.01630110200281532</v>
+        <v>-0.01626896653197163</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.02094520228129282</v>
+        <v>0.0209785545142247</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3462,25 +3459,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.2990463912051122</v>
+        <v>0.2955967814090403</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1305009753361384</v>
+        <v>0.1274988220944215</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2246315593205175</v>
+        <v>0.2246314346599192</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.03132496511208793</v>
+        <v>0.02858628793576035</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.05413734764211808</v>
+        <v>-0.05664908016637793</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>-0.0768644113961976</v>
+        <v>-0.07931579234079644</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.004445498192163999</v>
+        <v>0.001778199276865511</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3518,25 +3515,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.7742741801247295</v>
+        <v>0.7722490832291038</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.183133990316334</v>
+        <v>0.1817836009583993</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.2230669327581214</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.03118957545187051</v>
+        <v>0.0300126103404792</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.06679853925745594</v>
+        <v>-0.06786366402921484</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>-0.03264984227129342</v>
+        <v>-0.03375394321766567</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.02738922857860793</v>
+        <v>0.02621660105536483</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3570,25 +3567,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.4507071036476042</v>
+        <v>0.4481924601296652</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2575617085478299</v>
+        <v>0.25538200330259</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>0.2228146425795936</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1718704600464211</v>
+        <v>0.169839281638918</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.03843303335097925</v>
+        <v>0.03663313922710421</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0.02841564433259935</v>
+        <v>0.0266331131383033</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.01102979074322219</v>
+        <v>0.009277394083084145</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3622,25 +3619,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.4957988343358695</v>
+        <v>0.4972697293952346</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2178278155904925</v>
+        <v>0.2190253676115199</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0.2200577400434403</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.206956031555275</v>
+        <v>0.2081428927981999</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.00779217195634907</v>
+        <v>-0.006816483542485097</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.001827720426467949</v>
+        <v>-0.0008461668641055464</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.01623018607856652</v>
+        <v>0.01722949689869058</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3674,25 +3671,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.494587662319625</v>
+        <v>0.4960692909484445</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.217327108918048</v>
+        <v>0.218533881020269</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0.2195366916404247</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.2067593088405073</v>
+        <v>0.2079556047722546</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.007630205903225717</v>
+        <v>-0.006646440591642988</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.001811821438028716</v>
+        <v>-0.0008222881911054136</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.01630434782608692</v>
+        <v>0.01731184016346909</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3730,25 +3727,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3747768624180563</v>
+        <v>0.3713491666292976</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.07101985949841705</v>
+        <v>0.06834965291776762</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0.2186822834083209</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>-0.08013618815317425</v>
+        <v>-0.08242954096256561</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>-0.09658154554516185</v>
+        <v>-0.0988338977128379</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.1211656441717792</v>
-      </c>
-      <c r="L58" s="3" t="n">
-        <v>0.001685708934257457</v>
+        <v>-0.1233567046450482</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>-0.0008116376350127963</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3757,7 +3754,7 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3786,25 +3783,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2913738840880569</v>
+        <v>0.2888362878915047</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1107145629441855</v>
+        <v>0.1085318622300155</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2125369630839975</v>
+        <v>0.2125366846062464</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.02201146517244146</v>
+        <v>0.02000331201233574</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>-0.1290728457797824</v>
+        <v>-0.1307841329586147</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-0.08397467725918573</v>
+        <v>-0.08577457795431975</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.009162393162393201</v>
+        <v>0.007179487179487243</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -3842,25 +3839,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3055458696623015</v>
+        <v>0.3026154736153759</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1431368499365449</v>
+        <v>0.140571078165028</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.2076232471273391</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.174307861970167</v>
+        <v>0.1716721268318231</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.02798191570216146</v>
+        <v>0.02567460929253529</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.05339943342776199</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>0.00074872716382135</v>
+        <v>-0.05552407932011316</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>-0.001497454327642922</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3869,7 +3866,7 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3894,25 +3891,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3235487037743068</v>
+        <v>0.3195375168777692</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1382198325583388</v>
+        <v>0.1347702900823007</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.200380668492671</v>
+        <v>0.2003807911823312</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1103444841797456</v>
+        <v>0.106979198528065</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>-0.02828344717566222</v>
+        <v>-0.03122847601017475</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.05178426941212577</v>
+        <v>-0.054658073156441</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.01402357153513356</v>
+        <v>0.01095032075190217</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -3946,25 +3943,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.2502933383155079</v>
+        <v>0.2502345035262936</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1527030932739348</v>
+        <v>0.1526490569391667</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.1876646018689205</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1116087456342552</v>
+        <v>0.1115566357174338</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.02467175924842979</v>
+        <v>0.02462372475755936</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.02943719004504297</v>
+        <v>-0.02948268802038301</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.004899189749387522</v>
+        <v>0.004852082155643478</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -4002,25 +3999,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.09062905038199776</v>
+        <v>0.08276211942307299</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1416089823725264</v>
+        <v>0.1333744257783638</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0.1842789574513684</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1481992721796963</v>
+        <v>0.139917179068892</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.1417519341152982</v>
+        <v>0.1335163463938109</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.03603034134007588</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>0.001971090670170872</v>
+        <v>-0.04298356510745893</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>-0.00525624178712214</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -4029,7 +4026,7 @@
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4054,34 +4051,34 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.4954912202601172</v>
+        <v>0.4964964767992481</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1901173982861257</v>
+        <v>0.1909174117753552</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.1839450644878686</v>
+        <v>0.1839449612409185</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1944923180459537</v>
+        <v>0.1952954812738958</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.01702536182248826</v>
+        <v>0.01770910918445101</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.005213361652828707</v>
+        <v>0.005889167793010186</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.01610227383624485</v>
+        <v>0.01678540060505518</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4106,25 +4103,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2816675837120779</v>
+        <v>0.2853071838673542</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1548438092026281</v>
+        <v>0.1581233565373872</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1828171496166644</v>
+        <v>0.1828172450824099</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1293804971898489</v>
+        <v>0.1325875525207727</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.02028491847307201</v>
+        <v>0.02318226033838267</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.02364975890238163</v>
+        <v>-0.02087718001042682</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>0.004416432810415483</v>
+        <v>0.007268712333808658</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4158,25 +4155,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3688843547730598</v>
+        <v>0.3700857837304996</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1681728935475131</v>
+        <v>0.1691979269148745</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1762489654120805</v>
+        <v>0.1762488555649435</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.158245518774724</v>
+        <v>0.1592619494573599</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.03107479332768004</v>
+        <v>0.03197962398667498</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.006865954489267523</v>
+        <v>-0.005994419137336782</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.01038868229159773</v>
+        <v>0.0112753596336832</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4210,25 +4207,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3680489557893116</v>
+        <v>0.3692988836816284</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1678867628014238</v>
+        <v>0.1689538314383923</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1762408407888809</v>
+        <v>0.1762407210770465</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1582348582953645</v>
+        <v>0.1592932262179634</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.03084722905148496</v>
+        <v>0.03178919313805517</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.007102353274737738</v>
+        <v>-0.006195066628863044</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.01031388840805492</v>
+        <v>0.01123708960821634</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4262,25 +4259,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3663820755542719</v>
+        <v>0.3676375966334497</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1671849586397751</v>
+        <v>0.1682573165227621</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.1756872247120298</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1580196990711256</v>
+        <v>0.1590836363192552</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.03090968936648553</v>
+        <v>0.03185684356330487</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.00723174148152983</v>
+        <v>-0.006319629943318805</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.01041045023539566</v>
+        <v>0.01133877063855193</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4314,34 +4311,34 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.4471918050158954</v>
+        <v>0.442776404097492</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1783146390566579</v>
+        <v>0.1747195858498705</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0.1750071901064134</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>-0.1007462686567165</v>
+        <v>-0.1034899034240563</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.02887995981918623</v>
-      </c>
-      <c r="K69" s="3" t="n">
-        <v>0.002814832945783996</v>
+        <v>0.02574083375188341</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>-0.0002447680822420528</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.0201693227091635</v>
+        <v>0.0170567729083666</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4366,34 +4363,34 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.4439706573194087</v>
+        <v>0.4395258916633542</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1766836479283842</v>
+        <v>0.1730616331458525</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0.1736211313642924</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>-0.1015199892071773</v>
+        <v>-0.1042856500427216</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.02828100874935657</v>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>0.002609459289925953</v>
+        <v>0.02511580030880078</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>-0.0004767281395057221</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.02003880124572421</v>
+        <v>0.01689896359830501</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4422,25 +4419,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.4014513148009016</v>
+        <v>0.4029665954738411</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1614498181553188</v>
+        <v>0.1627054726892383</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0.1576126008259451</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.1775034876489061</v>
+        <v>0.1787764979588313</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.0435696376463286</v>
+        <v>0.04469785078691224</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.003314768106908783</v>
+        <v>0.004399461322086129</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0.01176533361790688</v>
+        <v>0.01285916282047861</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4474,25 +4471,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.5082311109402715</v>
+        <v>0.5186938766207752</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2760711005010701</v>
+        <v>0.2849233313847719</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1473744953811651</v>
+        <v>0.1473745698904827</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.04348614455125266</v>
+        <v>0.05072484245902564</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.09879800644972137</v>
+        <v>0.1064204045734389</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>0.1121661721068248</v>
-      </c>
-      <c r="L72" s="21" t="n">
-        <v>0</v>
+        <v>0.1198813056379822</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0.006937033084311706</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4501,7 +4498,7 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d flat.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4530,13 +4527,13 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2300283010861444</v>
+        <v>0.2300283958955347</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.09345236451776429</v>
+        <v>0.09345243944175219</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1423995134838574</v>
+        <v>0.142399591761732</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>0.1254337714345923</v>
@@ -4586,25 +4583,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.08066438180371849</v>
+        <v>0.0822474003294813</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1321993138397124</v>
+        <v>0.1338576249344288</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1409992989182709</v>
+        <v>0.1409992301734426</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.1282439126910577</v>
+        <v>0.1298964984598039</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.06540109608019828</v>
+        <v>0.06696163336259242</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.007712524527316744</v>
+        <v>-0.006259079804925238</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.00340608925344088</v>
+        <v>-0.001946336716251884</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
@@ -4638,25 +4635,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.320865985053165</v>
+        <v>0.3213071935583722</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1343117953085837</v>
+        <v>0.1346905117226209</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1295768153649013</v>
+        <v>0.1295767337529146</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1060907042943238</v>
+        <v>0.1064600783815817</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.00252764762908031</v>
+        <v>0.002862437292673103</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.004191817572099188</v>
+        <v>0.00452716297786715</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.01199729638391345</v>
+        <v>0.01233524839472788</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4690,25 +4687,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.4431733229178529</v>
+        <v>0.4441299293624781</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1415273007359035</v>
+        <v>0.1422840307993676</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>0.125635969403153</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.197572389012866</v>
+        <v>0.1983661509700461</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.04090329673621862</v>
+        <v>0.04159332212351474</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.01411764705882357</v>
+        <v>0.01478991596638646</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.01559694793536814</v>
+        <v>0.01627019748653491</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4742,25 +4739,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2197569806869759</v>
+        <v>0.2212932880096627</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.07825704639877906</v>
+        <v>0.0796150527544448</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>0.118318233890925</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>-0.0322424018039843</v>
+        <v>-0.03102356351910263</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.03728402546226128</v>
+        <v>-0.03607153682934228</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.03582270795385534</v>
+        <v>-0.03460837887067392</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>0.008414033973646706</v>
+        <v>0.009684076837593203</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -4794,25 +4791,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3882721833409437</v>
+        <v>0.3886645653388194</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1217785421374409</v>
+        <v>0.1220955861126491</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1173408762459676</v>
+        <v>0.1173409437986126</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1847017666285315</v>
+        <v>0.1850365227083925</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.05877104795890542</v>
+        <v>0.05907022033753173</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.003971631205673676</v>
+        <v>0.004255319148936065</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0.01258941344778242</v>
+        <v>0.01287553648068651</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
@@ -4846,25 +4843,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.4056157383461902</v>
+        <v>0.4073663920058155</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.119392002614475</v>
+        <v>0.1207860645263203</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1135618359341912</v>
+        <v>0.1135617282515264</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.1802096860476174</v>
+        <v>0.1816796030026135</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.03279925051883281</v>
+        <v>0.0340855720491442</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.005235602094240788</v>
+        <v>0.00648759389938558</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.01447277739490005</v>
+        <v>0.01573627383413734</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -4898,25 +4895,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.07263339727272355</v>
+        <v>0.07663073716026214</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.07180252219322658</v>
+        <v>0.07579687161459381</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.1027273364906989</v>
+        <v>0.1027272280845244</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.01922314974911066</v>
+        <v>0.0230215534681506</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.000922008334980795</v>
+        <v>0.004652301946231452</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.02804393549894824</v>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v>-0.001800072002880015</v>
+        <v>-0.02442159383033427</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.001920076803072046</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
@@ -4925,7 +4922,7 @@
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4950,25 +4947,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.1814106396820252</v>
+        <v>0.1832329224007336</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05809010308995055</v>
+        <v>0.05972211287583851</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.1002147421287896</v>
+        <v>0.1002146116516589</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.1517611809749688</v>
+        <v>0.1535378068601221</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.03489328500864253</v>
+        <v>0.03648963868758948</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.03828765187906202</v>
+        <v>-0.03680418197230861</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.002198768689533948</v>
+        <v>-0.0006596306068601399</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -5002,25 +4999,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.0829337855732375</v>
+        <v>0.08397383035165618</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.05619646143149937</v>
+        <v>0.05721064370185602</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.1001482988150126</v>
+        <v>0.1001482042231658</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.03911195478884255</v>
+        <v>0.04010982158281395</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.01112805495513758</v>
+        <v>-0.01017843400919183</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.03995082974800257</v>
+        <v>-0.03902888752304856</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0.002567394094993514</v>
+        <v>0.003530166880616248</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5039,7 +5036,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EDEN</t>
+          <t>EUO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5047,45 +5044,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>0.08423727729767871</v>
+          <t>2x Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>-0.03128950695322386</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.05751453587875899</v>
+        <v>0.1173897192854538</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.09912073717437253</v>
+        <v>0.09697411593146188</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1007048311609744</v>
+        <v>0.02064602064602061</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.04250372023809534</v>
-      </c>
-      <c r="K83" s="5" t="n">
-        <v>-0.03785407725321888</v>
+        <v>0.01523683338853909</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>0.01861083416417419</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.02428621169916423</v>
+        <v>-0.002927781392322748</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5095,53 +5092,49 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EUO</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D84" s="22" t="inlineStr">
-        <is>
-          <t>Currency</t>
+          <t>XLF</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2x Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>-0.0306573957016435</v>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0.1641574183933621</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1181188479766679</v>
+        <v>0.05950684601209089</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.09697411593146188</v>
+        <v>0.09666921927951577</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.02131202131202126</v>
+        <v>0.1509902667372396</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.0158993044054323</v>
-      </c>
-      <c r="K84" s="3" t="n">
-        <v>0.01927550681289469</v>
+        <v>0.0374791174702036</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>-0.03388658367911479</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.002277163305139829</v>
+        <v>-0.0008939746111209512</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5151,40 +5144,44 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>XLF</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>EDEN</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Denmark Equity</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1620740092576565</v>
+        <v>0.1150547362543821</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05761080655967143</v>
+        <v>0.07888152215490973</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.09666921927951577</v>
+        <v>0.08894606643307656</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1489305132176668</v>
+        <v>0.1450129189585754</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.03562249771810944</v>
+        <v>0.06926447282558046</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.03561549100968187</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>-0.002681923833363076</v>
+        <v>-0.00924246350522584</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>0.02328486038005173</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5193,7 +5190,7 @@
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5218,25 +5215,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.09159265977582076</v>
+        <v>0.09738349207726271</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.01322695455596112</v>
+        <v>0.01860216386395042</v>
       </c>
       <c r="H86" s="3" t="n">
         <v>0.07553051698947244</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-0.1006507517561467</v>
+        <v>-0.0958796682110864</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.06129542009596856</v>
+        <v>-0.05631555495058915</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.05792821444797824</v>
+        <v>-0.05293048614266249</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.003630203291384193</v>
+        <v>0.00895450145208132</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5263,7 +5260,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D87" s="22" t="inlineStr">
+      <c r="D87" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5274,25 +5271,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.03707791771946667</v>
+        <v>0.0378092843751221</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.08103814015490429</v>
+        <v>0.08180050837786257</v>
       </c>
       <c r="H87" s="3" t="n">
         <v>0.07265208970236281</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.01831238779174149</v>
+        <v>0.01903052064631949</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.00638750887154016</v>
+        <v>0.007097232079488869</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>0.007818052594172009</v>
+        <v>0.008528784648187626</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>-0.00140845070422535</v>
+        <v>-0.0007042253521126751</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
@@ -5326,25 +5323,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.3346879686868809</v>
+        <v>0.33489924653199</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.06338847524546032</v>
+        <v>0.06355696113517584</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.06692524401013467</v>
+        <v>0.0669253125560314</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.1243443285177783</v>
+        <v>0.124522400156758</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.008698680849675622</v>
+        <v>0.00885843673831177</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.003314917127071881</v>
+        <v>-0.003157063930544601</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.01650165016501637</v>
+        <v>0.01666264187394351</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5378,25 +5375,25 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.1462436979734618</v>
+        <v>0.1455912398473937</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.02464830559675701</v>
+        <v>0.02406512500165348</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>0.06576253755155004</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.008825584840932432</v>
+        <v>0.008251409778416097</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>-0.06470945297637065</v>
+        <v>-0.06524177542772169</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.03857729138166888</v>
+        <v>-0.03912448700410398</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>0.01209677419354849</v>
+        <v>0.01152073732718883</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -5430,25 +5427,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.3326121183081854</v>
+        <v>0.332177338671338</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.06198759566027379</v>
+        <v>0.06164102224241952</v>
       </c>
       <c r="H90" s="3" t="n">
         <v>0.06536126069574189</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.1238176130758573</v>
+        <v>0.1234508617947687</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.008883860189432102</v>
+        <v>0.00855461686392367</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>-0.003166686418900611</v>
+        <v>-0.003491997119261514</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0.0168408826945412</v>
+        <v>0.0165090426414467</v>
       </c>
       <c r="M90" s="6" t="inlineStr">
         <is>
@@ -5486,25 +5483,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.189741533130914</v>
+        <v>0.1880710222903916</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.01069607987194998</v>
+        <v>0.009276903212655174</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>0.06071340359587785</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.1050347360187334</v>
+        <v>0.1034830930112067</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.02932981470481388</v>
+        <v>-0.03069278869697478</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.04715441848322666</v>
+        <v>-0.04849236392115919</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.008531362254766695</v>
+        <v>0.007115225200331698</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
@@ -5531,7 +5528,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D92" s="22" t="inlineStr">
+      <c r="D92" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5542,25 +5539,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.0238218876940508</v>
+        <v>0.02536495007188644</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.05801478468431487</v>
+        <v>0.059609381194766</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0.05362964428057437</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.01066260472201064</v>
+        <v>0.01218583396801209</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.001131648434552934</v>
+        <v>0.002640513013956847</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.004161937192584064</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>-0.0007530120481927804</v>
+        <v>0.00567536889897835</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>0.0007530120481926694</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -5569,7 +5566,7 @@
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5594,25 +5591,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.08760741197627819</v>
+        <v>0.08746915340005357</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02948479467759824</v>
+        <v>0.02935423862351172</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03427757158260181</v>
+        <v>0.03427777794803943</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.02186521873237357</v>
+        <v>0.02173552628324615</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0.002314415191045915</v>
+        <v>0.002187007494769189</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.004633936804478767</v>
+        <v>-0.004760364603690781</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>0.003953073195613444</v>
+        <v>0.003825554705432221</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5635,7 +5632,7 @@
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr"/>
-      <c r="D94" s="23" t="inlineStr">
+      <c r="D94" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -5646,25 +5643,25 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.04337864791136203</v>
+        <v>0.04363499113196734</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01582144083877179</v>
+        <v>0.016070825276987</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.02126156297758142</v>
+        <v>0.02126117375314962</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.003580766045005568</v>
+        <v>0.00382743348171477</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>0.002338369412244745</v>
+        <v>0.002584825859112794</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.005326864670152087</v>
+        <v>-0.005082292962424129</v>
       </c>
       <c r="L94" s="3" t="n">
-        <v>0.00123092072870512</v>
+        <v>0.001477104874446189</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
@@ -5698,25 +5695,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1424054415587372</v>
+        <v>0.1407389128329042</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.04172729396279484</v>
+        <v>-0.04312521184176943</v>
       </c>
       <c r="H95" s="3" t="n">
         <v>0.007945090759379436</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.04903758990588658</v>
+        <v>0.04750726519413484</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-0.02385803005419451</v>
+        <v>-0.02528201542245967</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.04928084394433763</v>
+        <v>-0.05066774278614017</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>0.01136028326940086</v>
+        <v>0.00988492180584255</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -5743,7 +5740,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D96" s="24" t="inlineStr">
+      <c r="D96" s="23" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -5754,25 +5751,25 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.2226019798685404</v>
+        <v>0.2151193564468079</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.03978587560885494</v>
+        <v>-0.04566270501931169</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.004001639964004156</v>
+        <v>0.004001551698471051</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.06007737224120935</v>
+        <v>0.05358933694769163</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-0.01230280571457254</v>
+        <v>-0.01834775434154456</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.04361299208079883</v>
+        <v>-0.04946631470216922</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>0.007252508159071525</v>
+        <v>0.00108787622386064</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5810,25 +5807,25 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.03255588286597377</v>
+        <v>0.03382710825198387</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.01321743770248618</v>
+        <v>-0.0120024184460108</v>
       </c>
       <c r="H97" s="3" t="n">
         <v>0.000241237138472572</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.01842336574523251</v>
+        <v>-0.0172147565157087</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-0.01501406203977429</v>
+        <v>-0.01380125495571649</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.01345542889179585</v>
+        <v>-0.01224070267239774</v>
       </c>
       <c r="L97" s="3" t="n">
-        <v>0.001802827592750633</v>
+        <v>0.003036341208843218</v>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
@@ -5851,7 +5848,7 @@
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" s="23" t="inlineStr">
+      <c r="D98" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -5862,25 +5859,25 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.02199368950511493</v>
+        <v>0.02289055767266746</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.02490605187500006</v>
+        <v>-0.02405066375954712</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-0.009640379611043581</v>
+        <v>-0.009640622047912606</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.02832632783488509</v>
+        <v>-0.0274737020394128</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.02026603276279326</v>
+        <v>-0.01940633420648119</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.01541427169451937</v>
+        <v>-0.01455031580700772</v>
       </c>
       <c r="L98" s="3" t="n">
-        <v>0.004849553620632552</v>
+        <v>0.005731290642565723</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5914,25 +5911,25 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.03956830458517246</v>
+        <v>0.04125149682562945</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.02087617350838999</v>
+        <v>-0.01929077441796634</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>-0.01707542625358827</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.0109445890961839</v>
+        <v>-0.009343179967102322</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.02308235156167826</v>
+        <v>-0.02150052471879305</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.003866774070278023</v>
+        <v>-0.00225383332917839</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.005169937769267552</v>
+        <v>0.006797510770703674</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5955,7 +5952,7 @@
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" s="22" t="inlineStr">
+      <c r="D100" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -5966,25 +5963,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.06432290447583155</v>
+        <v>0.06301801377952443</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.02409229486407527</v>
+        <v>-0.02528864288719257</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.01749072081556802</v>
+        <v>-0.01749065182879961</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0.006022736396023021</v>
+        <v>0.004789473064955585</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.002125924785609357</v>
+        <v>0.0008974381980308976</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>-0.006719095878653825</v>
+        <v>-0.007936811057225879</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0.001794992914501803</v>
+        <v>0.0005668398677374231</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
@@ -6011,7 +6008,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D101" s="24" t="inlineStr">
+      <c r="D101" s="23" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -6022,25 +6019,25 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.167253522215207</v>
+        <v>0.1592504518409206</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.05541679625516382</v>
+        <v>-0.06189322131529607</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01796481273171724</v>
+        <v>-0.01796496318893859</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.03858130697455331</v>
+        <v>0.03146055286348681</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>-0.02643209189540552</v>
+        <v>-0.03310709907826448</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>-0.03813710955472627</v>
+        <v>-0.04473186442410915</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0.0163128612326473</v>
+        <v>0.009344784745854318</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -6063,7 +6060,7 @@
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr"/>
-      <c r="D102" s="23" t="inlineStr">
+      <c r="D102" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -6074,25 +6071,25 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03691694863707329</v>
+        <v>-0.03491094525165328</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.05535084308804594</v>
+        <v>-0.05338314875755268</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.05838022746581295</v>
+        <v>-0.05838031062165694</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.03956227806142787</v>
+        <v>-0.0375616113204702</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-0.04371002629977327</v>
+        <v>-0.04171799964214506</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>0.00321720557079419</v>
+        <v>0.005306985315274515</v>
       </c>
       <c r="L102" s="3" t="n">
-        <v>0.00902571711177047</v>
+        <v>0.01112759643916927</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
@@ -6130,25 +6127,25 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.02710355987055013</v>
+        <v>-0.02892394822006472</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.1071097085576387</v>
+        <v>-0.1087803972526452</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>-0.08334880267310185</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0.007963118189438401</v>
+        <v>0.006077116512992475</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>-0.01956787607011823</v>
+        <v>-0.02140236445169186</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>-0.02592142567841238</v>
+        <v>-0.02774402592142577</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0.01348504003371254</v>
+        <v>0.01158870627897168</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6186,25 +6183,25 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.09215756153142818</v>
+        <v>-0.09832192376794313</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.1685945076015311</v>
+        <v>-0.1742398535375701</v>
       </c>
       <c r="H104" s="5" t="n">
         <v>-0.1313010102058796</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.1371080954609265</v>
+        <v>0.1293869911090313</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.09681787406905884</v>
+        <v>0.08937034529451582</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>-0.04293028751476957</v>
+        <v>-0.04942890901929886</v>
       </c>
       <c r="L104" s="3" t="n">
-        <v>0.007253886010362809</v>
+        <v>0.000414507772020789</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.831883878141396</v>
+        <v>1.831884141209763</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1.191080927666467</v>
@@ -700,7 +700,7 @@
         <v>1.176101915391165</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.5234466551362986</v>
+        <v>0.52344680740206</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>-0.1410552550260734</v>
@@ -799,13 +799,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.568477522820564</v>
+        <v>1.568477710275704</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9669133822850637</v>
+        <v>0.9669136021450981</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.143605936403186</v>
+        <v>1.143606176013775</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.406813855503404</v>
@@ -907,25 +907,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.561707452085938</v>
+        <v>1.561510071228976</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.014108990986017</v>
+        <v>1.013953802867899</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>1.060288206804791</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.5363330616432453</v>
+        <v>0.5362146864025286</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1338111944164601</v>
+        <v>-0.1338779347027476</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.02241395920544154</v>
+        <v>-0.02248928270513673</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.03401983826634258</v>
+        <v>0.03394016651396248</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8008486568426647</v>
+        <v>0.8008488131937213</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.6959067402717898</v>
+        <v>0.6959066016120876</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7158396725745104</v>
+        <v>0.7158395322850641</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>0.3079460039685227</v>
@@ -1410,10 +1410,10 @@
         <v>1.179170680397156</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.7188267169654332</v>
+        <v>0.7188268224306218</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5377113432705916</v>
+        <v>0.5377114376227534</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>0.366899389859672</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.7199549150200295</v>
+        <v>0.7199547348754267</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.4883305575252326</v>
@@ -1567,25 +1567,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.4811919621264416</v>
+        <v>0.4814217111511239</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.4809279183154322</v>
+        <v>0.4811576263840402</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.4627809808954044</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.118589913660905</v>
+        <v>0.1187634191539502</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.1877619108598192</v>
+        <v>0.1879461456839018</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.01240577889447225</v>
+        <v>0.01256281407035176</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.006871778853662303</v>
+        <v>0.007027955645791062</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.5267664731581541</v>
+        <v>0.5267661296176143</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0.4721562809184545</v>
@@ -1906,10 +1906,10 @@
         <v>0.6241166636739779</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.4092022268564697</v>
+        <v>0.409202311107381</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.3924325401219269</v>
+        <v>0.3924326233702415</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>0.1472412982447002</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.7609797241353082</v>
+        <v>0.760979598323184</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>0.3881115942304727</v>
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.367850259940687</v>
+        <v>1.367850034828409</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.4717676483578479</v>
+        <v>0.4717674744179412</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3558975082703129</v>
+        <v>0.3558973480244436</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0.08274759708265123</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.7324276695682719</v>
+        <v>0.7324278274756291</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.3520418450471436</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.7276716550817506</v>
+        <v>0.7276712801824581</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.3479364776083087</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.7444947301863378</v>
+        <v>0.7444945483819121</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>0.3457044463147212</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.511559188235575</v>
+        <v>0.5115590328726138</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0.3013217290905161</v>
@@ -2288,7 +2288,7 @@
         <v>0.3071707844032689</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.2651582030976929</v>
+        <v>0.2651583119495087</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0.1538951610836405</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.2803913251187999</v>
+        <v>0.2803912328523221</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>0.2813482427834408</v>
@@ -2443,13 +2443,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.9273095236939657</v>
+        <v>0.9273096509826657</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.266171039183303</v>
+        <v>0.2661709293076167</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.2924453394035098</v>
+        <v>0.2924452272477944</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.03294585375770986</v>
@@ -2607,13 +2607,13 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.6146866565134639</v>
+        <v>0.6146867598994226</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2150560551120206</v>
+        <v>0.2150561721987492</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.285281748110179</v>
+        <v>0.2852818719640824</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0.01555764266412796</v>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4097719896485363</v>
+        <v>0.4097721034172619</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0.216351429935234</v>
@@ -2718,10 +2718,10 @@
         <v>0.2151973319991503</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2657122453235405</v>
+        <v>0.2657121682172785</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2729384988769445</v>
+        <v>0.2729384213304642</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>0.1714536573842973</v>
@@ -2767,25 +2767,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.4141983901447821</v>
+        <v>0.4144461647593567</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2098348269983137</v>
+        <v>0.210046874372197</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2694741390866771</v>
+        <v>0.2694742212062169</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1657823672667735</v>
+        <v>0.1659866181545842</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>-0.01295244169055865</v>
+        <v>-0.01277950603313527</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.04697954078156408</v>
+        <v>-0.04681256684169111</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.005142293603831893</v>
+        <v>0.005318399549168795</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.3948218541253792</v>
+        <v>0.3948217391331279</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.2564784740059423</v>
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.3329117040320986</v>
+        <v>0.3329114144617527</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2504068508705717</v>
+        <v>0.2504067234545331</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2613589296754624</v>
+        <v>0.2613588011434105</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0.1213981974097167</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.1803918049425355</v>
+        <v>0.1803915530564595</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0.2543521770678565</v>
@@ -2932,7 +2932,7 @@
         <v>0.2611882886898127</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1570716296608641</v>
+        <v>0.1570717506767647</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>0.12503817567258</v>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.5688033131735384</v>
+        <v>0.5688034413094696</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>0.2205500501560527</v>
@@ -3086,10 +3086,10 @@
         <v>0.2971148183882415</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2468289271927298</v>
+        <v>0.2468288421466855</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2516562329368497</v>
+        <v>0.2516561475615355</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>0.1304647708308591</v>
@@ -3138,13 +3138,13 @@
         <v>0.4063645636291147</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.0620502705220396</v>
+        <v>0.06205019005092627</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2506849730840535</v>
+        <v>0.2506848783201658</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>-0.07411203297592894</v>
+        <v>-0.07411209413582798</v>
       </c>
       <c r="J47" s="5" t="n">
         <v>-0.1180528853194105</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.1219988385489903</v>
+        <v>0.1219987361992272</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.3095003893625188</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.3826803515773269</v>
+        <v>0.3826802137403083</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>0.1480246502134568</v>
@@ -3299,13 +3299,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.3855578286807397</v>
+        <v>0.3855581508781267</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.1633407888966254</v>
+        <v>0.1633409024647747</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2405127795920026</v>
+        <v>0.2405129006938687</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>0.1550890933317735</v>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4231856880522911</v>
+        <v>0.4231855809628018</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0.2325462361497423</v>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.5187935094921006</v>
+        <v>0.5187937394314961</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2161956029603642</v>
+        <v>0.2161956766888407</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2363090739069289</v>
+        <v>0.2363091488547286</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>0.2470599257779149</v>
@@ -3462,10 +3462,10 @@
         <v>0.2955967814090403</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1274988220944215</v>
+        <v>0.1274987073214009</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2246314346599192</v>
+        <v>0.2246313099993467</v>
       </c>
       <c r="I53" s="3" t="n">
         <v>0.02858628793576035</v>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.4481924601296652</v>
+        <v>0.4481926235535985</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.25538200330259</v>
+        <v>0.2553818804979473</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2228146425795936</v>
+        <v>0.2228145229607725</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>0.169839281638918</v>
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4960692909484445</v>
+        <v>0.4960691956726087</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.218533881020269</v>
+        <v>0.2185337546093633</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2195366916404247</v>
+        <v>0.219536565125487</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>0.2079556047722546</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3713491666292976</v>
+        <v>0.3713493459323467</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0.06834965291776762</v>
@@ -3783,13 +3783,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2888362878915047</v>
+        <v>0.2888363739280313</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1085318622300155</v>
+        <v>0.1085319895257206</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2125366846062464</v>
+        <v>0.212536823845106</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>0.02000331201233574</v>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3026154736153759</v>
+        <v>0.3026155706880485</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0.140571078165028</v>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3195375168777692</v>
+        <v>0.3195373600494646</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0.1347702900823007</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.2502345035262936</v>
+        <v>0.250234615339175</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>0.1526490569391667</v>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.08276211942307299</v>
+        <v>0.08276221788743898</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>0.1333744257783638</v>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2853071838673542</v>
+        <v>0.2853074141276446</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>0.1581233565373872</v>
@@ -4155,25 +4155,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3700857837304996</v>
+        <v>0.3699598272261082</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1691979269148745</v>
+        <v>0.1690909316573896</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1762488555649435</v>
+        <v>0.1762489654120805</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1592619494573599</v>
+        <v>0.1591557552069354</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.03197962398667498</v>
+        <v>0.03188508944021295</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.005994419137336782</v>
+        <v>-0.006085475069627977</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.0112753596336832</v>
+        <v>0.01118272170242052</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3692988836816284</v>
+        <v>0.3692989653041518</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1689538314383923</v>
+        <v>0.1689539504086037</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1762407210770465</v>
+        <v>0.1762408407888809</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0.1592932262179634</v>
@@ -4262,10 +4262,10 @@
         <v>0.3676375966334497</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1682573165227621</v>
+        <v>0.1682574257573866</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1756872247120298</v>
+        <v>0.1756873346413668</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>0.1590836363192552</v>
@@ -4474,10 +4474,10 @@
         <v>0.5186938766207752</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2849233313847719</v>
+        <v>0.2849232479431802</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1473745698904827</v>
+        <v>0.1473744953811651</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>0.05072484245902564</v>
@@ -4527,13 +4527,13 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2300283958955347</v>
+        <v>0.2300283010861444</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.09345243944175219</v>
+        <v>0.09345236451776429</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.142399591761732</v>
+        <v>0.1423995134838574</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>0.1254337714345923</v>
@@ -4583,13 +4583,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.0822474003294813</v>
+        <v>0.08224715138119687</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1338576249344288</v>
+        <v>0.1338576932489777</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1409992301734426</v>
+        <v>0.1409992989182709</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>0.1298964984598039</v>
@@ -4638,10 +4638,10 @@
         <v>0.3213071935583722</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1346905117226209</v>
+        <v>0.1346905937040783</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1295767337529146</v>
+        <v>0.1295768153649013</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0.1064600783815817</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.4441299293624781</v>
+        <v>0.4441300171988722</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>0.1422840307993676</v>
@@ -4696,7 +4696,7 @@
         <v>0.125635969403153</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1983661509700461</v>
+        <v>0.1983662719356454</v>
       </c>
       <c r="J76" s="3" t="n">
         <v>0.04159332212351474</v>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2212932880096627</v>
+        <v>0.221293198546783</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0.0796150527544448</v>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3886645653388194</v>
+        <v>0.3886644614373949</v>
       </c>
       <c r="G78" s="3" t="n">
         <v>0.1220955861126491</v>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.4073663920058155</v>
+        <v>0.4073663065631494</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>0.1207860645263203</v>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.07663073716026214</v>
+        <v>0.07663094900576661</v>
       </c>
       <c r="G80" s="3" t="n">
         <v>0.07579687161459381</v>
@@ -4904,7 +4904,7 @@
         <v>0.1027272280845244</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.0230215534681506</v>
+        <v>0.02302164910499216</v>
       </c>
       <c r="J80" s="3" t="n">
         <v>0.004652301946231452</v>
@@ -4950,10 +4950,10 @@
         <v>0.1832329224007336</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05972211287583851</v>
+        <v>0.05972223855086511</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.1002146116516589</v>
+        <v>0.1002147421287896</v>
       </c>
       <c r="I81" s="3" t="n">
         <v>0.1535378068601221</v>
@@ -5008,7 +5008,7 @@
         <v>0.1001482042231658</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.04010982158281395</v>
+        <v>0.04010990956593696</v>
       </c>
       <c r="J82" s="5" t="n">
         <v>-0.01017843400919183</v>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1641574183933621</v>
+        <v>0.1641575109115532</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>0.05950684601209089</v>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.1455912398473937</v>
+        <v>0.1455913111220255</v>
       </c>
       <c r="G89" s="3" t="n">
         <v>0.02406512500165348</v>
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.332177338671338</v>
+        <v>0.3321771176606041</v>
       </c>
       <c r="G90" s="3" t="n">
         <v>0.06164102224241952</v>
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1880710222903916</v>
+        <v>0.1880709484239593</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.009276903212655174</v>
+        <v>0.009276796598968851</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.06071340359587785</v>
+        <v>0.06071329154876204</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>0.1034830930112067</v>
@@ -5594,10 +5594,10 @@
         <v>0.08746915340005357</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02935423862351172</v>
+        <v>0.02935413593197</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.03427777794803943</v>
+        <v>0.03427767476531041</v>
       </c>
       <c r="I93" s="3" t="n">
         <v>0.02173552628324615</v>
@@ -5643,19 +5643,19 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.04363499113196734</v>
+        <v>0.04363478686115729</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.016070825276987</v>
+        <v>0.01607092208852912</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.02126117375314962</v>
+        <v>0.0212612710592297</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.00382743348171477</v>
+        <v>0.003827338989244478</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>0.002584825859112794</v>
+        <v>0.002584920117812306</v>
       </c>
       <c r="K94" s="5" t="n">
         <v>-0.005082292962424129</v>
@@ -5760,7 +5760,7 @@
         <v>0.004001551698471051</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.05358933694769163</v>
+        <v>0.05358943920577164</v>
       </c>
       <c r="J96" s="5" t="n">
         <v>-0.01834775434154456</v>
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.03382710825198387</v>
+        <v>0.03382733966681895</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.0120024184460108</v>
+        <v>-0.01200248889678079</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.000241237138472572</v>
+        <v>0.000241165814648836</v>
       </c>
       <c r="I97" s="5" t="n">
         <v>-0.0172147565157087</v>
@@ -5862,13 +5862,13 @@
         <v>0.02289055767266746</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.02405066375954712</v>
+        <v>-0.02405050448666957</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-0.009640622047912606</v>
+        <v>-0.009640460423346542</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.0274737020394128</v>
+        <v>-0.02747362296063582</v>
       </c>
       <c r="J98" s="5" t="n">
         <v>-0.01940633420648119</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.04125149682562945</v>
+        <v>0.04125157548506286</v>
       </c>
       <c r="G99" s="5" t="n">
         <v>-0.01929077441796634</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.06301801377952443</v>
+        <v>0.06301793237766473</v>
       </c>
       <c r="G100" s="5" t="n">
         <v>-0.02528864288719257</v>
@@ -5975,7 +5975,7 @@
         <v>0.004789473064955585</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.0008974381980308976</v>
+        <v>0.0008973660320998889</v>
       </c>
       <c r="K100" s="5" t="n">
         <v>-0.007936811057225879</v>
@@ -6022,10 +6022,10 @@
         <v>0.1592504518409206</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.06189322131529607</v>
+        <v>-0.06189307758830676</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01796496318893859</v>
+        <v>-0.01796481273171724</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>0.03146055286348681</v>
@@ -6071,16 +6071,16 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03491094525165328</v>
+        <v>-0.03491085836005736</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.05338314875755268</v>
+        <v>-0.05338306516040192</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.05838031062165694</v>
+        <v>-0.05838022746581295</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.0375616113204702</v>
+        <v>-0.03756152490551978</v>
       </c>
       <c r="J102" s="5" t="n">
         <v>-0.04171799964214506</v>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -56,7 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00ECFCCB"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECFCCB"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,12 +96,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE7F3"/>
+        <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
+        <fgColor rgb="00FCE7F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -205,6 +205,9 @@
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -672,44 +675,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FTXL</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>EWY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Growth &amp; Technology</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>South Korea Equity</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.831884141209763</v>
+        <v>2.220472094704527</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.191080927666467</v>
+        <v>1.298262406814941</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.176101915391165</v>
+        <v>1.234094469576071</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.52344680740206</v>
+        <v>0.3309597982495178</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1410552550260734</v>
+        <v>-0.1813868613138686</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.006883414866444504</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.03872091465320904</v>
+        <v>0.02872212348793202</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>-0.01617413235374743</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -718,7 +717,7 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -728,40 +727,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EWY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>FTXL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>South Korea Equity</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.223065199009701</v>
+        <v>1.890666218800062</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.311148136033897</v>
+        <v>1.213673858839526</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>1.154782282650168</v>
+        <v>1.140032642057216</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.3829996966939642</v>
+        <v>0.5272253969795249</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.1106397503413303</v>
+        <v>-0.1891387262286988</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.07256689209056155</v>
+        <v>0.03441125865796102</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.03902244502677443</v>
+        <v>0.008126236133803255</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -788,7 +791,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -799,25 +802,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.568477710275704</v>
+        <v>1.655160531085811</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9669136021450981</v>
+        <v>0.9972484587502881</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.143606176013775</v>
+        <v>1.039948455086141</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.406813855503404</v>
+        <v>0.405170203535165</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.19833980846302</v>
+        <v>-0.2336180476027983</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.08242772196022141</v>
+        <v>-0.02093189964157693</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.03396487985212571</v>
+        <v>0.01735567970204843</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -844,7 +847,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -855,25 +858,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.949958298582152</v>
+        <v>2.021619330224671</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.100980100980101</v>
+        <v>1.11764705882353</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>1.068310068310068</v>
+        <v>1.030303030303031</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.5804289544235925</v>
+        <v>0.5787375415282392</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1147540983606558</v>
+        <v>-0.1669977795956527</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.01579551981619742</v>
+        <v>0.04302019315188765</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.04121283485428306</v>
+        <v>0.007633587786259666</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -896,7 +899,7 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -907,34 +910,34 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.561510071228976</v>
+        <v>1.625657550836926</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.013953802867899</v>
+        <v>1.037393014730554</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.060288206804791</v>
+        <v>1.015237418907003</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.5362146864025286</v>
+        <v>0.5450699362548255</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1338779347027476</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>-0.02248928270513673</v>
+        <v>-0.1783825788454104</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.0109940375340829</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.03394016651396248</v>
+        <v>0.01144288191099974</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -952,7 +955,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -963,34 +966,34 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.504288521691463</v>
+        <v>1.574357690667967</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9156461281882204</v>
+        <v>0.944402842892216</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.9794101074906643</v>
+        <v>0.9435613832609739</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4897417155960819</v>
+        <v>0.4955101126971917</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1388636448015874</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>-0.0322136272120378</v>
+        <v>-0.1798798359060113</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.0004329472886677177</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.03116179293214416</v>
+        <v>0.01204423519106546</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1011,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -1019,34 +1022,34 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.456125043258976</v>
+        <v>1.515032367041636</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8305210776740908</v>
+        <v>0.8572927526261342</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.8604305924374638</v>
+        <v>0.8432935539174267</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4240607615515533</v>
+        <v>0.4311252911982171</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1015433434299726</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>-0.01607666251294382</v>
+        <v>-0.1435109413832819</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.007594665906011544</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.02758633330889371</v>
+        <v>0.008151834608729702</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1056,53 +1059,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EWT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Taiwan Equity</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.282056452491151</v>
+        <v>0.8284807209080156</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.8275912643834651</v>
+        <v>0.6800442992075972</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.7243515192424976</v>
+        <v>0.8164233575478135</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5508830950378469</v>
+        <v>0.2832006756557617</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.05261154980496618</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.05987163521410088</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.02066420664206636</v>
+        <v>0.1155055451149154</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>-0.07508109702152765</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>-0.009036334913112176</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1111,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>EWT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1120,45 +1119,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dry Bulk Freight Futures</t>
+          <t>Taiwan Equity</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.301749271137026</v>
+        <v>1.309824393677887</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9639303482587065</v>
+        <v>0.834412012903645</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.718905472636816</v>
+        <v>0.7324818487372509</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.4757009345794392</v>
+        <v>0.5367341280842806</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.3291245791245789</v>
+        <v>0.007909809982725724</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.142547033285094</v>
+        <v>0.05883476599808968</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.03202614379084956</v>
+        <v>0.001988430947216235</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1168,49 +1167,53 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>BDRY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Defensive Equity</t>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Dry Bulk Freight Futures</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8008488131937213</v>
+        <v>1.353640416047548</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.6959066016120876</v>
+        <v>0.9459459459459458</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7158395322850641</v>
+        <v>0.7199017199017197</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.3079460039685227</v>
+        <v>0.5808383233532934</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.1364183395880485</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>-0.01161701330335407</v>
+        <v>0.3690579083837511</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.1314285714285715</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.02639771695420934</v>
+        <v>0.003166561114629651</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1223,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1235,29 +1238,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oil Services</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.5811958204770222</v>
+        <v>1.097375975906893</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.5662473002687165</v>
+        <v>0.6775892597547863</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6440122997753184</v>
+        <v>0.7095414966080174</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.04491627106265339</v>
+        <v>0.2009448821219126</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.008763094278807504</v>
+        <v>0.01689739254470579</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.04730195724036235</v>
+        <v>-0.01869053013140021</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.001875703388770855</v>
+        <v>0.0002309202170649449</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1276,7 +1279,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1291,38 +1294,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Oil Services</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.120759653976278</v>
+        <v>0.5685749394431592</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6553510406301049</v>
+        <v>0.5778734134590995</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.6354738315058084</v>
+        <v>0.6612347100210982</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1598067918968586</v>
+        <v>0.0128877795323723</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.00166343514214895</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0.01215379221689861</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>0.02874450647345284</v>
+        <v>0.03162209136423777</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>-0.05018032434498076</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>-0.007289066400399391</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1332,53 +1335,49 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EPU</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Peru Equity</t>
+          <t>Silver Bullion</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.172542730050186</v>
+        <v>0.9397082658022691</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5965972091884577</v>
+        <v>0.5834876951574492</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.5417912784977723</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0.1769413855573396</v>
+        <v>0.5879862397459645</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>-0.08891595615103531</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.01935193519351941</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.03554691964795986</v>
+        <v>0.005545286506469571</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>-0.002832861189801639</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.0148986221574996</v>
+        <v>0.01475326437171454</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1387,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BOAT</t>
+          <t>EPU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1396,45 +1395,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Global Shipping</t>
+          <t>Peru Equity</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.179170680397156</v>
+        <v>1.142682996457419</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.7188268224306218</v>
+        <v>0.6032679636576526</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5377114376227534</v>
+        <v>0.5872176463097045</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.366899389859672</v>
+        <v>0.2058020427999212</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.3299941254972338</v>
+        <v>0.03495388819310041</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.1177824267782428</v>
+        <v>0.0101122346927438</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.01693947468595347</v>
+        <v>0.003311258278145823</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1444,49 +1443,53 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>BOAT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Silver Bullion</t>
+          <t>Global Shipping</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.913988964621876</v>
+        <v>1.161018441839595</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.527720207253886</v>
+        <v>0.7003062619147618</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.4880829015544039</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>-0.1416302765647744</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>-0.0270582412143211</v>
+        <v>0.5671633089295693</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0.3370716638312938</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0.3266755943954871</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.02663649025069637</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0.03365468886941292</v>
+        <v>0.08495793145906005</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>-0.01048100318173317</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1496,105 +1499,109 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>IBB</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.5360870541080216</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.4599465173782737</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.5417298324120436</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>0.2494218740515404</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0.1832011586085018</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>-0.05304646333905305</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>-0.007871734196165492</v>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>PICK</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Global Metals &amp; Mining</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>0.7199547348754267</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0.4883305575252326</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>0.4773465681708029</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>0.1467516562074564</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>-0.02730961298377033</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.00743494423791824</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>0.02264150943396226</v>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>MIXED_TRANSITION</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr"/>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
       <c r="F18" s="3" t="n">
-        <v>0.4814217111511239</v>
+        <v>0.6924146726066096</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.4811576263840402</v>
+        <v>0.4839615313124372</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4627809808954044</v>
+        <v>0.522240227528965</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.1187634191539502</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0.1879461456839018</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0.01256281407035176</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0.007027955645791062</v>
+        <v>0.1553468259911501</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>-0.02018756954379264</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>-0.02514629131741253</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>-0.01107011070110697</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1604,14 +1611,10 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VDE</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>SIL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Natural Resources</t>
@@ -1619,94 +1622,90 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Silver Miners</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1.365523621189096</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0.4862409980894236</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.507468519750667</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0.1424303835596559</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0.1304234862966287</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>-0.01408156879107136</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>-0.005157351857699277</v>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr"/>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>0.4950688156528953</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0.4726954910230361</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>0.4580507096085207</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>0.1092050822374617</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0.1811367410654567</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>0.01004408236147536</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>0.004718028419183007</v>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="F20" s="3" t="n">
+        <v>0.4780040625423805</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.4763913184633428</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.4569138604361218</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.1003817011823882</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.2068932840744393</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.0133689839572193</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>-0.0007754342431761652</v>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>STEADY_POSITIVE</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>IBB</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.5267661296176143</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.4721562809184545</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>0.4471242881227626</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0.2645637492642674</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0.1939640882752187</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0.01729774906076931</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0.02307312252964411</v>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>STEADY_POSITIVE</t>
-        </is>
-      </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1715,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>VDE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1731,38 +1730,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.7223906242415876</v>
+        <v>0.489860667919126</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.3770130399083618</v>
+        <v>0.4689549692180532</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.4376093824261909</v>
+        <v>0.4544156858622317</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.02526673875951824</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>-0.142834065483448</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>-0.04215077006214529</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>0.01503221188260584</v>
+        <v>0.09066619473720983</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0.1992142873617502</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.009996649167876681</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>-0.0008839290646925901</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1771,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>QTEC</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1780,45 +1779,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.6816407606472576</v>
+        <v>0.5300696066643049</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.4013062936187397</v>
+        <v>0.4780995160308332</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.4359489938622265</v>
+        <v>0.4299807000105149</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.3814513196055542</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>-0.04710311566073522</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>-0.0241252999873689</v>
+        <v>0.1101568074882073</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0.2620239652369665</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0.03364997584929963</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.01728167484117327</v>
+        <v>5.192377589691155e-05</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1827,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1843,38 +1842,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Lithium &amp; Battery</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5390865339757844</v>
+        <v>0.709906651314469</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4770257668727447</v>
+        <v>0.3447443224575162</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.4215002123156095</v>
+        <v>0.428455614325598</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.12085699177552</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>0.2425935611576413</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>0.03906123550040475</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>0.004118873826902902</v>
+        <v>0.02562945157849117</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>-0.1417922576425917</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>-0.05860265522328001</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>-0.009873060648801113</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1883,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DXJ</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,43 +1893,43 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Japan Hedged Equity</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6241166636739779</v>
+        <v>0.7060335141418632</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.409202311107381</v>
+        <v>0.3975828035406301</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.3924326233702415</v>
+        <v>0.4142760158371741</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.1472412982447002</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>0.02930794305795836</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0.01204344645168565</v>
+        <v>0.3783075049771558</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>-0.07571399202220852</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>-0.01180336236322466</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.008637612877895773</v>
+        <v>0.002362153766502617</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1955,25 +1954,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5444091275822327</v>
+        <v>0.5539966880817335</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4996633251679281</v>
+        <v>0.5215929839846609</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.3830480529839169</v>
+        <v>0.4106148338567865</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.129142466689443</v>
+        <v>0.1504854368932038</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1927102129195235</v>
+        <v>0.2008686210640609</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.08431758530183719</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>-0.003317249698431834</v>
+        <v>0.07867360208062402</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.003933434190620311</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -1982,7 +1981,7 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1992,40 +1991,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>XLK</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>DXJ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Growth &amp; Technology</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Japan Hedged Equity</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.760979598323184</v>
+        <v>0.6173263345778801</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3881115942304727</v>
+        <v>0.4057778360812763</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3701014257208357</v>
+        <v>0.3732497774999188</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.366471156922533</v>
+        <v>0.1617555115172979</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.01337051465202665</v>
+        <v>0.009011093052382568</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.01314513522249761</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>0.02245419453052788</v>
+        <v>0.02368692070030898</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>-0.00506033476060741</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2034,7 +2037,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2044,49 +2047,49 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.367850034828409</v>
+        <v>0.788774811785184</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.4717674744179412</v>
+        <v>0.3933631743643067</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3558973480244436</v>
+        <v>0.3601808066141892</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.08274759708265123</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>0.1069345888783573</v>
+        <v>0.3622660443637624</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>-0.0161705495751634</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.08545641494344802</v>
+        <v>0.02439555652363334</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.04486967997360614</v>
+        <v>0.0003190471126235384</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FTEC</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2104,45 +2107,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.7324278274756291</v>
+        <v>0.8890165989964005</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3520418450471436</v>
+        <v>0.2528822258356649</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3324618997013125</v>
+        <v>0.3390078709017827</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.3537309014774321</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>0.0397926349479969</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>0.0146945630116857</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>0.02195285246132683</v>
+        <v>0.04291018223855358</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>-0.06328030000568863</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>-0.06432049201332524</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>-0.01598993891484002</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2152,49 +2155,53 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VGT</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>CALF</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Small Cap Cash Flow</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.7276712801824581</v>
+        <v>0.4982925716972519</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3479364776083087</v>
+        <v>0.2851123587713311</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3291843155474095</v>
+        <v>0.3281616603657511</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.3530900611649506</v>
+        <v>0.2472004432529185</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.04014884488748849</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>0.01410802237248521</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>0.02152707702657253</v>
+        <v>0.131605120298562</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>-0.03241269709785566</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>-0.01087344028520498</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2211,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IYW</t>
+          <t>FTEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,7 +2219,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -2223,25 +2230,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.7444945483819121</v>
+        <v>0.7576565409526026</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3457044463147212</v>
+        <v>0.3555185336577089</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3146792410827406</v>
+        <v>0.3264656928555607</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3545985122682489</v>
+        <v>0.3492187092517152</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.0368515454488374</v>
+        <v>0.01116772527395815</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.023599068322117</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>0.02106735958424943</v>
+        <v>0.02190244418580067</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>-0.0009654506585752287</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2250,7 +2257,7 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2260,14 +2267,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CALF</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>SCHD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -2275,29 +2278,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Small Cap Cash Flow</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5115590328726138</v>
+        <v>0.2727669372322632</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3013217290905161</v>
+        <v>0.2695809587373188</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3071707844032689</v>
+        <v>0.3243042759242722</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.2651583119495087</v>
+        <v>0.1178402303476256</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1538951610836405</v>
+        <v>0.06427862226222025</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.004474591524337712</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>0.001606855918586003</v>
+        <v>-0.04132231404958686</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>-0.007376807317792888</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2306,7 +2309,7 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2316,49 +2319,49 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SCHD</t>
+          <t>VGT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.2803912328523221</v>
+        <v>0.7524264072289166</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.2813482427834408</v>
+        <v>0.3528684859727971</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3047898453365754</v>
+        <v>0.3230225233253894</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.1265158710144492</v>
+        <v>0.3494905959943242</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.06983739459881999</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>-0.01796580701246009</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>0.001477541371158297</v>
+        <v>0.01320065912335444</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.02255892255892267</v>
+      </c>
+      <c r="L32" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>